--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יערה טופ – Kill Me</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%a2%d7%a8%d7%94-%d7%98%d7%95%d7%a4-kill-me/</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יערה טופ שרה בלדת פולק אקוסטית עדינה, כמעט חשופה, שמצליחה להחזיק בתוכה טקסט טעון  על תשוקה, תלות, ופחד מאינטימיות. למרות הכותרת הדרמטית, זה אינו שיר על מוות כפשוטו, אלא על הסכמה להיעלם בתוך אהבה ועל הסכנה שבכך. ה”Kill me” היא</v>
+        <v>2 days ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:20</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>georgemichael</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יערה טופ – Kill Me</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>אלדד ציטרין וגלי עטרי – רק במנגינה</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%9c%d7%93%d7%93-%d7%a6%d7%99%d7%98%d7%a8%d7%99%d7%9f-%d7%95%d7%92%d7%9c%d7%99-%d7%a2%d7%98%d7%a8%d7%99-%d7%a8%d7%a7-%d7%91%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-22</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>זהו שיר שקט, מינימליסטי, מעודן, תואם את גוון שירתה של גלי עטרי. בתוכו מתקיים דיאלוג על ערך עצמי אחרי פרידה. לא מדובר בשיר אהבה, אלא בשיר על תיקון חלקי. הוא נפתח בשאלות: “מי לך אמר את לא מיוחדת מי לך</v>
+        <v>2 days ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>4:50</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>Cliff Richard</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>אלדד ציטרין וגלי עטרי – רק במנגינה</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B4" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-22</v>
@@ -530,10 +530,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:20</v>
+        <v>3:14</v>
       </c>
       <c r="H4" t="str">
-        <v>georgemichael</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B5" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-22</v>
@@ -568,10 +568,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:50</v>
+        <v>4:37</v>
       </c>
       <c r="H5" t="str">
-        <v>Cliff Richard</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-22</v>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:14</v>
+        <v>3:16</v>
       </c>
       <c r="H6" t="str">
-        <v>Freya Ridings</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-22</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:37</v>
+        <v>4:22</v>
       </c>
       <c r="H7" t="str">
-        <v>Jessie Ware</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-22</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:16</v>
+        <v>3:45</v>
       </c>
       <c r="H8" t="str">
-        <v>Alan Walker</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-22</v>
@@ -717,13 +717,13 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:22</v>
+        <v>4:40</v>
       </c>
       <c r="H9" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-22</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:45</v>
+        <v>3:02</v>
       </c>
       <c r="H10" t="str">
-        <v>YUNGBLUD</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Suburban Requiem</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-22</v>
@@ -793,13 +793,13 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:40</v>
+        <v>3:12</v>
       </c>
       <c r="H11" t="str">
-        <v>YUNGBLUD</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-22</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:02</v>
+        <v>3:38</v>
       </c>
       <c r="H12" t="str">
-        <v>Calum Scott</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-22</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:12</v>
+        <v>4:40</v>
       </c>
       <c r="H13" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Cannons</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-22</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:38</v>
+        <v>2:57</v>
       </c>
       <c r="H14" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-22</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:40</v>
+        <v>2:13</v>
       </c>
       <c r="H15" t="str">
-        <v>Cannons</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-22</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>2:57</v>
+        <v>4:12</v>
       </c>
       <c r="H16" t="str">
-        <v>Mimi Webb</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-22</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:13</v>
+        <v>2:55</v>
       </c>
       <c r="H17" t="str">
-        <v>Jorja Smith</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-22</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:12</v>
+        <v>3:51</v>
       </c>
       <c r="H18" t="str">
-        <v>Sam Williams</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-22</v>
@@ -1100,10 +1100,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:55</v>
+        <v>2:51</v>
       </c>
       <c r="H19" t="str">
-        <v>YUNGBLUD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-22</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:51</v>
+        <v>3:24</v>
       </c>
       <c r="H20" t="str">
-        <v>Megan Moroney</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-22</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>2:51</v>
+        <v>4:11</v>
       </c>
       <c r="H21" t="str">
-        <v>Nico Santos</v>
+        <v>We Three</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-22</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:24</v>
+        <v>3:27</v>
       </c>
       <c r="H22" t="str">
-        <v>REALITY CLUB</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-22</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:11</v>
+        <v>3:06</v>
       </c>
       <c r="H23" t="str">
-        <v>We Three</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-22</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:27</v>
+        <v>3:01</v>
       </c>
       <c r="H24" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-22</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:06</v>
+        <v>5:38</v>
       </c>
       <c r="H25" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>georgemichael</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-22</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:01</v>
+        <v>3:43</v>
       </c>
       <c r="H26" t="str">
-        <v>Peach PRC</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-22</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>5:38</v>
+        <v>2:58</v>
       </c>
       <c r="H27" t="str">
-        <v>georgemichael</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-22</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:43</v>
+        <v>4:13</v>
       </c>
       <c r="H28" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-22</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:58</v>
+        <v>5:48</v>
       </c>
       <c r="H29" t="str">
-        <v>Catie Turner</v>
+        <v>U2</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-22</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>4:13</v>
+        <v>3:55</v>
       </c>
       <c r="H30" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Lawrence</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-22</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:48</v>
+        <v>5:24</v>
       </c>
       <c r="H31" t="str">
-        <v>U2</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:55</v>
+        <v>4:59</v>
       </c>
       <c r="H32" t="str">
-        <v>Lawrence</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>5:24</v>
+        <v>2:10</v>
       </c>
       <c r="H33" t="str">
-        <v>BUNT. Music</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B34" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-22</v>
@@ -1670,10 +1670,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:59</v>
+        <v>3:11</v>
       </c>
       <c r="H34" t="str">
-        <v>Bruno Mars</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B35" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-22</v>
@@ -1708,10 +1708,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>2:10</v>
+        <v>4:26</v>
       </c>
       <c r="H35" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-22</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:11</v>
+        <v>4:35</v>
       </c>
       <c r="H36" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B37" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-22</v>
@@ -1784,10 +1784,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>4:26</v>
+        <v>2:09</v>
       </c>
       <c r="H37" t="str">
-        <v>Neal Francis</v>
+        <v>Lola Young</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-22</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:35</v>
+        <v>4:11</v>
       </c>
       <c r="H38" t="str">
-        <v>mgk</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-22</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:09</v>
+        <v>3:01</v>
       </c>
       <c r="H39" t="str">
-        <v>Lola Young</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-22</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:11</v>
+        <v>3:28</v>
       </c>
       <c r="H40" t="str">
-        <v>Holly Humberstone</v>
+        <v>mgk</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-22</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:01</v>
+        <v>5:31</v>
       </c>
       <c r="H41" t="str">
-        <v>The Vaccines</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-22</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:28</v>
+        <v>2:49</v>
       </c>
       <c r="H42" t="str">
-        <v>mgk</v>
+        <v>Mýa</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B43" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-22</v>
@@ -2012,10 +2012,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>5:31</v>
+        <v>3:03</v>
       </c>
       <c r="H43" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B44" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-22</v>
@@ -2050,10 +2050,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:49</v>
+        <v>2:59</v>
       </c>
       <c r="H44" t="str">
-        <v>Mýa</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B45" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-22</v>
@@ -2088,10 +2088,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:03</v>
+        <v>2:41</v>
       </c>
       <c r="H45" t="str">
-        <v>Michael Bolton</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G46" t="str">
         <v>2:59</v>
       </c>
       <c r="H46" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-22</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:41</v>
+        <v>3:59</v>
       </c>
       <c r="H47" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:59</v>
+        <v>7:48</v>
       </c>
       <c r="H48" t="str">
-        <v>ENHYPEN</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B49" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-22</v>
@@ -2240,10 +2240,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:59</v>
+        <v>3:10</v>
       </c>
       <c r="H49" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B50" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-22</v>
@@ -2278,7 +2278,7 @@
         <v>8 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>7:48</v>
+        <v>5:57</v>
       </c>
       <c r="H50" t="str">
         <v>The Doobie Brothers</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-22</v>
@@ -2316,10 +2316,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:10</v>
+        <v>2:25</v>
       </c>
       <c r="H51" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B52" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-22</v>
@@ -2354,10 +2354,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:57</v>
+        <v>3:19</v>
       </c>
       <c r="H52" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-22</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:25</v>
+        <v>3:38</v>
       </c>
       <c r="H53" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-22</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:19</v>
+        <v>4:05</v>
       </c>
       <c r="H54" t="str">
-        <v>Michael Bolton</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-22</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:38</v>
+        <v>5:46</v>
       </c>
       <c r="H55" t="str">
-        <v>mgk</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-22</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>4:05</v>
+        <v>3:25</v>
       </c>
       <c r="H56" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-22</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:46</v>
+        <v>5:11</v>
       </c>
       <c r="H57" t="str">
-        <v>Jacob Collier</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-22</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:25</v>
+        <v>2:55</v>
       </c>
       <c r="H58" t="str">
-        <v>Victor Ray</v>
+        <v>The Warning</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-22</v>
@@ -2620,10 +2620,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>5:11</v>
+        <v>4:54</v>
       </c>
       <c r="H59" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Offspring</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-22</v>
@@ -2658,10 +2658,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:55</v>
+        <v>5:01</v>
       </c>
       <c r="H60" t="str">
-        <v>The Warning</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-22</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>4:54</v>
+        <v>3:55</v>
       </c>
       <c r="H61" t="str">
-        <v>The Offspring</v>
+        <v>HAUSER</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-22</v>
@@ -2734,10 +2734,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>5:01</v>
+        <v>3:43</v>
       </c>
       <c r="H62" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-22</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:55</v>
+        <v>2:53</v>
       </c>
       <c r="H63" t="str">
-        <v>HAUSER</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-22</v>
@@ -2810,10 +2810,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:43</v>
+        <v>3:30</v>
       </c>
       <c r="H64" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-22</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>2:53</v>
+        <v>3:37</v>
       </c>
       <c r="H65" t="str">
-        <v>Ultra Records</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-22</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:30</v>
+        <v>4:10</v>
       </c>
       <c r="H66" t="str">
-        <v>Anja Kotar</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-22</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:37</v>
+        <v>3:06</v>
       </c>
       <c r="H67" t="str">
-        <v>Michael Bolton</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-22</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>4:10</v>
+        <v>3:17</v>
       </c>
       <c r="H68" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-22</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:06</v>
+        <v>3:21</v>
       </c>
       <c r="H69" t="str">
-        <v>Alan Walker</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-22</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>3:17</v>
+        <v>6:58</v>
       </c>
       <c r="H70" t="str">
-        <v>Bruno Mars</v>
+        <v>Eric Church</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-22</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:21</v>
+        <v>3:29</v>
       </c>
       <c r="H71" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-22</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>6:58</v>
+        <v>3:14</v>
       </c>
       <c r="H72" t="str">
-        <v>Eric Church</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-22</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:29</v>
+        <v>3:51</v>
       </c>
       <c r="H73" t="str">
-        <v>Meghan Trainor</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-22</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:14</v>
+        <v>3:10</v>
       </c>
       <c r="H74" t="str">
-        <v>Ally Salort</v>
+        <v>elijah woods</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-22</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:51</v>
+        <v>3:26</v>
       </c>
       <c r="H75" t="str">
-        <v>Will Swinton</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-22</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:10</v>
+        <v>2:51</v>
       </c>
       <c r="H76" t="str">
-        <v>elijah woods</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-22</v>
@@ -3307,7 +3307,7 @@
         <v>3:26</v>
       </c>
       <c r="H77" t="str">
-        <v>Jackson Dean</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-22</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:51</v>
+        <v>3:06</v>
       </c>
       <c r="H78" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-22</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:26</v>
+        <v>3:04</v>
       </c>
       <c r="H79" t="str">
-        <v>Neil Sedaka</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-22</v>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:06</v>
+        <v>3:03</v>
       </c>
       <c r="H80" t="str">
-        <v>Sofia Camara</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-22</v>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:04</v>
+        <v>2:38</v>
       </c>
       <c r="H81" t="str">
-        <v>Russell Dickerson</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-22</v>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:03</v>
+        <v>3:29</v>
       </c>
       <c r="H82" t="str">
-        <v>Celine Dion</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-22</v>
@@ -3532,10 +3532,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:38</v>
+        <v>2:32</v>
       </c>
       <c r="H83" t="str">
-        <v>Bebe Rexha</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-22</v>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:29</v>
+        <v>3:32</v>
       </c>
       <c r="H84" t="str">
-        <v>Caroline Jones</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-22</v>
@@ -3608,10 +3608,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:32</v>
+        <v>2:51</v>
       </c>
       <c r="H85" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-22</v>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:32</v>
+        <v>3:38</v>
       </c>
       <c r="H86" t="str">
-        <v>Ingrid Andress</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-22</v>
@@ -3684,10 +3684,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H87" t="str">
-        <v>MusicByKnox</v>
+        <v>Nickless</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-22</v>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:38</v>
+        <v>3:57</v>
       </c>
       <c r="H88" t="str">
-        <v>Ella Langley</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Nickless - As I Am</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-22</v>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>3:08</v>
       </c>
       <c r="H89" t="str">
-        <v>Nickless</v>
+        <v>elijah woods</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B90" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-22</v>
@@ -3798,10 +3798,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:57</v>
+        <v>3:53</v>
       </c>
       <c r="H90" t="str">
-        <v>Caroline Jones</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-22</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:08</v>
+        <v>3:10</v>
       </c>
       <c r="H91" t="str">
-        <v>elijah woods</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-22</v>
@@ -3874,10 +3874,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:53</v>
+        <v>2:58</v>
       </c>
       <c r="H92" t="str">
-        <v>August Ponthier</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B93" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-22</v>
@@ -3912,10 +3912,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:10</v>
+        <v>2:44</v>
       </c>
       <c r="H93" t="str">
-        <v>Charli xcx</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-22</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:58</v>
+        <v>3:25</v>
       </c>
       <c r="H94" t="str">
-        <v>Caroline Jones</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-22</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:44</v>
+        <v>4:08</v>
       </c>
       <c r="H95" t="str">
-        <v>Leah Kate</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-22</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:25</v>
+        <v>3:09</v>
       </c>
       <c r="H96" t="str">
-        <v>Troye Sivan</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-22</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>4:08</v>
+        <v>3:11</v>
       </c>
       <c r="H97" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B98" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-22</v>
@@ -4102,10 +4102,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:09</v>
+        <v>3:02</v>
       </c>
       <c r="H98" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B99" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-22</v>
@@ -4140,10 +4140,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:11</v>
+        <v>4:20</v>
       </c>
       <c r="H99" t="str">
-        <v>The Happy Fits</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B100" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-22</v>
@@ -4178,10 +4178,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:02</v>
+        <v>4:09</v>
       </c>
       <c r="H100" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B101" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-22</v>
@@ -4216,10 +4216,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:20</v>
+        <v>4:34</v>
       </c>
       <c r="H101" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>We Three</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Badlands</v>
       </c>
       <c r="B102" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>9 days ago</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G102" t="str">
-        <v>4:09</v>
+        <v>2:58</v>
       </c>
       <c r="H102" t="str">
-        <v>Quinn XCII</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L102" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B103" t="str">
-        <v>9 days ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>9 days ago</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>4:34</v>
+        <v>3:48</v>
       </c>
       <c r="H103" t="str">
-        <v>We Three</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L103" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Badlands</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Prizefighter</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>2:58</v>
+        <v>3:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L104" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>ROSITA</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:48</v>
+        <v>4:05</v>
       </c>
       <c r="H105" t="str">
-        <v>Taylor Swift</v>
+        <v>Tainy</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L105" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G106" t="str">
-        <v>3:54</v>
+        <v>3:52</v>
       </c>
       <c r="H106" t="str">
-        <v>Lana Del Rey</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L106" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>ROSITA</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>ROSITA - Single</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>4:05</v>
+        <v>2:52</v>
       </c>
       <c r="H107" t="str">
-        <v>Tainy</v>
+        <v>SZA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L107" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>Medicine</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Ca$ino</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>3:52</v>
+        <v>3:11</v>
       </c>
       <c r="H108" t="str">
-        <v>Baby Keem</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>luck... or something</v>
       </c>
       <c r="G109" t="str">
-        <v>2:52</v>
+        <v>3:16</v>
       </c>
       <c r="H109" t="str">
-        <v>SZA</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L109" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Medicine</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>Cloud 9</v>
+        <v>petal rock black</v>
       </c>
       <c r="G110" t="str">
-        <v>3:11</v>
+        <v>4:18</v>
       </c>
       <c r="H110" t="str">
-        <v>Megan Moroney</v>
+        <v>WILLOW</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L110" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Weather For Tennis</v>
+        <v>Drag Path</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>luck... or something</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:16</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>Hilary Duff</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L111" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>ear to the cocoon</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>petal rock black</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>4:18</v>
+        <v>3:55</v>
       </c>
       <c r="H112" t="str">
-        <v>WILLOW</v>
+        <v>U2</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L112" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Drag Path</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Drag Path - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G113" t="str">
-        <v>3:44</v>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>twenty one pilots</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L113" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Song Of The Future</v>
+        <v>Trimski</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:55</v>
+        <v>3:02</v>
       </c>
       <c r="H114" t="str">
-        <v>U2</v>
+        <v>NAV</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L114" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Paracosm</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Paracosm</v>
       </c>
       <c r="G115" t="str">
-        <v>2:56</v>
+        <v>3:23</v>
       </c>
       <c r="H115" t="str">
-        <v>Foo Fighters</v>
+        <v>Absolutely</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L115" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Trimski</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Trimski - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:02</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>NAV</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L116" t="str">
-        <v>Trimski - NAV</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Paracosm</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Paracosm</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:23</v>
+        <v>4:18</v>
       </c>
       <c r="H117" t="str">
-        <v>Absolutely</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L117" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Casual Lady</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Casual Lady - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G118" t="str">
-        <v>3:14</v>
+        <v>4:20</v>
       </c>
       <c r="H118" t="str">
-        <v>flowerovlove</v>
+        <v>Pulp</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L118" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>My Maker</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G119" t="str">
-        <v>4:18</v>
+        <v>4:19</v>
       </c>
       <c r="H119" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L119" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Begging for Change</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>HELP(2)</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:20</v>
+        <v>3:32</v>
       </c>
       <c r="H120" t="str">
-        <v>Pulp</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L120" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>My Maker</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Ricochet</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:19</v>
+        <v>4:27</v>
       </c>
       <c r="H121" t="str">
-        <v>Snail Mail</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L121" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G122" t="str">
-        <v>3:32</v>
+        <v>3:33</v>
       </c>
       <c r="H122" t="str">
-        <v>Taylor Swift</v>
+        <v>Thundercat</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L122" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Tea Time</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>4:27</v>
+        <v>2:25</v>
       </c>
       <c r="H123" t="str">
-        <v>CHVRCHES</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L123" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>She Knows Too Much</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Distracted</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G124" t="str">
-        <v>3:33</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Thundercat</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L124" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Tea Time</v>
+        <v>Save My Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Tea Time - Single</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>2:25</v>
+        <v>3:30</v>
       </c>
       <c r="H125" t="str">
-        <v>Yung Miami</v>
+        <v>Kygo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L125" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G126" t="str">
-        <v>3:12</v>
+        <v>3:46</v>
       </c>
       <c r="H126" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L126" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Save My Love</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Save My Love - Single</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G127" t="str">
-        <v>3:30</v>
+        <v>4:39</v>
       </c>
       <c r="H127" t="str">
-        <v>Kygo</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L127" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Good Grief</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G128" t="str">
-        <v>3:46</v>
+        <v>4:21</v>
       </c>
       <c r="H128" t="str">
-        <v>Omar Courtz</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L128" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Suburban Requiem</v>
+        <v>Freak On</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Idols (Complete)</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:39</v>
+        <v>2:49</v>
       </c>
       <c r="H129" t="str">
-        <v>YUNGBLUD</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L129" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Good Grief</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:21</v>
+        <v>3:32</v>
       </c>
       <c r="H130" t="str">
-        <v>The Neighbourhood</v>
+        <v>deadmau5</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L130" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Freak On</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Freak On - Single</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>2:49</v>
+        <v>3:55</v>
       </c>
       <c r="H131" t="str">
-        <v>Steve Aoki</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L131" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>3:32</v>
+        <v>2:42</v>
       </c>
       <c r="H132" t="str">
-        <v>deadmau5</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:55</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Taylor Swift</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L133" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Yellow Eyes</v>
+        <v>only the best</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Jean</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:42</v>
+        <v>3:22</v>
       </c>
       <c r="H134" t="str">
-        <v>Yebba</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L134" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Word On The Street</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:56</v>
+        <v>2:59</v>
       </c>
       <c r="H135" t="str">
-        <v>Luke Bryan</v>
+        <v>Tiësto</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L135" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>only the best</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>only the best - Single</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:22</v>
+        <v>3:09</v>
       </c>
       <c r="H136" t="str">
-        <v>horsegiirL</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L136" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Beautiful Places</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G137" t="str">
-        <v>2:59</v>
+        <v>3:10</v>
       </c>
       <c r="H137" t="str">
-        <v>Tiësto</v>
+        <v>15 15</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L137" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>STAMPEDE</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G138" t="str">
-        <v>3:09</v>
+        <v>3:41</v>
       </c>
       <c r="H138" t="str">
-        <v>Genesis Owusu</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L138" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Infinite Beach</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Mārara</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>3:10</v>
+        <v>2:28</v>
       </c>
       <c r="H139" t="str">
-        <v>15 15</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L139" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Championship Ring</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>I Want Blood</v>
+        <v>Da Realest</v>
       </c>
       <c r="G140" t="str">
-        <v>3:41</v>
+        <v>1:51</v>
       </c>
       <c r="H140" t="str">
-        <v>SleazyWorld Go</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L140" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>2:28</v>
+        <v>1:53</v>
       </c>
       <c r="H141" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L141" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Da Realest</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>1:51</v>
+        <v>2:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Babyfxce E</v>
+        <v>Soulidified</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L142" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Fine Shit</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G143" t="str">
-        <v>1:53</v>
+        <v>2:53</v>
       </c>
       <c r="H143" t="str">
-        <v>Real Boston Richey</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L143" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>What's Your Name</v>
+        <v>Bully</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:20</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Soulidified</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L144" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Ends In Y</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:53</v>
+        <v>3:16</v>
       </c>
       <c r="H145" t="str">
-        <v>Mimi Webb</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L145" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Bully</v>
+        <v>Ride</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Bully - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G146" t="str">
-        <v>3:05</v>
+        <v>4:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Iris Copperman</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L146" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:16</v>
+        <v>4:18</v>
       </c>
       <c r="H147" t="str">
-        <v>Charles Leclerc</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L147" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Ride</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Superbloom</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:39</v>
+        <v>2:10</v>
       </c>
       <c r="H148" t="str">
-        <v>Jessie Ware</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L148" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Arkansas Mud</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>4:18</v>
+        <v>2:31</v>
       </c>
       <c r="H149" t="str">
-        <v>Ashley McBryde</v>
+        <v>JayDon</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L149" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>Don't Leave</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Don't Leave - Single</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:10</v>
+        <v>2:49</v>
       </c>
       <c r="H150" t="str">
-        <v>Jorja Smith</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L150" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>FLAMED UP</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:31</v>
+        <v>5:13</v>
       </c>
       <c r="H151" t="str">
-        <v>JayDon</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L151" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>3am in Paris</v>
+        <v>Migajero</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>3am in Paris - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:49</v>
+        <v>3:18</v>
       </c>
       <c r="H152" t="str">
-        <v>Anais Cardot</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L152" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>5:13</v>
+        <v>3:26</v>
       </c>
       <c r="H153" t="str">
-        <v>Elevation Worship</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L153" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Migajero</v>
+        <v>Old Man</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Migajero - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:18</v>
+        <v>4:05</v>
       </c>
       <c r="H154" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Trousdale</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L154" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:26</v>
+        <v>3:19</v>
       </c>
       <c r="H155" t="str">
-        <v>Taylor Swift</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L155" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Old Man</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Old Man - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G156" t="str">
-        <v>4:05</v>
+        <v>2:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Trousdale</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L156" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Refuge</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G157" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H157" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L157" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G158" t="str">
-        <v>2:56</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Denzel Curry</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L158" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Refuge</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G159" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L159" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:24</v>
+        <v>3:21</v>
       </c>
       <c r="H160" t="str">
-        <v>Leigh-Anne</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L160" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Smoke Screen</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:51</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Sweet Pill</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L161" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Roamer</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G162" t="str">
-        <v>3:21</v>
+        <v>2:19</v>
       </c>
       <c r="H162" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>spill tab</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L162" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Angel Wings</v>
+        <v>These Nights</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G163" t="str">
-        <v>3:52</v>
+        <v>4:39</v>
       </c>
       <c r="H163" t="str">
-        <v>PRESIDENT</v>
+        <v>Cannons</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L163" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Roamer</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:19</v>
+        <v>2:55</v>
       </c>
       <c r="H164" t="str">
-        <v>spill tab</v>
+        <v>The Cab</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L164" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>These Nights</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Everything Glows</v>
+        <v>EI8HT</v>
       </c>
       <c r="G165" t="str">
-        <v>4:39</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Cannons</v>
+        <v>Shinedown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L165" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Locked and Loaded</v>
+        <v>Flinch</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G166" t="str">
-        <v>2:55</v>
+        <v>2:15</v>
       </c>
       <c r="H166" t="str">
-        <v>The Cab</v>
+        <v>alexsucks</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L166" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Safe And Sound</v>
+        <v>Fall Up</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>EI8HT</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>3:21</v>
+        <v>3:10</v>
       </c>
       <c r="H167" t="str">
-        <v>Shinedown</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L167" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Flinch</v>
+        <v>No Typo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Autopilot</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G168" t="str">
-        <v>2:15</v>
+        <v>1:43</v>
       </c>
       <c r="H168" t="str">
-        <v>alexsucks</v>
+        <v>Nasty C</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L168" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Fall Up</v>
+        <v>Desiree</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Fall Up - Single</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G169" t="str">
-        <v>3:10</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>VOILÀ</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L169" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>No Typo</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Goliath</v>
       </c>
       <c r="G170" t="str">
-        <v>1:43</v>
+        <v>5:04</v>
       </c>
       <c r="H170" t="str">
-        <v>Nasty C</v>
+        <v>Exodus</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L170" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Desiree</v>
+        <v>Nomad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Wings of Desire</v>
+        <v>Loss</v>
       </c>
       <c r="G171" t="str">
-        <v>3:46</v>
+        <v>5:30</v>
       </c>
       <c r="H171" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Gaerea</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L171" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Empty Words</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Goliath</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:04</v>
+        <v>2:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Exodus</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L172" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Nomad</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Loss</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>5:30</v>
+        <v>3:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Gaerea</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L173" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Empty Words</v>
+        <v>Euphoria</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Empty Words - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:32</v>
+        <v>2:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Corey Kent</v>
+        <v>Bluff City</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L174" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Didn't Forget</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:48</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>Waylon Wyatt</v>
+        <v>kwn</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L175" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Euphoria</v>
+        <v>Stay Close</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Euphoria - Single</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:14</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>Bluff City</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L176" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>hopeless romantic</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G177" t="str">
-        <v>3:03</v>
+        <v>2:54</v>
       </c>
       <c r="H177" t="str">
-        <v>kwn</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L177" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Stay Close</v>
+        <v>peace at last</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Stay Close - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:58</v>
+        <v>2:34</v>
       </c>
       <c r="H178" t="str">
-        <v>Evelyn Cormier</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L178" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Metamorphosis</v>
+        <v>Aguántame</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Metamorphosis</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:54</v>
+        <v>2:08</v>
       </c>
       <c r="H179" t="str">
-        <v>lydi lynn</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L179" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>peace at last</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>peace at last - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:34</v>
+        <v>2:40</v>
       </c>
       <c r="H180" t="str">
-        <v>Aaron Cole</v>
+        <v>Codiciado</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L180" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Aguántame</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Aguántame - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:08</v>
+        <v>3:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L181" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:40</v>
+        <v>2:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Codiciado</v>
+        <v>Esty</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L182" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G183" t="str">
-        <v>3:11</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>La Joaqui</v>
+        <v>The Pale White</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L183" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>V3n3n0</v>
+        <v>lately in the void</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>2:32</v>
+        <v>3:41</v>
       </c>
       <c r="H184" t="str">
-        <v>Esty</v>
+        <v>bad tuner</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L184" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Moth In The Headlights</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>Nightjar</v>
       </c>
       <c r="G185" t="str">
-        <v>4:23</v>
+        <v>4:45</v>
       </c>
       <c r="H185" t="str">
-        <v>The Pale White</v>
+        <v>David Gray</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L185" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>lately in the void</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>lately in the void - EP</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:41</v>
+        <v>2:33</v>
       </c>
       <c r="H186" t="str">
-        <v>bad tuner</v>
+        <v>yeemz</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L186" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>When I Fall in Love</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Nightjar</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G187" t="str">
-        <v>4:45</v>
+        <v>4:11</v>
       </c>
       <c r="H187" t="str">
-        <v>David Gray</v>
+        <v>Beatrix</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L187" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Repeat Offender</v>
+        <v>Promise Me</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G188" t="str">
-        <v>2:33</v>
+        <v>5:34</v>
       </c>
       <c r="H188" t="str">
-        <v>yeemz</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L188" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Class Reunion</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>4:11</v>
+        <v>3:33</v>
       </c>
       <c r="H189" t="str">
-        <v>Beatrix</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L189" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Promise Me</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Instant Comfort</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>5:34</v>
+        <v>3:19</v>
       </c>
       <c r="H190" t="str">
-        <v>Lucid Express</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L190" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>So Good</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:33</v>
+        <v>2:47</v>
       </c>
       <c r="H191" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L191" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>YDH</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:19</v>
+        <v>3:17</v>
       </c>
       <c r="H192" t="str">
-        <v>Ray Vaughn</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L192" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>So Good</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>So Good - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G193" t="str">
-        <v>2:47</v>
+        <v>3:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Ari Abdul</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L193" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>YDH</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>YDH - Single</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:17</v>
+        <v>1:38</v>
       </c>
       <c r="H194" t="str">
-        <v>Chloe Qisha</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L194" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Eucalyptus</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Porcelain</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G195" t="str">
-        <v>3:00</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>Peach PRC</v>
+        <v>At The Gates</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L195" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Pearls In The Trap</v>
+        <v>The Air's on Fire</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-22</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>Location Lost</v>
       </c>
       <c r="G196" t="str">
-        <v>1:38</v>
+        <v>5:15</v>
       </c>
       <c r="H196" t="str">
-        <v>carolesdaughter</v>
+        <v>Failure</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
       </c>
       <c r="L196" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>The Air's on Fire - Failure</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>The Fever Mask</v>
+        <v>To The Last Breath</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-22</v>
@@ -7861,106 +7861,30 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>To The Last Breath - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>3:12</v>
+        <v>4:57</v>
       </c>
       <c r="H197" t="str">
-        <v>At The Gates</v>
+        <v>Arch Enemy</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
       <c r="L197" t="str">
-        <v>The Fever Mask - At The Gates</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>The Air's on Fire</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>Location Lost</v>
-      </c>
-      <c r="G198" t="str">
-        <v>5:15</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Failure</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
-      </c>
-      <c r="L198" t="str">
-        <v>The Air's on Fire - Failure</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>To The Last Breath</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>To The Last Breath - Single</v>
-      </c>
-      <c r="G199" t="str">
-        <v>4:57</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Arch Enemy</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
-      </c>
-      <c r="L199" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L199"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L207"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>ששון שאולוב - מלי מלי</v>
       </c>
       <c r="B2" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409712&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-22</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>3:20</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>georgemichael</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>ששון שאולוב - מלי מלי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>שי וינר - תן לי</v>
       </c>
       <c r="B3" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409711&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-22</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:50</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>Cliff Richard</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>שי וינר - תן לי</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>עדן גולן - מספיק ממך</v>
       </c>
       <c r="B4" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409710&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-22</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>3:14</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Freya Ridings</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>עדן גולן - מספיק ממך</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>סטטיק - מנדם</v>
       </c>
       <c r="B5" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409709&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-22</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>4:37</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Jessie Ware</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>סטטיק - מנדם</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409708&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-22</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>3:16</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>Alan Walker</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>יגל יובל שרעבי - מחושך לאור</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409707&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-22</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>4:22</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>The Neighbourhood</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>יגל יובל שרעבי - מחושך לאור</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>ויולט - לנוע</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409706&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-22</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>3:45</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>YUNGBLUD</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>ויולט - לנוע</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Suburban Requiem</v>
+        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
       </c>
       <c r="B9" t="str">
-        <v>3 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409705&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-22</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>3 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>4:40</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>YUNGBLUD</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>אלמוג זגרון - ג׳ורדן</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409704&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-22</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G10" t="str">
-        <v>3:02</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Calum Scott</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>אלמוג זגרון - ג׳ורדן</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>אדיר בובליל - בא לי שוב</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-22</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409703&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-22</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G11" t="str">
-        <v>3:12</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>אדיר בובליל - בא לי שוב</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-22</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:38</v>
+        <v>3:20</v>
       </c>
       <c r="H12" t="str">
-        <v>Dermot Kennedy</v>
+        <v>georgemichael</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-22</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:40</v>
+        <v>4:50</v>
       </c>
       <c r="H13" t="str">
-        <v>Cannons</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-22</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:57</v>
+        <v>3:14</v>
       </c>
       <c r="H14" t="str">
-        <v>Mimi Webb</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-22</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>2:13</v>
+        <v>4:37</v>
       </c>
       <c r="H15" t="str">
-        <v>Jorja Smith</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-22</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:12</v>
+        <v>3:16</v>
       </c>
       <c r="H16" t="str">
-        <v>Sam Williams</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-22</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>2:55</v>
+        <v>4:22</v>
       </c>
       <c r="H17" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-22</v>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:51</v>
+        <v>3:45</v>
       </c>
       <c r="H18" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-22</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>2:51</v>
+        <v>4:40</v>
       </c>
       <c r="H19" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-22</v>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:24</v>
+        <v>3:02</v>
       </c>
       <c r="H20" t="str">
-        <v>REALITY CLUB</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-22</v>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:11</v>
+        <v>3:12</v>
       </c>
       <c r="H21" t="str">
-        <v>We Three</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-22</v>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:27</v>
+        <v>3:38</v>
       </c>
       <c r="H22" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-22</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:06</v>
+        <v>4:40</v>
       </c>
       <c r="H23" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Cannons</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-22</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:01</v>
+        <v>2:57</v>
       </c>
       <c r="H24" t="str">
-        <v>Peach PRC</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B25" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-22</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>5:38</v>
+        <v>2:13</v>
       </c>
       <c r="H25" t="str">
-        <v>georgemichael</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-22</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:43</v>
+        <v>4:12</v>
       </c>
       <c r="H26" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-22</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:58</v>
+        <v>2:55</v>
       </c>
       <c r="H27" t="str">
-        <v>Catie Turner</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-22</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:13</v>
+        <v>3:51</v>
       </c>
       <c r="H28" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-22</v>
@@ -1477,13 +1477,13 @@
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>5:48</v>
+        <v>2:51</v>
       </c>
       <c r="H29" t="str">
-        <v>U2</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-22</v>
@@ -1515,13 +1515,13 @@
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:55</v>
+        <v>3:24</v>
       </c>
       <c r="H30" t="str">
-        <v>Lawrence</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B31" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-22</v>
@@ -1553,13 +1553,13 @@
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>4 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>5:24</v>
+        <v>4:11</v>
       </c>
       <c r="H31" t="str">
-        <v>BUNT. Music</v>
+        <v>We Three</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-22</v>
@@ -1591,13 +1591,13 @@
         <v/>
       </c>
       <c r="F32" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:59</v>
+        <v>3:27</v>
       </c>
       <c r="H32" t="str">
-        <v>Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-22</v>
@@ -1629,13 +1629,13 @@
         <v/>
       </c>
       <c r="F33" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>2:10</v>
+        <v>3:06</v>
       </c>
       <c r="H33" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-22</v>
@@ -1667,13 +1667,13 @@
         <v/>
       </c>
       <c r="F34" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:11</v>
+        <v>3:01</v>
       </c>
       <c r="H34" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-22</v>
@@ -1705,13 +1705,13 @@
         <v/>
       </c>
       <c r="F35" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:26</v>
+        <v>5:38</v>
       </c>
       <c r="H35" t="str">
-        <v>Neal Francis</v>
+        <v>georgemichael</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B36" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-22</v>
@@ -1746,10 +1746,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:35</v>
+        <v>3:43</v>
       </c>
       <c r="H36" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-22</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:09</v>
+        <v>2:58</v>
       </c>
       <c r="H37" t="str">
-        <v>Lola Young</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-22</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:11</v>
+        <v>4:13</v>
       </c>
       <c r="H38" t="str">
-        <v>Holly Humberstone</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B39" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-22</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:01</v>
+        <v>5:48</v>
       </c>
       <c r="H39" t="str">
-        <v>The Vaccines</v>
+        <v>U2</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B40" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-22</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:28</v>
+        <v>3:55</v>
       </c>
       <c r="H40" t="str">
-        <v>mgk</v>
+        <v>Lawrence</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B41" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-22</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:31</v>
+        <v>5:24</v>
       </c>
       <c r="H41" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B42" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-22</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:49</v>
+        <v>4:59</v>
       </c>
       <c r="H42" t="str">
-        <v>Mýa</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B43" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-22</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:03</v>
+        <v>2:10</v>
       </c>
       <c r="H43" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B44" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-22</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:59</v>
+        <v>3:11</v>
       </c>
       <c r="H44" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B45" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-22</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:41</v>
+        <v>4:26</v>
       </c>
       <c r="H45" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B46" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-22</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:59</v>
+        <v>4:35</v>
       </c>
       <c r="H46" t="str">
-        <v>ENHYPEN</v>
+        <v>mgk</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B47" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-22</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:59</v>
+        <v>2:09</v>
       </c>
       <c r="H47" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lola Young</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B48" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-22</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>7:48</v>
+        <v>4:11</v>
       </c>
       <c r="H48" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-22</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:10</v>
+        <v>3:01</v>
       </c>
       <c r="H49" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-22</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>5:57</v>
+        <v>3:28</v>
       </c>
       <c r="H50" t="str">
-        <v>The Doobie Brothers</v>
+        <v>mgk</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B51" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-22</v>
@@ -2316,7 +2316,7 @@
         <v>8 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>2:25</v>
+        <v>5:31</v>
       </c>
       <c r="H51" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-22</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:19</v>
+        <v>2:49</v>
       </c>
       <c r="H52" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-22</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:38</v>
+        <v>3:03</v>
       </c>
       <c r="H53" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-22</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:05</v>
+        <v>2:59</v>
       </c>
       <c r="H54" t="str">
-        <v>Dermot Kennedy</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-22</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>5:46</v>
+        <v>2:41</v>
       </c>
       <c r="H55" t="str">
-        <v>Jacob Collier</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-22</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:25</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>Victor Ray</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-22</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>5:11</v>
+        <v>3:59</v>
       </c>
       <c r="H57" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-22</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:55</v>
+        <v>7:48</v>
       </c>
       <c r="H58" t="str">
-        <v>The Warning</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-22</v>
@@ -2620,10 +2620,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>4:54</v>
+        <v>3:10</v>
       </c>
       <c r="H59" t="str">
-        <v>The Offspring</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-22</v>
@@ -2658,10 +2658,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:01</v>
+        <v>5:57</v>
       </c>
       <c r="H60" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-22</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:55</v>
+        <v>2:25</v>
       </c>
       <c r="H61" t="str">
-        <v>HAUSER</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-22</v>
@@ -2734,10 +2734,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:43</v>
+        <v>3:19</v>
       </c>
       <c r="H62" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B63" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-22</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>2 weeks ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:53</v>
+        <v>3:38</v>
       </c>
       <c r="H63" t="str">
-        <v>Ultra Records</v>
+        <v>mgk</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-22</v>
@@ -2810,10 +2810,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:30</v>
+        <v>4:05</v>
       </c>
       <c r="H64" t="str">
-        <v>Anja Kotar</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B65" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-22</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:37</v>
+        <v>5:46</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bolton</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B66" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-22</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:10</v>
+        <v>3:25</v>
       </c>
       <c r="H66" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-22</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:06</v>
+        <v>5:11</v>
       </c>
       <c r="H67" t="str">
-        <v>Alan Walker</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-22</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:17</v>
+        <v>2:55</v>
       </c>
       <c r="H68" t="str">
-        <v>Bruno Mars</v>
+        <v>The Warning</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-22</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:21</v>
+        <v>4:54</v>
       </c>
       <c r="H69" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>The Offspring</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-22</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>6:58</v>
+        <v>5:01</v>
       </c>
       <c r="H70" t="str">
-        <v>Eric Church</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-22</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:29</v>
+        <v>3:55</v>
       </c>
       <c r="H71" t="str">
-        <v>Meghan Trainor</v>
+        <v>HAUSER</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B72" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-22</v>
@@ -3111,13 +3111,13 @@
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:14</v>
+        <v>3:43</v>
       </c>
       <c r="H72" t="str">
-        <v>Ally Salort</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B73" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-22</v>
@@ -3149,13 +3149,13 @@
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:51</v>
+        <v>2:53</v>
       </c>
       <c r="H73" t="str">
-        <v>Will Swinton</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-22</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:10</v>
+        <v>3:30</v>
       </c>
       <c r="H74" t="str">
-        <v>elijah woods</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-22</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:26</v>
+        <v>3:37</v>
       </c>
       <c r="H75" t="str">
-        <v>Jackson Dean</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-22</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:51</v>
+        <v>4:10</v>
       </c>
       <c r="H76" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-22</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H77" t="str">
-        <v>Neil Sedaka</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-22</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H78" t="str">
-        <v>Sofia Camara</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-22</v>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:04</v>
+        <v>3:21</v>
       </c>
       <c r="H79" t="str">
-        <v>Russell Dickerson</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-22</v>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:03</v>
+        <v>6:58</v>
       </c>
       <c r="H80" t="str">
-        <v>Celine Dion</v>
+        <v>Eric Church</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-22</v>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H81" t="str">
-        <v>Bebe Rexha</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-22</v>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H82" t="str">
-        <v>Caroline Jones</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-22</v>
@@ -3532,10 +3532,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>2:32</v>
+        <v>3:51</v>
       </c>
       <c r="H83" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-22</v>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:32</v>
+        <v>3:10</v>
       </c>
       <c r="H84" t="str">
-        <v>Ingrid Andress</v>
+        <v>elijah woods</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B85" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-22</v>
@@ -3608,10 +3608,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H85" t="str">
-        <v>MusicByKnox</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-22</v>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H86" t="str">
-        <v>Ella Langley</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-22</v>
@@ -3687,7 +3687,7 @@
         <v>3:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Nickless</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-22</v>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:57</v>
+        <v>3:06</v>
       </c>
       <c r="H88" t="str">
-        <v>Caroline Jones</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-22</v>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:08</v>
+        <v>3:04</v>
       </c>
       <c r="H89" t="str">
-        <v>elijah woods</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B90" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-22</v>
@@ -3798,10 +3798,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:53</v>
+        <v>3:03</v>
       </c>
       <c r="H90" t="str">
-        <v>August Ponthier</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-22</v>
@@ -3836,10 +3836,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:10</v>
+        <v>2:38</v>
       </c>
       <c r="H91" t="str">
-        <v>Charli xcx</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-22</v>
@@ -3874,7 +3874,7 @@
         <v>9 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:58</v>
+        <v>3:29</v>
       </c>
       <c r="H92" t="str">
         <v>Caroline Jones</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B93" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-22</v>
@@ -3912,10 +3912,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:44</v>
+        <v>2:32</v>
       </c>
       <c r="H93" t="str">
-        <v>Leah Kate</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-22</v>
@@ -3950,10 +3950,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:25</v>
+        <v>3:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Troye Sivan</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-22</v>
@@ -3988,10 +3988,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>4:08</v>
+        <v>2:51</v>
       </c>
       <c r="H95" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B96" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-22</v>
@@ -4026,10 +4026,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:09</v>
+        <v>3:38</v>
       </c>
       <c r="H96" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B97" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-22</v>
@@ -4064,10 +4064,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:11</v>
+        <v>3:26</v>
       </c>
       <c r="H97" t="str">
-        <v>The Happy Fits</v>
+        <v>Nickless</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-22</v>
@@ -4102,10 +4102,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:02</v>
+        <v>3:57</v>
       </c>
       <c r="H98" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-22</v>
@@ -4140,10 +4140,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>4:20</v>
+        <v>3:08</v>
       </c>
       <c r="H99" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>elijah woods</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B100" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-22</v>
@@ -4178,10 +4178,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>4:09</v>
+        <v>3:53</v>
       </c>
       <c r="H100" t="str">
-        <v>Quinn XCII</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-22</v>
@@ -4216,10 +4216,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>4:34</v>
+        <v>3:10</v>
       </c>
       <c r="H101" t="str">
-        <v>We Three</v>
+        <v>Charli xcx</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Badlands</v>
+        <v>Caroline Jones - Family (Lyric Video)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-22</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Prizefighter</v>
+        <v>9 days ago</v>
       </c>
       <c r="G102" t="str">
         <v>2:58</v>
       </c>
       <c r="H102" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
       </c>
       <c r="B103" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-22</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>9 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>3:48</v>
+        <v>2:44</v>
       </c>
       <c r="H103" t="str">
-        <v>Taylor Swift</v>
+        <v>Leah Kate</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v/>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v/>
       </c>
       <c r="L103" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
       </c>
       <c r="B104" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-22</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>9 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:54</v>
+        <v>3:25</v>
       </c>
       <c r="H104" t="str">
-        <v>Lana Del Rey</v>
+        <v>Troye Sivan</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v/>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v/>
       </c>
       <c r="L104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ROSITA</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
       </c>
       <c r="B105" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-22</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>ROSITA - Single</v>
+        <v>9 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>4:05</v>
+        <v>4:08</v>
       </c>
       <c r="H105" t="str">
-        <v>Tainy</v>
+        <v>Romeo Santos and Prince Royce</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v/>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v/>
       </c>
       <c r="L105" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
       </c>
       <c r="B106" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-22</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ca$ino</v>
+        <v>9 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:52</v>
+        <v>3:09</v>
       </c>
       <c r="H106" t="str">
-        <v>Baby Keem</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v/>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v/>
       </c>
       <c r="L106" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
       </c>
       <c r="B107" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-22</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>9 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>2:52</v>
+        <v>3:11</v>
       </c>
       <c r="H107" t="str">
-        <v>SZA</v>
+        <v>The Happy Fits</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v/>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v/>
       </c>
       <c r="L107" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Medicine</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
       </c>
       <c r="B108" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-22</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>9 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:11</v>
+        <v>3:02</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>HYBE LABELS and SANTOS BRAVOS</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v/>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v/>
       </c>
       <c r="L108" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Weather For Tennis</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B109" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-22</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>luck... or something</v>
+        <v>9 days ago</v>
       </c>
       <c r="G109" t="str">
-        <v>3:16</v>
+        <v>4:20</v>
       </c>
       <c r="H109" t="str">
-        <v>Hilary Duff</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v/>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v/>
       </c>
       <c r="L109" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ear to the cocoon</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
       </c>
       <c r="B110" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-22</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>petal rock black</v>
+        <v>9 days ago</v>
       </c>
       <c r="G110" t="str">
-        <v>4:18</v>
+        <v>4:09</v>
       </c>
       <c r="H110" t="str">
-        <v>WILLOW</v>
+        <v>Quinn XCII</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v/>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v/>
       </c>
       <c r="L110" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag Path</v>
+        <v>We Three - Drunk Driving (Live Sessions)</v>
       </c>
       <c r="B111" t="str">
-        <v/>
+        <v>9 days ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-22</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Drag Path - Single</v>
+        <v>9 days ago</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>4:34</v>
       </c>
       <c r="H111" t="str">
-        <v>twenty one pilots</v>
+        <v>We Three</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v/>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v/>
       </c>
       <c r="L111" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Song Of The Future</v>
+        <v>Badlands</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-22</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G112" t="str">
-        <v>3:55</v>
+        <v>2:58</v>
       </c>
       <c r="H112" t="str">
-        <v>U2</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L112" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-22</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G113" t="str">
-        <v>2:56</v>
+        <v>3:48</v>
       </c>
       <c r="H113" t="str">
-        <v>Foo Fighters</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L113" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Trimski</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-22</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Trimski - Single</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:02</v>
+        <v>3:54</v>
       </c>
       <c r="H114" t="str">
-        <v>NAV</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L114" t="str">
-        <v>Trimski - NAV</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Paracosm</v>
+        <v>ROSITA</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-22</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Paracosm</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:23</v>
+        <v>4:05</v>
       </c>
       <c r="H115" t="str">
-        <v>Absolutely</v>
+        <v>Tainy</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L115" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Casual Lady</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-22</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G116" t="str">
-        <v>3:14</v>
+        <v>3:52</v>
       </c>
       <c r="H116" t="str">
-        <v>flowerovlove</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L116" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-22</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:18</v>
+        <v>2:52</v>
       </c>
       <c r="H117" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>SZA</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L117" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Begging for Change</v>
+        <v>Medicine</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-22</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>HELP(2)</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G118" t="str">
-        <v>4:20</v>
+        <v>3:11</v>
       </c>
       <c r="H118" t="str">
-        <v>Pulp</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L118" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>My Maker</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-22</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ricochet</v>
+        <v>luck... or something</v>
       </c>
       <c r="G119" t="str">
-        <v>4:19</v>
+        <v>3:16</v>
       </c>
       <c r="H119" t="str">
-        <v>Snail Mail</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L119" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-22</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>petal rock black</v>
       </c>
       <c r="G120" t="str">
-        <v>3:32</v>
+        <v>4:18</v>
       </c>
       <c r="H120" t="str">
-        <v>Taylor Swift</v>
+        <v>WILLOW</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L120" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Drag Path</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-22</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:27</v>
+        <v>3:44</v>
       </c>
       <c r="H121" t="str">
-        <v>CHVRCHES</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>She Knows Too Much</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-22</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Distracted</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G122" t="str">
-        <v>3:33</v>
+        <v>3:55</v>
       </c>
       <c r="H122" t="str">
-        <v>Thundercat</v>
+        <v>U2</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L122" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tea Time</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-22</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tea Time - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G123" t="str">
-        <v>2:25</v>
+        <v>2:56</v>
       </c>
       <c r="H123" t="str">
-        <v>Yung Miami</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L123" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Trimski</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-22</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H124" t="str">
-        <v>Brent Faiyaz</v>
+        <v>NAV</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L124" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Save My Love</v>
+        <v>Paracosm</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-22</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Save My Love - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G125" t="str">
-        <v>3:30</v>
+        <v>3:23</v>
       </c>
       <c r="H125" t="str">
-        <v>Kygo</v>
+        <v>Absolutely</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L125" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-22</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:46</v>
+        <v>3:14</v>
       </c>
       <c r="H126" t="str">
-        <v>Omar Courtz</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L126" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Suburban Requiem</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-22</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Idols (Complete)</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:39</v>
+        <v>4:18</v>
       </c>
       <c r="H127" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L127" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Good Grief</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-22</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G128" t="str">
-        <v>4:21</v>
+        <v>4:20</v>
       </c>
       <c r="H128" t="str">
-        <v>The Neighbourhood</v>
+        <v>Pulp</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L128" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Freak On</v>
+        <v>My Maker</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-22</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Freak On - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G129" t="str">
-        <v>2:49</v>
+        <v>4:19</v>
       </c>
       <c r="H129" t="str">
-        <v>Steve Aoki</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L129" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-22</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G130" t="str">
         <v>3:32</v>
       </c>
       <c r="H130" t="str">
-        <v>deadmau5</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L130" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-22</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:55</v>
+        <v>4:27</v>
       </c>
       <c r="H131" t="str">
-        <v>Taylor Swift</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L131" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Yellow Eyes</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-22</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Jean</v>
+        <v>Distracted</v>
       </c>
       <c r="G132" t="str">
-        <v>2:42</v>
+        <v>3:33</v>
       </c>
       <c r="H132" t="str">
-        <v>Yebba</v>
+        <v>Thundercat</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L132" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Word On The Street</v>
+        <v>Tea Time</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-22</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>2:25</v>
       </c>
       <c r="H133" t="str">
-        <v>Luke Bryan</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L133" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>only the best</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-22</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>only the best - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G134" t="str">
-        <v>3:22</v>
+        <v>3:12</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L134" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Beautiful Places</v>
+        <v>Save My Love</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-22</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:59</v>
+        <v>3:30</v>
       </c>
       <c r="H135" t="str">
-        <v>Tiësto</v>
+        <v>Kygo</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L135" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>STAMPEDE</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-22</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G136" t="str">
-        <v>3:09</v>
+        <v>3:46</v>
       </c>
       <c r="H136" t="str">
-        <v>Genesis Owusu</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L136" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Infinite Beach</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-22</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Mārara</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G137" t="str">
-        <v>3:10</v>
+        <v>4:39</v>
       </c>
       <c r="H137" t="str">
-        <v>15 15</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L137" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Championship Ring</v>
+        <v>Good Grief</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-22</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Want Blood</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G138" t="str">
-        <v>3:41</v>
+        <v>4:21</v>
       </c>
       <c r="H138" t="str">
-        <v>SleazyWorld Go</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L138" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>Freak On</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-22</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G139" t="str">
-        <v>2:28</v>
+        <v>2:49</v>
       </c>
       <c r="H139" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L139" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-22</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Da Realest</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>1:51</v>
+        <v>3:32</v>
       </c>
       <c r="H140" t="str">
-        <v>Babyfxce E</v>
+        <v>deadmau5</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L140" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Fine Shit</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-22</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:53</v>
+        <v>3:55</v>
       </c>
       <c r="H141" t="str">
-        <v>Real Boston Richey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L141" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>What's Your Name</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-22</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G142" t="str">
-        <v>2:20</v>
+        <v>2:42</v>
       </c>
       <c r="H142" t="str">
-        <v>Soulidified</v>
+        <v>Yebba</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L142" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ends In Y</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-22</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:53</v>
+        <v>2:56</v>
       </c>
       <c r="H143" t="str">
-        <v>Mimi Webb</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L143" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Bully</v>
+        <v>only the best</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-22</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Bully - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>3:22</v>
       </c>
       <c r="H144" t="str">
-        <v>Iris Copperman</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L144" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-22</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:16</v>
+        <v>2:59</v>
       </c>
       <c r="H145" t="str">
-        <v>Charles Leclerc</v>
+        <v>Tiësto</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L145" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Ride</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-22</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Superbloom</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:39</v>
+        <v>3:09</v>
       </c>
       <c r="H146" t="str">
-        <v>Jessie Ware</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L146" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Arkansas Mud</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-22</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G147" t="str">
-        <v>4:18</v>
+        <v>3:10</v>
       </c>
       <c r="H147" t="str">
-        <v>Ashley McBryde</v>
+        <v>15 15</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L147" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Don't Leave</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-22</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Don't Leave - Single</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G148" t="str">
-        <v>2:10</v>
+        <v>3:41</v>
       </c>
       <c r="H148" t="str">
-        <v>Jorja Smith</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L148" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FLAMED UP</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-22</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G149" t="str">
-        <v>2:31</v>
+        <v>2:28</v>
       </c>
       <c r="H149" t="str">
-        <v>JayDon</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L149" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>3am in Paris</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-22</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>3am in Paris - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G150" t="str">
-        <v>2:49</v>
+        <v>1:51</v>
       </c>
       <c r="H150" t="str">
-        <v>Anais Cardot</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L150" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-22</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:13</v>
+        <v>1:53</v>
       </c>
       <c r="H151" t="str">
-        <v>Elevation Worship</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L151" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Migajero</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-22</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Migajero - Single</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>3:18</v>
+        <v>2:20</v>
       </c>
       <c r="H152" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Soulidified</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L152" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-22</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G153" t="str">
-        <v>3:26</v>
+        <v>2:53</v>
       </c>
       <c r="H153" t="str">
-        <v>Taylor Swift</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L153" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Old Man</v>
+        <v>Bully</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-22</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Old Man - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:05</v>
+        <v>3:05</v>
       </c>
       <c r="H154" t="str">
-        <v>Trousdale</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L154" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-22</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:19</v>
+        <v>3:16</v>
       </c>
       <c r="H155" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L155" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Ride</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-22</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Superbloom</v>
       </c>
       <c r="G156" t="str">
-        <v>2:56</v>
+        <v>4:39</v>
       </c>
       <c r="H156" t="str">
-        <v>Denzel Curry</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L156" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Refuge</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-22</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G157" t="str">
-        <v>3:38</v>
+        <v>4:18</v>
       </c>
       <c r="H157" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L157" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-22</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>3:24</v>
+        <v>2:10</v>
       </c>
       <c r="H158" t="str">
-        <v>Leigh-Anne</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L158" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Smoke Screen</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-22</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Still There’s a Glow</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:51</v>
+        <v>2:31</v>
       </c>
       <c r="H159" t="str">
-        <v>Sweet Pill</v>
+        <v>JayDon</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L159" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-22</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>3:21</v>
+        <v>2:49</v>
       </c>
       <c r="H160" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Angel Wings</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-22</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Angel Wings - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G161" t="str">
-        <v>3:52</v>
+        <v>5:13</v>
       </c>
       <c r="H161" t="str">
-        <v>PRESIDENT</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L161" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Roamer</v>
+        <v>Migajero</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-22</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:19</v>
+        <v>3:18</v>
       </c>
       <c r="H162" t="str">
-        <v>spill tab</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L162" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>These Nights</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-22</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Everything Glows</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>4:39</v>
+        <v>3:26</v>
       </c>
       <c r="H163" t="str">
-        <v>Cannons</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L163" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Locked and Loaded</v>
+        <v>Old Man</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-22</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>2:55</v>
+        <v>4:05</v>
       </c>
       <c r="H164" t="str">
-        <v>The Cab</v>
+        <v>Trousdale</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L164" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Safe And Sound</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-22</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>EI8HT</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:21</v>
+        <v>3:19</v>
       </c>
       <c r="H165" t="str">
-        <v>Shinedown</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L165" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Flinch</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-22</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Autopilot</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G166" t="str">
-        <v>2:15</v>
+        <v>2:56</v>
       </c>
       <c r="H166" t="str">
-        <v>alexsucks</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L166" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fall Up</v>
+        <v>Refuge</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-22</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Fall Up - Single</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G167" t="str">
-        <v>3:10</v>
+        <v>3:38</v>
       </c>
       <c r="H167" t="str">
-        <v>VOILÀ</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L167" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>No Typo</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-22</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Free (Deluxe)</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G168" t="str">
-        <v>1:43</v>
+        <v>3:24</v>
       </c>
       <c r="H168" t="str">
-        <v>Nasty C</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L168" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Desiree</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-22</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Wings of Desire</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>2:51</v>
       </c>
       <c r="H169" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L169" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-22</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Goliath</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G170" t="str">
-        <v>5:04</v>
+        <v>3:21</v>
       </c>
       <c r="H170" t="str">
-        <v>Exodus</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L170" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Nomad</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-22</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Loss</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>5:30</v>
+        <v>3:52</v>
       </c>
       <c r="H171" t="str">
-        <v>Gaerea</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L171" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Empty Words</v>
+        <v>Roamer</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-22</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Empty Words - Single</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G172" t="str">
-        <v>2:32</v>
+        <v>2:19</v>
       </c>
       <c r="H172" t="str">
-        <v>Corey Kent</v>
+        <v>spill tab</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L172" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Didn't Forget</v>
+        <v>These Nights</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-22</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G173" t="str">
-        <v>3:48</v>
+        <v>4:39</v>
       </c>
       <c r="H173" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Cannons</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L173" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Euphoria</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-22</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Euphoria - Single</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:14</v>
+        <v>2:55</v>
       </c>
       <c r="H174" t="str">
-        <v>Bluff City</v>
+        <v>The Cab</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L174" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>hopeless romantic</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-22</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G175" t="str">
-        <v>3:03</v>
+        <v>3:21</v>
       </c>
       <c r="H175" t="str">
-        <v>kwn</v>
+        <v>Shinedown</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L175" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Stay Close</v>
+        <v>Flinch</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-22</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Stay Close - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G176" t="str">
-        <v>2:58</v>
+        <v>2:15</v>
       </c>
       <c r="H176" t="str">
-        <v>Evelyn Cormier</v>
+        <v>alexsucks</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L176" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Metamorphosis</v>
+        <v>Fall Up</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-22</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Metamorphosis</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:54</v>
+        <v>3:10</v>
       </c>
       <c r="H177" t="str">
-        <v>lydi lynn</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L177" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>peace at last</v>
+        <v>No Typo</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-22</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>peace at last - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G178" t="str">
-        <v>2:34</v>
+        <v>1:43</v>
       </c>
       <c r="H178" t="str">
-        <v>Aaron Cole</v>
+        <v>Nasty C</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L178" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Aguántame</v>
+        <v>Desiree</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-22</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Aguántame - Single</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G179" t="str">
-        <v>2:08</v>
+        <v>3:46</v>
       </c>
       <c r="H179" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L179" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-22</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>Goliath</v>
       </c>
       <c r="G180" t="str">
-        <v>2:40</v>
+        <v>5:04</v>
       </c>
       <c r="H180" t="str">
-        <v>Codiciado</v>
+        <v>Exodus</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L180" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Nomad</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-22</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G181" t="str">
-        <v>3:11</v>
+        <v>5:30</v>
       </c>
       <c r="H181" t="str">
-        <v>La Joaqui</v>
+        <v>Gaerea</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L181" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>V3n3n0</v>
+        <v>Empty Words</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-22</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G182" t="str">
         <v>2:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Esty</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L182" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Moth In The Headlights</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-22</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:23</v>
+        <v>3:48</v>
       </c>
       <c r="H183" t="str">
-        <v>The Pale White</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L183" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>lately in the void</v>
+        <v>Euphoria</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-22</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>lately in the void - EP</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>3:41</v>
+        <v>2:14</v>
       </c>
       <c r="H184" t="str">
-        <v>bad tuner</v>
+        <v>Bluff City</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L184" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>When I Fall in Love</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-22</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Nightjar</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>4:45</v>
+        <v>3:03</v>
       </c>
       <c r="H185" t="str">
-        <v>David Gray</v>
+        <v>kwn</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L185" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Repeat Offender</v>
+        <v>Stay Close</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-22</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:33</v>
+        <v>2:58</v>
       </c>
       <c r="H186" t="str">
-        <v>yeemz</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L186" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Class Reunion</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-22</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G187" t="str">
-        <v>4:11</v>
+        <v>2:54</v>
       </c>
       <c r="H187" t="str">
-        <v>Beatrix</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L187" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Promise Me</v>
+        <v>peace at last</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-22</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Instant Comfort</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G188" t="str">
-        <v>5:34</v>
+        <v>2:34</v>
       </c>
       <c r="H188" t="str">
-        <v>Lucid Express</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L188" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Aguántame</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-22</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>3:33</v>
+        <v>2:08</v>
       </c>
       <c r="H189" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L189" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-22</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:19</v>
+        <v>2:40</v>
       </c>
       <c r="H190" t="str">
-        <v>Ray Vaughn</v>
+        <v>Codiciado</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L190" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>So Good</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-22</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>So Good - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:47</v>
+        <v>3:11</v>
       </c>
       <c r="H191" t="str">
-        <v>Ari Abdul</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L191" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>YDH</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-22</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>YDH - Single</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:17</v>
+        <v>2:32</v>
       </c>
       <c r="H192" t="str">
-        <v>Chloe Qisha</v>
+        <v>Esty</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L192" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Eucalyptus</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-22</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Porcelain</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G193" t="str">
-        <v>3:00</v>
+        <v>4:23</v>
       </c>
       <c r="H193" t="str">
-        <v>Peach PRC</v>
+        <v>The Pale White</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L193" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Pearls In The Trap</v>
+        <v>lately in the void</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-22</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G194" t="str">
-        <v>1:38</v>
+        <v>3:41</v>
       </c>
       <c r="H194" t="str">
-        <v>carolesdaughter</v>
+        <v>bad tuner</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L194" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>The Fever Mask</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-22</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Nightjar</v>
       </c>
       <c r="G195" t="str">
-        <v>3:12</v>
+        <v>4:45</v>
       </c>
       <c r="H195" t="str">
-        <v>At The Gates</v>
+        <v>David Gray</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L195" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Air's on Fire</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-22</v>
@@ -7823,68 +7823,448 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Location Lost</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G196" t="str">
-        <v>5:15</v>
+        <v>2:33</v>
       </c>
       <c r="H196" t="str">
-        <v>Failure</v>
+        <v>yeemz</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L196" t="str">
-        <v>The Air's on Fire - Failure</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
+        <v>Class Reunion</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>We Swallowed The Sky</v>
+      </c>
+      <c r="G197" t="str">
+        <v>4:11</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Beatrix</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+      </c>
+      <c r="L197" t="str">
+        <v>Class Reunion - Beatrix</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>Promise Me</v>
+      </c>
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+      </c>
+      <c r="D198" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
+        <v>Instant Comfort</v>
+      </c>
+      <c r="G198" t="str">
+        <v>5:34</v>
+      </c>
+      <c r="H198" t="str">
+        <v>Lucid Express</v>
+      </c>
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+      </c>
+      <c r="K198" t="str">
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+      </c>
+      <c r="L198" t="str">
+        <v>Promise Me - Lucid Express</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+      </c>
+      <c r="B199" t="str">
+        <v/>
+      </c>
+      <c r="C199" t="str">
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+      </c>
+      <c r="D199" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E199" t="str">
+        <v/>
+      </c>
+      <c r="F199" t="str">
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+      </c>
+      <c r="G199" t="str">
+        <v>3:33</v>
+      </c>
+      <c r="H199" t="str">
+        <v>Zee Nxumalo</v>
+      </c>
+      <c r="I199" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J199" t="str">
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+      </c>
+      <c r="K199" t="str">
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+      </c>
+      <c r="L199" t="str">
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>Hit and Run (feat. AZ Chike)</v>
+      </c>
+      <c r="B200" t="str">
+        <v/>
+      </c>
+      <c r="C200" t="str">
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+      </c>
+      <c r="D200" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E200" t="str">
+        <v/>
+      </c>
+      <c r="F200" t="str">
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
+      </c>
+      <c r="G200" t="str">
+        <v>3:19</v>
+      </c>
+      <c r="H200" t="str">
+        <v>Ray Vaughn</v>
+      </c>
+      <c r="I200" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J200" t="str">
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+      </c>
+      <c r="K200" t="str">
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+      </c>
+      <c r="L200" t="str">
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>So Good</v>
+      </c>
+      <c r="B201" t="str">
+        <v/>
+      </c>
+      <c r="C201" t="str">
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+      </c>
+      <c r="D201" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E201" t="str">
+        <v/>
+      </c>
+      <c r="F201" t="str">
+        <v>So Good - Single</v>
+      </c>
+      <c r="G201" t="str">
+        <v>2:47</v>
+      </c>
+      <c r="H201" t="str">
+        <v>Ari Abdul</v>
+      </c>
+      <c r="I201" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J201" t="str">
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+      </c>
+      <c r="K201" t="str">
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+      </c>
+      <c r="L201" t="str">
+        <v>So Good - Ari Abdul</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>YDH</v>
+      </c>
+      <c r="B202" t="str">
+        <v/>
+      </c>
+      <c r="C202" t="str">
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+      </c>
+      <c r="D202" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E202" t="str">
+        <v/>
+      </c>
+      <c r="F202" t="str">
+        <v>YDH - Single</v>
+      </c>
+      <c r="G202" t="str">
+        <v>3:17</v>
+      </c>
+      <c r="H202" t="str">
+        <v>Chloe Qisha</v>
+      </c>
+      <c r="I202" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J202" t="str">
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+      </c>
+      <c r="K202" t="str">
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+      </c>
+      <c r="L202" t="str">
+        <v>YDH - Chloe Qisha</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>Eucalyptus</v>
+      </c>
+      <c r="B203" t="str">
+        <v/>
+      </c>
+      <c r="C203" t="str">
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+      </c>
+      <c r="D203" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E203" t="str">
+        <v/>
+      </c>
+      <c r="F203" t="str">
+        <v>Porcelain</v>
+      </c>
+      <c r="G203" t="str">
+        <v>3:00</v>
+      </c>
+      <c r="H203" t="str">
+        <v>Peach PRC</v>
+      </c>
+      <c r="I203" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J203" t="str">
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+      </c>
+      <c r="K203" t="str">
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+      </c>
+      <c r="L203" t="str">
+        <v>Eucalyptus - Peach PRC</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>Pearls In The Trap</v>
+      </c>
+      <c r="B204" t="str">
+        <v/>
+      </c>
+      <c r="C204" t="str">
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+      </c>
+      <c r="D204" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E204" t="str">
+        <v/>
+      </c>
+      <c r="F204" t="str">
+        <v>Pearls In The Trap - Single</v>
+      </c>
+      <c r="G204" t="str">
+        <v>1:38</v>
+      </c>
+      <c r="H204" t="str">
+        <v>carolesdaughter</v>
+      </c>
+      <c r="I204" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J204" t="str">
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+      </c>
+      <c r="K204" t="str">
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+      </c>
+      <c r="L204" t="str">
+        <v>Pearls In The Trap - carolesdaughter</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>The Fever Mask</v>
+      </c>
+      <c r="B205" t="str">
+        <v/>
+      </c>
+      <c r="C205" t="str">
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+      </c>
+      <c r="D205" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E205" t="str">
+        <v/>
+      </c>
+      <c r="F205" t="str">
+        <v>The Ghost of a Future Dead</v>
+      </c>
+      <c r="G205" t="str">
+        <v>3:12</v>
+      </c>
+      <c r="H205" t="str">
+        <v>At The Gates</v>
+      </c>
+      <c r="I205" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J205" t="str">
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+      </c>
+      <c r="K205" t="str">
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+      </c>
+      <c r="L205" t="str">
+        <v>The Fever Mask - At The Gates</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>The Air's on Fire</v>
+      </c>
+      <c r="B206" t="str">
+        <v/>
+      </c>
+      <c r="C206" t="str">
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+      </c>
+      <c r="D206" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E206" t="str">
+        <v/>
+      </c>
+      <c r="F206" t="str">
+        <v>Location Lost</v>
+      </c>
+      <c r="G206" t="str">
+        <v>5:15</v>
+      </c>
+      <c r="H206" t="str">
+        <v>Failure</v>
+      </c>
+      <c r="I206" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J206" t="str">
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
+      </c>
+      <c r="K206" t="str">
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+      </c>
+      <c r="L206" t="str">
+        <v>The Air's on Fire - Failure</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
         <v>To The Last Breath</v>
       </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
-      <c r="D197" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
+      <c r="D207" t="str">
+        <v>2026-02-22</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
         <v>To The Last Breath - Single</v>
       </c>
-      <c r="G197" t="str">
+      <c r="G207" t="str">
         <v>4:57</v>
       </c>
-      <c r="H197" t="str">
+      <c r="H207" t="str">
         <v>Arch Enemy</v>
       </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
         <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
-      <c r="K197" t="str">
+      <c r="K207" t="str">
         <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
-      <c r="L197" t="str">
+      <c r="L207" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L207"/>
+  <dimension ref="A1:L208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,16 +436,16 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ששון שאולוב - מלי מלי</v>
+        <v>קרן קריספיל - עד שמצאתי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409712&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409722&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E2" t="str">
         <v/>
@@ -469,21 +469,21 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ששון שאולוב - מלי מלי</v>
+        <v>קרן קריספיל - עד שמצאתי</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שי וינר - תן לי</v>
+        <v>סער הדר - טוב לך איתו</v>
       </c>
       <c r="B3" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409711&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409721&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D3" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E3" t="str">
         <v/>
@@ -507,21 +507,21 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שי וינר - תן לי</v>
+        <v>סער הדר - טוב לך איתו</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>עדן גולן - מספיק ממך</v>
+        <v>ים רפאלי - ערפדים</v>
       </c>
       <c r="B4" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409710&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409720&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D4" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E4" t="str">
         <v/>
@@ -545,21 +545,21 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>עדן גולן - מספיק ממך</v>
+        <v>ים רפאלי - ערפדים</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>סטטיק - מנדם</v>
+        <v>טל קייסי - בלב הסערה</v>
       </c>
       <c r="B5" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409709&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409719&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D5" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E5" t="str">
         <v/>
@@ -583,21 +583,21 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>סטטיק - מנדם</v>
+        <v>טל קייסי - בלב הסערה</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+        <v>אלי בי - רק תני לי סימן</v>
       </c>
       <c r="B6" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409708&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409718&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D6" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E6" t="str">
         <v/>
@@ -621,21 +621,21 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>נעומי טוב אלמליח - מעבר לדמיון</v>
+        <v>אלי בי - רק תני לי סימן</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>יגל יובל שרעבי - מחושך לאור</v>
+        <v>איתי אהרון - אהבה כאב וטעויות</v>
       </c>
       <c r="B7" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409707&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409717&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D7" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E7" t="str">
         <v/>
@@ -659,21 +659,21 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>יגל יובל שרעבי - מחושך לאור</v>
+        <v>איתי אהרון - אהבה כאב וטעויות</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ויולט - לנוע</v>
+        <v>אייל לוי - מדויק</v>
       </c>
       <c r="B8" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409706&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409716&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D8" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E8" t="str">
         <v/>
@@ -697,21 +697,21 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ויולט - לנוע</v>
+        <v>אייל לוי - מדויק</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+        <v>אחי נתן - לא בחור דתי</v>
       </c>
       <c r="B9" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409705&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409715&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D9" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E9" t="str">
         <v/>
@@ -735,21 +735,21 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>דניאלה גלבוע - איפה שהכל נגמר</v>
+        <v>אחי נתן - לא בחור דתי</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אלמוג זגרון - ג׳ורדן</v>
+        <v>אורן כדורי - למה ככה</v>
       </c>
       <c r="B10" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409704&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409714&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D10" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E10" t="str">
         <v/>
@@ -773,21 +773,21 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אלמוג זגרון - ג׳ורדן</v>
+        <v>אורן כדורי - למה ככה</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אדיר בובליל - בא לי שוב</v>
+        <v>אייל שלום - אתה חי</v>
       </c>
       <c r="B11" t="str">
         <v>2026-02-22</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409703&amp;sid=ddc78b2a390307e75226d54122c7f015</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409713&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
       </c>
       <c r="D11" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E11" t="str">
         <v/>
@@ -811,36 +811,36 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אדיר בובליל - בא לי שוב</v>
+        <v>אייל שלום - אתה חי</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Garden City Movement – I Can Be Your Salvation</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://yosmusic.com/garden-city-movement/</v>
       </c>
       <c r="D12" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E12" t="str">
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>בלב המוזיקה האוורירית-אלקטרונית של הצמד יוני שרוני  ורועי אביטל המהווים  את Garden City Movement מסתתר טקסט לא רגוע בכלל. זוהי מוסיקה ריחופית שמדברת על שליטה, בלבול ותלות רגשית בעידן של עודף גירויים. השורה הראשונה מציבה את הדילמה: “?Could you choose</v>
       </c>
       <c r="G12" t="str">
-        <v>3:20</v>
+        <v/>
       </c>
       <c r="H12" t="str">
-        <v>georgemichael</v>
+        <v/>
       </c>
       <c r="I12" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,33 +849,33 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Garden City Movement – I Can Be Your Salvation</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D13" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E13" t="str">
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>19 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:50</v>
+        <v>3:57</v>
       </c>
       <c r="H13" t="str">
-        <v>Cliff Richard</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,33 +887,33 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D14" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E14" t="str">
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:14</v>
+        <v>2:27</v>
       </c>
       <c r="H14" t="str">
-        <v>Freya Ridings</v>
+        <v>070 Shake</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,33 +925,33 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D15" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E15" t="str">
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:37</v>
+        <v>4:49</v>
       </c>
       <c r="H15" t="str">
-        <v>Jessie Ware</v>
+        <v>georgemichael</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,33 +963,33 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D16" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E16" t="str">
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:16</v>
+        <v>5:52</v>
       </c>
       <c r="H16" t="str">
-        <v>Alan Walker</v>
+        <v>georgemichael</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,21 +1001,21 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D17" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E17" t="str">
         <v/>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:22</v>
+        <v>3:22</v>
       </c>
       <c r="H17" t="str">
-        <v>The Neighbourhood</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,21 +1039,21 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B18" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D18" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E18" t="str">
         <v/>
@@ -1062,10 +1062,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:45</v>
+        <v>4:08</v>
       </c>
       <c r="H18" t="str">
-        <v>YUNGBLUD</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,33 +1077,33 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Suburban Requiem</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D19" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E19" t="str">
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:40</v>
+        <v>7:31</v>
       </c>
       <c r="H19" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,21 +1115,21 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B20" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D20" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E20" t="str">
         <v/>
@@ -1138,10 +1138,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:02</v>
+        <v>3:21</v>
       </c>
       <c r="H20" t="str">
-        <v>Calum Scott</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,21 +1153,21 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D21" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E21" t="str">
         <v/>
@@ -1176,10 +1176,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:12</v>
+        <v>4:36</v>
       </c>
       <c r="H21" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,21 +1191,21 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B22" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D22" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E22" t="str">
         <v/>
@@ -1214,10 +1214,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:38</v>
+        <v>5:06</v>
       </c>
       <c r="H22" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,21 +1229,21 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B23" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D23" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E23" t="str">
         <v/>
@@ -1252,10 +1252,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:40</v>
+        <v>4:17</v>
       </c>
       <c r="H23" t="str">
-        <v>Cannons</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,21 +1267,21 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B24" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D24" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E24" t="str">
         <v/>
@@ -1290,10 +1290,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>2:57</v>
+        <v>3:20</v>
       </c>
       <c r="H24" t="str">
-        <v>Mimi Webb</v>
+        <v>georgemichael</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,21 +1305,21 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B25" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D25" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E25" t="str">
         <v/>
@@ -1328,10 +1328,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:13</v>
+        <v>4:50</v>
       </c>
       <c r="H25" t="str">
-        <v>Jorja Smith</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,21 +1343,21 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B26" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D26" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E26" t="str">
         <v/>
@@ -1366,10 +1366,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:12</v>
+        <v>3:14</v>
       </c>
       <c r="H26" t="str">
-        <v>Sam Williams</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,21 +1381,21 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B27" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D27" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E27" t="str">
         <v/>
@@ -1404,10 +1404,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:55</v>
+        <v>4:37</v>
       </c>
       <c r="H27" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,21 +1419,21 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B28" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D28" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E28" t="str">
         <v/>
@@ -1442,10 +1442,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:51</v>
+        <v>3:16</v>
       </c>
       <c r="H28" t="str">
-        <v>Megan Moroney</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,33 +1457,33 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D29" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E29" t="str">
         <v/>
       </c>
       <c r="F29" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:51</v>
+        <v>4:22</v>
       </c>
       <c r="H29" t="str">
-        <v>Nico Santos</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,33 +1495,33 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D30" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E30" t="str">
         <v/>
       </c>
       <c r="F30" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:24</v>
+        <v>3:45</v>
       </c>
       <c r="H30" t="str">
-        <v>REALITY CLUB</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,33 +1533,33 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D31" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E31" t="str">
         <v/>
       </c>
       <c r="F31" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:11</v>
+        <v>4:40</v>
       </c>
       <c r="H31" t="str">
-        <v>We Three</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,21 +1571,21 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D32" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E32" t="str">
         <v/>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:27</v>
+        <v>3:02</v>
       </c>
       <c r="H32" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,21 +1609,21 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D33" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E33" t="str">
         <v/>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:06</v>
+        <v>3:12</v>
       </c>
       <c r="H33" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,21 +1647,21 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D34" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E34" t="str">
         <v/>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:01</v>
+        <v>3:38</v>
       </c>
       <c r="H34" t="str">
-        <v>Peach PRC</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,21 +1685,21 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D35" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E35" t="str">
         <v/>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>5:38</v>
+        <v>4:40</v>
       </c>
       <c r="H35" t="str">
-        <v>georgemichael</v>
+        <v>Cannons</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,33 +1723,33 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D36" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E36" t="str">
         <v/>
       </c>
       <c r="F36" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:43</v>
+        <v>2:57</v>
       </c>
       <c r="H36" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,21 +1761,21 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D37" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E37" t="str">
         <v/>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:58</v>
+        <v>2:13</v>
       </c>
       <c r="H37" t="str">
-        <v>Catie Turner</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,33 +1799,33 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B38" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D38" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E38" t="str">
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:13</v>
+        <v>4:12</v>
       </c>
       <c r="H38" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,33 +1837,33 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B39" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D39" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E39" t="str">
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>5:48</v>
+        <v>2:55</v>
       </c>
       <c r="H39" t="str">
-        <v>U2</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,33 +1875,33 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D40" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E40" t="str">
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:55</v>
+        <v>3:51</v>
       </c>
       <c r="H40" t="str">
-        <v>Lawrence</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,33 +1913,33 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B41" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D41" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E41" t="str">
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:24</v>
+        <v>2:51</v>
       </c>
       <c r="H41" t="str">
-        <v>BUNT. Music</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,33 +1951,33 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B42" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D42" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E42" t="str">
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>4:59</v>
+        <v>3:24</v>
       </c>
       <c r="H42" t="str">
-        <v>Bruno Mars</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,33 +1989,33 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B43" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D43" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E43" t="str">
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>2:10</v>
+        <v>4:11</v>
       </c>
       <c r="H43" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>We Three</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,33 +2027,33 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D44" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E44" t="str">
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:11</v>
+        <v>3:27</v>
       </c>
       <c r="H44" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,33 +2065,33 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D45" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E45" t="str">
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:26</v>
+        <v>3:06</v>
       </c>
       <c r="H45" t="str">
-        <v>Neal Francis</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,33 +2103,33 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D46" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E46" t="str">
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:35</v>
+        <v>3:01</v>
       </c>
       <c r="H46" t="str">
-        <v>mgk</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,33 +2141,33 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B47" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D47" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E47" t="str">
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>5 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>2:09</v>
+        <v>5:38</v>
       </c>
       <c r="H47" t="str">
-        <v>Lola Young</v>
+        <v>georgemichael</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,33 +2179,33 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B48" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D48" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E48" t="str">
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:11</v>
+        <v>3:43</v>
       </c>
       <c r="H48" t="str">
-        <v>Holly Humberstone</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,33 +2217,33 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D49" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E49" t="str">
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:01</v>
+        <v>2:58</v>
       </c>
       <c r="H49" t="str">
-        <v>The Vaccines</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,33 +2255,33 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D50" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E50" t="str">
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:28</v>
+        <v>4:13</v>
       </c>
       <c r="H50" t="str">
-        <v>mgk</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,33 +2293,33 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D51" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E51" t="str">
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:31</v>
+        <v>5:48</v>
       </c>
       <c r="H51" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>U2</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,33 +2331,33 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D52" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E52" t="str">
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:49</v>
+        <v>3:55</v>
       </c>
       <c r="H52" t="str">
-        <v>Mýa</v>
+        <v>Lawrence</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,33 +2369,33 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D53" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E53" t="str">
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:03</v>
+        <v>5:24</v>
       </c>
       <c r="H53" t="str">
-        <v>Michael Bolton</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,33 +2407,33 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B54" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D54" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E54" t="str">
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>7 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:59</v>
+        <v>4:59</v>
       </c>
       <c r="H54" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,33 +2445,33 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D55" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E55" t="str">
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:41</v>
+        <v>2:10</v>
       </c>
       <c r="H55" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,33 +2483,33 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B56" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D56" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E56" t="str">
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>3:11</v>
       </c>
       <c r="H56" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,33 +2521,33 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B57" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D57" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E57" t="str">
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>3:59</v>
+        <v>4:26</v>
       </c>
       <c r="H57" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,33 +2559,33 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B58" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D58" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E58" t="str">
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>7:48</v>
+        <v>4:35</v>
       </c>
       <c r="H58" t="str">
-        <v>The Doobie Brothers</v>
+        <v>mgk</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,33 +2597,33 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B59" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D59" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E59" t="str">
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>8 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:10</v>
+        <v>2:09</v>
       </c>
       <c r="H59" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Lola Young</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,33 +2635,33 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D60" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E60" t="str">
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>5:57</v>
+        <v>4:11</v>
       </c>
       <c r="H60" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,33 +2673,33 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D61" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E61" t="str">
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:25</v>
+        <v>3:01</v>
       </c>
       <c r="H61" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,33 +2711,33 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B62" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D62" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E62" t="str">
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:19</v>
+        <v>3:28</v>
       </c>
       <c r="H62" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,21 +2749,21 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B63" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D63" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E63" t="str">
         <v/>
@@ -2772,10 +2772,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:38</v>
+        <v>5:31</v>
       </c>
       <c r="H63" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,21 +2787,21 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B64" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D64" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E64" t="str">
         <v/>
@@ -2810,10 +2810,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>4:05</v>
+        <v>2:49</v>
       </c>
       <c r="H64" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mýa</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,21 +2825,21 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D65" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E65" t="str">
         <v/>
@@ -2848,10 +2848,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:46</v>
+        <v>3:03</v>
       </c>
       <c r="H65" t="str">
-        <v>Jacob Collier</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,21 +2863,21 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B66" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D66" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E66" t="str">
         <v/>
@@ -2886,10 +2886,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:25</v>
+        <v>2:59</v>
       </c>
       <c r="H66" t="str">
-        <v>Victor Ray</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,33 +2901,33 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D67" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E67" t="str">
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:11</v>
+        <v>2:41</v>
       </c>
       <c r="H67" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,33 +2939,33 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B68" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D68" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E68" t="str">
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:55</v>
+        <v>2:59</v>
       </c>
       <c r="H68" t="str">
-        <v>The Warning</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,33 +2977,33 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B69" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D69" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E69" t="str">
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:54</v>
+        <v>3:59</v>
       </c>
       <c r="H69" t="str">
-        <v>The Offspring</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,21 +3015,21 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D70" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E70" t="str">
         <v/>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:01</v>
+        <v>7:48</v>
       </c>
       <c r="H70" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,21 +3053,21 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D71" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E71" t="str">
         <v/>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:55</v>
+        <v>3:10</v>
       </c>
       <c r="H71" t="str">
-        <v>HAUSER</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,33 +3091,33 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D72" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E72" t="str">
         <v/>
       </c>
       <c r="F72" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:43</v>
+        <v>5:57</v>
       </c>
       <c r="H72" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,33 +3129,33 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B73" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D73" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E73" t="str">
         <v/>
       </c>
       <c r="F73" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:53</v>
+        <v>2:25</v>
       </c>
       <c r="H73" t="str">
-        <v>Ultra Records</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,33 +3167,33 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D74" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E74" t="str">
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:30</v>
+        <v>3:19</v>
       </c>
       <c r="H74" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,21 +3205,21 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D75" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E75" t="str">
         <v/>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:37</v>
+        <v>3:38</v>
       </c>
       <c r="H75" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,21 +3243,21 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D76" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E76" t="str">
         <v/>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:10</v>
+        <v>4:05</v>
       </c>
       <c r="H76" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,21 +3281,21 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D77" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E77" t="str">
         <v/>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:06</v>
+        <v>5:46</v>
       </c>
       <c r="H77" t="str">
-        <v>Alan Walker</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,21 +3319,21 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D78" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E78" t="str">
         <v/>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:17</v>
+        <v>3:25</v>
       </c>
       <c r="H78" t="str">
-        <v>Bruno Mars</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,21 +3357,21 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B79" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D79" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E79" t="str">
         <v/>
@@ -3380,10 +3380,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:21</v>
+        <v>5:11</v>
       </c>
       <c r="H79" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,21 +3395,21 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B80" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D80" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E80" t="str">
         <v/>
@@ -3418,10 +3418,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>6:58</v>
+        <v>2:55</v>
       </c>
       <c r="H80" t="str">
-        <v>Eric Church</v>
+        <v>The Warning</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,21 +3433,21 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B81" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D81" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E81" t="str">
         <v/>
@@ -3456,10 +3456,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:29</v>
+        <v>4:54</v>
       </c>
       <c r="H81" t="str">
-        <v>Meghan Trainor</v>
+        <v>The Offspring</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,21 +3471,21 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D82" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E82" t="str">
         <v/>
@@ -3494,10 +3494,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:14</v>
+        <v>5:01</v>
       </c>
       <c r="H82" t="str">
-        <v>Ally Salort</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,21 +3509,21 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B83" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D83" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E83" t="str">
         <v/>
@@ -3532,10 +3532,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:51</v>
+        <v>3:55</v>
       </c>
       <c r="H83" t="str">
-        <v>Will Swinton</v>
+        <v>HAUSER</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,21 +3547,21 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B84" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D84" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E84" t="str">
         <v/>
@@ -3570,10 +3570,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:10</v>
+        <v>3:43</v>
       </c>
       <c r="H84" t="str">
-        <v>elijah woods</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,33 +3585,33 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B85" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D85" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E85" t="str">
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:26</v>
+        <v>2:53</v>
       </c>
       <c r="H85" t="str">
-        <v>Jackson Dean</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,21 +3623,21 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B86" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D86" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E86" t="str">
         <v/>
@@ -3646,10 +3646,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>2:51</v>
+        <v>3:30</v>
       </c>
       <c r="H86" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,21 +3661,21 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B87" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D87" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E87" t="str">
         <v/>
@@ -3684,10 +3684,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>3:37</v>
       </c>
       <c r="H87" t="str">
-        <v>Neil Sedaka</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,21 +3699,21 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B88" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D88" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E88" t="str">
         <v/>
@@ -3722,10 +3722,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H88" t="str">
-        <v>Sofia Camara</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,21 +3737,21 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D89" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E89" t="str">
         <v/>
@@ -3760,10 +3760,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H89" t="str">
-        <v>Russell Dickerson</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,33 +3775,33 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D90" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E90" t="str">
         <v/>
       </c>
       <c r="F90" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:03</v>
+        <v>3:17</v>
       </c>
       <c r="H90" t="str">
-        <v>Celine Dion</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,33 +3813,33 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D91" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E91" t="str">
         <v/>
       </c>
       <c r="F91" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:38</v>
+        <v>3:21</v>
       </c>
       <c r="H91" t="str">
-        <v>Bebe Rexha</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,33 +3851,33 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D92" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E92" t="str">
         <v/>
       </c>
       <c r="F92" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H92" t="str">
-        <v>Caroline Jones</v>
+        <v>Eric Church</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,33 +3889,33 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D93" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E93" t="str">
         <v/>
       </c>
       <c r="F93" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H93" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,33 +3927,33 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D94" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E94" t="str">
         <v/>
       </c>
       <c r="F94" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:32</v>
+        <v>3:14</v>
       </c>
       <c r="H94" t="str">
-        <v>Ingrid Andress</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,33 +3965,33 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D95" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E95" t="str">
         <v/>
       </c>
       <c r="F95" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H95" t="str">
-        <v>MusicByKnox</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,33 +4003,33 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D96" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E96" t="str">
         <v/>
       </c>
       <c r="F96" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:38</v>
+        <v>3:10</v>
       </c>
       <c r="H96" t="str">
-        <v>Ella Langley</v>
+        <v>elijah woods</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,33 +4041,33 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B97" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D97" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E97" t="str">
         <v/>
       </c>
       <c r="F97" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
         <v>3:26</v>
       </c>
       <c r="H97" t="str">
-        <v>Nickless</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,33 +4079,33 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D98" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E98" t="str">
         <v/>
       </c>
       <c r="F98" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:57</v>
+        <v>2:51</v>
       </c>
       <c r="H98" t="str">
-        <v>Caroline Jones</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,33 +4117,33 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D99" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E99" t="str">
         <v/>
       </c>
       <c r="F99" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:08</v>
+        <v>3:26</v>
       </c>
       <c r="H99" t="str">
-        <v>elijah woods</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,33 +4155,33 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D100" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E100" t="str">
         <v/>
       </c>
       <c r="F100" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:53</v>
+        <v>3:06</v>
       </c>
       <c r="H100" t="str">
-        <v>August Ponthier</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,33 +4193,33 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=B2DUdBwkwlY</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D101" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E101" t="str">
         <v/>
       </c>
       <c r="F101" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:10</v>
+        <v>3:04</v>
       </c>
       <c r="H101" t="str">
-        <v>Charli xcx</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,33 +4231,33 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Charli xcx - Always Everywhere (Official Lyric Video) - Charli xcx</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Caroline Jones - Family (Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B102" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=9pS6Ni9cUnU</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D102" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E102" t="str">
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H102" t="str">
-        <v>Caroline Jones</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4269,33 +4269,33 @@
         <v/>
       </c>
       <c r="L102" t="str">
-        <v>Caroline Jones - Family (Lyric Video) - Caroline Jones</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B103" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=O97vOxlLtr4</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D103" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E103" t="str">
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G103" t="str">
-        <v>2:44</v>
+        <v>2:38</v>
       </c>
       <c r="H103" t="str">
-        <v>Leah Kate</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4307,33 +4307,33 @@
         <v/>
       </c>
       <c r="L103" t="str">
-        <v>Leah Kate – World's Best Ex-Girlfriend (Official Visualizer) - Leah Kate</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B104" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=a9td-QhCGSk</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D104" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E104" t="str">
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G104" t="str">
-        <v>3:25</v>
+        <v>3:29</v>
       </c>
       <c r="H104" t="str">
-        <v>Troye Sivan</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4345,33 +4345,33 @@
         <v/>
       </c>
       <c r="L104" t="str">
-        <v>Troye Sivan - SWIMMING POOLS (Official Audio) - Troye Sivan</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B105" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=7KrNh9YaeDg</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D105" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E105" t="str">
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G105" t="str">
-        <v>4:08</v>
+        <v>2:32</v>
       </c>
       <c r="H105" t="str">
-        <v>Romeo Santos and Prince Royce</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4383,33 +4383,33 @@
         <v/>
       </c>
       <c r="L105" t="str">
-        <v>Romeo Santos, Prince Royce - Dardos (Official Video) - Romeo Santos and Prince Royce</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B106" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=wrBy72CiCF8</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D106" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E106" t="str">
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G106" t="str">
-        <v>3:09</v>
+        <v>3:32</v>
       </c>
       <c r="H106" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4421,33 +4421,33 @@
         <v/>
       </c>
       <c r="L106" t="str">
-        <v>Darren Criss &amp; Helen J. Shen Perform “Maybe Happy Ending” LIVE at the 2026 GRAMMYs Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B107" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=EjI0ilIyzPk</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D107" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E107" t="str">
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G107" t="str">
-        <v>3:11</v>
+        <v>2:51</v>
       </c>
       <c r="H107" t="str">
-        <v>The Happy Fits</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4459,33 +4459,33 @@
         <v/>
       </c>
       <c r="L107" t="str">
-        <v>The Happy Fits - I Could Stare at You for Hours (Official Music Video) - The Happy Fits</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B108" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=zkQI78ankMU</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D108" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E108" t="str">
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G108" t="str">
-        <v>3:02</v>
+        <v>3:38</v>
       </c>
       <c r="H108" t="str">
-        <v>HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4497,33 +4497,33 @@
         <v/>
       </c>
       <c r="L108" t="str">
-        <v>SANTOS BRAVOS "KAWASAKI" Official MV - HYBE LABELS and SANTOS BRAVOS</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B109" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=ShFhryNLNI0</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D109" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E109" t="str">
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G109" t="str">
-        <v>4:20</v>
+        <v>3:26</v>
       </c>
       <c r="H109" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Nickless</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4535,33 +4535,33 @@
         <v/>
       </c>
       <c r="L109" t="str">
-        <v>Reba McEntire, Brandy Clark &amp; Lukas Nelson Honor Music Legends | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B110" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=WNC82J_-B2k</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D110" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E110" t="str">
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G110" t="str">
-        <v>4:09</v>
+        <v>3:57</v>
       </c>
       <c r="H110" t="str">
-        <v>Quinn XCII</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4573,33 +4573,33 @@
         <v/>
       </c>
       <c r="L110" t="str">
-        <v>Quinn XCII - Another Day In Paradise (Live From Red Rocks) - Quinn XCII</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>We Three - Drunk Driving (Live Sessions)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B111" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=dESx7wyG52Y</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D111" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E111" t="str">
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G111" t="str">
-        <v>4:34</v>
+        <v>3:08</v>
       </c>
       <c r="H111" t="str">
-        <v>We Three</v>
+        <v>elijah woods</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4611,3660 +4611,3698 @@
         <v/>
       </c>
       <c r="L111" t="str">
-        <v>We Three - Drunk Driving (Live Sessions) - We Three</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Badlands</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B112" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D112" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E112" t="str">
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Prizefighter</v>
+        <v>10 days ago</v>
       </c>
       <c r="G112" t="str">
-        <v>2:58</v>
+        <v>3:53</v>
       </c>
       <c r="H112" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v/>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v/>
       </c>
       <c r="L112" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>Badlands</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D113" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E113" t="str">
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G113" t="str">
-        <v>3:48</v>
+        <v>2:58</v>
       </c>
       <c r="H113" t="str">
-        <v>Taylor Swift</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L113" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D114" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E114" t="str">
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:54</v>
+        <v>3:48</v>
       </c>
       <c r="H114" t="str">
-        <v>Lana Del Rey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L114" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>ROSITA</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D115" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E115" t="str">
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>ROSITA - Single</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>4:05</v>
+        <v>3:54</v>
       </c>
       <c r="H115" t="str">
-        <v>Tainy</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L115" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>ROSITA</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D116" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E116" t="str">
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Ca$ino</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H116" t="str">
-        <v>Baby Keem</v>
+        <v>Tainy</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L116" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D117" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E117" t="str">
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G117" t="str">
-        <v>2:52</v>
+        <v>3:52</v>
       </c>
       <c r="H117" t="str">
-        <v>SZA</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L117" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Medicine</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D118" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E118" t="str">
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Cloud 9</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>3:11</v>
+        <v>2:52</v>
       </c>
       <c r="H118" t="str">
-        <v>Megan Moroney</v>
+        <v>SZA</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L118" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Weather For Tennis</v>
+        <v>Medicine</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D119" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E119" t="str">
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>luck... or something</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G119" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H119" t="str">
-        <v>Hilary Duff</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L119" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>ear to the cocoon</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D120" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E120" t="str">
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>petal rock black</v>
+        <v>luck... or something</v>
       </c>
       <c r="G120" t="str">
-        <v>4:18</v>
+        <v>3:16</v>
       </c>
       <c r="H120" t="str">
-        <v>WILLOW</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L120" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Drag Path</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D121" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E121" t="str">
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Drag Path - Single</v>
+        <v>petal rock black</v>
       </c>
       <c r="G121" t="str">
-        <v>3:44</v>
+        <v>4:18</v>
       </c>
       <c r="H121" t="str">
-        <v>twenty one pilots</v>
+        <v>WILLOW</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L121" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Song Of The Future</v>
+        <v>Drag Path</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D122" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E122" t="str">
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:55</v>
+        <v>3:44</v>
       </c>
       <c r="H122" t="str">
-        <v>U2</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L122" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D123" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E123" t="str">
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G123" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H123" t="str">
-        <v>Foo Fighters</v>
+        <v>U2</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L123" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Trimski</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D124" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E124" t="str">
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Trimski - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G124" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H124" t="str">
-        <v>NAV</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L124" t="str">
-        <v>Trimski - NAV</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D125" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E125" t="str">
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H125" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L125" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D126" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E126" t="str">
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G126" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H126" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L126" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D127" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E127" t="str">
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G127" t="str">
-        <v>4:18</v>
+        <v>3:14</v>
       </c>
       <c r="H127" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L127" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Begging for Change</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D128" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E128" t="str">
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>HELP(2)</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G128" t="str">
-        <v>4:20</v>
+        <v>4:18</v>
       </c>
       <c r="H128" t="str">
-        <v>Pulp</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L128" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>My Maker</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D129" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E129" t="str">
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Ricochet</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G129" t="str">
-        <v>4:19</v>
+        <v>4:20</v>
       </c>
       <c r="H129" t="str">
-        <v>Snail Mail</v>
+        <v>Pulp</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L129" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>My Maker</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D130" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E130" t="str">
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G130" t="str">
-        <v>3:32</v>
+        <v>4:19</v>
       </c>
       <c r="H130" t="str">
-        <v>Taylor Swift</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L130" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D131" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E131" t="str">
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>4:27</v>
+        <v>3:32</v>
       </c>
       <c r="H131" t="str">
-        <v>CHVRCHES</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L131" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>She Knows Too Much</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D132" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E132" t="str">
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Distracted</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>3:33</v>
+        <v>4:27</v>
       </c>
       <c r="H132" t="str">
-        <v>Thundercat</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L132" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Tea Time</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D133" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E133" t="str">
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Tea Time - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G133" t="str">
-        <v>2:25</v>
+        <v>3:33</v>
       </c>
       <c r="H133" t="str">
-        <v>Yung Miami</v>
+        <v>Thundercat</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L133" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Tea Time</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D134" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E134" t="str">
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H134" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L134" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Save My Love</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D135" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E135" t="str">
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Save My Love - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G135" t="str">
-        <v>3:30</v>
+        <v>3:12</v>
       </c>
       <c r="H135" t="str">
-        <v>Kygo</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L135" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Save My Love</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D136" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E136" t="str">
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H136" t="str">
-        <v>Omar Courtz</v>
+        <v>Kygo</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L136" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Suburban Requiem</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D137" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E137" t="str">
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Idols (Complete)</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G137" t="str">
-        <v>4:39</v>
+        <v>3:46</v>
       </c>
       <c r="H137" t="str">
-        <v>YUNGBLUD</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L137" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Good Grief</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D138" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E138" t="str">
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G138" t="str">
-        <v>4:21</v>
+        <v>4:39</v>
       </c>
       <c r="H138" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L138" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Freak On</v>
+        <v>Good Grief</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D139" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E139" t="str">
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>Freak On - Single</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G139" t="str">
-        <v>2:49</v>
+        <v>4:21</v>
       </c>
       <c r="H139" t="str">
-        <v>Steve Aoki</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L139" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Freak On</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D140" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E140" t="str">
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G140" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H140" t="str">
-        <v>deadmau5</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L140" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D141" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E141" t="str">
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H141" t="str">
-        <v>Taylor Swift</v>
+        <v>deadmau5</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L141" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Yellow Eyes</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D142" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E142" t="str">
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Jean</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:42</v>
+        <v>3:55</v>
       </c>
       <c r="H142" t="str">
-        <v>Yebba</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L142" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Word On The Street</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D143" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E143" t="str">
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G143" t="str">
-        <v>2:56</v>
+        <v>2:42</v>
       </c>
       <c r="H143" t="str">
-        <v>Luke Bryan</v>
+        <v>Yebba</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L143" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>only the best</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D144" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E144" t="str">
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>only the best - Single</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H144" t="str">
-        <v>horsegiirL</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L144" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Beautiful Places</v>
+        <v>only the best</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D145" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E145" t="str">
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H145" t="str">
-        <v>Tiësto</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L145" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>STAMPEDE</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D146" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E146" t="str">
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>3:09</v>
+        <v>2:59</v>
       </c>
       <c r="H146" t="str">
-        <v>Genesis Owusu</v>
+        <v>Tiësto</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L146" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Infinite Beach</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D147" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E147" t="str">
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Mārara</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H147" t="str">
-        <v>15 15</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L147" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Championship Ring</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D148" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E148" t="str">
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>I Want Blood</v>
+        <v>Mārara</v>
       </c>
       <c r="G148" t="str">
-        <v>3:41</v>
+        <v>3:10</v>
       </c>
       <c r="H148" t="str">
-        <v>SleazyWorld Go</v>
+        <v>15 15</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L148" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D149" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E149" t="str">
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G149" t="str">
-        <v>2:28</v>
+        <v>3:41</v>
       </c>
       <c r="H149" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L149" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D150" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E150" t="str">
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>Da Realest</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G150" t="str">
-        <v>1:51</v>
+        <v>2:28</v>
       </c>
       <c r="H150" t="str">
-        <v>Babyfxce E</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L150" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>Fine Shit</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D151" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E151" t="str">
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G151" t="str">
-        <v>1:53</v>
+        <v>1:51</v>
       </c>
       <c r="H151" t="str">
-        <v>Real Boston Richey</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L151" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>What's Your Name</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D152" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E152" t="str">
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>2:20</v>
+        <v>1:53</v>
       </c>
       <c r="H152" t="str">
-        <v>Soulidified</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L152" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Ends In Y</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D153" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E153" t="str">
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:53</v>
+        <v>2:20</v>
       </c>
       <c r="H153" t="str">
-        <v>Mimi Webb</v>
+        <v>Soulidified</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L153" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Bully</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D154" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E154" t="str">
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Bully - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G154" t="str">
-        <v>3:05</v>
+        <v>2:53</v>
       </c>
       <c r="H154" t="str">
-        <v>Iris Copperman</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L154" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Bully</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D155" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E155" t="str">
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:16</v>
+        <v>3:05</v>
       </c>
       <c r="H155" t="str">
-        <v>Charles Leclerc</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L155" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Ride</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D156" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E156" t="str">
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Superbloom</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>4:39</v>
+        <v>3:16</v>
       </c>
       <c r="H156" t="str">
-        <v>Jessie Ware</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L156" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Arkansas Mud</v>
+        <v>Ride</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D157" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E157" t="str">
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G157" t="str">
-        <v>4:18</v>
+        <v>4:39</v>
       </c>
       <c r="H157" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L157" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Don't Leave</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D158" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E158" t="str">
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Don't Leave - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G158" t="str">
-        <v>2:10</v>
+        <v>4:18</v>
       </c>
       <c r="H158" t="str">
-        <v>Jorja Smith</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L158" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>FLAMED UP</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D159" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E159" t="str">
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G159" t="str">
-        <v>2:31</v>
+        <v>2:10</v>
       </c>
       <c r="H159" t="str">
-        <v>JayDon</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L159" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>3am in Paris</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D160" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E160" t="str">
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>3am in Paris - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:49</v>
+        <v>2:31</v>
       </c>
       <c r="H160" t="str">
-        <v>Anais Cardot</v>
+        <v>JayDon</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L160" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D161" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E161" t="str">
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>5:13</v>
+        <v>2:49</v>
       </c>
       <c r="H161" t="str">
-        <v>Elevation Worship</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L161" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Migajero</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D162" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E162" t="str">
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Migajero - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G162" t="str">
-        <v>3:18</v>
+        <v>5:13</v>
       </c>
       <c r="H162" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L162" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Migajero</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D163" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E163" t="str">
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G163" t="str">
-        <v>3:26</v>
+        <v>3:18</v>
       </c>
       <c r="H163" t="str">
-        <v>Taylor Swift</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L163" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Old Man</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D164" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E164" t="str">
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Old Man - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H164" t="str">
-        <v>Trousdale</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L164" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Old Man</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D165" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E165" t="str">
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:19</v>
+        <v>4:05</v>
       </c>
       <c r="H165" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Trousdale</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L165" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D166" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E166" t="str">
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G166" t="str">
-        <v>2:56</v>
+        <v>3:19</v>
       </c>
       <c r="H166" t="str">
-        <v>Denzel Curry</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L166" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Refuge</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D167" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E167" t="str">
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G167" t="str">
-        <v>3:38</v>
+        <v>2:56</v>
       </c>
       <c r="H167" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L167" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Refuge</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D168" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E168" t="str">
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>My Ego Told Me To</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G168" t="str">
-        <v>3:24</v>
+        <v>3:38</v>
       </c>
       <c r="H168" t="str">
-        <v>Leigh-Anne</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L168" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Smoke Screen</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D169" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E169" t="str">
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Still There’s a Glow</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G169" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H169" t="str">
-        <v>Sweet Pill</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L169" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D170" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E170" t="str">
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G170" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H170" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L170" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Angel Wings</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D171" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E171" t="str">
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G171" t="str">
-        <v>3:52</v>
+        <v>3:21</v>
       </c>
       <c r="H171" t="str">
-        <v>PRESIDENT</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L171" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Roamer</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D172" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E172" t="str">
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>2:19</v>
+        <v>3:52</v>
       </c>
       <c r="H172" t="str">
-        <v>spill tab</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L172" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>These Nights</v>
+        <v>Roamer</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D173" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E173" t="str">
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Everything Glows</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G173" t="str">
-        <v>4:39</v>
+        <v>2:19</v>
       </c>
       <c r="H173" t="str">
-        <v>Cannons</v>
+        <v>spill tab</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L173" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Locked and Loaded</v>
+        <v>These Nights</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D174" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E174" t="str">
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G174" t="str">
-        <v>2:55</v>
+        <v>4:39</v>
       </c>
       <c r="H174" t="str">
-        <v>The Cab</v>
+        <v>Cannons</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L174" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Safe And Sound</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D175" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E175" t="str">
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>EI8HT</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H175" t="str">
-        <v>Shinedown</v>
+        <v>The Cab</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L175" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Flinch</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D176" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E176" t="str">
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Autopilot</v>
+        <v>EI8HT</v>
       </c>
       <c r="G176" t="str">
-        <v>2:15</v>
+        <v>3:21</v>
       </c>
       <c r="H176" t="str">
-        <v>alexsucks</v>
+        <v>Shinedown</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L176" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Fall Up</v>
+        <v>Flinch</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D177" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E177" t="str">
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Fall Up - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G177" t="str">
-        <v>3:10</v>
+        <v>2:15</v>
       </c>
       <c r="H177" t="str">
-        <v>VOILÀ</v>
+        <v>alexsucks</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L177" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>No Typo</v>
+        <v>Fall Up</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D178" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E178" t="str">
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>1:43</v>
+        <v>3:10</v>
       </c>
       <c r="H178" t="str">
-        <v>Nasty C</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L178" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Desiree</v>
+        <v>No Typo</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D179" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E179" t="str">
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Wings of Desire</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G179" t="str">
-        <v>3:46</v>
+        <v>1:43</v>
       </c>
       <c r="H179" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Nasty C</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L179" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Desiree</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D180" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E180" t="str">
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Goliath</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G180" t="str">
-        <v>5:04</v>
+        <v>3:46</v>
       </c>
       <c r="H180" t="str">
-        <v>Exodus</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L180" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Nomad</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D181" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E181" t="str">
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Loss</v>
+        <v>Goliath</v>
       </c>
       <c r="G181" t="str">
-        <v>5:30</v>
+        <v>5:04</v>
       </c>
       <c r="H181" t="str">
-        <v>Gaerea</v>
+        <v>Exodus</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L181" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Empty Words</v>
+        <v>Nomad</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D182" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E182" t="str">
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Empty Words - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G182" t="str">
-        <v>2:32</v>
+        <v>5:30</v>
       </c>
       <c r="H182" t="str">
-        <v>Corey Kent</v>
+        <v>Gaerea</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L182" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Didn't Forget</v>
+        <v>Empty Words</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D183" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E183" t="str">
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>3:48</v>
+        <v>2:32</v>
       </c>
       <c r="H183" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L183" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Euphoria</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D184" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E184" t="str">
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Euphoria - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G184" t="str">
-        <v>2:14</v>
+        <v>3:48</v>
       </c>
       <c r="H184" t="str">
-        <v>Bluff City</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L184" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>hopeless romantic</v>
+        <v>Euphoria</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D185" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E185" t="str">
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G185" t="str">
-        <v>3:03</v>
+        <v>2:14</v>
       </c>
       <c r="H185" t="str">
-        <v>kwn</v>
+        <v>Bluff City</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L185" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Stay Close</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D186" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E186" t="str">
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Stay Close - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H186" t="str">
-        <v>Evelyn Cormier</v>
+        <v>kwn</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L186" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D187" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E187" t="str">
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H187" t="str">
-        <v>lydi lynn</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L187" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>peace at last</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D188" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E188" t="str">
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>peace at last - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G188" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H188" t="str">
-        <v>Aaron Cole</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L188" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Aguántame</v>
+        <v>peace at last</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D189" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E189" t="str">
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Aguántame - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:08</v>
+        <v>2:34</v>
       </c>
       <c r="H189" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L189" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>Aguántame</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D190" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E190" t="str">
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:40</v>
+        <v>2:08</v>
       </c>
       <c r="H190" t="str">
-        <v>Codiciado</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L190" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D191" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E191" t="str">
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:11</v>
+        <v>2:40</v>
       </c>
       <c r="H191" t="str">
-        <v>La Joaqui</v>
+        <v>Codiciado</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L191" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>V3n3n0</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D192" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E192" t="str">
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:32</v>
+        <v>3:11</v>
       </c>
       <c r="H192" t="str">
-        <v>Esty</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L192" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Moth In The Headlights</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D193" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E193" t="str">
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>4:23</v>
+        <v>2:32</v>
       </c>
       <c r="H193" t="str">
-        <v>The Pale White</v>
+        <v>Esty</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L193" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>lately in the void</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D194" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E194" t="str">
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>lately in the void - EP</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G194" t="str">
-        <v>3:41</v>
+        <v>4:23</v>
       </c>
       <c r="H194" t="str">
-        <v>bad tuner</v>
+        <v>The Pale White</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L194" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>When I Fall in Love</v>
+        <v>lately in the void</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D195" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E195" t="str">
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Nightjar</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G195" t="str">
-        <v>4:45</v>
+        <v>3:41</v>
       </c>
       <c r="H195" t="str">
-        <v>David Gray</v>
+        <v>bad tuner</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L195" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>Repeat Offender</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D196" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E196" t="str">
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>Nightjar</v>
       </c>
       <c r="G196" t="str">
-        <v>2:33</v>
+        <v>4:45</v>
       </c>
       <c r="H196" t="str">
-        <v>yeemz</v>
+        <v>David Gray</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L196" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Class Reunion</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D197" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E197" t="str">
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>4:11</v>
+        <v>2:33</v>
       </c>
       <c r="H197" t="str">
-        <v>Beatrix</v>
+        <v>yeemz</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L197" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="str">
-        <v>Promise Me</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B198" t="str">
         <v/>
       </c>
       <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D198" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E198" t="str">
         <v/>
       </c>
       <c r="F198" t="str">
-        <v>Instant Comfort</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G198" t="str">
-        <v>5:34</v>
+        <v>4:11</v>
       </c>
       <c r="H198" t="str">
-        <v>Lucid Express</v>
+        <v>Beatrix</v>
       </c>
       <c r="I198" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L198" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Promise Me</v>
       </c>
       <c r="B199" t="str">
         <v/>
       </c>
       <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D199" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E199" t="str">
         <v/>
       </c>
       <c r="F199" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G199" t="str">
-        <v>3:33</v>
+        <v>5:34</v>
       </c>
       <c r="H199" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I199" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L199" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B200" t="str">
         <v/>
       </c>
       <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D200" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E200" t="str">
         <v/>
       </c>
       <c r="F200" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G200" t="str">
-        <v>3:19</v>
+        <v>3:33</v>
       </c>
       <c r="H200" t="str">
-        <v>Ray Vaughn</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I200" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L200" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="str">
-        <v>So Good</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B201" t="str">
         <v/>
       </c>
       <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D201" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E201" t="str">
         <v/>
       </c>
       <c r="F201" t="str">
-        <v>So Good - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G201" t="str">
-        <v>2:47</v>
+        <v>3:19</v>
       </c>
       <c r="H201" t="str">
-        <v>Ari Abdul</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I201" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L201" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="str">
-        <v>YDH</v>
+        <v>So Good</v>
       </c>
       <c r="B202" t="str">
         <v/>
       </c>
       <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D202" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E202" t="str">
         <v/>
       </c>
       <c r="F202" t="str">
-        <v>YDH - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G202" t="str">
-        <v>3:17</v>
+        <v>2:47</v>
       </c>
       <c r="H202" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I202" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L202" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="str">
-        <v>Eucalyptus</v>
+        <v>YDH</v>
       </c>
       <c r="B203" t="str">
         <v/>
       </c>
       <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D203" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E203" t="str">
         <v/>
       </c>
       <c r="F203" t="str">
-        <v>Porcelain</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G203" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H203" t="str">
-        <v>Peach PRC</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I203" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L203" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="str">
-        <v>Pearls In The Trap</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B204" t="str">
         <v/>
       </c>
       <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D204" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E204" t="str">
         <v/>
       </c>
       <c r="F204" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G204" t="str">
-        <v>1:38</v>
+        <v>3:00</v>
       </c>
       <c r="H204" t="str">
-        <v>carolesdaughter</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I204" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L204" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="str">
-        <v>The Fever Mask</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B205" t="str">
         <v/>
       </c>
       <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D205" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E205" t="str">
         <v/>
       </c>
       <c r="F205" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G205" t="str">
-        <v>3:12</v>
+        <v>1:38</v>
       </c>
       <c r="H205" t="str">
-        <v>At The Gates</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I205" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L205" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="str">
-        <v>The Air's on Fire</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B206" t="str">
         <v/>
       </c>
       <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D206" t="str">
-        <v>2026-02-22</v>
+        <v>2026-02-23</v>
       </c>
       <c r="E206" t="str">
         <v/>
       </c>
       <c r="F206" t="str">
-        <v>Location Lost</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G206" t="str">
-        <v>5:15</v>
+        <v>3:12</v>
       </c>
       <c r="H206" t="str">
-        <v>Failure</v>
+        <v>At The Gates</v>
       </c>
       <c r="I206" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L206" t="str">
-        <v>The Air's on Fire - Failure</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="str">
+        <v>The Air's on Fire</v>
+      </c>
+      <c r="B207" t="str">
+        <v/>
+      </c>
+      <c r="C207" t="str">
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+      </c>
+      <c r="D207" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E207" t="str">
+        <v/>
+      </c>
+      <c r="F207" t="str">
+        <v>Location Lost</v>
+      </c>
+      <c r="G207" t="str">
+        <v>5:15</v>
+      </c>
+      <c r="H207" t="str">
+        <v>Failure</v>
+      </c>
+      <c r="I207" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J207" t="str">
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
+      </c>
+      <c r="K207" t="str">
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+      </c>
+      <c r="L207" t="str">
+        <v>The Air's on Fire - Failure</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
         <v>To The Last Breath</v>
       </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
+      <c r="B208" t="str">
+        <v/>
+      </c>
+      <c r="C208" t="str">
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
-      <c r="D207" t="str">
-        <v>2026-02-22</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
+      <c r="D208" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E208" t="str">
+        <v/>
+      </c>
+      <c r="F208" t="str">
         <v>To The Last Breath - Single</v>
       </c>
-      <c r="G207" t="str">
+      <c r="G208" t="str">
         <v>4:57</v>
       </c>
-      <c r="H207" t="str">
+      <c r="H208" t="str">
         <v>Arch Enemy</v>
       </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
+      <c r="I208" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J208" t="str">
         <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
-      <c r="K207" t="str">
+      <c r="K208" t="str">
         <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
-      <c r="L207" t="str">
+      <c r="L208" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L207"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L208"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>קרן קריספיל - עד שמצאתי</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-22</v>
+        <v>20 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409722&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>20 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>3:57</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>Self Esteem</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>קרן קריספיל - עד שמצאתי</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>סער הדר - טוב לך איתו</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B3" t="str">
-        <v>2026-02-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409721&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
-        <v/>
+        <v>2:27</v>
       </c>
       <c r="H3" t="str">
-        <v/>
+        <v>070 Shake</v>
       </c>
       <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>סער הדר - טוב לך איתו</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ים רפאלי - ערפדים</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-02-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409720&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v/>
+        <v>4:49</v>
       </c>
       <c r="H4" t="str">
-        <v/>
+        <v>georgemichael</v>
       </c>
       <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>ים רפאלי - ערפדים</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>טל קייסי - בלב הסערה</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
-        <v>2026-02-22</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409719&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v/>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v/>
+        <v>5:52</v>
       </c>
       <c r="H5" t="str">
-        <v/>
+        <v>georgemichael</v>
       </c>
       <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>טל קייסי - בלב הסערה</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אלי בי - רק תני לי סימן</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B6" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409718&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v/>
+        <v>3:22</v>
       </c>
       <c r="H6" t="str">
-        <v/>
+        <v>Foo Fighters</v>
       </c>
       <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אלי בי - רק תני לי סימן</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איתי אהרון - אהבה כאב וטעויות</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B7" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409717&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v/>
+        <v>4:08</v>
       </c>
       <c r="H7" t="str">
-        <v/>
+        <v>Romeo Santos</v>
       </c>
       <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איתי אהרון - אהבה כאב וטעויות</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>אייל לוי - מדויק</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B8" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409716&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v/>
+        <v>7:31</v>
       </c>
       <c r="H8" t="str">
-        <v/>
+        <v>Jacob Collier</v>
       </c>
       <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>אייל לוי - מדויק</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אחי נתן - לא בחור דתי</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B9" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409715&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v/>
+        <v>3:21</v>
       </c>
       <c r="H9" t="str">
-        <v/>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I9" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אחי נתן - לא בחור דתי</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אורן כדורי - למה ככה</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B10" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409714&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v/>
+        <v>4:36</v>
       </c>
       <c r="H10" t="str">
-        <v/>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I10" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אורן כדורי - למה ככה</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אייל שלום - אתה חי</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B11" t="str">
-        <v>2026-02-22</v>
+        <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409713&amp;sid=b57867d720f6c2e2edaca76769be49a4</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v/>
+        <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v/>
+        <v>5:06</v>
       </c>
       <c r="H11" t="str">
-        <v/>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I11" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אייל שלום - אתה חי</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Garden City Movement – I Can Be Your Salvation</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B12" t="str">
-        <v>2026-02-23</v>
+        <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://yosmusic.com/garden-city-movement/</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -831,16 +831,16 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>בלב המוזיקה האוורירית-אלקטרונית של הצמד יוני שרוני  ורועי אביטל המהווים  את Garden City Movement מסתתר טקסט לא רגוע בכלל. זוהי מוסיקה ריחופית שמדברת על שליטה, בלבול ותלות רגשית בעידן של עודף גירויים. השורה הראשונה מציבה את הדילמה: “?Could you choose</v>
+        <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v/>
+        <v>4:17</v>
       </c>
       <c r="H12" t="str">
-        <v/>
+        <v>Marc Anthony</v>
       </c>
       <c r="I12" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J12" t="str">
         <v/>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Garden City Movement – I Can Be Your Salvation</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B13" t="str">
-        <v>19 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>19 hours ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:57</v>
+        <v>3:20</v>
       </c>
       <c r="H13" t="str">
-        <v>Self Esteem</v>
+        <v>georgemichael</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>2:27</v>
+        <v>4:50</v>
       </c>
       <c r="H14" t="str">
-        <v>070 Shake</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:49</v>
+        <v>3:14</v>
       </c>
       <c r="H15" t="str">
-        <v>georgemichael</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>5:52</v>
+        <v>4:37</v>
       </c>
       <c r="H16" t="str">
-        <v>georgemichael</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B17" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1024,10 +1024,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:22</v>
+        <v>3:16</v>
       </c>
       <c r="H17" t="str">
-        <v>Foo Fighters</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:08</v>
+        <v>4:22</v>
       </c>
       <c r="H18" t="str">
-        <v>Romeo Santos</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>7:31</v>
+        <v>3:45</v>
       </c>
       <c r="H19" t="str">
-        <v>Jacob Collier</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1135,13 +1135,13 @@
         <v/>
       </c>
       <c r="F20" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:21</v>
+        <v>4:40</v>
       </c>
       <c r="H20" t="str">
-        <v>Gabi Sklar</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1173,13 +1173,13 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:36</v>
+        <v>3:02</v>
       </c>
       <c r="H21" t="str">
-        <v>YUNGBLUD</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>5:06</v>
+        <v>3:12</v>
       </c>
       <c r="H22" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1249,13 +1249,13 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>4:17</v>
+        <v>3:38</v>
       </c>
       <c r="H23" t="str">
-        <v>Marc Anthony</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:20</v>
+        <v>4:40</v>
       </c>
       <c r="H24" t="str">
-        <v>georgemichael</v>
+        <v>Cannons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1325,13 +1325,13 @@
         <v/>
       </c>
       <c r="F25" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:50</v>
+        <v>2:57</v>
       </c>
       <c r="H25" t="str">
-        <v>Cliff Richard</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1363,13 +1363,13 @@
         <v/>
       </c>
       <c r="F26" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:14</v>
+        <v>2:13</v>
       </c>
       <c r="H26" t="str">
-        <v>Freya Ridings</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1401,13 +1401,13 @@
         <v/>
       </c>
       <c r="F27" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:37</v>
+        <v>4:12</v>
       </c>
       <c r="H27" t="str">
-        <v>Jessie Ware</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1439,13 +1439,13 @@
         <v/>
       </c>
       <c r="F28" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>3:16</v>
+        <v>2:55</v>
       </c>
       <c r="H28" t="str">
-        <v>Alan Walker</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:22</v>
+        <v>3:51</v>
       </c>
       <c r="H29" t="str">
-        <v>The Neighbourhood</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:45</v>
+        <v>2:51</v>
       </c>
       <c r="H30" t="str">
-        <v>YUNGBLUD</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Suburban Requiem</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:40</v>
+        <v>3:24</v>
       </c>
       <c r="H31" t="str">
-        <v>YUNGBLUD</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:02</v>
+        <v>4:11</v>
       </c>
       <c r="H32" t="str">
-        <v>Calum Scott</v>
+        <v>We Three</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:12</v>
+        <v>3:27</v>
       </c>
       <c r="H33" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:38</v>
+        <v>3:06</v>
       </c>
       <c r="H34" t="str">
-        <v>Dermot Kennedy</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>4:40</v>
+        <v>3:01</v>
       </c>
       <c r="H35" t="str">
-        <v>Cannons</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>2:57</v>
+        <v>5:38</v>
       </c>
       <c r="H36" t="str">
-        <v>Mimi Webb</v>
+        <v>georgemichael</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>2:13</v>
+        <v>3:43</v>
       </c>
       <c r="H37" t="str">
-        <v>Jorja Smith</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1819,13 +1819,13 @@
         <v/>
       </c>
       <c r="F38" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>4:12</v>
+        <v>2:58</v>
       </c>
       <c r="H38" t="str">
-        <v>Sam Williams</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1857,13 +1857,13 @@
         <v/>
       </c>
       <c r="F39" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:55</v>
+        <v>4:13</v>
       </c>
       <c r="H39" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1895,13 +1895,13 @@
         <v/>
       </c>
       <c r="F40" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>3:51</v>
+        <v>5:48</v>
       </c>
       <c r="H40" t="str">
-        <v>Megan Moroney</v>
+        <v>U2</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1933,13 +1933,13 @@
         <v/>
       </c>
       <c r="F41" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>2:51</v>
+        <v>3:55</v>
       </c>
       <c r="H41" t="str">
-        <v>Nico Santos</v>
+        <v>Lawrence</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1971,13 +1971,13 @@
         <v/>
       </c>
       <c r="F42" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:24</v>
+        <v>5:24</v>
       </c>
       <c r="H42" t="str">
-        <v>REALITY CLUB</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2009,13 +2009,13 @@
         <v/>
       </c>
       <c r="F43" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:11</v>
+        <v>4:59</v>
       </c>
       <c r="H43" t="str">
-        <v>We Three</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2047,13 +2047,13 @@
         <v/>
       </c>
       <c r="F44" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>3:27</v>
+        <v>2:10</v>
       </c>
       <c r="H44" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B45" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:06</v>
+        <v>3:11</v>
       </c>
       <c r="H45" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B46" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:01</v>
+        <v>4:26</v>
       </c>
       <c r="H46" t="str">
-        <v>Peach PRC</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B47" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2161,13 +2161,13 @@
         <v/>
       </c>
       <c r="F47" t="str">
-        <v>3 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>5:38</v>
+        <v>4:35</v>
       </c>
       <c r="H47" t="str">
-        <v>georgemichael</v>
+        <v>mgk</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2199,13 +2199,13 @@
         <v/>
       </c>
       <c r="F48" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>3:43</v>
+        <v>2:09</v>
       </c>
       <c r="H48" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lola Young</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B49" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:58</v>
+        <v>4:11</v>
       </c>
       <c r="H49" t="str">
-        <v>Catie Turner</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B50" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>4 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:13</v>
+        <v>3:01</v>
       </c>
       <c r="H50" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>4 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>5:48</v>
+        <v>3:28</v>
       </c>
       <c r="H51" t="str">
-        <v>U2</v>
+        <v>mgk</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B52" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:55</v>
+        <v>5:31</v>
       </c>
       <c r="H52" t="str">
-        <v>Lawrence</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>5:24</v>
+        <v>2:49</v>
       </c>
       <c r="H53" t="str">
-        <v>BUNT. Music</v>
+        <v>Mýa</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B54" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>4:59</v>
+        <v>3:03</v>
       </c>
       <c r="H54" t="str">
-        <v>Bruno Mars</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B55" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>4 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:10</v>
+        <v>2:59</v>
       </c>
       <c r="H55" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B56" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2503,13 +2503,13 @@
         <v/>
       </c>
       <c r="F56" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:11</v>
+        <v>2:41</v>
       </c>
       <c r="H56" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B57" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2541,13 +2541,13 @@
         <v/>
       </c>
       <c r="F57" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>4:26</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>Neal Francis</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B58" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2579,13 +2579,13 @@
         <v/>
       </c>
       <c r="F58" t="str">
-        <v>5 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>4:35</v>
+        <v>3:59</v>
       </c>
       <c r="H58" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B59" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>5 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:09</v>
+        <v>7:48</v>
       </c>
       <c r="H59" t="str">
-        <v>Lola Young</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B60" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>4:11</v>
+        <v>3:10</v>
       </c>
       <c r="H60" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B61" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>6 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:01</v>
+        <v>5:57</v>
       </c>
       <c r="H61" t="str">
-        <v>The Vaccines</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B62" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2731,13 +2731,13 @@
         <v/>
       </c>
       <c r="F62" t="str">
-        <v>7 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:28</v>
+        <v>2:25</v>
       </c>
       <c r="H62" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2769,13 +2769,13 @@
         <v/>
       </c>
       <c r="F63" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>5:31</v>
+        <v>3:19</v>
       </c>
       <c r="H63" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2807,13 +2807,13 @@
         <v/>
       </c>
       <c r="F64" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:49</v>
+        <v>3:38</v>
       </c>
       <c r="H64" t="str">
-        <v>Mýa</v>
+        <v>mgk</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2845,13 +2845,13 @@
         <v/>
       </c>
       <c r="F65" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:03</v>
+        <v>4:05</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bolton</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2883,13 +2883,13 @@
         <v/>
       </c>
       <c r="F66" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:59</v>
+        <v>5:46</v>
       </c>
       <c r="H66" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2921,13 +2921,13 @@
         <v/>
       </c>
       <c r="F67" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>2:41</v>
+        <v>3:25</v>
       </c>
       <c r="H67" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2959,13 +2959,13 @@
         <v/>
       </c>
       <c r="F68" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>2:59</v>
+        <v>5:11</v>
       </c>
       <c r="H68" t="str">
-        <v>ENHYPEN</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -2997,13 +2997,13 @@
         <v/>
       </c>
       <c r="F69" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:59</v>
+        <v>2:55</v>
       </c>
       <c r="H69" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Warning</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>7:48</v>
+        <v>4:54</v>
       </c>
       <c r="H70" t="str">
-        <v>The Doobie Brothers</v>
+        <v>The Offspring</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:10</v>
+        <v>5:01</v>
       </c>
       <c r="H71" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:57</v>
+        <v>3:55</v>
       </c>
       <c r="H72" t="str">
-        <v>The Doobie Brothers</v>
+        <v>HAUSER</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:25</v>
+        <v>3:43</v>
       </c>
       <c r="H73" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:19</v>
+        <v>2:53</v>
       </c>
       <c r="H74" t="str">
-        <v>Michael Bolton</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:38</v>
+        <v>3:30</v>
       </c>
       <c r="H75" t="str">
-        <v>mgk</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>4:05</v>
+        <v>3:37</v>
       </c>
       <c r="H76" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>5:46</v>
+        <v>4:10</v>
       </c>
       <c r="H77" t="str">
-        <v>Jacob Collier</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B78" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3342,10 +3342,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:25</v>
+        <v>3:06</v>
       </c>
       <c r="H78" t="str">
-        <v>Victor Ray</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>5:11</v>
+        <v>3:17</v>
       </c>
       <c r="H79" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3415,13 +3415,13 @@
         <v/>
       </c>
       <c r="F80" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>2:55</v>
+        <v>3:21</v>
       </c>
       <c r="H80" t="str">
-        <v>The Warning</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3453,13 +3453,13 @@
         <v/>
       </c>
       <c r="F81" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:54</v>
+        <v>6:58</v>
       </c>
       <c r="H81" t="str">
-        <v>The Offspring</v>
+        <v>Eric Church</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3491,13 +3491,13 @@
         <v/>
       </c>
       <c r="F82" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>5:01</v>
+        <v>3:29</v>
       </c>
       <c r="H82" t="str">
-        <v>Caitlyn Smith</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3529,13 +3529,13 @@
         <v/>
       </c>
       <c r="F83" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:55</v>
+        <v>3:14</v>
       </c>
       <c r="H83" t="str">
-        <v>HAUSER</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3567,13 +3567,13 @@
         <v/>
       </c>
       <c r="F84" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:43</v>
+        <v>3:51</v>
       </c>
       <c r="H84" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B85" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3605,13 +3605,13 @@
         <v/>
       </c>
       <c r="F85" t="str">
-        <v>2 weeks ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>2:53</v>
+        <v>3:10</v>
       </c>
       <c r="H85" t="str">
-        <v>Ultra Records</v>
+        <v>elijah woods</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3643,13 +3643,13 @@
         <v/>
       </c>
       <c r="F86" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:30</v>
+        <v>3:26</v>
       </c>
       <c r="H86" t="str">
-        <v>Anja Kotar</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3681,13 +3681,13 @@
         <v/>
       </c>
       <c r="F87" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:37</v>
+        <v>2:51</v>
       </c>
       <c r="H87" t="str">
-        <v>Michael Bolton</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3719,13 +3719,13 @@
         <v/>
       </c>
       <c r="F88" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>4:10</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3757,13 +3757,13 @@
         <v/>
       </c>
       <c r="F89" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
         <v>3:06</v>
       </c>
       <c r="H89" t="str">
-        <v>Alan Walker</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:17</v>
+        <v>3:04</v>
       </c>
       <c r="H90" t="str">
-        <v>Bruno Mars</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:21</v>
+        <v>3:03</v>
       </c>
       <c r="H91" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>6:58</v>
+        <v>2:38</v>
       </c>
       <c r="H92" t="str">
-        <v>Eric Church</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3915,7 +3915,7 @@
         <v>3:29</v>
       </c>
       <c r="H93" t="str">
-        <v>Meghan Trainor</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:14</v>
+        <v>2:32</v>
       </c>
       <c r="H94" t="str">
-        <v>Ally Salort</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:51</v>
+        <v>3:32</v>
       </c>
       <c r="H95" t="str">
-        <v>Will Swinton</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:10</v>
+        <v>2:51</v>
       </c>
       <c r="H96" t="str">
-        <v>elijah woods</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H97" t="str">
-        <v>Jackson Dean</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H98" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Nickless</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:26</v>
+        <v>3:57</v>
       </c>
       <c r="H99" t="str">
-        <v>Neil Sedaka</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:06</v>
+        <v>3:08</v>
       </c>
       <c r="H100" t="str">
-        <v>Sofia Camara</v>
+        <v>elijah woods</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:04</v>
+        <v>3:53</v>
       </c>
       <c r="H101" t="str">
-        <v>Russell Dickerson</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Badlands</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G102" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H102" t="str">
-        <v>Celine Dion</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L102" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B103" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>10 days ago</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>2:38</v>
+        <v>3:48</v>
       </c>
       <c r="H103" t="str">
-        <v>Bebe Rexha</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K103" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L103" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B104" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>10 days ago</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:29</v>
+        <v>3:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Caroline Jones</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K104" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L104" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>ROSITA</v>
       </c>
       <c r="B105" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>10 days ago</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>2:32</v>
+        <v>4:05</v>
       </c>
       <c r="H105" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Tainy</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K105" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L105" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B106" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>10 days ago</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G106" t="str">
-        <v>3:32</v>
+        <v>3:52</v>
       </c>
       <c r="H106" t="str">
-        <v>Ingrid Andress</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K106" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L106" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B107" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>10 days ago</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>2:51</v>
+        <v>2:52</v>
       </c>
       <c r="H107" t="str">
-        <v>MusicByKnox</v>
+        <v>SZA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K107" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L107" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Medicine</v>
       </c>
       <c r="B108" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>10 days ago</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>3:38</v>
+        <v>3:11</v>
       </c>
       <c r="H108" t="str">
-        <v>Ella Langley</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B109" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>10 days ago</v>
+        <v>luck... or something</v>
       </c>
       <c r="G109" t="str">
-        <v>3:26</v>
+        <v>3:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Nickless</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K109" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L109" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B110" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>10 days ago</v>
+        <v>petal rock black</v>
       </c>
       <c r="G110" t="str">
-        <v>3:57</v>
+        <v>4:18</v>
       </c>
       <c r="H110" t="str">
-        <v>Caroline Jones</v>
+        <v>WILLOW</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K110" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L110" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Drag Path</v>
       </c>
       <c r="B111" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>10 days ago</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>3:08</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>elijah woods</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K111" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L111" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B112" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>10 days ago</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>3:53</v>
+        <v>3:55</v>
       </c>
       <c r="H112" t="str">
-        <v>August Ponthier</v>
+        <v>U2</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K112" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L112" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Badlands</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Prizefighter</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G113" t="str">
-        <v>2:58</v>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L113" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>Trimski</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>3:48</v>
+        <v>3:02</v>
       </c>
       <c r="H114" t="str">
-        <v>Taylor Swift</v>
+        <v>NAV</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L114" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>Paracosm</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G115" t="str">
-        <v>3:54</v>
+        <v>3:23</v>
       </c>
       <c r="H115" t="str">
-        <v>Lana Del Rey</v>
+        <v>Absolutely</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L115" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>ROSITA</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>ROSITA - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>4:05</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Tainy</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L116" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Ca$ino</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:52</v>
+        <v>4:18</v>
       </c>
       <c r="H117" t="str">
-        <v>Baby Keem</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L117" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G118" t="str">
-        <v>2:52</v>
+        <v>4:20</v>
       </c>
       <c r="H118" t="str">
-        <v>SZA</v>
+        <v>Pulp</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L118" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Medicine</v>
+        <v>My Maker</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Cloud 9</v>
+        <v>Ricochet</v>
       </c>
       <c r="G119" t="str">
-        <v>3:11</v>
+        <v>4:19</v>
       </c>
       <c r="H119" t="str">
-        <v>Megan Moroney</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L119" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Weather For Tennis</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>luck... or something</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>3:16</v>
+        <v>3:32</v>
       </c>
       <c r="H120" t="str">
-        <v>Hilary Duff</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L120" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>ear to the cocoon</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>petal rock black</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:18</v>
+        <v>4:27</v>
       </c>
       <c r="H121" t="str">
-        <v>WILLOW</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L121" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Drag Path</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Drag Path - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G122" t="str">
-        <v>3:44</v>
+        <v>3:33</v>
       </c>
       <c r="H122" t="str">
-        <v>twenty one pilots</v>
+        <v>Thundercat</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L122" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Song Of The Future</v>
+        <v>Tea Time</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:55</v>
+        <v>2:25</v>
       </c>
       <c r="H123" t="str">
-        <v>U2</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L123" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Your Favorite Toy</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:56</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Foo Fighters</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L124" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Trimski</v>
+        <v>Save My Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Trimski - Single</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:02</v>
+        <v>3:30</v>
       </c>
       <c r="H125" t="str">
-        <v>NAV</v>
+        <v>Kygo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L125" t="str">
-        <v>Trimski - NAV</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Paracosm</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Paracosm</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G126" t="str">
-        <v>3:23</v>
+        <v>3:46</v>
       </c>
       <c r="H126" t="str">
-        <v>Absolutely</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L126" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Casual Lady</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G127" t="str">
-        <v>3:14</v>
+        <v>4:39</v>
       </c>
       <c r="H127" t="str">
-        <v>flowerovlove</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L127" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Good Grief</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G128" t="str">
-        <v>4:18</v>
+        <v>4:21</v>
       </c>
       <c r="H128" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L128" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Begging for Change</v>
+        <v>Freak On</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>HELP(2)</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:20</v>
+        <v>2:49</v>
       </c>
       <c r="H129" t="str">
-        <v>Pulp</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L129" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>My Maker</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Ricochet</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>4:19</v>
+        <v>3:32</v>
       </c>
       <c r="H130" t="str">
-        <v>Snail Mail</v>
+        <v>deadmau5</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L130" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-23</v>
@@ -5353,10 +5353,10 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:32</v>
+        <v>3:55</v>
       </c>
       <c r="H131" t="str">
         <v>Taylor Swift</v>
@@ -5368,21 +5368,21 @@
         <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L131" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>4:27</v>
+        <v>2:42</v>
       </c>
       <c r="H132" t="str">
-        <v>CHVRCHES</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>She Knows Too Much</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Distracted</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>3:33</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Thundercat</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L133" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Tea Time</v>
+        <v>only the best</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Tea Time - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:25</v>
+        <v>3:22</v>
       </c>
       <c r="H134" t="str">
-        <v>Yung Miami</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L134" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:12</v>
+        <v>2:59</v>
       </c>
       <c r="H135" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Tiësto</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L135" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Save My Love</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Save My Love - Single</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:30</v>
+        <v>3:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Kygo</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L136" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Mārara</v>
       </c>
       <c r="G137" t="str">
-        <v>3:46</v>
+        <v>3:10</v>
       </c>
       <c r="H137" t="str">
-        <v>Omar Courtz</v>
+        <v>15 15</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L137" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Suburban Requiem</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Idols (Complete)</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G138" t="str">
-        <v>4:39</v>
+        <v>3:41</v>
       </c>
       <c r="H138" t="str">
-        <v>YUNGBLUD</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L138" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Good Grief</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>4:21</v>
+        <v>2:28</v>
       </c>
       <c r="H139" t="str">
-        <v>The Neighbourhood</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L139" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>Freak On</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Freak On - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G140" t="str">
-        <v>2:49</v>
+        <v>1:51</v>
       </c>
       <c r="H140" t="str">
-        <v>Steve Aoki</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L140" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>3:32</v>
+        <v>1:53</v>
       </c>
       <c r="H141" t="str">
-        <v>deadmau5</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L141" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>3:55</v>
+        <v>2:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Taylor Swift</v>
+        <v>Soulidified</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L142" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Yellow Eyes</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Jean</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G143" t="str">
-        <v>2:42</v>
+        <v>2:53</v>
       </c>
       <c r="H143" t="str">
-        <v>Yebba</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L143" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Word On The Street</v>
+        <v>Bully</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:56</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Luke Bryan</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L144" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>only the best</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>only the best - Single</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:22</v>
+        <v>3:16</v>
       </c>
       <c r="H145" t="str">
-        <v>horsegiirL</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L145" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Beautiful Places</v>
+        <v>Ride</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G146" t="str">
-        <v>2:59</v>
+        <v>4:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Tiësto</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L146" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>STAMPEDE</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>3:09</v>
+        <v>4:18</v>
       </c>
       <c r="H147" t="str">
-        <v>Genesis Owusu</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L147" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Infinite Beach</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Mārara</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>3:10</v>
+        <v>2:10</v>
       </c>
       <c r="H148" t="str">
-        <v>15 15</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L148" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Championship Ring</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>I Want Blood</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>3:41</v>
+        <v>2:31</v>
       </c>
       <c r="H149" t="str">
-        <v>SleazyWorld Go</v>
+        <v>JayDon</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L149" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:28</v>
+        <v>2:49</v>
       </c>
       <c r="H150" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L150" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>Da Realest</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G151" t="str">
-        <v>1:51</v>
+        <v>5:13</v>
       </c>
       <c r="H151" t="str">
-        <v>Babyfxce E</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L151" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Fine Shit</v>
+        <v>Migajero</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>1:53</v>
+        <v>3:18</v>
       </c>
       <c r="H152" t="str">
-        <v>Real Boston Richey</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L152" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>What's Your Name</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>2:20</v>
+        <v>3:26</v>
       </c>
       <c r="H153" t="str">
-        <v>Soulidified</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L153" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Ends In Y</v>
+        <v>Old Man</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>2:53</v>
+        <v>4:05</v>
       </c>
       <c r="H154" t="str">
-        <v>Mimi Webb</v>
+        <v>Trousdale</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L154" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Bully</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Bully - Single</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:05</v>
+        <v>3:19</v>
       </c>
       <c r="H155" t="str">
-        <v>Iris Copperman</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L155" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>MC24 (1:4)</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G156" t="str">
-        <v>3:16</v>
+        <v>2:56</v>
       </c>
       <c r="H156" t="str">
-        <v>Charles Leclerc</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L156" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Ride</v>
+        <v>Refuge</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Superbloom</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G157" t="str">
-        <v>4:39</v>
+        <v>3:38</v>
       </c>
       <c r="H157" t="str">
-        <v>Jessie Ware</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L157" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Arkansas Mud</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G158" t="str">
-        <v>4:18</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Ashley McBryde</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L158" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Don't Leave</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Don't Leave - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G159" t="str">
-        <v>2:10</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>Jorja Smith</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L159" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>FLAMED UP</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:31</v>
+        <v>3:21</v>
       </c>
       <c r="H160" t="str">
-        <v>JayDon</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L160" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>3am in Paris</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>3am in Paris - Single</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>2:49</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>Anais Cardot</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L161" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>Roamer</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G162" t="str">
-        <v>5:13</v>
+        <v>2:19</v>
       </c>
       <c r="H162" t="str">
-        <v>Elevation Worship</v>
+        <v>spill tab</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L162" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Migajero</v>
+        <v>These Nights</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Migajero - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G163" t="str">
-        <v>3:18</v>
+        <v>4:39</v>
       </c>
       <c r="H163" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Cannons</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L163" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>3:26</v>
+        <v>2:55</v>
       </c>
       <c r="H164" t="str">
-        <v>Taylor Swift</v>
+        <v>The Cab</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L164" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Old Man</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Old Man - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G165" t="str">
-        <v>4:05</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>Trousdale</v>
+        <v>Shinedown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L165" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Flinch</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G166" t="str">
-        <v>3:19</v>
+        <v>2:15</v>
       </c>
       <c r="H166" t="str">
-        <v>DJ Seinfeld</v>
+        <v>alexsucks</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L166" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Fall Up</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:56</v>
+        <v>3:10</v>
       </c>
       <c r="H167" t="str">
-        <v>Denzel Curry</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L167" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Refuge</v>
+        <v>No Typo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G168" t="str">
-        <v>3:38</v>
+        <v>1:43</v>
       </c>
       <c r="H168" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Nasty C</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L168" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Desiree</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G169" t="str">
-        <v>3:24</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Leigh-Anne</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L169" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Smoke Screen</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Goliath</v>
       </c>
       <c r="G170" t="str">
-        <v>2:51</v>
+        <v>5:04</v>
       </c>
       <c r="H170" t="str">
-        <v>Sweet Pill</v>
+        <v>Exodus</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L170" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Nomad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G171" t="str">
-        <v>3:21</v>
+        <v>5:30</v>
       </c>
       <c r="H171" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Gaerea</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L171" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Angel Wings</v>
+        <v>Empty Words</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>3:52</v>
+        <v>2:32</v>
       </c>
       <c r="H172" t="str">
-        <v>PRESIDENT</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L172" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Roamer</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:19</v>
+        <v>3:48</v>
       </c>
       <c r="H173" t="str">
-        <v>spill tab</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L173" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>These Nights</v>
+        <v>Euphoria</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Everything Glows</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>4:39</v>
+        <v>2:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Cannons</v>
+        <v>Bluff City</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L174" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Locked and Loaded</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:55</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>The Cab</v>
+        <v>kwn</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L175" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Safe And Sound</v>
+        <v>Stay Close</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>EI8HT</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:21</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>Shinedown</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L176" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Flinch</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Autopilot</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G177" t="str">
-        <v>2:15</v>
+        <v>2:54</v>
       </c>
       <c r="H177" t="str">
-        <v>alexsucks</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L177" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Fall Up</v>
+        <v>peace at last</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Fall Up - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>3:10</v>
+        <v>2:34</v>
       </c>
       <c r="H178" t="str">
-        <v>VOILÀ</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L178" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>No Typo</v>
+        <v>Aguántame</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>1:43</v>
+        <v>2:08</v>
       </c>
       <c r="H179" t="str">
-        <v>Nasty C</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L179" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Desiree</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Wings of Desire</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>3:46</v>
+        <v>2:40</v>
       </c>
       <c r="H180" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Codiciado</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L180" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Goliath</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>5:04</v>
+        <v>3:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Exodus</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L181" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>Nomad</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>Loss</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>5:30</v>
+        <v>2:32</v>
       </c>
       <c r="H182" t="str">
-        <v>Gaerea</v>
+        <v>Esty</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L182" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Empty Words</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Empty Words - Single</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G183" t="str">
-        <v>2:32</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Corey Kent</v>
+        <v>The Pale White</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L183" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Didn't Forget</v>
+        <v>lately in the void</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>3:48</v>
+        <v>3:41</v>
       </c>
       <c r="H184" t="str">
-        <v>Waylon Wyatt</v>
+        <v>bad tuner</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L184" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>Euphoria</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Euphoria - Single</v>
+        <v>Nightjar</v>
       </c>
       <c r="G185" t="str">
-        <v>2:14</v>
+        <v>4:45</v>
       </c>
       <c r="H185" t="str">
-        <v>Bluff City</v>
+        <v>David Gray</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L185" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>hopeless romantic</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>3:03</v>
+        <v>2:33</v>
       </c>
       <c r="H186" t="str">
-        <v>kwn</v>
+        <v>yeemz</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L186" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Stay Close</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Stay Close - Single</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G187" t="str">
-        <v>2:58</v>
+        <v>4:11</v>
       </c>
       <c r="H187" t="str">
-        <v>Evelyn Cormier</v>
+        <v>Beatrix</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L187" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Metamorphosis</v>
+        <v>Promise Me</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Metamorphosis</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G188" t="str">
-        <v>2:54</v>
+        <v>5:34</v>
       </c>
       <c r="H188" t="str">
-        <v>lydi lynn</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L188" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>peace at last</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>peace at last - Single</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>2:34</v>
+        <v>3:33</v>
       </c>
       <c r="H189" t="str">
-        <v>Aaron Cole</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L189" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Aguántame</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Aguántame - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>2:08</v>
+        <v>3:19</v>
       </c>
       <c r="H190" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L190" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>So Good</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:40</v>
+        <v>2:47</v>
       </c>
       <c r="H191" t="str">
-        <v>Codiciado</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L191" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>NADA PERSONAL</v>
+        <v>YDH</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:11</v>
+        <v>3:17</v>
       </c>
       <c r="H192" t="str">
-        <v>La Joaqui</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L192" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>V3n3n0</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G193" t="str">
-        <v>2:32</v>
+        <v>3:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Esty</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L193" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Moth In The Headlights</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>4:23</v>
+        <v>1:38</v>
       </c>
       <c r="H194" t="str">
-        <v>The Pale White</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L194" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>lately in the void</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>lately in the void - EP</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G195" t="str">
-        <v>3:41</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>bad tuner</v>
+        <v>At The Gates</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L195" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>When I Fall in Love</v>
+        <v>The Air's on Fire</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Nightjar</v>
+        <v>Location Lost</v>
       </c>
       <c r="G196" t="str">
-        <v>4:45</v>
+        <v>5:15</v>
       </c>
       <c r="H196" t="str">
-        <v>David Gray</v>
+        <v>Failure</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
       </c>
       <c r="L196" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>The Air's on Fire - Failure</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>Repeat Offender</v>
+        <v>To The Last Breath</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-23</v>
@@ -7861,448 +7861,30 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>To The Last Breath - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>2:33</v>
+        <v>4:57</v>
       </c>
       <c r="H197" t="str">
-        <v>yeemz</v>
+        <v>Arch Enemy</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
       <c r="L197" t="str">
-        <v>Repeat Offender - yeemz</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>Class Reunion</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>We Swallowed The Sky</v>
-      </c>
-      <c r="G198" t="str">
-        <v>4:11</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Beatrix</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
-      </c>
-      <c r="L198" t="str">
-        <v>Class Reunion - Beatrix</v>
-      </c>
-    </row>
-    <row r="199">
-      <c r="A199" t="str">
-        <v>Promise Me</v>
-      </c>
-      <c r="B199" t="str">
-        <v/>
-      </c>
-      <c r="C199" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
-      </c>
-      <c r="D199" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E199" t="str">
-        <v/>
-      </c>
-      <c r="F199" t="str">
-        <v>Instant Comfort</v>
-      </c>
-      <c r="G199" t="str">
-        <v>5:34</v>
-      </c>
-      <c r="H199" t="str">
-        <v>Lucid Express</v>
-      </c>
-      <c r="I199" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J199" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
-      </c>
-      <c r="K199" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
-      </c>
-      <c r="L199" t="str">
-        <v>Promise Me - Lucid Express</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
-      </c>
-      <c r="B200" t="str">
-        <v/>
-      </c>
-      <c r="C200" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
-      </c>
-      <c r="D200" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E200" t="str">
-        <v/>
-      </c>
-      <c r="F200" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
-      </c>
-      <c r="G200" t="str">
-        <v>3:33</v>
-      </c>
-      <c r="H200" t="str">
-        <v>Zee Nxumalo</v>
-      </c>
-      <c r="I200" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J200" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
-      </c>
-      <c r="K200" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
-      </c>
-      <c r="L200" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
-      </c>
-      <c r="B201" t="str">
-        <v/>
-      </c>
-      <c r="C201" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
-      </c>
-      <c r="D201" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E201" t="str">
-        <v/>
-      </c>
-      <c r="F201" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
-      </c>
-      <c r="G201" t="str">
-        <v>3:19</v>
-      </c>
-      <c r="H201" t="str">
-        <v>Ray Vaughn</v>
-      </c>
-      <c r="I201" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J201" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
-      </c>
-      <c r="K201" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
-      </c>
-      <c r="L201" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="str">
-        <v>So Good</v>
-      </c>
-      <c r="B202" t="str">
-        <v/>
-      </c>
-      <c r="C202" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
-      </c>
-      <c r="D202" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E202" t="str">
-        <v/>
-      </c>
-      <c r="F202" t="str">
-        <v>So Good - Single</v>
-      </c>
-      <c r="G202" t="str">
-        <v>2:47</v>
-      </c>
-      <c r="H202" t="str">
-        <v>Ari Abdul</v>
-      </c>
-      <c r="I202" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J202" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
-      </c>
-      <c r="K202" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
-      </c>
-      <c r="L202" t="str">
-        <v>So Good - Ari Abdul</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="str">
-        <v>YDH</v>
-      </c>
-      <c r="B203" t="str">
-        <v/>
-      </c>
-      <c r="C203" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
-      </c>
-      <c r="D203" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E203" t="str">
-        <v/>
-      </c>
-      <c r="F203" t="str">
-        <v>YDH - Single</v>
-      </c>
-      <c r="G203" t="str">
-        <v>3:17</v>
-      </c>
-      <c r="H203" t="str">
-        <v>Chloe Qisha</v>
-      </c>
-      <c r="I203" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J203" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
-      </c>
-      <c r="K203" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
-      </c>
-      <c r="L203" t="str">
-        <v>YDH - Chloe Qisha</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="str">
-        <v>Eucalyptus</v>
-      </c>
-      <c r="B204" t="str">
-        <v/>
-      </c>
-      <c r="C204" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
-      </c>
-      <c r="D204" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E204" t="str">
-        <v/>
-      </c>
-      <c r="F204" t="str">
-        <v>Porcelain</v>
-      </c>
-      <c r="G204" t="str">
-        <v>3:00</v>
-      </c>
-      <c r="H204" t="str">
-        <v>Peach PRC</v>
-      </c>
-      <c r="I204" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J204" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
-      </c>
-      <c r="K204" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
-      </c>
-      <c r="L204" t="str">
-        <v>Eucalyptus - Peach PRC</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="str">
-        <v>Pearls In The Trap</v>
-      </c>
-      <c r="B205" t="str">
-        <v/>
-      </c>
-      <c r="C205" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
-      </c>
-      <c r="D205" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E205" t="str">
-        <v/>
-      </c>
-      <c r="F205" t="str">
-        <v>Pearls In The Trap - Single</v>
-      </c>
-      <c r="G205" t="str">
-        <v>1:38</v>
-      </c>
-      <c r="H205" t="str">
-        <v>carolesdaughter</v>
-      </c>
-      <c r="I205" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J205" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
-      </c>
-      <c r="K205" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
-      </c>
-      <c r="L205" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="str">
-        <v>The Fever Mask</v>
-      </c>
-      <c r="B206" t="str">
-        <v/>
-      </c>
-      <c r="C206" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
-      </c>
-      <c r="D206" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E206" t="str">
-        <v/>
-      </c>
-      <c r="F206" t="str">
-        <v>The Ghost of a Future Dead</v>
-      </c>
-      <c r="G206" t="str">
-        <v>3:12</v>
-      </c>
-      <c r="H206" t="str">
-        <v>At The Gates</v>
-      </c>
-      <c r="I206" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J206" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
-      </c>
-      <c r="K206" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
-      </c>
-      <c r="L206" t="str">
-        <v>The Fever Mask - At The Gates</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="str">
-        <v>The Air's on Fire</v>
-      </c>
-      <c r="B207" t="str">
-        <v/>
-      </c>
-      <c r="C207" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
-      </c>
-      <c r="D207" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E207" t="str">
-        <v/>
-      </c>
-      <c r="F207" t="str">
-        <v>Location Lost</v>
-      </c>
-      <c r="G207" t="str">
-        <v>5:15</v>
-      </c>
-      <c r="H207" t="str">
-        <v>Failure</v>
-      </c>
-      <c r="I207" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J207" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
-      </c>
-      <c r="K207" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
-      </c>
-      <c r="L207" t="str">
-        <v>The Air's on Fire - Failure</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="str">
-        <v>To The Last Breath</v>
-      </c>
-      <c r="B208" t="str">
-        <v/>
-      </c>
-      <c r="C208" t="str">
-        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
-      </c>
-      <c r="D208" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E208" t="str">
-        <v/>
-      </c>
-      <c r="F208" t="str">
-        <v>To The Last Breath - Single</v>
-      </c>
-      <c r="G208" t="str">
-        <v>4:57</v>
-      </c>
-      <c r="H208" t="str">
-        <v>Arch Enemy</v>
-      </c>
-      <c r="I208" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J208" t="str">
-        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
-      </c>
-      <c r="K208" t="str">
-        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
-      </c>
-      <c r="L208" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L208"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Wuthering Heights צ'רלי XCX</v>
       </c>
       <c r="B2" t="str">
-        <v>20 hours ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>20 hours ago</v>
+        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
       </c>
       <c r="G2" t="str">
-        <v>3:57</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>Self Esteem</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Wuthering Heights צ'רלי XCX</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>22 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H3" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H4" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -568,7 +568,7 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H5" t="str">
         <v>georgemichael</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B6" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -606,10 +606,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H6" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H7" t="str">
-        <v>Romeo Santos</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>7:31</v>
+        <v>4:08</v>
       </c>
       <c r="H8" t="str">
-        <v>Jacob Collier</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>3:21</v>
+        <v>7:31</v>
       </c>
       <c r="H9" t="str">
-        <v>Gabi Sklar</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>4:36</v>
+        <v>3:21</v>
       </c>
       <c r="H10" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>5:06</v>
+        <v>4:36</v>
       </c>
       <c r="H11" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:17</v>
+        <v>5:06</v>
       </c>
       <c r="H12" t="str">
-        <v>Marc Anthony</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:20</v>
+        <v>4:17</v>
       </c>
       <c r="H13" t="str">
-        <v>georgemichael</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:50</v>
+        <v>3:20</v>
       </c>
       <c r="H14" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:14</v>
+        <v>4:50</v>
       </c>
       <c r="H15" t="str">
-        <v>Freya Ridings</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B16" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -986,10 +986,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:37</v>
+        <v>3:14</v>
       </c>
       <c r="H16" t="str">
-        <v>Jessie Ware</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H17" t="str">
-        <v>Alan Walker</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:22</v>
+        <v>3:16</v>
       </c>
       <c r="H18" t="str">
-        <v>The Neighbourhood</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:45</v>
+        <v>4:22</v>
       </c>
       <c r="H19" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Suburban Requiem</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1138,7 +1138,7 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:40</v>
+        <v>3:45</v>
       </c>
       <c r="H20" t="str">
         <v>YUNGBLUD</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:02</v>
+        <v>4:40</v>
       </c>
       <c r="H21" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H22" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H23" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:40</v>
+        <v>3:38</v>
       </c>
       <c r="H24" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H25" t="str">
-        <v>Mimi Webb</v>
+        <v>Cannons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:13</v>
+        <v>2:57</v>
       </c>
       <c r="H26" t="str">
-        <v>Jorja Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>4:12</v>
+        <v>2:13</v>
       </c>
       <c r="H27" t="str">
-        <v>Sam Williams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:55</v>
+        <v>4:12</v>
       </c>
       <c r="H28" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H29" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H30" t="str">
-        <v>Nico Santos</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H31" t="str">
-        <v>REALITY CLUB</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H32" t="str">
-        <v>We Three</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:27</v>
+        <v>4:11</v>
       </c>
       <c r="H33" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>We Three</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H34" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H35" t="str">
-        <v>Peach PRC</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>5:38</v>
+        <v>3:01</v>
       </c>
       <c r="H36" t="str">
-        <v>georgemichael</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:43</v>
+        <v>5:38</v>
       </c>
       <c r="H37" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>georgemichael</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H38" t="str">
-        <v>Catie Turner</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>4:13</v>
+        <v>2:58</v>
       </c>
       <c r="H39" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>5:48</v>
+        <v>4:13</v>
       </c>
       <c r="H40" t="str">
-        <v>U2</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:55</v>
+        <v>5:48</v>
       </c>
       <c r="H41" t="str">
-        <v>Lawrence</v>
+        <v>U2</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:24</v>
+        <v>3:55</v>
       </c>
       <c r="H42" t="str">
-        <v>BUNT. Music</v>
+        <v>Lawrence</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:59</v>
+        <v>5:24</v>
       </c>
       <c r="H43" t="str">
-        <v>Bruno Mars</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>2:10</v>
+        <v>4:59</v>
       </c>
       <c r="H44" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B45" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2085,10 +2085,10 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:11</v>
+        <v>2:10</v>
       </c>
       <c r="H45" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B46" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2126,10 +2126,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>4:26</v>
+        <v>3:11</v>
       </c>
       <c r="H46" t="str">
-        <v>Neal Francis</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:35</v>
+        <v>4:26</v>
       </c>
       <c r="H47" t="str">
-        <v>mgk</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:09</v>
+        <v>4:35</v>
       </c>
       <c r="H48" t="str">
-        <v>Lola Young</v>
+        <v>mgk</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B49" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2237,13 +2237,13 @@
         <v/>
       </c>
       <c r="F49" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:11</v>
+        <v>2:09</v>
       </c>
       <c r="H49" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lola Young</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B50" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2278,10 +2278,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>3:01</v>
+        <v>4:11</v>
       </c>
       <c r="H50" t="str">
-        <v>The Vaccines</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H51" t="str">
-        <v>mgk</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H52" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B53" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2392,10 +2392,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H53" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H54" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H55" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H56" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H57" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H58" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2617,13 +2617,13 @@
         <v/>
       </c>
       <c r="F59" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H59" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B60" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2658,10 +2658,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H60" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H61" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H62" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H63" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H64" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H65" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H66" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H67" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H68" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H69" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H70" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H71" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H72" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H73" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H74" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H75" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H76" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H77" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H78" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H79" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H80" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H81" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H82" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H83" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H84" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H85" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H86" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H87" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3722,10 +3722,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H88" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H90" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H91" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H92" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H93" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H94" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H95" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H96" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H97" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H98" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H99" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H100" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>elijah woods - DNA (Official Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:53</v>
+        <v>3:08</v>
       </c>
       <c r="H101" t="str">
-        <v>August Ponthier</v>
+        <v>elijah woods</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Badlands</v>
+        <v>Ribbons + Taxes (Visualizer)</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Prizefighter</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:58</v>
+        <v>3:53</v>
       </c>
       <c r="H102" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>August Ponthier</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>Badlands</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G103" t="str">
-        <v>3:48</v>
+        <v>2:58</v>
       </c>
       <c r="H103" t="str">
-        <v>Taylor Swift</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L103" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:54</v>
+        <v>3:48</v>
       </c>
       <c r="H104" t="str">
-        <v>Lana Del Rey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ROSITA</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>ROSITA - Single</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:05</v>
+        <v>3:54</v>
       </c>
       <c r="H105" t="str">
-        <v>Tainy</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L105" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>ROSITA</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ca$ino</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H106" t="str">
-        <v>Baby Keem</v>
+        <v>Tainy</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L106" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G107" t="str">
-        <v>2:52</v>
+        <v>3:52</v>
       </c>
       <c r="H107" t="str">
-        <v>SZA</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L107" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Medicine</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:11</v>
+        <v>2:52</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>SZA</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L108" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Weather For Tennis</v>
+        <v>Medicine</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>luck... or something</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G109" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H109" t="str">
-        <v>Hilary Duff</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L109" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ear to the cocoon</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>petal rock black</v>
+        <v>luck... or something</v>
       </c>
       <c r="G110" t="str">
-        <v>4:18</v>
+        <v>3:16</v>
       </c>
       <c r="H110" t="str">
-        <v>WILLOW</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L110" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag Path</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Drag Path - Single</v>
+        <v>petal rock black</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>4:18</v>
       </c>
       <c r="H111" t="str">
-        <v>twenty one pilots</v>
+        <v>WILLOW</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L111" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Song Of The Future</v>
+        <v>Drag Path</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:55</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>U2</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L112" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H113" t="str">
-        <v>Foo Fighters</v>
+        <v>U2</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L113" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Trimski</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Trimski - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G114" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H114" t="str">
-        <v>NAV</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L114" t="str">
-        <v>Trimski - NAV</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H115" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L115" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G116" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H116" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L116" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:18</v>
+        <v>3:14</v>
       </c>
       <c r="H117" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L117" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Begging for Change</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>HELP(2)</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:20</v>
+        <v>4:18</v>
       </c>
       <c r="H118" t="str">
-        <v>Pulp</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L118" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>My Maker</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ricochet</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G119" t="str">
-        <v>4:19</v>
+        <v>4:20</v>
       </c>
       <c r="H119" t="str">
-        <v>Snail Mail</v>
+        <v>Pulp</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L119" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>My Maker</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G120" t="str">
-        <v>3:32</v>
+        <v>4:19</v>
       </c>
       <c r="H120" t="str">
-        <v>Taylor Swift</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L120" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:27</v>
+        <v>3:32</v>
       </c>
       <c r="H121" t="str">
-        <v>CHVRCHES</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>She Knows Too Much</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Distracted</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:33</v>
+        <v>4:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Thundercat</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L122" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tea Time</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tea Time - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G123" t="str">
-        <v>2:25</v>
+        <v>3:33</v>
       </c>
       <c r="H123" t="str">
-        <v>Yung Miami</v>
+        <v>Thundercat</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L123" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Tea Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L124" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Save My Love</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Save My Love - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G125" t="str">
-        <v>3:30</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Kygo</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L125" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Save My Love</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H126" t="str">
-        <v>Omar Courtz</v>
+        <v>Kygo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L126" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Suburban Requiem</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Idols (Complete)</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G127" t="str">
-        <v>4:39</v>
+        <v>3:46</v>
       </c>
       <c r="H127" t="str">
-        <v>YUNGBLUD</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L127" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Good Grief</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G128" t="str">
-        <v>4:21</v>
+        <v>4:39</v>
       </c>
       <c r="H128" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L128" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Freak On</v>
+        <v>Good Grief</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Freak On - Single</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G129" t="str">
-        <v>2:49</v>
+        <v>4:21</v>
       </c>
       <c r="H129" t="str">
-        <v>Steve Aoki</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L129" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Freak On</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H130" t="str">
-        <v>deadmau5</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L130" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H131" t="str">
-        <v>Taylor Swift</v>
+        <v>deadmau5</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L131" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Yellow Eyes</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Jean</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:42</v>
+        <v>3:55</v>
       </c>
       <c r="H132" t="str">
-        <v>Yebba</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L132" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Word On The Street</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>2:42</v>
       </c>
       <c r="H133" t="str">
-        <v>Luke Bryan</v>
+        <v>Yebba</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L133" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>only the best</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>only the best - Single</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L134" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Beautiful Places</v>
+        <v>only the best</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H135" t="str">
-        <v>Tiësto</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L135" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>STAMPEDE</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:09</v>
+        <v>2:59</v>
       </c>
       <c r="H136" t="str">
-        <v>Genesis Owusu</v>
+        <v>Tiësto</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L136" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Infinite Beach</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Mārara</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H137" t="str">
-        <v>15 15</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L137" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Championship Ring</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Want Blood</v>
+        <v>Mārara</v>
       </c>
       <c r="G138" t="str">
-        <v>3:41</v>
+        <v>3:10</v>
       </c>
       <c r="H138" t="str">
-        <v>SleazyWorld Go</v>
+        <v>15 15</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L138" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G139" t="str">
-        <v>2:28</v>
+        <v>3:41</v>
       </c>
       <c r="H139" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L139" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Da Realest</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>1:51</v>
+        <v>2:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Babyfxce E</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L140" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Fine Shit</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G141" t="str">
-        <v>1:53</v>
+        <v>1:51</v>
       </c>
       <c r="H141" t="str">
-        <v>Real Boston Richey</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L141" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>What's Your Name</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:20</v>
+        <v>1:53</v>
       </c>
       <c r="H142" t="str">
-        <v>Soulidified</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L142" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ends In Y</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:53</v>
+        <v>2:20</v>
       </c>
       <c r="H143" t="str">
-        <v>Mimi Webb</v>
+        <v>Soulidified</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L143" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Bully</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Bully - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>2:53</v>
       </c>
       <c r="H144" t="str">
-        <v>Iris Copperman</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L144" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Bully</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:16</v>
+        <v>3:05</v>
       </c>
       <c r="H145" t="str">
-        <v>Charles Leclerc</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L145" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Ride</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Superbloom</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:39</v>
+        <v>3:16</v>
       </c>
       <c r="H146" t="str">
-        <v>Jessie Ware</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L146" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Arkansas Mud</v>
+        <v>Ride</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G147" t="str">
-        <v>4:18</v>
+        <v>4:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L147" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Don't Leave</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Don't Leave - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:10</v>
+        <v>4:18</v>
       </c>
       <c r="H148" t="str">
-        <v>Jorja Smith</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L148" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FLAMED UP</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:31</v>
+        <v>2:10</v>
       </c>
       <c r="H149" t="str">
-        <v>JayDon</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L149" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>3am in Paris</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>3am in Paris - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:49</v>
+        <v>2:31</v>
       </c>
       <c r="H150" t="str">
-        <v>Anais Cardot</v>
+        <v>JayDon</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L150" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:13</v>
+        <v>2:49</v>
       </c>
       <c r="H151" t="str">
-        <v>Elevation Worship</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L151" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Migajero</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Migajero - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:18</v>
+        <v>5:13</v>
       </c>
       <c r="H152" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L152" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Migajero</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:26</v>
+        <v>3:18</v>
       </c>
       <c r="H153" t="str">
-        <v>Taylor Swift</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L153" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Old Man</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Old Man - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H154" t="str">
-        <v>Trousdale</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L154" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Old Man</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:19</v>
+        <v>4:05</v>
       </c>
       <c r="H155" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Trousdale</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L155" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:56</v>
+        <v>3:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Denzel Curry</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L156" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Refuge</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G157" t="str">
-        <v>3:38</v>
+        <v>2:56</v>
       </c>
       <c r="H157" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L157" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Refuge</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>My Ego Told Me To</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G158" t="str">
-        <v>3:24</v>
+        <v>3:38</v>
       </c>
       <c r="H158" t="str">
-        <v>Leigh-Anne</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L158" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Smoke Screen</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Still There’s a Glow</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G159" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Sweet Pill</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L159" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G160" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H160" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Angel Wings</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:52</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>PRESIDENT</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L161" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Roamer</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:19</v>
+        <v>3:52</v>
       </c>
       <c r="H162" t="str">
-        <v>spill tab</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L162" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>These Nights</v>
+        <v>Roamer</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Everything Glows</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G163" t="str">
-        <v>4:39</v>
+        <v>2:19</v>
       </c>
       <c r="H163" t="str">
-        <v>Cannons</v>
+        <v>spill tab</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L163" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Locked and Loaded</v>
+        <v>These Nights</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G164" t="str">
-        <v>2:55</v>
+        <v>4:39</v>
       </c>
       <c r="H164" t="str">
-        <v>The Cab</v>
+        <v>Cannons</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L164" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Safe And Sound</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>EI8HT</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H165" t="str">
-        <v>Shinedown</v>
+        <v>The Cab</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L165" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Flinch</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Autopilot</v>
+        <v>EI8HT</v>
       </c>
       <c r="G166" t="str">
-        <v>2:15</v>
+        <v>3:21</v>
       </c>
       <c r="H166" t="str">
-        <v>alexsucks</v>
+        <v>Shinedown</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L166" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fall Up</v>
+        <v>Flinch</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Fall Up - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G167" t="str">
-        <v>3:10</v>
+        <v>2:15</v>
       </c>
       <c r="H167" t="str">
-        <v>VOILÀ</v>
+        <v>alexsucks</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L167" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>No Typo</v>
+        <v>Fall Up</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>1:43</v>
+        <v>3:10</v>
       </c>
       <c r="H168" t="str">
-        <v>Nasty C</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L168" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Desiree</v>
+        <v>No Typo</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Wings of Desire</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>1:43</v>
       </c>
       <c r="H169" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Nasty C</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L169" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Desiree</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Goliath</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G170" t="str">
-        <v>5:04</v>
+        <v>3:46</v>
       </c>
       <c r="H170" t="str">
-        <v>Exodus</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L170" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Nomad</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Loss</v>
+        <v>Goliath</v>
       </c>
       <c r="G171" t="str">
-        <v>5:30</v>
+        <v>5:04</v>
       </c>
       <c r="H171" t="str">
-        <v>Gaerea</v>
+        <v>Exodus</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L171" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Empty Words</v>
+        <v>Nomad</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Empty Words - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G172" t="str">
-        <v>2:32</v>
+        <v>5:30</v>
       </c>
       <c r="H172" t="str">
-        <v>Corey Kent</v>
+        <v>Gaerea</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L172" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Didn't Forget</v>
+        <v>Empty Words</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:48</v>
+        <v>2:32</v>
       </c>
       <c r="H173" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L173" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Euphoria</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Euphoria - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:14</v>
+        <v>3:48</v>
       </c>
       <c r="H174" t="str">
-        <v>Bluff City</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L174" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>hopeless romantic</v>
+        <v>Euphoria</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:03</v>
+        <v>2:14</v>
       </c>
       <c r="H175" t="str">
-        <v>kwn</v>
+        <v>Bluff City</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L175" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Stay Close</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Stay Close - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H176" t="str">
-        <v>Evelyn Cormier</v>
+        <v>kwn</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L176" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H177" t="str">
-        <v>lydi lynn</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L177" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>peace at last</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>peace at last - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G178" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H178" t="str">
-        <v>Aaron Cole</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L178" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Aguántame</v>
+        <v>peace at last</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Aguántame - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:08</v>
+        <v>2:34</v>
       </c>
       <c r="H179" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L179" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>Aguántame</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:40</v>
+        <v>2:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Codiciado</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L180" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:11</v>
+        <v>2:40</v>
       </c>
       <c r="H181" t="str">
-        <v>La Joaqui</v>
+        <v>Codiciado</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L181" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>V3n3n0</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:32</v>
+        <v>3:11</v>
       </c>
       <c r="H182" t="str">
-        <v>Esty</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L182" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Moth In The Headlights</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:23</v>
+        <v>2:32</v>
       </c>
       <c r="H183" t="str">
-        <v>The Pale White</v>
+        <v>Esty</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L183" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>lately in the void</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>lately in the void - EP</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G184" t="str">
-        <v>3:41</v>
+        <v>4:23</v>
       </c>
       <c r="H184" t="str">
-        <v>bad tuner</v>
+        <v>The Pale White</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L184" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>When I Fall in Love</v>
+        <v>lately in the void</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Nightjar</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>4:45</v>
+        <v>3:41</v>
       </c>
       <c r="H185" t="str">
-        <v>David Gray</v>
+        <v>bad tuner</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L185" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Repeat Offender</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>Nightjar</v>
       </c>
       <c r="G186" t="str">
-        <v>2:33</v>
+        <v>4:45</v>
       </c>
       <c r="H186" t="str">
-        <v>yeemz</v>
+        <v>David Gray</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L186" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Class Reunion</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:11</v>
+        <v>2:33</v>
       </c>
       <c r="H187" t="str">
-        <v>Beatrix</v>
+        <v>yeemz</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L187" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Promise Me</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Instant Comfort</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G188" t="str">
-        <v>5:34</v>
+        <v>4:11</v>
       </c>
       <c r="H188" t="str">
-        <v>Lucid Express</v>
+        <v>Beatrix</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L188" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Promise Me</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G189" t="str">
-        <v>3:33</v>
+        <v>5:34</v>
       </c>
       <c r="H189" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L189" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:19</v>
+        <v>3:33</v>
       </c>
       <c r="H190" t="str">
-        <v>Ray Vaughn</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L190" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>So Good</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>So Good - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:47</v>
+        <v>3:19</v>
       </c>
       <c r="H191" t="str">
-        <v>Ari Abdul</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L191" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>YDH</v>
+        <v>So Good</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>YDH - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:17</v>
+        <v>2:47</v>
       </c>
       <c r="H192" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L192" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Eucalyptus</v>
+        <v>YDH</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Porcelain</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H193" t="str">
-        <v>Peach PRC</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L193" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Pearls In The Trap</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G194" t="str">
-        <v>1:38</v>
+        <v>3:00</v>
       </c>
       <c r="H194" t="str">
-        <v>carolesdaughter</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L194" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>The Fever Mask</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:12</v>
+        <v>1:38</v>
       </c>
       <c r="H195" t="str">
-        <v>At The Gates</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L195" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Air's on Fire</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-23</v>
@@ -7823,68 +7823,106 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Location Lost</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G196" t="str">
-        <v>5:15</v>
+        <v>3:12</v>
       </c>
       <c r="H196" t="str">
-        <v>Failure</v>
+        <v>At The Gates</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L196" t="str">
-        <v>The Air's on Fire - Failure</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
+        <v>The Air's on Fire</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>Location Lost</v>
+      </c>
+      <c r="G197" t="str">
+        <v>5:15</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Failure</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+      </c>
+      <c r="L197" t="str">
+        <v>The Air's on Fire - Failure</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
         <v>To The Last Breath</v>
       </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
-      <c r="D197" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
+      <c r="D198" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
         <v>To The Last Breath - Single</v>
       </c>
-      <c r="G197" t="str">
+      <c r="G198" t="str">
         <v>4:57</v>
       </c>
-      <c r="H197" t="str">
+      <c r="H198" t="str">
         <v>Arch Enemy</v>
       </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
         <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
-      <c r="K197" t="str">
+      <c r="K198" t="str">
         <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
-      <c r="L197" t="str">
+      <c r="L198" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>מירי מסיקה – גידי</v>
       </c>
       <c r="B2" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/wuthering-heights-%d7%a6%d7%a8%d7%9c%d7%99-xcx/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%92%d7%99%d7%93%d7%99/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>Wuthering Heights הוא אלבום האולפן השביעי של צ'רלי XCX. האלבום נוצר כאלבום קונספט ופסקול נלווה לעיבוד הקולנועי של אמרלד פנל לרומן הקלאסי "אנקת גבהים" (מאת אמילי ברונטה), בכיכובם של מרגו רובי וג'ייקוב אלורד מדובר בשינוי כיוון דרסטי מבחינתה מעבר מאסתטיקה של פופ</v>
+        <v>"גידי” הוא שיר פופ דרמטי של שרון ליפשיץ משנות ה־80 שמגלם נשיות תיאטרלית, הנמצאת בסיטואציה של אהבה תלויה.החידוש של מירי מסיקה (במסגרת הסדרה "ריסט") לוקח את אותו טקסט טעון  ומלביש עליו אסתטיקה אלקטרונית עדכנית עם גרוב פאנקי ובס מודגש, מה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>Wuthering Heights צ'רלי XCX</v>
+        <v>מירי מסיקה – גידי</v>
       </c>
     </row>
     <row r="3">
@@ -477,7 +477,7 @@
         <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B3" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C3" t="str">
         <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
@@ -489,7 +489,7 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>22 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G3" t="str">
         <v>3:57</v>
@@ -933,7 +933,7 @@
         <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
         <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
@@ -945,7 +945,7 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
         <v>4:50</v>
@@ -971,7 +971,7 @@
         <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
         <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
@@ -983,7 +983,7 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
         <v>3:14</v>
@@ -1161,7 +1161,7 @@
         <v>Suburban Requiem</v>
       </c>
       <c r="B21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C21" t="str">
         <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
@@ -1173,7 +1173,7 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G21" t="str">
         <v>4:40</v>
@@ -3289,7 +3289,7 @@
         <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C77" t="str">
         <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
@@ -3301,7 +3301,7 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G77" t="str">
         <v>3:37</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
@@ -3471,7 +3471,7 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="82">

--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מירי מסיקה – גידי</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-20</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a8%d7%99-%d7%9e%d7%a1%d7%99%d7%a7%d7%94-%d7%92%d7%99%d7%93%d7%99/</v>
+        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"גידי” הוא שיר פופ דרמטי של שרון ליפשיץ משנות ה־80 שמגלם נשיות תיאטרלית, הנמצאת בסיטואציה של אהבה תלויה.החידוש של מירי מסיקה (במסגרת הסדרה "ריסט") לוקח את אותו טקסט טעון  ומלביש עליו אסתטיקה אלקטרונית עדכנית עם גרוב פאנקי ובס מודגש, מה</v>
+        <v>13:35</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -460,7 +460,7 @@
         <v/>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>אלבומים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מירי מסיקה – גידי</v>
+        <v>רותם כהן - הבן של נורית</v>
       </c>
     </row>
     <row r="3">
@@ -895,7 +895,7 @@
         <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
         <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
@@ -907,7 +907,7 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
         <v>3:20</v>
@@ -3438,7 +3438,7 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
@@ -3471,7 +3471,7 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="82">

--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-20</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://rotter.name/cgi-bin/nor/dcboard.cgi?az=show_thread&amp;om=24452&amp;forum=music&amp;viewmode=all</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>13:35</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>4:39</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>georgemichael</v>
       </c>
       <c r="I2" t="str">
-        <v>אלבומים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>רותם כהן - הבן של נורית</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 day ago</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:57</v>
+        <v>3:40</v>
       </c>
       <c r="H3" t="str">
-        <v>Self Esteem</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B4" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -530,10 +530,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G4" t="str">
-        <v>2:27</v>
+        <v>3:57</v>
       </c>
       <c r="H4" t="str">
-        <v>070 Shake</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B5" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -568,10 +568,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>4:49</v>
+        <v>2:27</v>
       </c>
       <c r="H5" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B6" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -603,10 +603,10 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>5:52</v>
+        <v>4:49</v>
       </c>
       <c r="H6" t="str">
         <v>georgemichael</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -644,10 +644,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>3:22</v>
+        <v>5:52</v>
       </c>
       <c r="H7" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B8" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -682,10 +682,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:08</v>
+        <v>3:22</v>
       </c>
       <c r="H8" t="str">
-        <v>Romeo Santos</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>7:31</v>
+        <v>4:08</v>
       </c>
       <c r="H9" t="str">
-        <v>Jacob Collier</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:21</v>
+        <v>7:31</v>
       </c>
       <c r="H10" t="str">
-        <v>Gabi Sklar</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:36</v>
+        <v>3:21</v>
       </c>
       <c r="H11" t="str">
-        <v>YUNGBLUD</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>5:06</v>
+        <v>4:36</v>
       </c>
       <c r="H12" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:17</v>
+        <v>5:06</v>
       </c>
       <c r="H13" t="str">
-        <v>Marc Anthony</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>3:20</v>
+        <v>4:17</v>
       </c>
       <c r="H14" t="str">
-        <v>georgemichael</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B15" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -948,10 +948,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:50</v>
+        <v>3:20</v>
       </c>
       <c r="H15" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B16" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -986,10 +986,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:14</v>
+        <v>4:50</v>
       </c>
       <c r="H16" t="str">
-        <v>Freya Ridings</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:37</v>
+        <v>3:14</v>
       </c>
       <c r="H17" t="str">
-        <v>Jessie Ware</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:16</v>
+        <v>4:37</v>
       </c>
       <c r="H18" t="str">
-        <v>Alan Walker</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:22</v>
+        <v>3:16</v>
       </c>
       <c r="H19" t="str">
-        <v>The Neighbourhood</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>3:45</v>
+        <v>4:22</v>
       </c>
       <c r="H20" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Suburban Requiem</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B21" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1173,10 +1173,10 @@
         <v/>
       </c>
       <c r="F21" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>4:40</v>
+        <v>3:45</v>
       </c>
       <c r="H21" t="str">
         <v>YUNGBLUD</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>3:02</v>
+        <v>4:40</v>
       </c>
       <c r="H22" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:12</v>
+        <v>3:02</v>
       </c>
       <c r="H23" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B24" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1290,10 +1290,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:38</v>
+        <v>3:12</v>
       </c>
       <c r="H24" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>4:40</v>
+        <v>3:38</v>
       </c>
       <c r="H25" t="str">
-        <v>Cannons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>2:57</v>
+        <v>4:40</v>
       </c>
       <c r="H26" t="str">
-        <v>Mimi Webb</v>
+        <v>Cannons</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:13</v>
+        <v>2:57</v>
       </c>
       <c r="H27" t="str">
-        <v>Jorja Smith</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:12</v>
+        <v>2:13</v>
       </c>
       <c r="H28" t="str">
-        <v>Sam Williams</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:55</v>
+        <v>4:12</v>
       </c>
       <c r="H29" t="str">
-        <v>YUNGBLUD</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>3:51</v>
+        <v>2:55</v>
       </c>
       <c r="H30" t="str">
-        <v>Megan Moroney</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>2:51</v>
+        <v>3:51</v>
       </c>
       <c r="H31" t="str">
-        <v>Nico Santos</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H32" t="str">
-        <v>REALITY CLUB</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>4:11</v>
+        <v>3:24</v>
       </c>
       <c r="H33" t="str">
-        <v>We Three</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>3:27</v>
+        <v>4:11</v>
       </c>
       <c r="H34" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>We Three</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:06</v>
+        <v>3:27</v>
       </c>
       <c r="H35" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:01</v>
+        <v>3:06</v>
       </c>
       <c r="H36" t="str">
-        <v>Peach PRC</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>5:38</v>
+        <v>3:01</v>
       </c>
       <c r="H37" t="str">
-        <v>georgemichael</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:43</v>
+        <v>5:38</v>
       </c>
       <c r="H38" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>georgemichael</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>2:58</v>
+        <v>3:43</v>
       </c>
       <c r="H39" t="str">
-        <v>Catie Turner</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>4:13</v>
+        <v>2:58</v>
       </c>
       <c r="H40" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>5:48</v>
+        <v>4:13</v>
       </c>
       <c r="H41" t="str">
-        <v>U2</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>3:55</v>
+        <v>5:48</v>
       </c>
       <c r="H42" t="str">
-        <v>Lawrence</v>
+        <v>U2</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>5:24</v>
+        <v>3:55</v>
       </c>
       <c r="H43" t="str">
-        <v>BUNT. Music</v>
+        <v>Lawrence</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>4:59</v>
+        <v>5:24</v>
       </c>
       <c r="H44" t="str">
-        <v>Bruno Mars</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>2:10</v>
+        <v>4:59</v>
       </c>
       <c r="H45" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B46" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2123,10 +2123,10 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>5 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>3:11</v>
+        <v>2:10</v>
       </c>
       <c r="H46" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:26</v>
+        <v>3:11</v>
       </c>
       <c r="H47" t="str">
-        <v>Neal Francis</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:35</v>
+        <v>4:26</v>
       </c>
       <c r="H48" t="str">
-        <v>mgk</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B49" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2240,10 +2240,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>2:09</v>
+        <v>4:35</v>
       </c>
       <c r="H49" t="str">
-        <v>Lola Young</v>
+        <v>mgk</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B50" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2275,13 +2275,13 @@
         <v/>
       </c>
       <c r="F50" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:11</v>
+        <v>2:09</v>
       </c>
       <c r="H50" t="str">
-        <v>Holly Humberstone</v>
+        <v>Lola Young</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B51" t="str">
         <v>6 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2316,10 +2316,10 @@
         <v>6 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>3:01</v>
+        <v>4:11</v>
       </c>
       <c r="H51" t="str">
-        <v>The Vaccines</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B52" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2354,10 +2354,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:28</v>
+        <v>3:01</v>
       </c>
       <c r="H52" t="str">
-        <v>mgk</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>5:31</v>
+        <v>3:28</v>
       </c>
       <c r="H53" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>mgk</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B54" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2430,10 +2430,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>2:49</v>
+        <v>5:31</v>
       </c>
       <c r="H54" t="str">
-        <v>Mýa</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B55" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2468,10 +2468,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:03</v>
+        <v>2:49</v>
       </c>
       <c r="H55" t="str">
-        <v>Michael Bolton</v>
+        <v>Mýa</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>2:59</v>
+        <v>3:03</v>
       </c>
       <c r="H56" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H57" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H58" t="str">
-        <v>ENHYPEN</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2620,10 +2620,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>3:59</v>
+        <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B60" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>7:48</v>
+        <v>3:59</v>
       </c>
       <c r="H60" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B61" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2696,10 +2696,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>3:10</v>
+        <v>7:48</v>
       </c>
       <c r="H61" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>5:57</v>
+        <v>3:10</v>
       </c>
       <c r="H62" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>2:25</v>
+        <v>5:57</v>
       </c>
       <c r="H63" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:19</v>
+        <v>2:25</v>
       </c>
       <c r="H64" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:38</v>
+        <v>3:19</v>
       </c>
       <c r="H65" t="str">
-        <v>mgk</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>4:05</v>
+        <v>3:38</v>
       </c>
       <c r="H66" t="str">
-        <v>Dermot Kennedy</v>
+        <v>mgk</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>5:46</v>
+        <v>4:05</v>
       </c>
       <c r="H67" t="str">
-        <v>Jacob Collier</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:25</v>
+        <v>5:46</v>
       </c>
       <c r="H68" t="str">
-        <v>Victor Ray</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>5:11</v>
+        <v>3:25</v>
       </c>
       <c r="H69" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>2:55</v>
+        <v>5:11</v>
       </c>
       <c r="H70" t="str">
-        <v>The Warning</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>4:54</v>
+        <v>2:55</v>
       </c>
       <c r="H71" t="str">
-        <v>The Offspring</v>
+        <v>The Warning</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:01</v>
+        <v>4:54</v>
       </c>
       <c r="H72" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Offspring</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>3:55</v>
+        <v>5:01</v>
       </c>
       <c r="H73" t="str">
-        <v>HAUSER</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:43</v>
+        <v>3:55</v>
       </c>
       <c r="H74" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>HAUSER</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B75" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>2:53</v>
+        <v>3:43</v>
       </c>
       <c r="H75" t="str">
-        <v>Ultra Records</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B76" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:30</v>
+        <v>2:53</v>
       </c>
       <c r="H76" t="str">
-        <v>Anja Kotar</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B77" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:37</v>
+        <v>3:30</v>
       </c>
       <c r="H77" t="str">
-        <v>Michael Bolton</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B78" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3342,10 +3342,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>4:10</v>
+        <v>3:37</v>
       </c>
       <c r="H78" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B79" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3380,10 +3380,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:06</v>
+        <v>4:10</v>
       </c>
       <c r="H79" t="str">
-        <v>Alan Walker</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:17</v>
+        <v>3:06</v>
       </c>
       <c r="H80" t="str">
-        <v>Bruno Mars</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:21</v>
+        <v>3:17</v>
       </c>
       <c r="H81" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>6:58</v>
+        <v>3:21</v>
       </c>
       <c r="H82" t="str">
-        <v>Eric Church</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:29</v>
+        <v>6:58</v>
       </c>
       <c r="H83" t="str">
-        <v>Meghan Trainor</v>
+        <v>Eric Church</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:14</v>
+        <v>3:29</v>
       </c>
       <c r="H84" t="str">
-        <v>Ally Salort</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:51</v>
+        <v>3:14</v>
       </c>
       <c r="H85" t="str">
-        <v>Will Swinton</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:10</v>
+        <v>3:51</v>
       </c>
       <c r="H86" t="str">
-        <v>elijah woods</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:26</v>
+        <v>3:10</v>
       </c>
       <c r="H87" t="str">
-        <v>Jackson Dean</v>
+        <v>elijah woods</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3722,10 +3722,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H88" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H89" t="str">
-        <v>Neil Sedaka</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:06</v>
+        <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Sofia Camara</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:04</v>
+        <v>3:06</v>
       </c>
       <c r="H91" t="str">
-        <v>Russell Dickerson</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:03</v>
+        <v>3:04</v>
       </c>
       <c r="H92" t="str">
-        <v>Celine Dion</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>2:38</v>
+        <v>3:03</v>
       </c>
       <c r="H93" t="str">
-        <v>Bebe Rexha</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:29</v>
+        <v>2:38</v>
       </c>
       <c r="H94" t="str">
-        <v>Caroline Jones</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>2:32</v>
+        <v>3:29</v>
       </c>
       <c r="H95" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>3:32</v>
+        <v>2:32</v>
       </c>
       <c r="H96" t="str">
-        <v>Ingrid Andress</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>2:51</v>
+        <v>3:32</v>
       </c>
       <c r="H97" t="str">
-        <v>MusicByKnox</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>3:38</v>
+        <v>2:51</v>
       </c>
       <c r="H98" t="str">
-        <v>Ella Langley</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:26</v>
+        <v>3:38</v>
       </c>
       <c r="H99" t="str">
-        <v>Nickless</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:57</v>
+        <v>3:26</v>
       </c>
       <c r="H100" t="str">
-        <v>Caroline Jones</v>
+        <v>Nickless</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>elijah woods - DNA (Official Lyric Video)</v>
+        <v>Caroline Jones - The Bridge (Lyric Video)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=NaCz8FdxJfI</v>
+        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:08</v>
+        <v>3:57</v>
       </c>
       <c r="H101" t="str">
-        <v>elijah woods</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>elijah woods - DNA (Official Lyric Video) - elijah woods</v>
+        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Ribbons + Taxes (Visualizer)</v>
+        <v>Badlands</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=EuPKFU3FM70</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G102" t="str">
-        <v>3:53</v>
+        <v>2:58</v>
       </c>
       <c r="H102" t="str">
-        <v>August Ponthier</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L102" t="str">
-        <v>Ribbons + Taxes (Visualizer) - August Ponthier</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Badlands</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Prizefighter</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>2:58</v>
+        <v>3:48</v>
       </c>
       <c r="H103" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L103" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>3:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Taylor Swift</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L104" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>ROSITA</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:54</v>
+        <v>4:05</v>
       </c>
       <c r="H105" t="str">
-        <v>Lana Del Rey</v>
+        <v>Tainy</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L105" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ROSITA</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>ROSITA - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G106" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H106" t="str">
-        <v>Tainy</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L106" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Ca$ino</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:52</v>
+        <v>2:52</v>
       </c>
       <c r="H107" t="str">
-        <v>Baby Keem</v>
+        <v>SZA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L107" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Medicine</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>2:52</v>
+        <v>3:11</v>
       </c>
       <c r="H108" t="str">
-        <v>SZA</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Medicine</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Cloud 9</v>
+        <v>luck... or something</v>
       </c>
       <c r="G109" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Megan Moroney</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L109" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Weather For Tennis</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>luck... or something</v>
+        <v>petal rock black</v>
       </c>
       <c r="G110" t="str">
-        <v>3:16</v>
+        <v>4:18</v>
       </c>
       <c r="H110" t="str">
-        <v>Hilary Duff</v>
+        <v>WILLOW</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L110" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ear to the cocoon</v>
+        <v>Drag Path</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>petal rock black</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:18</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L111" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag Path</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Drag Path - Single</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>3:55</v>
       </c>
       <c r="H112" t="str">
-        <v>twenty one pilots</v>
+        <v>U2</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L112" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Song Of The Future</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G113" t="str">
-        <v>3:55</v>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>U2</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L113" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Trimski</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:56</v>
+        <v>3:02</v>
       </c>
       <c r="H114" t="str">
-        <v>Foo Fighters</v>
+        <v>NAV</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L114" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trimski</v>
+        <v>Paracosm</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Trimski - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>3:23</v>
       </c>
       <c r="H115" t="str">
-        <v>NAV</v>
+        <v>Absolutely</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L115" t="str">
-        <v>Trimski - NAV</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Paracosm</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Paracosm</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:23</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Absolutely</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L116" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Casual Lady</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:14</v>
+        <v>4:18</v>
       </c>
       <c r="H117" t="str">
-        <v>flowerovlove</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L117" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G118" t="str">
-        <v>4:18</v>
+        <v>4:20</v>
       </c>
       <c r="H118" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Pulp</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L118" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Begging for Change</v>
+        <v>My Maker</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>HELP(2)</v>
+        <v>Ricochet</v>
       </c>
       <c r="G119" t="str">
-        <v>4:20</v>
+        <v>4:19</v>
       </c>
       <c r="H119" t="str">
-        <v>Pulp</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L119" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>My Maker</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ricochet</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:19</v>
+        <v>3:32</v>
       </c>
       <c r="H120" t="str">
-        <v>Snail Mail</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L120" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:32</v>
+        <v>4:27</v>
       </c>
       <c r="H121" t="str">
-        <v>Taylor Swift</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L121" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G122" t="str">
-        <v>4:27</v>
+        <v>3:33</v>
       </c>
       <c r="H122" t="str">
-        <v>CHVRCHES</v>
+        <v>Thundercat</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L122" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>She Knows Too Much</v>
+        <v>Tea Time</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Distracted</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:33</v>
+        <v>2:25</v>
       </c>
       <c r="H123" t="str">
-        <v>Thundercat</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L123" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tea Time</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Tea Time - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Yung Miami</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L124" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Save My Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>3:30</v>
       </c>
       <c r="H125" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L125" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Save My Love</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Save My Love - Single</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G126" t="str">
-        <v>3:30</v>
+        <v>3:46</v>
       </c>
       <c r="H126" t="str">
-        <v>Kygo</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L126" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G127" t="str">
-        <v>3:46</v>
+        <v>4:39</v>
       </c>
       <c r="H127" t="str">
-        <v>Omar Courtz</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L127" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Suburban Requiem</v>
+        <v>Good Grief</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Idols (Complete)</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G128" t="str">
-        <v>4:39</v>
+        <v>4:21</v>
       </c>
       <c r="H128" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L128" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Good Grief</v>
+        <v>Freak On</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:21</v>
+        <v>2:49</v>
       </c>
       <c r="H129" t="str">
-        <v>The Neighbourhood</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L129" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Freak On</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Freak On - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:49</v>
+        <v>3:32</v>
       </c>
       <c r="H130" t="str">
-        <v>Steve Aoki</v>
+        <v>deadmau5</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L130" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:32</v>
+        <v>3:55</v>
       </c>
       <c r="H131" t="str">
-        <v>deadmau5</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L131" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>3:55</v>
+        <v>2:42</v>
       </c>
       <c r="H132" t="str">
-        <v>Taylor Swift</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Yellow Eyes</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Jean</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:42</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Yebba</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L133" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Word On The Street</v>
+        <v>only the best</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Word On The Street - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H134" t="str">
-        <v>Luke Bryan</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L134" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>only the best</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>only the best - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H135" t="str">
-        <v>horsegiirL</v>
+        <v>Tiësto</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L135" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Beautiful Places</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:59</v>
+        <v>3:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Tiësto</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L136" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>STAMPEDE</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G137" t="str">
-        <v>3:09</v>
+        <v>3:10</v>
       </c>
       <c r="H137" t="str">
-        <v>Genesis Owusu</v>
+        <v>15 15</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L137" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Infinite Beach</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Mārara</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G138" t="str">
-        <v>3:10</v>
+        <v>3:41</v>
       </c>
       <c r="H138" t="str">
-        <v>15 15</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L138" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Championship Ring</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Want Blood</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>3:41</v>
+        <v>2:28</v>
       </c>
       <c r="H139" t="str">
-        <v>SleazyWorld Go</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L139" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Da Realest</v>
       </c>
       <c r="G140" t="str">
-        <v>2:28</v>
+        <v>1:51</v>
       </c>
       <c r="H140" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L140" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Da Realest</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:51</v>
+        <v>1:53</v>
       </c>
       <c r="H141" t="str">
-        <v>Babyfxce E</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L141" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Fine Shit</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Fine Shit - Single</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>1:53</v>
+        <v>2:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Real Boston Richey</v>
+        <v>Soulidified</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L142" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>What's Your Name</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G143" t="str">
-        <v>2:20</v>
+        <v>2:53</v>
       </c>
       <c r="H143" t="str">
-        <v>Soulidified</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L143" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Ends In Y</v>
+        <v>Bully</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:53</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Mimi Webb</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L144" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bully</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Bully - Single</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>3:16</v>
       </c>
       <c r="H145" t="str">
-        <v>Iris Copperman</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L145" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Ride</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G146" t="str">
-        <v>3:16</v>
+        <v>4:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Charles Leclerc</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L146" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ride</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Superbloom</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:39</v>
+        <v>4:18</v>
       </c>
       <c r="H147" t="str">
-        <v>Jessie Ware</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L147" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Arkansas Mud</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:18</v>
+        <v>2:10</v>
       </c>
       <c r="H148" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L148" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Don't Leave</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Don't Leave - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:10</v>
+        <v>2:31</v>
       </c>
       <c r="H149" t="str">
-        <v>Jorja Smith</v>
+        <v>JayDon</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L149" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>FLAMED UP</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:31</v>
+        <v>2:49</v>
       </c>
       <c r="H150" t="str">
-        <v>JayDon</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L150" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>3am in Paris</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>3am in Paris - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:49</v>
+        <v>5:13</v>
       </c>
       <c r="H151" t="str">
-        <v>Anais Cardot</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L151" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>Migajero</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>5:13</v>
+        <v>3:18</v>
       </c>
       <c r="H152" t="str">
-        <v>Elevation Worship</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L152" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Migajero</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Migajero - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:18</v>
+        <v>3:26</v>
       </c>
       <c r="H153" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L153" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Old Man</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:26</v>
+        <v>4:05</v>
       </c>
       <c r="H154" t="str">
-        <v>Taylor Swift</v>
+        <v>Trousdale</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L154" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Old Man</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Old Man - Single</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>4:05</v>
+        <v>3:19</v>
       </c>
       <c r="H155" t="str">
-        <v>Trousdale</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L155" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G156" t="str">
-        <v>3:19</v>
+        <v>2:56</v>
       </c>
       <c r="H156" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L156" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Refuge</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G157" t="str">
-        <v>2:56</v>
+        <v>3:38</v>
       </c>
       <c r="H157" t="str">
-        <v>Denzel Curry</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L157" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Refuge</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>The Weight of the Woods</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G158" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L158" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>Leigh-Anne</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L159" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Smoke Screen</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:51</v>
+        <v>3:21</v>
       </c>
       <c r="H160" t="str">
-        <v>Sweet Pill</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L160" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:21</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L161" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Angel Wings</v>
+        <v>Roamer</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Angel Wings - Single</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G162" t="str">
-        <v>3:52</v>
+        <v>2:19</v>
       </c>
       <c r="H162" t="str">
-        <v>PRESIDENT</v>
+        <v>spill tab</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L162" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Roamer</v>
+        <v>These Nights</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G163" t="str">
-        <v>2:19</v>
+        <v>4:39</v>
       </c>
       <c r="H163" t="str">
-        <v>spill tab</v>
+        <v>Cannons</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L163" t="str">
-        <v>Roamer - spill tab</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>These Nights</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everything Glows</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>2:55</v>
       </c>
       <c r="H164" t="str">
-        <v>Cannons</v>
+        <v>The Cab</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L164" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Locked and Loaded</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G165" t="str">
-        <v>2:55</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>The Cab</v>
+        <v>Shinedown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L165" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Safe And Sound</v>
+        <v>Flinch</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>EI8HT</v>
+        <v>Autopilot</v>
       </c>
       <c r="G166" t="str">
-        <v>3:21</v>
+        <v>2:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Shinedown</v>
+        <v>alexsucks</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L166" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Flinch</v>
+        <v>Fall Up</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Autopilot</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:15</v>
+        <v>3:10</v>
       </c>
       <c r="H167" t="str">
-        <v>alexsucks</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L167" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fall Up</v>
+        <v>No Typo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Fall Up - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G168" t="str">
-        <v>3:10</v>
+        <v>1:43</v>
       </c>
       <c r="H168" t="str">
-        <v>VOILÀ</v>
+        <v>Nasty C</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L168" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>No Typo</v>
+        <v>Desiree</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G169" t="str">
-        <v>1:43</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Nasty C</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L169" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Desiree</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Wings of Desire</v>
+        <v>Goliath</v>
       </c>
       <c r="G170" t="str">
-        <v>3:46</v>
+        <v>5:04</v>
       </c>
       <c r="H170" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Exodus</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L170" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Nomad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Goliath</v>
+        <v>Loss</v>
       </c>
       <c r="G171" t="str">
-        <v>5:04</v>
+        <v>5:30</v>
       </c>
       <c r="H171" t="str">
-        <v>Exodus</v>
+        <v>Gaerea</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L171" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Nomad</v>
+        <v>Empty Words</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Loss</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:30</v>
+        <v>2:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Gaerea</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L172" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Empty Words</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Empty Words - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:32</v>
+        <v>3:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Corey Kent</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L173" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Didn't Forget</v>
+        <v>Euphoria</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:48</v>
+        <v>2:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Bluff City</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L174" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Euphoria</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Euphoria - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:14</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>Bluff City</v>
+        <v>kwn</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L175" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>hopeless romantic</v>
+        <v>Stay Close</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>kwn</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L176" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Stay Close</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Stay Close - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G177" t="str">
-        <v>2:58</v>
+        <v>2:54</v>
       </c>
       <c r="H177" t="str">
-        <v>Evelyn Cormier</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L177" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Metamorphosis</v>
+        <v>peace at last</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Metamorphosis</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:54</v>
+        <v>2:34</v>
       </c>
       <c r="H178" t="str">
-        <v>lydi lynn</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L178" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>peace at last</v>
+        <v>Aguántame</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>peace at last - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:34</v>
+        <v>2:08</v>
       </c>
       <c r="H179" t="str">
-        <v>Aaron Cole</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L179" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Aguántame</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Aguántame - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:08</v>
+        <v>2:40</v>
       </c>
       <c r="H180" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Codiciado</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L180" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:40</v>
+        <v>3:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Codiciado</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L181" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NADA PERSONAL</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:11</v>
+        <v>2:32</v>
       </c>
       <c r="H182" t="str">
-        <v>La Joaqui</v>
+        <v>Esty</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L182" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>V3n3n0</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G183" t="str">
-        <v>2:32</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Esty</v>
+        <v>The Pale White</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L183" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Moth In The Headlights</v>
+        <v>lately in the void</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>4:23</v>
+        <v>3:41</v>
       </c>
       <c r="H184" t="str">
-        <v>The Pale White</v>
+        <v>bad tuner</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L184" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>lately in the void</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>lately in the void - EP</v>
+        <v>Nightjar</v>
       </c>
       <c r="G185" t="str">
-        <v>3:41</v>
+        <v>4:45</v>
       </c>
       <c r="H185" t="str">
-        <v>bad tuner</v>
+        <v>David Gray</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L185" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>When I Fall in Love</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Nightjar</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:45</v>
+        <v>2:33</v>
       </c>
       <c r="H186" t="str">
-        <v>David Gray</v>
+        <v>yeemz</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L186" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Repeat Offender</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G187" t="str">
-        <v>2:33</v>
+        <v>4:11</v>
       </c>
       <c r="H187" t="str">
-        <v>yeemz</v>
+        <v>Beatrix</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L187" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Class Reunion</v>
+        <v>Promise Me</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G188" t="str">
-        <v>4:11</v>
+        <v>5:34</v>
       </c>
       <c r="H188" t="str">
-        <v>Beatrix</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L188" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Promise Me</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Instant Comfort</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>5:34</v>
+        <v>3:33</v>
       </c>
       <c r="H189" t="str">
-        <v>Lucid Express</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L189" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:33</v>
+        <v>3:19</v>
       </c>
       <c r="H190" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L190" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>So Good</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:19</v>
+        <v>2:47</v>
       </c>
       <c r="H191" t="str">
-        <v>Ray Vaughn</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L191" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>So Good</v>
+        <v>YDH</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>So Good - Single</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:47</v>
+        <v>3:17</v>
       </c>
       <c r="H192" t="str">
-        <v>Ari Abdul</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L192" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>YDH</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>YDH - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G193" t="str">
-        <v>3:17</v>
+        <v>3:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Chloe Qisha</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L193" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Eucalyptus</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Porcelain</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:00</v>
+        <v>1:38</v>
       </c>
       <c r="H194" t="str">
-        <v>Peach PRC</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L194" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Pearls In The Trap</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G195" t="str">
-        <v>1:38</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>carolesdaughter</v>
+        <v>At The Gates</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L195" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Fever Mask</v>
+        <v>The Air's on Fire</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Location Lost</v>
       </c>
       <c r="G196" t="str">
-        <v>3:12</v>
+        <v>5:15</v>
       </c>
       <c r="H196" t="str">
-        <v>At The Gates</v>
+        <v>Failure</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
       </c>
       <c r="L196" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>The Air's on Fire - Failure</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>The Air's on Fire</v>
+        <v>To The Last Breath</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-23</v>
@@ -7861,68 +7861,30 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Location Lost</v>
+        <v>To The Last Breath - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>5:15</v>
+        <v>4:57</v>
       </c>
       <c r="H197" t="str">
-        <v>Failure</v>
+        <v>Arch Enemy</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
       <c r="L197" t="str">
-        <v>The Air's on Fire - Failure</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>To The Last Breath</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>To The Last Breath - Single</v>
-      </c>
-      <c r="G198" t="str">
-        <v>4:57</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Arch Enemy</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
-      </c>
-      <c r="L198" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L198"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>בר צברי – ראש לאריות</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%a8%d7%90%d7%a9-%d7%9c%d7%90%d7%a8%d7%99%d7%95%d7%aa/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v>השיר "ראש לאריות" של בר צברי נכתב לזכרו של לוחם הימ״מ ארנון זמורה ז״ל, שנהרג במבצע חילוץ בעזה במהלך מלחמת חרבות ברזל. זוהי בלדה אישית ואינטימית שהופכת מדמות פרטית – אדם, אב ובעל – לסמל של גבורה ישראלית. כבר מן</v>
       </c>
       <c r="G2" t="str">
-        <v>4:39</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>georgemichael</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>בר צברי – ראש לאריות</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
       </c>
       <c r="B3" t="str">
-        <v>4 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>4 hours ago</v>
+        <v>1 hour ago</v>
       </c>
       <c r="G3" t="str">
-        <v>3:40</v>
+        <v>5:32</v>
       </c>
       <c r="H3" t="str">
-        <v>Nothing But Thieves</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B4" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>3:57</v>
+        <v>4:39</v>
       </c>
       <c r="H4" t="str">
-        <v>Self Esteem</v>
+        <v>georgemichael</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v>6 hours ago</v>
       </c>
       <c r="G5" t="str">
-        <v>2:27</v>
+        <v>3:40</v>
       </c>
       <c r="H5" t="str">
-        <v>070 Shake</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>4:49</v>
+        <v>3:57</v>
       </c>
       <c r="H6" t="str">
-        <v>georgemichael</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G7" t="str">
-        <v>5:52</v>
+        <v>2:27</v>
       </c>
       <c r="H7" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -679,13 +679,13 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G8" t="str">
-        <v>3:22</v>
+        <v>4:49</v>
       </c>
       <c r="H8" t="str">
-        <v>Foo Fighters</v>
+        <v>georgemichael</v>
       </c>
       <c r="I8" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>4:08</v>
+        <v>5:52</v>
       </c>
       <c r="H9" t="str">
-        <v>Romeo Santos</v>
+        <v>georgemichael</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>7:31</v>
+        <v>3:22</v>
       </c>
       <c r="H10" t="str">
-        <v>Jacob Collier</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>3:21</v>
+        <v>4:08</v>
       </c>
       <c r="H11" t="str">
-        <v>Gabi Sklar</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>4:36</v>
+        <v>7:31</v>
       </c>
       <c r="H12" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B13" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -872,10 +872,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>5:06</v>
+        <v>3:21</v>
       </c>
       <c r="H13" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B14" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -910,10 +910,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:17</v>
+        <v>4:36</v>
       </c>
       <c r="H14" t="str">
-        <v>Marc Anthony</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>3:20</v>
+        <v>5:06</v>
       </c>
       <c r="H15" t="str">
-        <v>georgemichael</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:50</v>
+        <v>4:17</v>
       </c>
       <c r="H16" t="str">
-        <v>Cliff Richard</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:14</v>
+        <v>3:20</v>
       </c>
       <c r="H17" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:37</v>
+        <v>4:50</v>
       </c>
       <c r="H18" t="str">
-        <v>Jessie Ware</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:16</v>
+        <v>3:14</v>
       </c>
       <c r="H19" t="str">
-        <v>Alan Walker</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:22</v>
+        <v>4:37</v>
       </c>
       <c r="H20" t="str">
-        <v>The Neighbourhood</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:45</v>
+        <v>3:16</v>
       </c>
       <c r="H21" t="str">
-        <v>YUNGBLUD</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>Suburban Requiem</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B22" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1211,13 +1211,13 @@
         <v/>
       </c>
       <c r="F22" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:40</v>
+        <v>4:22</v>
       </c>
       <c r="H22" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B23" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1252,10 +1252,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:02</v>
+        <v>3:45</v>
       </c>
       <c r="H23" t="str">
-        <v>Calum Scott</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I23" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>3:12</v>
+        <v>4:40</v>
       </c>
       <c r="H24" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:38</v>
+        <v>3:02</v>
       </c>
       <c r="H25" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>4:40</v>
+        <v>3:12</v>
       </c>
       <c r="H26" t="str">
-        <v>Cannons</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>2:57</v>
+        <v>3:38</v>
       </c>
       <c r="H27" t="str">
-        <v>Mimi Webb</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>2:13</v>
+        <v>4:40</v>
       </c>
       <c r="H28" t="str">
-        <v>Jorja Smith</v>
+        <v>Cannons</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>4:12</v>
+        <v>2:57</v>
       </c>
       <c r="H29" t="str">
-        <v>Sam Williams</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:55</v>
+        <v>2:13</v>
       </c>
       <c r="H30" t="str">
-        <v>YUNGBLUD</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>3:51</v>
+        <v>4:12</v>
       </c>
       <c r="H31" t="str">
-        <v>Megan Moroney</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:51</v>
+        <v>2:55</v>
       </c>
       <c r="H32" t="str">
-        <v>Nico Santos</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:24</v>
+        <v>3:51</v>
       </c>
       <c r="H33" t="str">
-        <v>REALITY CLUB</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>4:11</v>
+        <v>2:51</v>
       </c>
       <c r="H34" t="str">
-        <v>We Three</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:27</v>
+        <v>3:24</v>
       </c>
       <c r="H35" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>3:06</v>
+        <v>4:11</v>
       </c>
       <c r="H36" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>We Three</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B37" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1784,10 +1784,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:01</v>
+        <v>3:27</v>
       </c>
       <c r="H37" t="str">
-        <v>Peach PRC</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>5:38</v>
+        <v>3:06</v>
       </c>
       <c r="H38" t="str">
-        <v>georgemichael</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:43</v>
+        <v>3:01</v>
       </c>
       <c r="H39" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>2:58</v>
+        <v>5:38</v>
       </c>
       <c r="H40" t="str">
-        <v>Catie Turner</v>
+        <v>georgemichael</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>4:13</v>
+        <v>3:43</v>
       </c>
       <c r="H41" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>5:48</v>
+        <v>2:58</v>
       </c>
       <c r="H42" t="str">
-        <v>U2</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>3:55</v>
+        <v>4:13</v>
       </c>
       <c r="H43" t="str">
-        <v>Lawrence</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:24</v>
+        <v>5:48</v>
       </c>
       <c r="H44" t="str">
-        <v>BUNT. Music</v>
+        <v>U2</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B45" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2088,10 +2088,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>4:59</v>
+        <v>3:55</v>
       </c>
       <c r="H45" t="str">
-        <v>Bruno Mars</v>
+        <v>Lawrence</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B46" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2126,10 +2126,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>2:10</v>
+        <v>5:24</v>
       </c>
       <c r="H46" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>3:11</v>
+        <v>4:59</v>
       </c>
       <c r="H47" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2202,10 +2202,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>4:26</v>
+        <v>2:10</v>
       </c>
       <c r="H48" t="str">
-        <v>Neal Francis</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I48" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B49" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2240,10 +2240,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>4:35</v>
+        <v>3:11</v>
       </c>
       <c r="H49" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B50" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2278,10 +2278,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>2:09</v>
+        <v>4:26</v>
       </c>
       <c r="H50" t="str">
-        <v>Lola Young</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B51" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2313,13 +2313,13 @@
         <v/>
       </c>
       <c r="F51" t="str">
-        <v>6 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:11</v>
+        <v>4:35</v>
       </c>
       <c r="H51" t="str">
-        <v>Holly Humberstone</v>
+        <v>mgk</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B52" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>7 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>3:01</v>
+        <v>2:09</v>
       </c>
       <c r="H52" t="str">
-        <v>The Vaccines</v>
+        <v>Lola Young</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B53" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>7 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>3:28</v>
+        <v>4:11</v>
       </c>
       <c r="H53" t="str">
-        <v>mgk</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2427,13 +2427,13 @@
         <v/>
       </c>
       <c r="F54" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>5:31</v>
+        <v>3:01</v>
       </c>
       <c r="H54" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>8 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>2:49</v>
+        <v>3:28</v>
       </c>
       <c r="H55" t="str">
-        <v>Mýa</v>
+        <v>mgk</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>3:03</v>
+        <v>5:31</v>
       </c>
       <c r="H56" t="str">
-        <v>Michael Bolton</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:59</v>
+        <v>2:49</v>
       </c>
       <c r="H57" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>Mýa</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>2:41</v>
+        <v>3:03</v>
       </c>
       <c r="H58" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2623,7 +2623,7 @@
         <v>2:59</v>
       </c>
       <c r="H59" t="str">
-        <v>ENHYPEN</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B60" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2658,10 +2658,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>3:59</v>
+        <v>2:41</v>
       </c>
       <c r="H60" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B61" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>9 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>7:48</v>
+        <v>2:59</v>
       </c>
       <c r="H61" t="str">
-        <v>The Doobie Brothers</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:10</v>
+        <v>3:59</v>
       </c>
       <c r="H62" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2772,7 +2772,7 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>5:57</v>
+        <v>7:48</v>
       </c>
       <c r="H63" t="str">
         <v>The Doobie Brothers</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>2:25</v>
+        <v>3:10</v>
       </c>
       <c r="H64" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>3:19</v>
+        <v>5:57</v>
       </c>
       <c r="H65" t="str">
-        <v>Michael Bolton</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>3:38</v>
+        <v>2:25</v>
       </c>
       <c r="H66" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>4:05</v>
+        <v>3:19</v>
       </c>
       <c r="H67" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>5:46</v>
+        <v>3:38</v>
       </c>
       <c r="H68" t="str">
-        <v>Jacob Collier</v>
+        <v>mgk</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>3:25</v>
+        <v>4:05</v>
       </c>
       <c r="H69" t="str">
-        <v>Victor Ray</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:11</v>
+        <v>5:46</v>
       </c>
       <c r="H70" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>2:55</v>
+        <v>3:25</v>
       </c>
       <c r="H71" t="str">
-        <v>The Warning</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>4:54</v>
+        <v>5:11</v>
       </c>
       <c r="H72" t="str">
-        <v>The Offspring</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>5:01</v>
+        <v>2:55</v>
       </c>
       <c r="H73" t="str">
-        <v>Caitlyn Smith</v>
+        <v>The Warning</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B74" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3190,10 +3190,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>3:55</v>
+        <v>4:54</v>
       </c>
       <c r="H74" t="str">
-        <v>HAUSER</v>
+        <v>The Offspring</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B75" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3228,10 +3228,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>3:43</v>
+        <v>5:01</v>
       </c>
       <c r="H75" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3263,13 +3263,13 @@
         <v/>
       </c>
       <c r="F76" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>2:53</v>
+        <v>3:55</v>
       </c>
       <c r="H76" t="str">
-        <v>Ultra Records</v>
+        <v>HAUSER</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B77" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3304,10 +3304,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:30</v>
+        <v>3:43</v>
       </c>
       <c r="H77" t="str">
-        <v>Anja Kotar</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B78" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>10 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G78" t="str">
-        <v>3:37</v>
+        <v>2:53</v>
       </c>
       <c r="H78" t="str">
-        <v>Michael Bolton</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>10 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>4:10</v>
+        <v>3:30</v>
       </c>
       <c r="H79" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:06</v>
+        <v>3:37</v>
       </c>
       <c r="H80" t="str">
-        <v>Alan Walker</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>3:17</v>
+        <v>4:10</v>
       </c>
       <c r="H81" t="str">
-        <v>Bruno Mars</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:21</v>
+        <v>3:06</v>
       </c>
       <c r="H82" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad (Official Visualizer) - Claire Rosinkranz</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>6:58</v>
+        <v>3:17</v>
       </c>
       <c r="H83" t="str">
-        <v>Eric Church</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:29</v>
+        <v>3:21</v>
       </c>
       <c r="H84" t="str">
-        <v>Meghan Trainor</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>3:14</v>
+        <v>6:58</v>
       </c>
       <c r="H85" t="str">
-        <v>Ally Salort</v>
+        <v>Eric Church</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:51</v>
+        <v>3:29</v>
       </c>
       <c r="H86" t="str">
-        <v>Will Swinton</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:10</v>
+        <v>3:14</v>
       </c>
       <c r="H87" t="str">
-        <v>elijah woods</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3722,10 +3722,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:26</v>
+        <v>3:51</v>
       </c>
       <c r="H88" t="str">
-        <v>Jackson Dean</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>2:51</v>
+        <v>3:10</v>
       </c>
       <c r="H89" t="str">
-        <v>Matteo Bocelli</v>
+        <v>elijah woods</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3801,7 +3801,7 @@
         <v>3:26</v>
       </c>
       <c r="H90" t="str">
-        <v>Neil Sedaka</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>3:06</v>
+        <v>2:51</v>
       </c>
       <c r="H91" t="str">
-        <v>Sofia Camara</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:04</v>
+        <v>3:26</v>
       </c>
       <c r="H92" t="str">
-        <v>Russell Dickerson</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:03</v>
+        <v>3:06</v>
       </c>
       <c r="H93" t="str">
-        <v>Celine Dion</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>2:38</v>
+        <v>3:04</v>
       </c>
       <c r="H94" t="str">
-        <v>Bebe Rexha</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:29</v>
+        <v>3:03</v>
       </c>
       <c r="H95" t="str">
-        <v>Caroline Jones</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:32</v>
+        <v>2:38</v>
       </c>
       <c r="H96" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:32</v>
+        <v>3:29</v>
       </c>
       <c r="H97" t="str">
-        <v>Ingrid Andress</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:51</v>
+        <v>2:32</v>
       </c>
       <c r="H98" t="str">
-        <v>MusicByKnox</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:38</v>
+        <v>3:32</v>
       </c>
       <c r="H99" t="str">
-        <v>Ella Langley</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H100" t="str">
-        <v>Nickless</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=NF9gahFiJEQ</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:57</v>
+        <v>3:38</v>
       </c>
       <c r="H101" t="str">
-        <v>Caroline Jones</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Caroline Jones - The Bridge (Lyric Video) - Caroline Jones</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Badlands</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B102" t="str">
-        <v/>
+        <v>10 days ago</v>
       </c>
       <c r="C102" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>Prizefighter</v>
+        <v>10 days ago</v>
       </c>
       <c r="G102" t="str">
-        <v>2:58</v>
+        <v>3:26</v>
       </c>
       <c r="H102" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Nickless</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v/>
       </c>
       <c r="K102" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v/>
       </c>
       <c r="L102" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>Badlands</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G103" t="str">
-        <v>3:48</v>
+        <v>2:58</v>
       </c>
       <c r="H103" t="str">
-        <v>Taylor Swift</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L103" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:54</v>
+        <v>3:48</v>
       </c>
       <c r="H104" t="str">
-        <v>Lana Del Rey</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L104" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>ROSITA</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>ROSITA - Single</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>4:05</v>
+        <v>3:54</v>
       </c>
       <c r="H105" t="str">
-        <v>Tainy</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L105" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>ROSITA</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>Ca$ino</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G106" t="str">
-        <v>3:52</v>
+        <v>4:05</v>
       </c>
       <c r="H106" t="str">
-        <v>Baby Keem</v>
+        <v>Tainy</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L106" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G107" t="str">
-        <v>2:52</v>
+        <v>3:52</v>
       </c>
       <c r="H107" t="str">
-        <v>SZA</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L107" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Medicine</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Cloud 9</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G108" t="str">
-        <v>3:11</v>
+        <v>2:52</v>
       </c>
       <c r="H108" t="str">
-        <v>Megan Moroney</v>
+        <v>SZA</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L108" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Weather For Tennis</v>
+        <v>Medicine</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>luck... or something</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G109" t="str">
-        <v>3:16</v>
+        <v>3:11</v>
       </c>
       <c r="H109" t="str">
-        <v>Hilary Duff</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L109" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>ear to the cocoon</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>petal rock black</v>
+        <v>luck... or something</v>
       </c>
       <c r="G110" t="str">
-        <v>4:18</v>
+        <v>3:16</v>
       </c>
       <c r="H110" t="str">
-        <v>WILLOW</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L110" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>Drag Path</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>Drag Path - Single</v>
+        <v>petal rock black</v>
       </c>
       <c r="G111" t="str">
-        <v>3:44</v>
+        <v>4:18</v>
       </c>
       <c r="H111" t="str">
-        <v>twenty one pilots</v>
+        <v>WILLOW</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L111" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Song Of The Future</v>
+        <v>Drag Path</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G112" t="str">
-        <v>3:55</v>
+        <v>3:44</v>
       </c>
       <c r="H112" t="str">
-        <v>U2</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L112" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G113" t="str">
-        <v>2:56</v>
+        <v>3:55</v>
       </c>
       <c r="H113" t="str">
-        <v>Foo Fighters</v>
+        <v>U2</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L113" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Trimski</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Trimski - Single</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G114" t="str">
-        <v>3:02</v>
+        <v>2:56</v>
       </c>
       <c r="H114" t="str">
-        <v>NAV</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L114" t="str">
-        <v>Trimski - NAV</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Paracosm</v>
+        <v>Trimski</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Paracosm</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G115" t="str">
-        <v>3:23</v>
+        <v>3:02</v>
       </c>
       <c r="H115" t="str">
-        <v>Absolutely</v>
+        <v>NAV</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L115" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Casual Lady</v>
+        <v>Paracosm</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G116" t="str">
-        <v>3:14</v>
+        <v>3:23</v>
       </c>
       <c r="H116" t="str">
-        <v>flowerovlove</v>
+        <v>Absolutely</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L116" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>4:18</v>
+        <v>3:14</v>
       </c>
       <c r="H117" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L117" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Begging for Change</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>HELP(2)</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G118" t="str">
-        <v>4:20</v>
+        <v>4:18</v>
       </c>
       <c r="H118" t="str">
-        <v>Pulp</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L118" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>My Maker</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>Ricochet</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G119" t="str">
-        <v>4:19</v>
+        <v>4:20</v>
       </c>
       <c r="H119" t="str">
-        <v>Snail Mail</v>
+        <v>Pulp</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L119" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>My Maker</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Ricochet</v>
       </c>
       <c r="G120" t="str">
-        <v>3:32</v>
+        <v>4:19</v>
       </c>
       <c r="H120" t="str">
-        <v>Taylor Swift</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L120" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>4:27</v>
+        <v>3:32</v>
       </c>
       <c r="H121" t="str">
-        <v>CHVRCHES</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L121" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>She Knows Too Much</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Distracted</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G122" t="str">
-        <v>3:33</v>
+        <v>4:27</v>
       </c>
       <c r="H122" t="str">
-        <v>Thundercat</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L122" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>Tea Time</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Tea Time - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G123" t="str">
-        <v>2:25</v>
+        <v>3:33</v>
       </c>
       <c r="H123" t="str">
-        <v>Yung Miami</v>
+        <v>Thundercat</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L123" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Tea Time</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G124" t="str">
-        <v>3:12</v>
+        <v>2:25</v>
       </c>
       <c r="H124" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L124" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>Save My Love</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Save My Love - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G125" t="str">
-        <v>3:30</v>
+        <v>3:12</v>
       </c>
       <c r="H125" t="str">
-        <v>Kygo</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L125" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Save My Love</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G126" t="str">
-        <v>3:46</v>
+        <v>3:30</v>
       </c>
       <c r="H126" t="str">
-        <v>Omar Courtz</v>
+        <v>Kygo</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L126" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>Suburban Requiem</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>Idols (Complete)</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G127" t="str">
-        <v>4:39</v>
+        <v>3:46</v>
       </c>
       <c r="H127" t="str">
-        <v>YUNGBLUD</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L127" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Good Grief</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G128" t="str">
-        <v>4:21</v>
+        <v>4:39</v>
       </c>
       <c r="H128" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L128" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Freak On</v>
+        <v>Good Grief</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>Freak On - Single</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G129" t="str">
-        <v>2:49</v>
+        <v>4:21</v>
       </c>
       <c r="H129" t="str">
-        <v>Steve Aoki</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L129" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Freak On</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>3:32</v>
+        <v>2:49</v>
       </c>
       <c r="H130" t="str">
-        <v>deadmau5</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L130" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:55</v>
+        <v>3:32</v>
       </c>
       <c r="H131" t="str">
-        <v>Taylor Swift</v>
+        <v>deadmau5</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L131" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Yellow Eyes</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Jean</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G132" t="str">
-        <v>2:42</v>
+        <v>3:55</v>
       </c>
       <c r="H132" t="str">
-        <v>Yebba</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L132" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Word On The Street</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Word On The Street - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G133" t="str">
-        <v>2:56</v>
+        <v>2:42</v>
       </c>
       <c r="H133" t="str">
-        <v>Luke Bryan</v>
+        <v>Yebba</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L133" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>only the best</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>only the best - Single</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>3:22</v>
+        <v>2:56</v>
       </c>
       <c r="H134" t="str">
-        <v>horsegiirL</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L134" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>Beautiful Places</v>
+        <v>only the best</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>2:59</v>
+        <v>3:22</v>
       </c>
       <c r="H135" t="str">
-        <v>Tiësto</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L135" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>STAMPEDE</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>3:09</v>
+        <v>2:59</v>
       </c>
       <c r="H136" t="str">
-        <v>Genesis Owusu</v>
+        <v>Tiësto</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L136" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>Infinite Beach</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>Mārara</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G137" t="str">
-        <v>3:10</v>
+        <v>3:09</v>
       </c>
       <c r="H137" t="str">
-        <v>15 15</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L137" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Championship Ring</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>I Want Blood</v>
+        <v>Mārara</v>
       </c>
       <c r="G138" t="str">
-        <v>3:41</v>
+        <v>3:10</v>
       </c>
       <c r="H138" t="str">
-        <v>SleazyWorld Go</v>
+        <v>15 15</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L138" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G139" t="str">
-        <v>2:28</v>
+        <v>3:41</v>
       </c>
       <c r="H139" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L139" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>Da Realest</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G140" t="str">
-        <v>1:51</v>
+        <v>2:28</v>
       </c>
       <c r="H140" t="str">
-        <v>Babyfxce E</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L140" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>Fine Shit</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Fine Shit - Single</v>
+        <v>Da Realest</v>
       </c>
       <c r="G141" t="str">
-        <v>1:53</v>
+        <v>1:51</v>
       </c>
       <c r="H141" t="str">
-        <v>Real Boston Richey</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L141" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>What's Your Name</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>2:20</v>
+        <v>1:53</v>
       </c>
       <c r="H142" t="str">
-        <v>Soulidified</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L142" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>Ends In Y</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G143" t="str">
-        <v>2:53</v>
+        <v>2:20</v>
       </c>
       <c r="H143" t="str">
-        <v>Mimi Webb</v>
+        <v>Soulidified</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L143" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Bully</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Bully - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G144" t="str">
-        <v>3:05</v>
+        <v>2:53</v>
       </c>
       <c r="H144" t="str">
-        <v>Iris Copperman</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L144" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Bully</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:16</v>
+        <v>3:05</v>
       </c>
       <c r="H145" t="str">
-        <v>Charles Leclerc</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L145" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>Ride</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>Superbloom</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G146" t="str">
-        <v>4:39</v>
+        <v>3:16</v>
       </c>
       <c r="H146" t="str">
-        <v>Jessie Ware</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L146" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Arkansas Mud</v>
+        <v>Ride</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G147" t="str">
-        <v>4:18</v>
+        <v>4:39</v>
       </c>
       <c r="H147" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L147" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Don't Leave</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Don't Leave - Single</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>2:10</v>
+        <v>4:18</v>
       </c>
       <c r="H148" t="str">
-        <v>Jorja Smith</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L148" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>FLAMED UP</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:31</v>
+        <v>2:10</v>
       </c>
       <c r="H149" t="str">
-        <v>JayDon</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L149" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>3am in Paris</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>3am in Paris - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:49</v>
+        <v>2:31</v>
       </c>
       <c r="H150" t="str">
-        <v>Anais Cardot</v>
+        <v>JayDon</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L150" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G151" t="str">
-        <v>5:13</v>
+        <v>2:49</v>
       </c>
       <c r="H151" t="str">
-        <v>Elevation Worship</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L151" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>Migajero</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>Migajero - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G152" t="str">
-        <v>3:18</v>
+        <v>5:13</v>
       </c>
       <c r="H152" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L152" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Migajero</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:26</v>
+        <v>3:18</v>
       </c>
       <c r="H153" t="str">
-        <v>Taylor Swift</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L153" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Old Man</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Old Man - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>4:05</v>
+        <v>3:26</v>
       </c>
       <c r="H154" t="str">
-        <v>Trousdale</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L154" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>Old Man</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>3:19</v>
+        <v>4:05</v>
       </c>
       <c r="H155" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Trousdale</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L155" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G156" t="str">
-        <v>2:56</v>
+        <v>3:19</v>
       </c>
       <c r="H156" t="str">
-        <v>Denzel Curry</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L156" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>Refuge</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>The Weight of the Woods</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G157" t="str">
-        <v>3:38</v>
+        <v>2:56</v>
       </c>
       <c r="H157" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L157" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Refuge</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>My Ego Told Me To</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G158" t="str">
-        <v>3:24</v>
+        <v>3:38</v>
       </c>
       <c r="H158" t="str">
-        <v>Leigh-Anne</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L158" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Smoke Screen</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>Still There’s a Glow</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G159" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H159" t="str">
-        <v>Sweet Pill</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L159" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G160" t="str">
-        <v>3:21</v>
+        <v>2:51</v>
       </c>
       <c r="H160" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L160" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Angel Wings</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Angel Wings - Single</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:52</v>
+        <v>3:21</v>
       </c>
       <c r="H161" t="str">
-        <v>PRESIDENT</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L161" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Roamer</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G162" t="str">
-        <v>2:19</v>
+        <v>3:52</v>
       </c>
       <c r="H162" t="str">
-        <v>spill tab</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L162" t="str">
-        <v>Roamer - spill tab</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>These Nights</v>
+        <v>Roamer</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>Everything Glows</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G163" t="str">
-        <v>4:39</v>
+        <v>2:19</v>
       </c>
       <c r="H163" t="str">
-        <v>Cannons</v>
+        <v>spill tab</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L163" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>Locked and Loaded</v>
+        <v>These Nights</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G164" t="str">
-        <v>2:55</v>
+        <v>4:39</v>
       </c>
       <c r="H164" t="str">
-        <v>The Cab</v>
+        <v>Cannons</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L164" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Safe And Sound</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>EI8HT</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G165" t="str">
-        <v>3:21</v>
+        <v>2:55</v>
       </c>
       <c r="H165" t="str">
-        <v>Shinedown</v>
+        <v>The Cab</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L165" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Flinch</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>Autopilot</v>
+        <v>EI8HT</v>
       </c>
       <c r="G166" t="str">
-        <v>2:15</v>
+        <v>3:21</v>
       </c>
       <c r="H166" t="str">
-        <v>alexsucks</v>
+        <v>Shinedown</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L166" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Fall Up</v>
+        <v>Flinch</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Fall Up - Single</v>
+        <v>Autopilot</v>
       </c>
       <c r="G167" t="str">
-        <v>3:10</v>
+        <v>2:15</v>
       </c>
       <c r="H167" t="str">
-        <v>VOILÀ</v>
+        <v>alexsucks</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L167" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>No Typo</v>
+        <v>Fall Up</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G168" t="str">
-        <v>1:43</v>
+        <v>3:10</v>
       </c>
       <c r="H168" t="str">
-        <v>Nasty C</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L168" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>Desiree</v>
+        <v>No Typo</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Wings of Desire</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G169" t="str">
-        <v>3:46</v>
+        <v>1:43</v>
       </c>
       <c r="H169" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Nasty C</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L169" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Desiree</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Goliath</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G170" t="str">
-        <v>5:04</v>
+        <v>3:46</v>
       </c>
       <c r="H170" t="str">
-        <v>Exodus</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L170" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Nomad</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Loss</v>
+        <v>Goliath</v>
       </c>
       <c r="G171" t="str">
-        <v>5:30</v>
+        <v>5:04</v>
       </c>
       <c r="H171" t="str">
-        <v>Gaerea</v>
+        <v>Exodus</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L171" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Empty Words</v>
+        <v>Nomad</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Empty Words - Single</v>
+        <v>Loss</v>
       </c>
       <c r="G172" t="str">
-        <v>2:32</v>
+        <v>5:30</v>
       </c>
       <c r="H172" t="str">
-        <v>Corey Kent</v>
+        <v>Gaerea</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L172" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Didn't Forget</v>
+        <v>Empty Words</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>3:48</v>
+        <v>2:32</v>
       </c>
       <c r="H173" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L173" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Euphoria</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Euphoria - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>2:14</v>
+        <v>3:48</v>
       </c>
       <c r="H174" t="str">
-        <v>Bluff City</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L174" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>hopeless romantic</v>
+        <v>Euphoria</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>3:03</v>
+        <v>2:14</v>
       </c>
       <c r="H175" t="str">
-        <v>kwn</v>
+        <v>Bluff City</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L175" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>Stay Close</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>Stay Close - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>2:58</v>
+        <v>3:03</v>
       </c>
       <c r="H176" t="str">
-        <v>Evelyn Cormier</v>
+        <v>kwn</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L176" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Metamorphosis</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G177" t="str">
-        <v>2:54</v>
+        <v>2:58</v>
       </c>
       <c r="H177" t="str">
-        <v>lydi lynn</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L177" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>peace at last</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>peace at last - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G178" t="str">
-        <v>2:34</v>
+        <v>2:54</v>
       </c>
       <c r="H178" t="str">
-        <v>Aaron Cole</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L178" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>Aguántame</v>
+        <v>peace at last</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>Aguántame - Single</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:08</v>
+        <v>2:34</v>
       </c>
       <c r="H179" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L179" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>Aguántame</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:40</v>
+        <v>2:08</v>
       </c>
       <c r="H180" t="str">
-        <v>Codiciado</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L180" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>NADA PERSONAL</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>3:11</v>
+        <v>2:40</v>
       </c>
       <c r="H181" t="str">
-        <v>La Joaqui</v>
+        <v>Codiciado</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L181" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>V3n3n0</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>2:32</v>
+        <v>3:11</v>
       </c>
       <c r="H182" t="str">
-        <v>Esty</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L182" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>Moth In The Headlights</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G183" t="str">
-        <v>4:23</v>
+        <v>2:32</v>
       </c>
       <c r="H183" t="str">
-        <v>The Pale White</v>
+        <v>Esty</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L183" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>lately in the void</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>lately in the void - EP</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G184" t="str">
-        <v>3:41</v>
+        <v>4:23</v>
       </c>
       <c r="H184" t="str">
-        <v>bad tuner</v>
+        <v>The Pale White</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L184" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>When I Fall in Love</v>
+        <v>lately in the void</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>Nightjar</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G185" t="str">
-        <v>4:45</v>
+        <v>3:41</v>
       </c>
       <c r="H185" t="str">
-        <v>David Gray</v>
+        <v>bad tuner</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L185" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>Repeat Offender</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>Nightjar</v>
       </c>
       <c r="G186" t="str">
-        <v>2:33</v>
+        <v>4:45</v>
       </c>
       <c r="H186" t="str">
-        <v>yeemz</v>
+        <v>David Gray</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L186" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Class Reunion</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G187" t="str">
-        <v>4:11</v>
+        <v>2:33</v>
       </c>
       <c r="H187" t="str">
-        <v>Beatrix</v>
+        <v>yeemz</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L187" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Promise Me</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>Instant Comfort</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G188" t="str">
-        <v>5:34</v>
+        <v>4:11</v>
       </c>
       <c r="H188" t="str">
-        <v>Lucid Express</v>
+        <v>Beatrix</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L188" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Promise Me</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G189" t="str">
-        <v>3:33</v>
+        <v>5:34</v>
       </c>
       <c r="H189" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L189" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:19</v>
+        <v>3:33</v>
       </c>
       <c r="H190" t="str">
-        <v>Ray Vaughn</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L190" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>So Good</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>So Good - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>2:47</v>
+        <v>3:19</v>
       </c>
       <c r="H191" t="str">
-        <v>Ari Abdul</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L191" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>YDH</v>
+        <v>So Good</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>YDH - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>3:17</v>
+        <v>2:47</v>
       </c>
       <c r="H192" t="str">
-        <v>Chloe Qisha</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L192" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>Eucalyptus</v>
+        <v>YDH</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>Porcelain</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G193" t="str">
-        <v>3:00</v>
+        <v>3:17</v>
       </c>
       <c r="H193" t="str">
-        <v>Peach PRC</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L193" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Pearls In The Trap</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G194" t="str">
-        <v>1:38</v>
+        <v>3:00</v>
       </c>
       <c r="H194" t="str">
-        <v>carolesdaughter</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L194" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>The Fever Mask</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G195" t="str">
-        <v>3:12</v>
+        <v>1:38</v>
       </c>
       <c r="H195" t="str">
-        <v>At The Gates</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L195" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Air's on Fire</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-23</v>
@@ -7823,68 +7823,106 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>Location Lost</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G196" t="str">
-        <v>5:15</v>
+        <v>3:12</v>
       </c>
       <c r="H196" t="str">
-        <v>Failure</v>
+        <v>At The Gates</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L196" t="str">
-        <v>The Air's on Fire - Failure</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
+        <v>The Air's on Fire</v>
+      </c>
+      <c r="B197" t="str">
+        <v/>
+      </c>
+      <c r="C197" t="str">
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+      </c>
+      <c r="D197" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E197" t="str">
+        <v/>
+      </c>
+      <c r="F197" t="str">
+        <v>Location Lost</v>
+      </c>
+      <c r="G197" t="str">
+        <v>5:15</v>
+      </c>
+      <c r="H197" t="str">
+        <v>Failure</v>
+      </c>
+      <c r="I197" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J197" t="str">
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
+      </c>
+      <c r="K197" t="str">
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+      </c>
+      <c r="L197" t="str">
+        <v>The Air's on Fire - Failure</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
         <v>To The Last Breath</v>
       </c>
-      <c r="B197" t="str">
-        <v/>
-      </c>
-      <c r="C197" t="str">
+      <c r="B198" t="str">
+        <v/>
+      </c>
+      <c r="C198" t="str">
         <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
-      <c r="D197" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E197" t="str">
-        <v/>
-      </c>
-      <c r="F197" t="str">
+      <c r="D198" t="str">
+        <v>2026-02-23</v>
+      </c>
+      <c r="E198" t="str">
+        <v/>
+      </c>
+      <c r="F198" t="str">
         <v>To The Last Breath - Single</v>
       </c>
-      <c r="G197" t="str">
+      <c r="G198" t="str">
         <v>4:57</v>
       </c>
-      <c r="H197" t="str">
+      <c r="H198" t="str">
         <v>Arch Enemy</v>
       </c>
-      <c r="I197" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J197" t="str">
+      <c r="I198" t="str">
+        <v>מוזיקה לועזית חדשה</v>
+      </c>
+      <c r="J198" t="str">
         <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
-      <c r="K197" t="str">
+      <c r="K198" t="str">
         <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
-      <c r="L197" t="str">
+      <c r="L198" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L198"/>
+  <dimension ref="A1:L197"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>בר צברי – ראש לאריות</v>
+        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-02-23</v>
+        <v>4 hours ago</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%91%d7%a8-%d7%a6%d7%91%d7%a8%d7%99-%d7%a8%d7%90%d7%a9-%d7%9c%d7%90%d7%a8%d7%99%d7%95%d7%aa/</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר "ראש לאריות" של בר צברי נכתב לזכרו של לוחם הימ״מ ארנון זמורה ז״ל, שנהרג במבצע חילוץ בעזה במהלך מלחמת חרבות ברזל. זוהי בלדה אישית ואינטימית שהופכת מדמות פרטית – אדם, אב ובעל – לסמל של גבורה ישראלית. כבר מן</v>
+        <v>4 hours ago</v>
       </c>
       <c r="G2" t="str">
-        <v/>
+        <v>5:32</v>
       </c>
       <c r="H2" t="str">
-        <v/>
+        <v>earMUSIC</v>
       </c>
       <c r="I2" t="str">
-        <v>סינגלים חדשים</v>
+        <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>בר צברי – ראש לאריות</v>
+        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B3" t="str">
-        <v>1 hour ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,13 +489,13 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>1 hour ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G3" t="str">
-        <v>5:32</v>
+        <v>4:39</v>
       </c>
       <c r="H3" t="str">
-        <v>earMUSIC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I3" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio) - earMUSIC</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B4" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -527,13 +527,13 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>6 hours ago</v>
+        <v>8 hours ago</v>
       </c>
       <c r="G4" t="str">
-        <v>4:39</v>
+        <v>3:40</v>
       </c>
       <c r="H4" t="str">
-        <v>georgemichael</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I4" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B5" t="str">
-        <v>6 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -565,13 +565,13 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>6 hours ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G5" t="str">
-        <v>3:40</v>
+        <v>3:57</v>
       </c>
       <c r="H5" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I5" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B6" t="str">
         <v>1 day ago</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -606,10 +606,10 @@
         <v>1 day ago</v>
       </c>
       <c r="G6" t="str">
-        <v>3:57</v>
+        <v>2:27</v>
       </c>
       <c r="H6" t="str">
-        <v>Self Esteem</v>
+        <v>070 Shake</v>
       </c>
       <c r="I6" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -641,13 +641,13 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G7" t="str">
-        <v>2:27</v>
+        <v>4:49</v>
       </c>
       <c r="H7" t="str">
-        <v>070 Shake</v>
+        <v>georgemichael</v>
       </c>
       <c r="I7" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -679,10 +679,10 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>1 day ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G8" t="str">
-        <v>4:49</v>
+        <v>5:52</v>
       </c>
       <c r="H8" t="str">
         <v>georgemichael</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B9" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -720,10 +720,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G9" t="str">
-        <v>5:52</v>
+        <v>3:22</v>
       </c>
       <c r="H9" t="str">
-        <v>georgemichael</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I9" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B10" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -758,10 +758,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G10" t="str">
-        <v>3:22</v>
+        <v>4:08</v>
       </c>
       <c r="H10" t="str">
-        <v>Foo Fighters</v>
+        <v>Romeo Santos</v>
       </c>
       <c r="I10" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
       </c>
       <c r="B11" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -796,10 +796,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G11" t="str">
-        <v>4:08</v>
+        <v>7:31</v>
       </c>
       <c r="H11" t="str">
-        <v>Romeo Santos</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I11" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>Gabi Sklar - Snowbird</v>
       </c>
       <c r="B12" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -834,10 +834,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G12" t="str">
-        <v>7:31</v>
+        <v>3:21</v>
       </c>
       <c r="H12" t="str">
-        <v>Jacob Collier</v>
+        <v>Gabi Sklar</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
       </c>
       <c r="B13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G13" t="str">
-        <v>3:21</v>
+        <v>4:36</v>
       </c>
       <c r="H13" t="str">
-        <v>Gabi Sklar</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>Chris Norman - Run (Official Video)</v>
       </c>
       <c r="B14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G14" t="str">
-        <v>4:36</v>
+        <v>5:06</v>
       </c>
       <c r="H14" t="str">
-        <v>YUNGBLUD</v>
+        <v>Chris Norman and STARS</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
       </c>
       <c r="B15" t="str">
         <v>2 days ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -948,10 +948,10 @@
         <v>2 days ago</v>
       </c>
       <c r="G15" t="str">
-        <v>5:06</v>
+        <v>4:17</v>
       </c>
       <c r="H15" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Marc Anthony</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
       </c>
       <c r="B16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>2 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>4:17</v>
+        <v>3:20</v>
       </c>
       <c r="H16" t="str">
-        <v>Marc Anthony</v>
+        <v>georgemichael</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
       </c>
       <c r="B17" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1024,10 +1024,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>3:20</v>
+        <v>4:50</v>
       </c>
       <c r="H17" t="str">
-        <v>georgemichael</v>
+        <v>Cliff Richard</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>Freya Ridings - Wild Horse (Official Video)</v>
       </c>
       <c r="B18" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1062,10 +1062,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>4:50</v>
+        <v>3:14</v>
       </c>
       <c r="H18" t="str">
-        <v>Cliff Richard</v>
+        <v>Freya Ridings</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>Jessie Ware - Ride</v>
       </c>
       <c r="B19" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1100,10 +1100,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>3:14</v>
+        <v>4:37</v>
       </c>
       <c r="H19" t="str">
-        <v>Freya Ridings</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>Jessie Ware - Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
       </c>
       <c r="B20" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C20" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
       </c>
       <c r="D20" t="str">
         <v>2026-02-23</v>
@@ -1138,10 +1138,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G20" t="str">
-        <v>4:37</v>
+        <v>3:16</v>
       </c>
       <c r="H20" t="str">
-        <v>Jessie Ware</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I20" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1153,18 +1153,18 @@
         <v/>
       </c>
       <c r="L20" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter)</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
       </c>
       <c r="B21" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C21" t="str">
-        <v>https://www.youtube.com/watch?v=n_gf7X8cBYg</v>
+        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
       </c>
       <c r="D21" t="str">
         <v>2026-02-23</v>
@@ -1176,10 +1176,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G21" t="str">
-        <v>3:16</v>
+        <v>4:22</v>
       </c>
       <c r="H21" t="str">
-        <v>Alan Walker</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I21" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1191,18 +1191,18 @@
         <v/>
       </c>
       <c r="L21" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - Old Habits (Walkerworld Final Chapter) - Alan Walker</v>
+        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video)</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
       </c>
       <c r="B22" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C22" t="str">
-        <v>https://www.youtube.com/watch?v=u48v3AdS4I0</v>
+        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
       </c>
       <c r="D22" t="str">
         <v>2026-02-23</v>
@@ -1214,10 +1214,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G22" t="str">
-        <v>4:22</v>
+        <v>3:45</v>
       </c>
       <c r="H22" t="str">
-        <v>The Neighbourhood</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I22" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1229,18 +1229,18 @@
         <v/>
       </c>
       <c r="L22" t="str">
-        <v>The Neighbourhood - Good Grief (Official Lyric Video) - The Neighbourhood</v>
+        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio)</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C23" t="str">
-        <v>https://www.youtube.com/watch?v=XBmwQuMzrsg</v>
+        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
       </c>
       <c r="D23" t="str">
         <v>2026-02-23</v>
@@ -1249,10 +1249,10 @@
         <v/>
       </c>
       <c r="F23" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G23" t="str">
-        <v>3:45</v>
+        <v>4:40</v>
       </c>
       <c r="H23" t="str">
         <v>YUNGBLUD</v>
@@ -1267,18 +1267,18 @@
         <v/>
       </c>
       <c r="L23" t="str">
-        <v>YUNGBLUD - War Pt. II (Official Audio) - YUNGBLUD</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>Suburban Requiem</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
       </c>
       <c r="B24" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="C24" t="str">
-        <v>https://www.youtube.com/watch?v=PqUBHqwWC-E</v>
+        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
       </c>
       <c r="D24" t="str">
         <v>2026-02-23</v>
@@ -1287,13 +1287,13 @@
         <v/>
       </c>
       <c r="F24" t="str">
-        <v>4 days ago</v>
+        <v>3 days ago</v>
       </c>
       <c r="G24" t="str">
-        <v>4:40</v>
+        <v>3:02</v>
       </c>
       <c r="H24" t="str">
-        <v>YUNGBLUD</v>
+        <v>Calum Scott</v>
       </c>
       <c r="I24" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1305,18 +1305,18 @@
         <v/>
       </c>
       <c r="L24" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version)</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
       </c>
       <c r="B25" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C25" t="str">
-        <v>https://www.youtube.com/watch?v=SXJyb6WZeys</v>
+        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
       </c>
       <c r="D25" t="str">
         <v>2026-02-23</v>
@@ -1328,10 +1328,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G25" t="str">
-        <v>3:02</v>
+        <v>3:12</v>
       </c>
       <c r="H25" t="str">
-        <v>Calum Scott</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I25" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1343,18 +1343,18 @@
         <v/>
       </c>
       <c r="L25" t="str">
-        <v>Calum Scott, Aitch - Unsteady (Aitch Version) - Calum Scott</v>
+        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video)</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
       </c>
       <c r="B26" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C26" t="str">
-        <v>https://www.youtube.com/watch?v=T7CBfaBTbvM</v>
+        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
       </c>
       <c r="D26" t="str">
         <v>2026-02-23</v>
@@ -1366,10 +1366,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G26" t="str">
-        <v>3:12</v>
+        <v>3:38</v>
       </c>
       <c r="H26" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I26" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1381,18 +1381,18 @@
         <v/>
       </c>
       <c r="L26" t="str">
-        <v>Mumford &amp; Sons, Chris Stapleton - Here (Lyric Video) - Mumford &amp; Sons</v>
+        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser)</v>
+        <v>Cannons - These Nights (Official Visualizer)</v>
       </c>
       <c r="B27" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C27" t="str">
-        <v>https://www.youtube.com/watch?v=LPaD1T8_6-c</v>
+        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
       </c>
       <c r="D27" t="str">
         <v>2026-02-23</v>
@@ -1404,10 +1404,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G27" t="str">
-        <v>3:38</v>
+        <v>4:40</v>
       </c>
       <c r="H27" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Cannons</v>
       </c>
       <c r="I27" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1419,18 +1419,18 @@
         <v/>
       </c>
       <c r="L27" t="str">
-        <v>Dermot Kennedy - Refuge (Official Visualiser) - Dermot Kennedy</v>
+        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="str">
-        <v>Cannons - These Nights (Official Visualizer)</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
       </c>
       <c r="B28" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C28" t="str">
-        <v>https://www.youtube.com/watch?v=E3oGl_DnLz8</v>
+        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
       </c>
       <c r="D28" t="str">
         <v>2026-02-23</v>
@@ -1442,10 +1442,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G28" t="str">
-        <v>4:40</v>
+        <v>2:57</v>
       </c>
       <c r="H28" t="str">
-        <v>Cannons</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I28" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1457,18 +1457,18 @@
         <v/>
       </c>
       <c r="L28" t="str">
-        <v>Cannons - These Nights (Official Visualizer) - Cannons</v>
+        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video)</v>
+        <v>Jorja Smith - Don't Leave</v>
       </c>
       <c r="B29" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C29" t="str">
-        <v>https://www.youtube.com/watch?v=B63wg4JXdtA</v>
+        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
       </c>
       <c r="D29" t="str">
         <v>2026-02-23</v>
@@ -1480,10 +1480,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G29" t="str">
-        <v>2:57</v>
+        <v>2:13</v>
       </c>
       <c r="H29" t="str">
-        <v>Mimi Webb</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I29" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1495,18 +1495,18 @@
         <v/>
       </c>
       <c r="L29" t="str">
-        <v>Mimi Webb - Ends In Y (Official Lyric Video) - Mimi Webb</v>
+        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="str">
-        <v>Jorja Smith - Don't Leave</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
       </c>
       <c r="B30" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C30" t="str">
-        <v>https://www.youtube.com/watch?v=54PhnOLr-tw</v>
+        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
       </c>
       <c r="D30" t="str">
         <v>2026-02-23</v>
@@ -1518,10 +1518,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G30" t="str">
-        <v>2:13</v>
+        <v>4:12</v>
       </c>
       <c r="H30" t="str">
-        <v>Jorja Smith</v>
+        <v>Sam Williams</v>
       </c>
       <c r="I30" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1533,18 +1533,18 @@
         <v/>
       </c>
       <c r="L30" t="str">
-        <v>Jorja Smith - Don't Leave - Jorja Smith</v>
+        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video)</v>
+        <v>YUNGBLUD - The Postman (Official Audio)</v>
       </c>
       <c r="B31" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C31" t="str">
-        <v>https://www.youtube.com/watch?v=4QAKD2qI8GY</v>
+        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
       </c>
       <c r="D31" t="str">
         <v>2026-02-23</v>
@@ -1556,10 +1556,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G31" t="str">
-        <v>4:12</v>
+        <v>2:55</v>
       </c>
       <c r="H31" t="str">
-        <v>Sam Williams</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I31" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1571,18 +1571,18 @@
         <v/>
       </c>
       <c r="L31" t="str">
-        <v>Sam Williams - The River Will Flow (Official Music Video) - Sam Williams</v>
+        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio)</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
       </c>
       <c r="B32" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C32" t="str">
-        <v>https://www.youtube.com/watch?v=0JRZMRZ-yEo</v>
+        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
       </c>
       <c r="D32" t="str">
         <v>2026-02-23</v>
@@ -1594,10 +1594,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G32" t="str">
-        <v>2:55</v>
+        <v>3:51</v>
       </c>
       <c r="H32" t="str">
-        <v>YUNGBLUD</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I32" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1609,18 +1609,18 @@
         <v/>
       </c>
       <c r="L32" t="str">
-        <v>YUNGBLUD - The Postman (Official Audio) - YUNGBLUD</v>
+        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video)</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
       </c>
       <c r="B33" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C33" t="str">
-        <v>https://www.youtube.com/watch?v=iJ2sRS8FkCs</v>
+        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
       </c>
       <c r="D33" t="str">
         <v>2026-02-23</v>
@@ -1632,10 +1632,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G33" t="str">
-        <v>3:51</v>
+        <v>2:51</v>
       </c>
       <c r="H33" t="str">
-        <v>Megan Moroney</v>
+        <v>Nico Santos</v>
       </c>
       <c r="I33" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1647,18 +1647,18 @@
         <v/>
       </c>
       <c r="L33" t="str">
-        <v>Megan Moroney - Wedding Dress (Official Lyric Video) - Megan Moroney</v>
+        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video)</v>
+        <v>Reality Club - Close to You (Official Lyric Video)</v>
       </c>
       <c r="B34" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C34" t="str">
-        <v>https://www.youtube.com/watch?v=0FuKD-jJFC4</v>
+        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
       </c>
       <c r="D34" t="str">
         <v>2026-02-23</v>
@@ -1670,10 +1670,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G34" t="str">
-        <v>2:51</v>
+        <v>3:24</v>
       </c>
       <c r="H34" t="str">
-        <v>Nico Santos</v>
+        <v>REALITY CLUB</v>
       </c>
       <c r="I34" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1685,18 +1685,18 @@
         <v/>
       </c>
       <c r="L34" t="str">
-        <v>Nico Santos &amp; Anne Mosters - Letting Go (Official Lyric Video) - Nico Santos</v>
+        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video)</v>
+        <v>We Three - Drops of Jupiter (Live Sessions)</v>
       </c>
       <c r="B35" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C35" t="str">
-        <v>https://www.youtube.com/watch?v=--5LF0iqCkc</v>
+        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
       </c>
       <c r="D35" t="str">
         <v>2026-02-23</v>
@@ -1708,10 +1708,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G35" t="str">
-        <v>3:24</v>
+        <v>4:11</v>
       </c>
       <c r="H35" t="str">
-        <v>REALITY CLUB</v>
+        <v>We Three</v>
       </c>
       <c r="I35" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1723,18 +1723,18 @@
         <v/>
       </c>
       <c r="L35" t="str">
-        <v>Reality Club - Close to You (Official Lyric Video) - REALITY CLUB</v>
+        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions)</v>
+        <v>Good Neighbours - The Buzz (Lyric Video)</v>
       </c>
       <c r="B36" t="str">
         <v>3 days ago</v>
       </c>
       <c r="C36" t="str">
-        <v>https://www.youtube.com/watch?v=PVBq14Mz0B0</v>
+        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
       </c>
       <c r="D36" t="str">
         <v>2026-02-23</v>
@@ -1746,10 +1746,10 @@
         <v>3 days ago</v>
       </c>
       <c r="G36" t="str">
-        <v>4:11</v>
+        <v>3:27</v>
       </c>
       <c r="H36" t="str">
-        <v>We Three</v>
+        <v>GOOD NEIGHBOURS</v>
       </c>
       <c r="I36" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1761,18 +1761,18 @@
         <v/>
       </c>
       <c r="L36" t="str">
-        <v>We Three - Drops of Jupiter (Live Sessions) - We Three</v>
+        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video)</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="C37" t="str">
-        <v>https://www.youtube.com/watch?v=3h2ZicF01qA</v>
+        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
       </c>
       <c r="D37" t="str">
         <v>2026-02-23</v>
@@ -1781,13 +1781,13 @@
         <v/>
       </c>
       <c r="F37" t="str">
-        <v>3 days ago</v>
+        <v>4 days ago</v>
       </c>
       <c r="G37" t="str">
-        <v>3:27</v>
+        <v>3:06</v>
       </c>
       <c r="H37" t="str">
-        <v>GOOD NEIGHBOURS</v>
+        <v>ROSÉ and Bruno Mars</v>
       </c>
       <c r="I37" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1799,18 +1799,18 @@
         <v/>
       </c>
       <c r="L37" t="str">
-        <v>Good Neighbours - The Buzz (Lyric Video) - GOOD NEIGHBOURS</v>
+        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards)</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
       </c>
       <c r="B38" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C38" t="str">
-        <v>https://www.youtube.com/watch?v=Dw3JSLBNf04</v>
+        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
       </c>
       <c r="D38" t="str">
         <v>2026-02-23</v>
@@ -1822,10 +1822,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G38" t="str">
-        <v>3:06</v>
+        <v>3:01</v>
       </c>
       <c r="H38" t="str">
-        <v>ROSÉ and Bruno Mars</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I38" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1837,18 +1837,18 @@
         <v/>
       </c>
       <c r="L38" t="str">
-        <v>ROSÉ &amp; Bruno Mars - APT. (Live at the 68th Annual Grammy Awards) - ROSÉ and Bruno Mars</v>
+        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser)</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
       </c>
       <c r="B39" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C39" t="str">
-        <v>https://www.youtube.com/watch?v=MjN2bMqamps</v>
+        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
       </c>
       <c r="D39" t="str">
         <v>2026-02-23</v>
@@ -1860,10 +1860,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G39" t="str">
-        <v>3:01</v>
+        <v>5:38</v>
       </c>
       <c r="H39" t="str">
-        <v>Peach PRC</v>
+        <v>georgemichael</v>
       </c>
       <c r="I39" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1875,18 +1875,18 @@
         <v/>
       </c>
       <c r="L39" t="str">
-        <v>Peach PRC - Eucalyptus (Official Visualiser) - Peach PRC</v>
+        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser)</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B40" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C40" t="str">
-        <v>https://www.youtube.com/watch?v=9-XXV-hxdmM</v>
+        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
       </c>
       <c r="D40" t="str">
         <v>2026-02-23</v>
@@ -1898,10 +1898,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G40" t="str">
-        <v>5:38</v>
+        <v>3:43</v>
       </c>
       <c r="H40" t="str">
-        <v>georgemichael</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I40" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1913,18 +1913,18 @@
         <v/>
       </c>
       <c r="L40" t="str">
-        <v>George Michael - Father Figure (Remastered - Official Visualiser) - georgemichael</v>
+        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs</v>
+        <v>Catie Turner - Hurt You Now (Official Audio)</v>
       </c>
       <c r="B41" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C41" t="str">
-        <v>https://www.youtube.com/watch?v=43K2pPExXms</v>
+        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
       </c>
       <c r="D41" t="str">
         <v>2026-02-23</v>
@@ -1936,10 +1936,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G41" t="str">
-        <v>3:43</v>
+        <v>2:58</v>
       </c>
       <c r="H41" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Catie Turner</v>
       </c>
       <c r="I41" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1951,18 +1951,18 @@
         <v/>
       </c>
       <c r="L41" t="str">
-        <v>Bruno Mars Performs “I Just Might” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio)</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
       </c>
       <c r="B42" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C42" t="str">
-        <v>https://www.youtube.com/watch?v=s2hrvN1ESho</v>
+        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
       </c>
       <c r="D42" t="str">
         <v>2026-02-23</v>
@@ -1974,10 +1974,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G42" t="str">
-        <v>2:58</v>
+        <v>4:13</v>
       </c>
       <c r="H42" t="str">
-        <v>Catie Turner</v>
+        <v>Sabrina Carpenter</v>
       </c>
       <c r="I42" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1989,18 +1989,18 @@
         <v/>
       </c>
       <c r="L42" t="str">
-        <v>Catie Turner - Hurt You Now (Official Audio) - Catie Turner</v>
+        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026)</v>
+        <v>U2 - The Tears Of Things (Lyric Video)</v>
       </c>
       <c r="B43" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C43" t="str">
-        <v>https://www.youtube.com/watch?v=7uEp74EuZSk</v>
+        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
       </c>
       <c r="D43" t="str">
         <v>2026-02-23</v>
@@ -2012,10 +2012,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G43" t="str">
-        <v>4:13</v>
+        <v>5:48</v>
       </c>
       <c r="H43" t="str">
-        <v>Sabrina Carpenter</v>
+        <v>U2</v>
       </c>
       <c r="I43" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2027,18 +2027,18 @@
         <v/>
       </c>
       <c r="L43" t="str">
-        <v>Sabrina Carpenter - Manchild (Live From The 68th Annual GRAMMY Awards / 2026) - Sabrina Carpenter</v>
+        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video)</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence</v>
       </c>
       <c r="B44" t="str">
         <v>4 days ago</v>
       </c>
       <c r="C44" t="str">
-        <v>https://www.youtube.com/watch?v=a4pBXzDPErQ</v>
+        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
       </c>
       <c r="D44" t="str">
         <v>2026-02-23</v>
@@ -2050,10 +2050,10 @@
         <v>4 days ago</v>
       </c>
       <c r="G44" t="str">
-        <v>5:48</v>
+        <v>3:55</v>
       </c>
       <c r="H44" t="str">
-        <v>U2</v>
+        <v>Lawrence</v>
       </c>
       <c r="I44" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2065,18 +2065,18 @@
         <v/>
       </c>
       <c r="L44" t="str">
-        <v>U2 - The Tears Of Things (Lyric Video) - U2</v>
+        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
       </c>
       <c r="B45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C45" t="str">
-        <v>https://www.youtube.com/watch?v=TU-yPbwQieI</v>
+        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
       </c>
       <c r="D45" t="str">
         <v>2026-02-23</v>
@@ -2085,13 +2085,13 @@
         <v/>
       </c>
       <c r="F45" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G45" t="str">
-        <v>3:55</v>
+        <v>5:24</v>
       </c>
       <c r="H45" t="str">
-        <v>Lawrence</v>
+        <v>BUNT. Music</v>
       </c>
       <c r="I45" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2103,18 +2103,18 @@
         <v/>
       </c>
       <c r="L45" t="str">
-        <v>Tomorrow (Live From Staycation) - Lawrence - Lawrence</v>
+        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition)</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
       </c>
       <c r="B46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="C46" t="str">
-        <v>https://www.youtube.com/watch?v=MOZa-WkYh8A</v>
+        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
       </c>
       <c r="D46" t="str">
         <v>2026-02-23</v>
@@ -2123,13 +2123,13 @@
         <v/>
       </c>
       <c r="F46" t="str">
-        <v>4 days ago</v>
+        <v>5 days ago</v>
       </c>
       <c r="G46" t="str">
-        <v>5:24</v>
+        <v>4:59</v>
       </c>
       <c r="H46" t="str">
-        <v>BUNT. Music</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I46" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2141,18 +2141,18 @@
         <v/>
       </c>
       <c r="L46" t="str">
-        <v>BUNT., The Temper Trap - What If You Fly (Sweet Disposition) - BUNT. Music</v>
+        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards)</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B47" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C47" t="str">
-        <v>https://www.youtube.com/watch?v=AnY9kgflPPk</v>
+        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
       </c>
       <c r="D47" t="str">
         <v>2026-02-23</v>
@@ -2164,10 +2164,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G47" t="str">
-        <v>4:59</v>
+        <v>2:10</v>
       </c>
       <c r="H47" t="str">
-        <v>Bruno Mars</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I47" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2179,18 +2179,18 @@
         <v/>
       </c>
       <c r="L47" t="str">
-        <v>Bruno Mars - I Just Might (Live at the 68th Annual Grammy Awards) - Bruno Mars</v>
+        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
       </c>
       <c r="B48" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C48" t="str">
-        <v>https://www.youtube.com/watch?v=0-Vv3sStmLU</v>
+        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
       </c>
       <c r="D48" t="str">
         <v>2026-02-23</v>
@@ -2202,7 +2202,7 @@
         <v>5 days ago</v>
       </c>
       <c r="G48" t="str">
-        <v>2:10</v>
+        <v>3:11</v>
       </c>
       <c r="H48" t="str">
         <v>Recording Academy / GRAMMYs</v>
@@ -2217,18 +2217,18 @@
         <v/>
       </c>
       <c r="L48" t="str">
-        <v>Olivia Dean Performs “Man I Need” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
       </c>
       <c r="B49" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C49" t="str">
-        <v>https://www.youtube.com/watch?v=VkYDixQ-Kd8</v>
+        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
       </c>
       <c r="D49" t="str">
         <v>2026-02-23</v>
@@ -2240,10 +2240,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G49" t="str">
-        <v>3:11</v>
+        <v>4:26</v>
       </c>
       <c r="H49" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Neal Francis</v>
       </c>
       <c r="I49" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2255,18 +2255,18 @@
         <v/>
       </c>
       <c r="L49" t="str">
-        <v>ROSÉ &amp; Bruno Mars Open The 2026 Grammys With A Rock-Fueled "APT." Performance - Recording Academy / GRAMMYs</v>
+        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed)</v>
+        <v>mgk - orpheus (Official Lyric Video)</v>
       </c>
       <c r="B50" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C50" t="str">
-        <v>https://www.youtube.com/watch?v=ZgpuGTU_thk</v>
+        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
       </c>
       <c r="D50" t="str">
         <v>2026-02-23</v>
@@ -2278,10 +2278,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G50" t="str">
-        <v>4:26</v>
+        <v>4:35</v>
       </c>
       <c r="H50" t="str">
-        <v>Neal Francis</v>
+        <v>mgk</v>
       </c>
       <c r="I50" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2293,18 +2293,18 @@
         <v/>
       </c>
       <c r="L50" t="str">
-        <v>Neal Francis - Broken Glass (Live at The Salt Shed) - Neal Francis</v>
+        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="str">
-        <v>mgk - orpheus (Official Lyric Video)</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
       </c>
       <c r="B51" t="str">
         <v>5 days ago</v>
       </c>
       <c r="C51" t="str">
-        <v>https://www.youtube.com/watch?v=WOP88DvphKs</v>
+        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
       </c>
       <c r="D51" t="str">
         <v>2026-02-23</v>
@@ -2316,10 +2316,10 @@
         <v>5 days ago</v>
       </c>
       <c r="G51" t="str">
-        <v>4:35</v>
+        <v>2:09</v>
       </c>
       <c r="H51" t="str">
-        <v>mgk</v>
+        <v>Lola Young</v>
       </c>
       <c r="I51" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2331,18 +2331,18 @@
         <v/>
       </c>
       <c r="L51" t="str">
-        <v>mgk - orpheus (Official Lyric Video) - mgk</v>
+        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026)</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
       </c>
       <c r="B52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="C52" t="str">
-        <v>https://www.youtube.com/watch?v=KEp8Y_0ugaw</v>
+        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
       </c>
       <c r="D52" t="str">
         <v>2026-02-23</v>
@@ -2351,13 +2351,13 @@
         <v/>
       </c>
       <c r="F52" t="str">
-        <v>5 days ago</v>
+        <v>6 days ago</v>
       </c>
       <c r="G52" t="str">
-        <v>2:09</v>
+        <v>4:11</v>
       </c>
       <c r="H52" t="str">
-        <v>Lola Young</v>
+        <v>Holly Humberstone</v>
       </c>
       <c r="I52" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2369,18 +2369,18 @@
         <v/>
       </c>
       <c r="L52" t="str">
-        <v>Lola Young - Messy (Live From The 68th Grammy Awards | 2026) - Lola Young</v>
+        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon")</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
       </c>
       <c r="B53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="C53" t="str">
-        <v>https://www.youtube.com/watch?v=TqL7_fRc51I</v>
+        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
       </c>
       <c r="D53" t="str">
         <v>2026-02-23</v>
@@ -2389,13 +2389,13 @@
         <v/>
       </c>
       <c r="F53" t="str">
-        <v>6 days ago</v>
+        <v>7 days ago</v>
       </c>
       <c r="G53" t="str">
-        <v>4:11</v>
+        <v>3:01</v>
       </c>
       <c r="H53" t="str">
-        <v>Holly Humberstone</v>
+        <v>The Vaccines</v>
       </c>
       <c r="I53" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2407,18 +2407,18 @@
         <v/>
       </c>
       <c r="L53" t="str">
-        <v>Holly Humberstone - To Love Somebody (Live On "The Tonight Show Starring Jimmy Fallon") - Holly Humberstone</v>
+        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio)</v>
+        <v>mgk - cant stay here (Official Lyric Video)</v>
       </c>
       <c r="B54" t="str">
         <v>7 days ago</v>
       </c>
       <c r="C54" t="str">
-        <v>https://www.youtube.com/watch?v=szY9mlhHdt4</v>
+        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
       </c>
       <c r="D54" t="str">
         <v>2026-02-23</v>
@@ -2430,10 +2430,10 @@
         <v>7 days ago</v>
       </c>
       <c r="G54" t="str">
-        <v>3:01</v>
+        <v>3:28</v>
       </c>
       <c r="H54" t="str">
-        <v>The Vaccines</v>
+        <v>mgk</v>
       </c>
       <c r="I54" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2445,18 +2445,18 @@
         <v/>
       </c>
       <c r="L54" t="str">
-        <v>The Vaccines - A Lack of Understanding (Official Audio) - The Vaccines</v>
+        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="str">
-        <v>mgk - cant stay here (Official Lyric Video)</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
       </c>
       <c r="B55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="C55" t="str">
-        <v>https://www.youtube.com/watch?v=6FCaMkvyHyU</v>
+        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
       </c>
       <c r="D55" t="str">
         <v>2026-02-23</v>
@@ -2465,13 +2465,13 @@
         <v/>
       </c>
       <c r="F55" t="str">
-        <v>7 days ago</v>
+        <v>8 days ago</v>
       </c>
       <c r="G55" t="str">
-        <v>3:28</v>
+        <v>5:31</v>
       </c>
       <c r="H55" t="str">
-        <v>mgk</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I55" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2483,18 +2483,18 @@
         <v/>
       </c>
       <c r="L55" t="str">
-        <v>mgk - cant stay here (Official Lyric Video) - mgk</v>
+        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video)</v>
       </c>
       <c r="B56" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C56" t="str">
-        <v>https://www.youtube.com/watch?v=dgvcgBleRr0</v>
+        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
       </c>
       <c r="D56" t="str">
         <v>2026-02-23</v>
@@ -2506,10 +2506,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G56" t="str">
-        <v>5:31</v>
+        <v>2:49</v>
       </c>
       <c r="H56" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Mýa</v>
       </c>
       <c r="I56" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2521,18 +2521,18 @@
         <v/>
       </c>
       <c r="L56" t="str">
-        <v>Post Malone, Slash and more Honor Ozzy Osbourne With “War Pigs” | In Memoriam at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="str">
-        <v>Mýa - ASAP (Official Music Video)</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
       </c>
       <c r="B57" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C57" t="str">
-        <v>https://www.youtube.com/watch?v=KAGfFAGQXfY</v>
+        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
       </c>
       <c r="D57" t="str">
         <v>2026-02-23</v>
@@ -2544,10 +2544,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G57" t="str">
-        <v>2:49</v>
+        <v>3:03</v>
       </c>
       <c r="H57" t="str">
-        <v>Mýa</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I57" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2559,18 +2559,18 @@
         <v/>
       </c>
       <c r="L57" t="str">
-        <v>Mýa - ASAP (Official Music Video) - Mýa</v>
+        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer)</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
       </c>
       <c r="B58" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C58" t="str">
-        <v>https://www.youtube.com/watch?v=Rft8YmGXY8w</v>
+        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
       </c>
       <c r="D58" t="str">
         <v>2026-02-23</v>
@@ -2582,10 +2582,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G58" t="str">
-        <v>3:03</v>
+        <v>2:59</v>
       </c>
       <c r="H58" t="str">
-        <v>Michael Bolton</v>
+        <v>The Happy Fits and Raina Mullen</v>
       </c>
       <c r="I58" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2597,18 +2597,18 @@
         <v/>
       </c>
       <c r="L58" t="str">
-        <v>Michael Bolton | Whatever She Wants (Official Visualizer) - Michael Bolton</v>
+        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
       </c>
       <c r="B59" t="str">
         <v>8 days ago</v>
       </c>
       <c r="C59" t="str">
-        <v>https://www.youtube.com/watch?v=4jcvnupWCfw</v>
+        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
       </c>
       <c r="D59" t="str">
         <v>2026-02-23</v>
@@ -2620,10 +2620,10 @@
         <v>8 days ago</v>
       </c>
       <c r="G59" t="str">
-        <v>2:59</v>
+        <v>2:41</v>
       </c>
       <c r="H59" t="str">
-        <v>The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS</v>
       </c>
       <c r="I59" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2635,18 +2635,18 @@
         <v/>
       </c>
       <c r="L59" t="str">
-        <v>The Happy Fits LIVE! - Let Them Fall (Raina Mullen Original) - Feb 13, 2026 - The Happy Fits and Raina Mullen</v>
+        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video)</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
       </c>
       <c r="B60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C60" t="str">
-        <v>https://www.youtube.com/watch?v=98wAhPJ2bYo</v>
+        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
       </c>
       <c r="D60" t="str">
         <v>2026-02-23</v>
@@ -2655,13 +2655,13 @@
         <v/>
       </c>
       <c r="F60" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G60" t="str">
-        <v>2:41</v>
+        <v>2:59</v>
       </c>
       <c r="H60" t="str">
-        <v>FULL CIRCLE BOYS</v>
+        <v>ENHYPEN</v>
       </c>
       <c r="I60" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2673,18 +2673,18 @@
         <v/>
       </c>
       <c r="L60" t="str">
-        <v>FULL CIRCLE BOYS - YOU SHOULD BE MINE (Lyric Video) - FULL CIRCLE BOYS</v>
+        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit)</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
       </c>
       <c r="B61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C61" t="str">
-        <v>https://www.youtube.com/watch?v=Mds7WAYiAck</v>
+        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
       </c>
       <c r="D61" t="str">
         <v>2026-02-23</v>
@@ -2693,13 +2693,13 @@
         <v/>
       </c>
       <c r="F61" t="str">
-        <v>8 days ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G61" t="str">
-        <v>2:59</v>
+        <v>3:59</v>
       </c>
       <c r="H61" t="str">
-        <v>ENHYPEN</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I61" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2711,18 +2711,18 @@
         <v/>
       </c>
       <c r="L61" t="str">
-        <v>ENHYPEN (엔하이픈) 'Stealer' MV (Special edit) - ENHYPEN</v>
+        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
       </c>
       <c r="B62" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C62" t="str">
-        <v>https://www.youtube.com/watch?v=hE13BJtbwIk</v>
+        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
       </c>
       <c r="D62" t="str">
         <v>2026-02-23</v>
@@ -2734,10 +2734,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G62" t="str">
-        <v>3:59</v>
+        <v>7:48</v>
       </c>
       <c r="H62" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I62" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2749,18 +2749,18 @@
         <v/>
       </c>
       <c r="L62" t="str">
-        <v>Watch Zara Larsson Perform A Gorgeous "Midnight Sun" | 2026 Grammy Awards Premiere Ceremony - Recording Academy / GRAMMYs</v>
+        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show)</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
       </c>
       <c r="B63" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C63" t="str">
-        <v>https://www.youtube.com/watch?v=-4bK8K-m22c</v>
+        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
       </c>
       <c r="D63" t="str">
         <v>2026-02-23</v>
@@ -2772,10 +2772,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G63" t="str">
-        <v>7:48</v>
+        <v>3:10</v>
       </c>
       <c r="H63" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Lauren Spencer Smith</v>
       </c>
       <c r="I63" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2787,18 +2787,18 @@
         <v/>
       </c>
       <c r="L63" t="str">
-        <v>The Doobie Brothers - Long Train Runnin' (Live from The Late Show) - The Doobie Brothers</v>
+        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer)</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
       </c>
       <c r="B64" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C64" t="str">
-        <v>https://www.youtube.com/watch?v=6sQVH-QhcI8</v>
+        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
       </c>
       <c r="D64" t="str">
         <v>2026-02-23</v>
@@ -2810,10 +2810,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G64" t="str">
-        <v>3:10</v>
+        <v>5:57</v>
       </c>
       <c r="H64" t="str">
-        <v>Lauren Spencer Smith</v>
+        <v>The Doobie Brothers</v>
       </c>
       <c r="I64" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2825,18 +2825,18 @@
         <v/>
       </c>
       <c r="L64" t="str">
-        <v>Lauren Spencer Smith - somebody you’re supposed to love (Visualizer) - Lauren Spencer Smith</v>
+        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show)</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
       </c>
       <c r="B65" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C65" t="str">
-        <v>https://www.youtube.com/watch?v=0EXCX91GHY4</v>
+        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
       </c>
       <c r="D65" t="str">
         <v>2026-02-23</v>
@@ -2848,10 +2848,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G65" t="str">
-        <v>5:57</v>
+        <v>2:25</v>
       </c>
       <c r="H65" t="str">
-        <v>The Doobie Brothers</v>
+        <v>Recording Academy / GRAMMYs</v>
       </c>
       <c r="I65" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2863,18 +2863,18 @@
         <v/>
       </c>
       <c r="L65" t="str">
-        <v>The Doobie Brothers - Listen to the Music (Live from The Late Show) - The Doobie Brothers</v>
+        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
       </c>
       <c r="B66" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C66" t="str">
-        <v>https://www.youtube.com/watch?v=QnxNUBb3Dfo</v>
+        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
       </c>
       <c r="D66" t="str">
         <v>2026-02-23</v>
@@ -2886,10 +2886,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G66" t="str">
-        <v>2:25</v>
+        <v>3:19</v>
       </c>
       <c r="H66" t="str">
-        <v>Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I66" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2901,18 +2901,18 @@
         <v/>
       </c>
       <c r="L66" t="str">
-        <v>KATSEYE Performs “Gnarly” LIVE at the 2026 GRAMMYs - Recording Academy / GRAMMYs</v>
+        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer)</v>
+        <v>mgk - starman (Official Lyric Video)</v>
       </c>
       <c r="B67" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C67" t="str">
-        <v>https://www.youtube.com/watch?v=TDOakF45zLg</v>
+        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
       </c>
       <c r="D67" t="str">
         <v>2026-02-23</v>
@@ -2924,10 +2924,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G67" t="str">
-        <v>3:19</v>
+        <v>3:38</v>
       </c>
       <c r="H67" t="str">
-        <v>Michael Bolton</v>
+        <v>mgk</v>
       </c>
       <c r="I67" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2939,18 +2939,18 @@
         <v/>
       </c>
       <c r="L67" t="str">
-        <v>Michael Bolton | Spark of Light (Official Visualizer) - Michael Bolton</v>
+        <v>mgk - starman (Official Lyric Video) - mgk</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="str">
-        <v>mgk - starman (Official Lyric Video)</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
       </c>
       <c r="B68" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C68" t="str">
-        <v>https://www.youtube.com/watch?v=GfprcnXlZYY</v>
+        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
       </c>
       <c r="D68" t="str">
         <v>2026-02-23</v>
@@ -2962,10 +2962,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G68" t="str">
-        <v>3:38</v>
+        <v>4:05</v>
       </c>
       <c r="H68" t="str">
-        <v>mgk</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I68" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -2977,18 +2977,18 @@
         <v/>
       </c>
       <c r="L68" t="str">
-        <v>mgk - starman (Official Lyric Video) - mgk</v>
+        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video)</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
       </c>
       <c r="B69" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C69" t="str">
-        <v>https://www.youtube.com/watch?v=IfYOENFt83I</v>
+        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
       </c>
       <c r="D69" t="str">
         <v>2026-02-23</v>
@@ -3000,10 +3000,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G69" t="str">
-        <v>4:05</v>
+        <v>5:46</v>
       </c>
       <c r="H69" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Jacob Collier</v>
       </c>
       <c r="I69" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3015,18 +3015,18 @@
         <v/>
       </c>
       <c r="L69" t="str">
-        <v>Dermot Kennedy - Funeral (Official Lyric Video) - Dermot Kennedy</v>
+        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video]</v>
+        <v>Victor Ray - Disappear (Official Music Video)</v>
       </c>
       <c r="B70" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C70" t="str">
-        <v>https://www.youtube.com/watch?v=4RNDueKyrKY</v>
+        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
       </c>
       <c r="D70" t="str">
         <v>2026-02-23</v>
@@ -3038,10 +3038,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G70" t="str">
-        <v>5:46</v>
+        <v>3:25</v>
       </c>
       <c r="H70" t="str">
-        <v>Jacob Collier</v>
+        <v>Victor Ray</v>
       </c>
       <c r="I70" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3053,18 +3053,18 @@
         <v/>
       </c>
       <c r="L70" t="str">
-        <v>Jacob Collier – Something Heavy [Official Music Video] - Jacob Collier</v>
+        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>Victor Ray - Disappear (Official Music Video)</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
       </c>
       <c r="B71" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C71" t="str">
-        <v>https://www.youtube.com/watch?v=a-1ZDZMI3qY</v>
+        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
       </c>
       <c r="D71" t="str">
         <v>2026-02-23</v>
@@ -3076,10 +3076,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G71" t="str">
-        <v>3:25</v>
+        <v>5:11</v>
       </c>
       <c r="H71" t="str">
-        <v>Victor Ray</v>
+        <v>PAUL McCARTNEY</v>
       </c>
       <c r="I71" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3091,18 +3091,18 @@
         <v/>
       </c>
       <c r="L71" t="str">
-        <v>Victor Ray - Disappear (Official Music Video) - Victor Ray</v>
+        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser)</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
       </c>
       <c r="B72" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C72" t="str">
-        <v>https://www.youtube.com/watch?v=Jwc3CQS5G3Y</v>
+        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
       </c>
       <c r="D72" t="str">
         <v>2026-02-23</v>
@@ -3114,10 +3114,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G72" t="str">
-        <v>5:11</v>
+        <v>2:55</v>
       </c>
       <c r="H72" t="str">
-        <v>PAUL McCARTNEY</v>
+        <v>The Warning</v>
       </c>
       <c r="I72" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3129,18 +3129,18 @@
         <v/>
       </c>
       <c r="L72" t="str">
-        <v>Paul McCartney &amp; Wings - Let 'Em In (Visualiser) - PAUL McCARTNEY</v>
+        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video)</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
       </c>
       <c r="B73" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C73" t="str">
-        <v>https://www.youtube.com/watch?v=bx9AUS4Titw</v>
+        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
       </c>
       <c r="D73" t="str">
         <v>2026-02-23</v>
@@ -3152,10 +3152,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G73" t="str">
-        <v>2:55</v>
+        <v>4:54</v>
       </c>
       <c r="H73" t="str">
-        <v>The Warning</v>
+        <v>The Offspring</v>
       </c>
       <c r="I73" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3167,18 +3167,18 @@
         <v/>
       </c>
       <c r="L73" t="str">
-        <v>The Warning, Carín León - Love To Be Loved (Performance Video) - The Warning</v>
+        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026)</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
       </c>
       <c r="B74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C74" t="str">
-        <v>https://www.youtube.com/watch?v=HFnDI-xRTNA</v>
+        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
       </c>
       <c r="D74" t="str">
         <v>2026-02-23</v>
@@ -3187,13 +3187,13 @@
         <v/>
       </c>
       <c r="F74" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G74" t="str">
-        <v>4:54</v>
+        <v>5:01</v>
       </c>
       <c r="H74" t="str">
-        <v>The Offspring</v>
+        <v>Caitlyn Smith</v>
       </c>
       <c r="I74" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3205,18 +3205,18 @@
         <v/>
       </c>
       <c r="L74" t="str">
-        <v>The Offspring - Gone Away | Live in Calgary, AB (2026) - The Offspring</v>
+        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer)</v>
+        <v>HAUSER – You Raise Me Up</v>
       </c>
       <c r="B75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C75" t="str">
-        <v>https://www.youtube.com/watch?v=hd-PnKb4pCM</v>
+        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
       </c>
       <c r="D75" t="str">
         <v>2026-02-23</v>
@@ -3225,13 +3225,13 @@
         <v/>
       </c>
       <c r="F75" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G75" t="str">
-        <v>5:01</v>
+        <v>3:55</v>
       </c>
       <c r="H75" t="str">
-        <v>Caitlyn Smith</v>
+        <v>HAUSER</v>
       </c>
       <c r="I75" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3243,18 +3243,18 @@
         <v/>
       </c>
       <c r="L75" t="str">
-        <v>Caitlyn Smith - Circling Around It (Official Visualizer) - Caitlyn Smith</v>
+        <v>HAUSER – You Raise Me Up - HAUSER</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>HAUSER – You Raise Me Up</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
       </c>
       <c r="B76" t="str">
         <v>9 days ago</v>
       </c>
       <c r="C76" t="str">
-        <v>https://www.youtube.com/watch?v=U5juor5xiVQ</v>
+        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
       </c>
       <c r="D76" t="str">
         <v>2026-02-23</v>
@@ -3266,10 +3266,10 @@
         <v>9 days ago</v>
       </c>
       <c r="G76" t="str">
-        <v>3:55</v>
+        <v>3:43</v>
       </c>
       <c r="H76" t="str">
-        <v>HAUSER</v>
+        <v>Jillian Jacqueline</v>
       </c>
       <c r="I76" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3281,18 +3281,18 @@
         <v/>
       </c>
       <c r="L76" t="str">
-        <v>HAUSER – You Raise Me Up - HAUSER</v>
+        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video)</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
       </c>
       <c r="B77" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="C77" t="str">
-        <v>https://www.youtube.com/watch?v=eqYjA3UIl78</v>
+        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
       </c>
       <c r="D77" t="str">
         <v>2026-02-23</v>
@@ -3301,13 +3301,13 @@
         <v/>
       </c>
       <c r="F77" t="str">
-        <v>9 days ago</v>
+        <v>2 weeks ago</v>
       </c>
       <c r="G77" t="str">
-        <v>3:43</v>
+        <v>2:53</v>
       </c>
       <c r="H77" t="str">
-        <v>Jillian Jacqueline</v>
+        <v>Ultra Records</v>
       </c>
       <c r="I77" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3319,18 +3319,18 @@
         <v/>
       </c>
       <c r="L77" t="str">
-        <v>Jillian Jacqueline - Another Lover (Official Video) - Jillian Jacqueline</v>
+        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records]</v>
+        <v>The Art Of Letting Go (group music video)</v>
       </c>
       <c r="B78" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="C78" t="str">
-        <v>https://www.youtube.com/watch?v=KoTaher3w90</v>
+        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
       </c>
       <c r="D78" t="str">
         <v>2026-02-23</v>
@@ -3339,13 +3339,13 @@
         <v/>
       </c>
       <c r="F78" t="str">
-        <v>2 weeks ago</v>
+        <v>9 days ago</v>
       </c>
       <c r="G78" t="str">
-        <v>2:53</v>
+        <v>3:30</v>
       </c>
       <c r="H78" t="str">
-        <v>Ultra Records</v>
+        <v>Anja Kotar</v>
       </c>
       <c r="I78" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3357,18 +3357,18 @@
         <v/>
       </c>
       <c r="L78" t="str">
-        <v>Alex Mills - Deeper Than Love [Ultra Records] - Ultra Records</v>
+        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="str">
-        <v>The Art Of Letting Go (group music video)</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
       </c>
       <c r="B79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="C79" t="str">
-        <v>https://www.youtube.com/watch?v=1CryACYe9OM</v>
+        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
       </c>
       <c r="D79" t="str">
         <v>2026-02-23</v>
@@ -3377,13 +3377,13 @@
         <v/>
       </c>
       <c r="F79" t="str">
-        <v>9 days ago</v>
+        <v>10 days ago</v>
       </c>
       <c r="G79" t="str">
-        <v>3:30</v>
+        <v>3:37</v>
       </c>
       <c r="H79" t="str">
-        <v>Anja Kotar</v>
+        <v>Michael Bolton</v>
       </c>
       <c r="I79" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3395,18 +3395,18 @@
         <v/>
       </c>
       <c r="L79" t="str">
-        <v>The Art Of Letting Go (group music video) - Anja Kotar</v>
+        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer)</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
       </c>
       <c r="B80" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C80" t="str">
-        <v>https://www.youtube.com/watch?v=TYy1Is8tzuI</v>
+        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
       </c>
       <c r="D80" t="str">
         <v>2026-02-23</v>
@@ -3418,10 +3418,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G80" t="str">
-        <v>3:37</v>
+        <v>4:10</v>
       </c>
       <c r="H80" t="str">
-        <v>Michael Bolton</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I80" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3433,18 +3433,18 @@
         <v/>
       </c>
       <c r="L80" t="str">
-        <v>Michael Bolton &amp; Dolly Parton | I Will Always Love You (Official Visualizer) - Michael Bolton</v>
+        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018)</v>
+        <v>Alan Walker - Adagio (Official Lyric Video)</v>
       </c>
       <c r="B81" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C81" t="str">
-        <v>https://www.youtube.com/watch?v=WSqo_Qcj7UM</v>
+        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
       </c>
       <c r="D81" t="str">
         <v>2026-02-23</v>
@@ -3456,10 +3456,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G81" t="str">
-        <v>4:10</v>
+        <v>3:06</v>
       </c>
       <c r="H81" t="str">
-        <v>Nothing But Thieves</v>
+        <v>Alan Walker</v>
       </c>
       <c r="I81" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3471,18 +3471,18 @@
         <v/>
       </c>
       <c r="L81" t="str">
-        <v>Nothing But Thieves - I Was Just a Kid (Live from TRNSMT Festival, 2018) - Nothing But Thieves</v>
+        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video)</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
       </c>
       <c r="B82" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C82" t="str">
-        <v>https://www.youtube.com/watch?v=_oDJbLVySkY</v>
+        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
       </c>
       <c r="D82" t="str">
         <v>2026-02-23</v>
@@ -3494,10 +3494,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G82" t="str">
-        <v>3:06</v>
+        <v>3:17</v>
       </c>
       <c r="H82" t="str">
-        <v>Alan Walker</v>
+        <v>Bruno Mars</v>
       </c>
       <c r="I82" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3509,18 +3509,18 @@
         <v/>
       </c>
       <c r="L82" t="str">
-        <v>Alan Walker - Adagio (Official Lyric Video) - Alan Walker</v>
+        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio]</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
       </c>
       <c r="B83" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C83" t="str">
-        <v>https://www.youtube.com/watch?v=OTrCs1Cm9Mc</v>
+        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
       </c>
       <c r="D83" t="str">
         <v>2026-02-23</v>
@@ -3532,10 +3532,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G83" t="str">
-        <v>3:17</v>
+        <v>3:21</v>
       </c>
       <c r="H83" t="str">
-        <v>Bruno Mars</v>
+        <v>Claire Rosinkranz</v>
       </c>
       <c r="I83" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3547,18 +3547,18 @@
         <v/>
       </c>
       <c r="L83" t="str">
-        <v>Bruno Mars - I Just Might (Austin Millz Remix) [Official Audio] - Bruno Mars</v>
+        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
       </c>
       <c r="B84" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C84" t="str">
-        <v>https://www.youtube.com/watch?v=UtluJloE_UQ</v>
+        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
       </c>
       <c r="D84" t="str">
         <v>2026-02-23</v>
@@ -3570,10 +3570,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G84" t="str">
-        <v>3:21</v>
+        <v>6:58</v>
       </c>
       <c r="H84" t="str">
-        <v>Claire Rosinkranz</v>
+        <v>Eric Church</v>
       </c>
       <c r="I84" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3585,18 +3585,18 @@
         <v/>
       </c>
       <c r="L84" t="str">
-        <v>Claire Rosinkranz - I Wanna Be In Love So Bad - Claire Rosinkranz</v>
+        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025)</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
       </c>
       <c r="B85" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C85" t="str">
-        <v>https://www.youtube.com/watch?v=kPgC8BBFixE</v>
+        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
       </c>
       <c r="D85" t="str">
         <v>2026-02-23</v>
@@ -3608,10 +3608,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G85" t="str">
-        <v>6:58</v>
+        <v>3:29</v>
       </c>
       <c r="H85" t="str">
-        <v>Eric Church</v>
+        <v>Meghan Trainor</v>
       </c>
       <c r="I85" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3623,18 +3623,18 @@
         <v/>
       </c>
       <c r="L85" t="str">
-        <v>Eric Church - Springsteen (Live At The Pinnacle, Nashville, TN / May 24, 2025) - Eric Church</v>
+        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio)</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
       </c>
       <c r="B86" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C86" t="str">
-        <v>https://www.youtube.com/watch?v=u30H4AcCe_g</v>
+        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
       </c>
       <c r="D86" t="str">
         <v>2026-02-23</v>
@@ -3646,10 +3646,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G86" t="str">
-        <v>3:29</v>
+        <v>3:14</v>
       </c>
       <c r="H86" t="str">
-        <v>Meghan Trainor</v>
+        <v>Ally Salort</v>
       </c>
       <c r="I86" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3661,18 +3661,18 @@
         <v/>
       </c>
       <c r="L86" t="str">
-        <v>Meghan Trainor - Get In Girl (Official Audio) - Meghan Trainor</v>
+        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video)</v>
+        <v>Will Swinton - Better Off (Official Video)</v>
       </c>
       <c r="B87" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C87" t="str">
-        <v>https://www.youtube.com/watch?v=vesdU5PD_v0</v>
+        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
       </c>
       <c r="D87" t="str">
         <v>2026-02-23</v>
@@ -3684,10 +3684,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G87" t="str">
-        <v>3:14</v>
+        <v>3:51</v>
       </c>
       <c r="H87" t="str">
-        <v>Ally Salort</v>
+        <v>Will Swinton</v>
       </c>
       <c r="I87" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3699,18 +3699,18 @@
         <v/>
       </c>
       <c r="L87" t="str">
-        <v>Ally Salort - I've Never Met Her (Lyric Video) - Ally Salort</v>
+        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="str">
-        <v>Will Swinton - Better Off (Official Video)</v>
+        <v>elijah woods - Old (Official Lyric Video)</v>
       </c>
       <c r="B88" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C88" t="str">
-        <v>https://www.youtube.com/watch?v=rMxHUJrvy1Q</v>
+        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
       </c>
       <c r="D88" t="str">
         <v>2026-02-23</v>
@@ -3722,10 +3722,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G88" t="str">
-        <v>3:51</v>
+        <v>3:10</v>
       </c>
       <c r="H88" t="str">
-        <v>Will Swinton</v>
+        <v>elijah woods</v>
       </c>
       <c r="I88" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3737,18 +3737,18 @@
         <v/>
       </c>
       <c r="L88" t="str">
-        <v>Will Swinton - Better Off (Official Video) - Will Swinton</v>
+        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="str">
-        <v>elijah woods - Old (Official Lyric Video)</v>
+        <v>Jackson Dean - Wildfire</v>
       </c>
       <c r="B89" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C89" t="str">
-        <v>https://www.youtube.com/watch?v=qvDqxfnJghQ</v>
+        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
       </c>
       <c r="D89" t="str">
         <v>2026-02-23</v>
@@ -3760,10 +3760,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G89" t="str">
-        <v>3:10</v>
+        <v>3:26</v>
       </c>
       <c r="H89" t="str">
-        <v>elijah woods</v>
+        <v>Jackson Dean</v>
       </c>
       <c r="I89" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3775,18 +3775,18 @@
         <v/>
       </c>
       <c r="L89" t="str">
-        <v>elijah woods - Old (Official Lyric Video) - elijah woods</v>
+        <v>Jackson Dean - Wildfire - Jackson Dean</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="str">
-        <v>Jackson Dean - Wildfire</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
       </c>
       <c r="B90" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C90" t="str">
-        <v>https://www.youtube.com/watch?v=rR2oLCan3jM</v>
+        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
       </c>
       <c r="D90" t="str">
         <v>2026-02-23</v>
@@ -3798,10 +3798,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G90" t="str">
-        <v>3:26</v>
+        <v>2:51</v>
       </c>
       <c r="H90" t="str">
-        <v>Jackson Dean</v>
+        <v>Matteo Bocelli</v>
       </c>
       <c r="I90" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3813,18 +3813,18 @@
         <v/>
       </c>
       <c r="L90" t="str">
-        <v>Jackson Dean - Wildfire - Jackson Dean</v>
+        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
       </c>
       <c r="B91" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C91" t="str">
-        <v>https://www.youtube.com/watch?v=mJbFEaCPvOM</v>
+        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
       </c>
       <c r="D91" t="str">
         <v>2026-02-23</v>
@@ -3836,10 +3836,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G91" t="str">
-        <v>2:51</v>
+        <v>3:26</v>
       </c>
       <c r="H91" t="str">
-        <v>Matteo Bocelli</v>
+        <v>Neil Sedaka</v>
       </c>
       <c r="I91" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3851,18 +3851,18 @@
         <v/>
       </c>
       <c r="L91" t="str">
-        <v>Matteo Bocelli - Cuándo, Cuándo, Cuándo - Matteo Bocelli</v>
+        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official)</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
       </c>
       <c r="B92" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C92" t="str">
-        <v>https://www.youtube.com/watch?v=o2y02DvRbjg</v>
+        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
       </c>
       <c r="D92" t="str">
         <v>2026-02-23</v>
@@ -3874,10 +3874,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G92" t="str">
-        <v>3:26</v>
+        <v>3:06</v>
       </c>
       <c r="H92" t="str">
-        <v>Neil Sedaka</v>
+        <v>Sofia Camara</v>
       </c>
       <c r="I92" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3889,18 +3889,18 @@
         <v/>
       </c>
       <c r="L92" t="str">
-        <v>Neil Sedaka - Love in the Shadows (Lyric Video) (Official) - Neil Sedaka</v>
+        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video)</v>
+        <v>Russell Dickerson - The Roses (Official Video)</v>
       </c>
       <c r="B93" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C93" t="str">
-        <v>https://www.youtube.com/watch?v=ieDehLfGM84</v>
+        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
       </c>
       <c r="D93" t="str">
         <v>2026-02-23</v>
@@ -3912,10 +3912,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G93" t="str">
-        <v>3:06</v>
+        <v>3:04</v>
       </c>
       <c r="H93" t="str">
-        <v>Sofia Camara</v>
+        <v>Russell Dickerson</v>
       </c>
       <c r="I93" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3927,18 +3927,18 @@
         <v/>
       </c>
       <c r="L93" t="str">
-        <v>Sofia Camara - Ingrained (DNA) (Acoustic/Lyric Video) - Sofia Camara</v>
+        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="str">
-        <v>Russell Dickerson - The Roses (Official Video)</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
       </c>
       <c r="B94" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C94" t="str">
-        <v>https://www.youtube.com/watch?v=kdXOFRWRor8</v>
+        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
       </c>
       <c r="D94" t="str">
         <v>2026-02-23</v>
@@ -3950,10 +3950,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G94" t="str">
-        <v>3:04</v>
+        <v>3:03</v>
       </c>
       <c r="H94" t="str">
-        <v>Russell Dickerson</v>
+        <v>Celine Dion</v>
       </c>
       <c r="I94" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -3965,18 +3965,18 @@
         <v/>
       </c>
       <c r="L94" t="str">
-        <v>Russell Dickerson - The Roses (Official Video) - Russell Dickerson</v>
+        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002)</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
       </c>
       <c r="B95" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C95" t="str">
-        <v>https://www.youtube.com/watch?v=gIJLz9Th2eI</v>
+        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
       </c>
       <c r="D95" t="str">
         <v>2026-02-23</v>
@@ -3988,10 +3988,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G95" t="str">
-        <v>3:03</v>
+        <v>2:38</v>
       </c>
       <c r="H95" t="str">
-        <v>Celine Dion</v>
+        <v>Bebe Rexha</v>
       </c>
       <c r="I95" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4003,18 +4003,18 @@
         <v/>
       </c>
       <c r="L95" t="str">
-        <v>Céline Dion - At Last (Live on Parkinson - BBC, 2002) - Celine Dion</v>
+        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video)</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
       </c>
       <c r="B96" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C96" t="str">
-        <v>https://www.youtube.com/watch?v=ZMaKQk9J2zM</v>
+        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
       </c>
       <c r="D96" t="str">
         <v>2026-02-23</v>
@@ -4026,10 +4026,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G96" t="str">
-        <v>2:38</v>
+        <v>3:29</v>
       </c>
       <c r="H96" t="str">
-        <v>Bebe Rexha</v>
+        <v>Caroline Jones</v>
       </c>
       <c r="I96" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4041,18 +4041,18 @@
         <v/>
       </c>
       <c r="L96" t="str">
-        <v>Bebe Rexha - I Like You Better Than Me (Official Lyric Video) - Bebe Rexha</v>
+        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video)</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
       </c>
       <c r="B97" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C97" t="str">
-        <v>https://www.youtube.com/watch?v=VB5ZAUSqcdk</v>
+        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
       </c>
       <c r="D97" t="str">
         <v>2026-02-23</v>
@@ -4064,10 +4064,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G97" t="str">
-        <v>3:29</v>
+        <v>2:32</v>
       </c>
       <c r="H97" t="str">
-        <v>Caroline Jones</v>
+        <v>Billy Raffoul and Emily James</v>
       </c>
       <c r="I97" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4079,18 +4079,18 @@
         <v/>
       </c>
       <c r="L97" t="str">
-        <v>Caroline Jones - Cutting It Close (Lyric Video) - Caroline Jones</v>
+        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio)</v>
+        <v>Ingrid Andress - Now I Know (Audio)</v>
       </c>
       <c r="B98" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C98" t="str">
-        <v>https://www.youtube.com/watch?v=Vwbc6dCuUFs</v>
+        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
       </c>
       <c r="D98" t="str">
         <v>2026-02-23</v>
@@ -4102,10 +4102,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G98" t="str">
-        <v>2:32</v>
+        <v>3:32</v>
       </c>
       <c r="H98" t="str">
-        <v>Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress</v>
       </c>
       <c r="I98" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4117,18 +4117,18 @@
         <v/>
       </c>
       <c r="L98" t="str">
-        <v>Billy Raffoul &amp; Emily James: Fit Together - Broke For The Better Version (Official Audio) - Billy Raffoul and Emily James</v>
+        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="str">
-        <v>Ingrid Andress - Now I Know (Audio)</v>
+        <v>Knox - Go For Broke (Lyric Video)</v>
       </c>
       <c r="B99" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C99" t="str">
-        <v>https://www.youtube.com/watch?v=Wu6owGPQ9ik</v>
+        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
       </c>
       <c r="D99" t="str">
         <v>2026-02-23</v>
@@ -4140,10 +4140,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G99" t="str">
-        <v>3:32</v>
+        <v>2:51</v>
       </c>
       <c r="H99" t="str">
-        <v>Ingrid Andress</v>
+        <v>MusicByKnox</v>
       </c>
       <c r="I99" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4155,18 +4155,18 @@
         <v/>
       </c>
       <c r="L99" t="str">
-        <v>Ingrid Andress - Now I Know (Audio) - Ingrid Andress</v>
+        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="str">
-        <v>Knox - Go For Broke (Lyric Video)</v>
+        <v>Ella Langley - Be Her (Official Video)</v>
       </c>
       <c r="B100" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C100" t="str">
-        <v>https://www.youtube.com/watch?v=S1Rgt4Wk3lg</v>
+        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
       </c>
       <c r="D100" t="str">
         <v>2026-02-23</v>
@@ -4178,10 +4178,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G100" t="str">
-        <v>2:51</v>
+        <v>3:38</v>
       </c>
       <c r="H100" t="str">
-        <v>MusicByKnox</v>
+        <v>Ella Langley</v>
       </c>
       <c r="I100" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4193,18 +4193,18 @@
         <v/>
       </c>
       <c r="L100" t="str">
-        <v>Knox - Go For Broke (Lyric Video) - MusicByKnox</v>
+        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="str">
-        <v>Ella Langley - Be Her (Official Video)</v>
+        <v>Nickless - As I Am</v>
       </c>
       <c r="B101" t="str">
         <v>10 days ago</v>
       </c>
       <c r="C101" t="str">
-        <v>https://www.youtube.com/watch?v=Dg47eNL_Usw</v>
+        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
       </c>
       <c r="D101" t="str">
         <v>2026-02-23</v>
@@ -4216,10 +4216,10 @@
         <v>10 days ago</v>
       </c>
       <c r="G101" t="str">
-        <v>3:38</v>
+        <v>3:26</v>
       </c>
       <c r="H101" t="str">
-        <v>Ella Langley</v>
+        <v>Nickless</v>
       </c>
       <c r="I101" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -4231,18 +4231,18 @@
         <v/>
       </c>
       <c r="L101" t="str">
-        <v>Ella Langley - Be Her (Official Video) - Ella Langley</v>
+        <v>Nickless - As I Am - Nickless</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="str">
-        <v>Nickless - As I Am</v>
+        <v>Badlands</v>
       </c>
       <c r="B102" t="str">
-        <v>10 days ago</v>
+        <v/>
       </c>
       <c r="C102" t="str">
-        <v>https://www.youtube.com/watch?v=DM4tgKNW5kI</v>
+        <v>https://music.apple.com/us/song/badlands/1848218132</v>
       </c>
       <c r="D102" t="str">
         <v>2026-02-23</v>
@@ -4251,36 +4251,36 @@
         <v/>
       </c>
       <c r="F102" t="str">
-        <v>10 days ago</v>
+        <v>Prizefighter</v>
       </c>
       <c r="G102" t="str">
-        <v>3:26</v>
+        <v>2:58</v>
       </c>
       <c r="H102" t="str">
-        <v>Nickless</v>
+        <v>Mumford &amp; Sons</v>
       </c>
       <c r="I102" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
       </c>
       <c r="K102" t="str">
-        <v/>
+        <v>https://music.apple.com/us/album/badlands/1848218113</v>
       </c>
       <c r="L102" t="str">
-        <v>Nickless - As I Am - Nickless</v>
+        <v>Badlands - Mumford &amp; Sons</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="str">
-        <v>Badlands</v>
+        <v>Opalite (Chris Lake Remix)</v>
       </c>
       <c r="B103" t="str">
         <v/>
       </c>
       <c r="C103" t="str">
-        <v>https://music.apple.com/us/song/badlands/1848218132</v>
+        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
       </c>
       <c r="D103" t="str">
         <v>2026-02-23</v>
@@ -4289,36 +4289,36 @@
         <v/>
       </c>
       <c r="F103" t="str">
-        <v>Prizefighter</v>
+        <v>Opalite (Chris Lake Remix) - Single</v>
       </c>
       <c r="G103" t="str">
-        <v>2:58</v>
+        <v>3:48</v>
       </c>
       <c r="H103" t="str">
-        <v>Mumford &amp; Sons</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I103" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J103" t="str">
-        <v>https://music.apple.com/us/artist/mumford-sons/307699986</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K103" t="str">
-        <v>https://music.apple.com/us/album/badlands/1848218113</v>
+        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
       </c>
       <c r="L103" t="str">
-        <v>Badlands - Mumford &amp; Sons</v>
+        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="str">
-        <v>Opalite (Chris Lake Remix)</v>
+        <v>White Feather Hawk Tail Deer Hunter</v>
       </c>
       <c r="B104" t="str">
         <v/>
       </c>
       <c r="C104" t="str">
-        <v>https://music.apple.com/us/song/opalite-chris-lake-remix/1878187199</v>
+        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
       </c>
       <c r="D104" t="str">
         <v>2026-02-23</v>
@@ -4327,36 +4327,36 @@
         <v/>
       </c>
       <c r="F104" t="str">
-        <v>Opalite (Chris Lake Remix) - Single</v>
+        <v>White Feather Hawk Tail Deer Hunter - Single</v>
       </c>
       <c r="G104" t="str">
-        <v>3:48</v>
+        <v>3:54</v>
       </c>
       <c r="H104" t="str">
-        <v>Taylor Swift</v>
+        <v>Lana Del Rey</v>
       </c>
       <c r="I104" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J104" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
       </c>
       <c r="K104" t="str">
-        <v>https://music.apple.com/us/album/opalite-chris-lake-remix/1878187190</v>
+        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
       </c>
       <c r="L104" t="str">
-        <v>Opalite (Chris Lake Remix) - Taylor Swift</v>
+        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="str">
-        <v>White Feather Hawk Tail Deer Hunter</v>
+        <v>ROSITA</v>
       </c>
       <c r="B105" t="str">
         <v/>
       </c>
       <c r="C105" t="str">
-        <v>https://music.apple.com/us/song/white-feather-hawk-tail-deer-hunter/1877234387</v>
+        <v>https://music.apple.com/us/song/rosita/1877264687</v>
       </c>
       <c r="D105" t="str">
         <v>2026-02-23</v>
@@ -4365,36 +4365,36 @@
         <v/>
       </c>
       <c r="F105" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Single</v>
+        <v>ROSITA - Single</v>
       </c>
       <c r="G105" t="str">
-        <v>3:54</v>
+        <v>4:05</v>
       </c>
       <c r="H105" t="str">
-        <v>Lana Del Rey</v>
+        <v>Tainy</v>
       </c>
       <c r="I105" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J105" t="str">
-        <v>https://music.apple.com/us/artist/lana-del-rey/464296584</v>
+        <v>https://music.apple.com/us/artist/tainy/193167653</v>
       </c>
       <c r="K105" t="str">
-        <v>https://music.apple.com/us/album/white-feather-hawk-tail-deer-hunter/1877234145</v>
+        <v>https://music.apple.com/us/album/rosita/1877264686</v>
       </c>
       <c r="L105" t="str">
-        <v>White Feather Hawk Tail Deer Hunter - Lana Del Rey</v>
+        <v>ROSITA - Tainy</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="str">
-        <v>ROSITA</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
       </c>
       <c r="B106" t="str">
         <v/>
       </c>
       <c r="C106" t="str">
-        <v>https://music.apple.com/us/song/rosita/1877264687</v>
+        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
       </c>
       <c r="D106" t="str">
         <v>2026-02-23</v>
@@ -4403,36 +4403,36 @@
         <v/>
       </c>
       <c r="F106" t="str">
-        <v>ROSITA - Single</v>
+        <v>Ca$ino</v>
       </c>
       <c r="G106" t="str">
-        <v>4:05</v>
+        <v>3:52</v>
       </c>
       <c r="H106" t="str">
-        <v>Tainy</v>
+        <v>Baby Keem</v>
       </c>
       <c r="I106" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J106" t="str">
-        <v>https://music.apple.com/us/artist/tainy/193167653</v>
+        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
       </c>
       <c r="K106" t="str">
-        <v>https://music.apple.com/us/album/rosita/1877264686</v>
+        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
       </c>
       <c r="L106" t="str">
-        <v>ROSITA - Tainy</v>
+        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd)</v>
+        <v>Save The Day (From "Hoppers")</v>
       </c>
       <c r="B107" t="str">
         <v/>
       </c>
       <c r="C107" t="str">
-        <v>https://music.apple.com/us/song/good-flirts-feat-kendrick-lamar-momo-boyd/1878400231</v>
+        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
       </c>
       <c r="D107" t="str">
         <v>2026-02-23</v>
@@ -4441,36 +4441,36 @@
         <v/>
       </c>
       <c r="F107" t="str">
-        <v>Ca$ino</v>
+        <v>Save The Day (From "Hoppers") - Single</v>
       </c>
       <c r="G107" t="str">
-        <v>3:52</v>
+        <v>2:52</v>
       </c>
       <c r="H107" t="str">
-        <v>Baby Keem</v>
+        <v>SZA</v>
       </c>
       <c r="I107" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J107" t="str">
-        <v>https://music.apple.com/us/artist/baby-keem/1413572916</v>
+        <v>https://music.apple.com/us/artist/sza/605800394</v>
       </c>
       <c r="K107" t="str">
-        <v>https://music.apple.com/us/album/good-flirts-feat-kendrick-lamar-momo-boyd/1878399948</v>
+        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
       </c>
       <c r="L107" t="str">
-        <v>Good Flirts (feat. Kendrick Lamar &amp; Momo Boyd) - Baby Keem</v>
+        <v>Save The Day (From "Hoppers") - SZA</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="str">
-        <v>Save The Day (From "Hoppers")</v>
+        <v>Medicine</v>
       </c>
       <c r="B108" t="str">
         <v/>
       </c>
       <c r="C108" t="str">
-        <v>https://music.apple.com/us/song/save-the-day-from-hoppers/1877213780</v>
+        <v>https://music.apple.com/us/song/medicine/1851297056</v>
       </c>
       <c r="D108" t="str">
         <v>2026-02-23</v>
@@ -4479,36 +4479,36 @@
         <v/>
       </c>
       <c r="F108" t="str">
-        <v>Save The Day (From "Hoppers") - Single</v>
+        <v>Cloud 9</v>
       </c>
       <c r="G108" t="str">
-        <v>2:52</v>
+        <v>3:11</v>
       </c>
       <c r="H108" t="str">
-        <v>SZA</v>
+        <v>Megan Moroney</v>
       </c>
       <c r="I108" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J108" t="str">
-        <v>https://music.apple.com/us/artist/sza/605800394</v>
+        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
       </c>
       <c r="K108" t="str">
-        <v>https://music.apple.com/us/album/save-the-day-from-hoppers/1877213779</v>
+        <v>https://music.apple.com/us/album/medicine/1851296746</v>
       </c>
       <c r="L108" t="str">
-        <v>Save The Day (From "Hoppers") - SZA</v>
+        <v>Medicine - Megan Moroney</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="str">
-        <v>Medicine</v>
+        <v>Weather For Tennis</v>
       </c>
       <c r="B109" t="str">
         <v/>
       </c>
       <c r="C109" t="str">
-        <v>https://music.apple.com/us/song/medicine/1851297056</v>
+        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
       </c>
       <c r="D109" t="str">
         <v>2026-02-23</v>
@@ -4517,36 +4517,36 @@
         <v/>
       </c>
       <c r="F109" t="str">
-        <v>Cloud 9</v>
+        <v>luck... or something</v>
       </c>
       <c r="G109" t="str">
-        <v>3:11</v>
+        <v>3:16</v>
       </c>
       <c r="H109" t="str">
-        <v>Megan Moroney</v>
+        <v>Hilary Duff</v>
       </c>
       <c r="I109" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J109" t="str">
-        <v>https://music.apple.com/us/artist/megan-moroney/1552469569</v>
+        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
       </c>
       <c r="K109" t="str">
-        <v>https://music.apple.com/us/album/medicine/1851296746</v>
+        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
       </c>
       <c r="L109" t="str">
-        <v>Medicine - Megan Moroney</v>
+        <v>Weather For Tennis - Hilary Duff</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="str">
-        <v>Weather For Tennis</v>
+        <v>ear to the cocoon</v>
       </c>
       <c r="B110" t="str">
         <v/>
       </c>
       <c r="C110" t="str">
-        <v>https://music.apple.com/us/song/weather-for-tennis/1854567104</v>
+        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
       </c>
       <c r="D110" t="str">
         <v>2026-02-23</v>
@@ -4555,36 +4555,36 @@
         <v/>
       </c>
       <c r="F110" t="str">
-        <v>luck... or something</v>
+        <v>petal rock black</v>
       </c>
       <c r="G110" t="str">
-        <v>3:16</v>
+        <v>4:18</v>
       </c>
       <c r="H110" t="str">
-        <v>Hilary Duff</v>
+        <v>WILLOW</v>
       </c>
       <c r="I110" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J110" t="str">
-        <v>https://music.apple.com/us/artist/hilary-duff/3296003</v>
+        <v>https://music.apple.com/us/artist/willow/400531893</v>
       </c>
       <c r="K110" t="str">
-        <v>https://music.apple.com/us/album/weather-for-tennis/1854567102</v>
+        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
       </c>
       <c r="L110" t="str">
-        <v>Weather For Tennis - Hilary Duff</v>
+        <v>ear to the cocoon - WILLOW</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="str">
-        <v>ear to the cocoon</v>
+        <v>Drag Path</v>
       </c>
       <c r="B111" t="str">
         <v/>
       </c>
       <c r="C111" t="str">
-        <v>https://music.apple.com/us/song/ear-to-the-cocoon/1872767745</v>
+        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
       </c>
       <c r="D111" t="str">
         <v>2026-02-23</v>
@@ -4593,36 +4593,36 @@
         <v/>
       </c>
       <c r="F111" t="str">
-        <v>petal rock black</v>
+        <v>Drag Path - Single</v>
       </c>
       <c r="G111" t="str">
-        <v>4:18</v>
+        <v>3:44</v>
       </c>
       <c r="H111" t="str">
-        <v>WILLOW</v>
+        <v>twenty one pilots</v>
       </c>
       <c r="I111" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J111" t="str">
-        <v>https://music.apple.com/us/artist/willow/400531893</v>
+        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
       </c>
       <c r="K111" t="str">
-        <v>https://music.apple.com/us/album/ear-to-the-cocoon/1872767488</v>
+        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
       </c>
       <c r="L111" t="str">
-        <v>ear to the cocoon - WILLOW</v>
+        <v>Drag Path - twenty one pilots</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="str">
-        <v>Drag Path</v>
+        <v>Song Of The Future</v>
       </c>
       <c r="B112" t="str">
         <v/>
       </c>
       <c r="C112" t="str">
-        <v>https://music.apple.com/us/song/drag-path/1876977596</v>
+        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
       </c>
       <c r="D112" t="str">
         <v>2026-02-23</v>
@@ -4631,36 +4631,36 @@
         <v/>
       </c>
       <c r="F112" t="str">
-        <v>Drag Path - Single</v>
+        <v>Days Of Ash - EP</v>
       </c>
       <c r="G112" t="str">
-        <v>3:44</v>
+        <v>3:55</v>
       </c>
       <c r="H112" t="str">
-        <v>twenty one pilots</v>
+        <v>U2</v>
       </c>
       <c r="I112" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J112" t="str">
-        <v>https://music.apple.com/us/artist/twenty-one-pilots/349736311</v>
+        <v>https://music.apple.com/us/artist/u2/78500</v>
       </c>
       <c r="K112" t="str">
-        <v>https://music.apple.com/us/album/drag-path/1876977594</v>
+        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
       </c>
       <c r="L112" t="str">
-        <v>Drag Path - twenty one pilots</v>
+        <v>Song Of The Future - U2</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="str">
-        <v>Song Of The Future</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="B113" t="str">
         <v/>
       </c>
       <c r="C113" t="str">
-        <v>https://music.apple.com/us/song/song-of-the-future/1875348244</v>
+        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
       </c>
       <c r="D113" t="str">
         <v>2026-02-23</v>
@@ -4669,36 +4669,36 @@
         <v/>
       </c>
       <c r="F113" t="str">
-        <v>Days Of Ash - EP</v>
+        <v>Your Favorite Toy</v>
       </c>
       <c r="G113" t="str">
-        <v>3:55</v>
+        <v>2:56</v>
       </c>
       <c r="H113" t="str">
-        <v>U2</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I113" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J113" t="str">
-        <v>https://music.apple.com/us/artist/u2/78500</v>
+        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
       </c>
       <c r="K113" t="str">
-        <v>https://music.apple.com/us/album/song-of-the-future/1875348241</v>
+        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
       </c>
       <c r="L113" t="str">
-        <v>Song Of The Future - U2</v>
+        <v>Your Favorite Toy - Foo Fighters</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Trimski</v>
       </c>
       <c r="B114" t="str">
         <v/>
       </c>
       <c r="C114" t="str">
-        <v>https://music.apple.com/us/song/your-favorite-toy/1877913734</v>
+        <v>https://music.apple.com/us/song/trimski/1876695030</v>
       </c>
       <c r="D114" t="str">
         <v>2026-02-23</v>
@@ -4707,36 +4707,36 @@
         <v/>
       </c>
       <c r="F114" t="str">
-        <v>Your Favorite Toy</v>
+        <v>Trimski - Single</v>
       </c>
       <c r="G114" t="str">
-        <v>2:56</v>
+        <v>3:02</v>
       </c>
       <c r="H114" t="str">
-        <v>Foo Fighters</v>
+        <v>NAV</v>
       </c>
       <c r="I114" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J114" t="str">
-        <v>https://music.apple.com/us/artist/foo-fighters/6906197</v>
+        <v>https://music.apple.com/us/artist/nav/1200089113</v>
       </c>
       <c r="K114" t="str">
-        <v>https://music.apple.com/us/album/your-favorite-toy/1877913489</v>
+        <v>https://music.apple.com/us/album/trimski/1876695024</v>
       </c>
       <c r="L114" t="str">
-        <v>Your Favorite Toy - Foo Fighters</v>
+        <v>Trimski - NAV</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="str">
-        <v>Trimski</v>
+        <v>Paracosm</v>
       </c>
       <c r="B115" t="str">
         <v/>
       </c>
       <c r="C115" t="str">
-        <v>https://music.apple.com/us/song/trimski/1876695030</v>
+        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
       </c>
       <c r="D115" t="str">
         <v>2026-02-23</v>
@@ -4745,36 +4745,36 @@
         <v/>
       </c>
       <c r="F115" t="str">
-        <v>Trimski - Single</v>
+        <v>Paracosm</v>
       </c>
       <c r="G115" t="str">
-        <v>3:02</v>
+        <v>3:23</v>
       </c>
       <c r="H115" t="str">
-        <v>NAV</v>
+        <v>Absolutely</v>
       </c>
       <c r="I115" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J115" t="str">
-        <v>https://music.apple.com/us/artist/nav/1200089113</v>
+        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
       </c>
       <c r="K115" t="str">
-        <v>https://music.apple.com/us/album/trimski/1876695024</v>
+        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
       </c>
       <c r="L115" t="str">
-        <v>Trimski - NAV</v>
+        <v>Paracosm - Absolutely</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="str">
-        <v>Paracosm</v>
+        <v>Casual Lady</v>
       </c>
       <c r="B116" t="str">
         <v/>
       </c>
       <c r="C116" t="str">
-        <v>https://music.apple.com/us/song/paracosm/1869706756</v>
+        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
       </c>
       <c r="D116" t="str">
         <v>2026-02-23</v>
@@ -4783,36 +4783,36 @@
         <v/>
       </c>
       <c r="F116" t="str">
-        <v>Paracosm</v>
+        <v>Casual Lady - Single</v>
       </c>
       <c r="G116" t="str">
-        <v>3:23</v>
+        <v>3:14</v>
       </c>
       <c r="H116" t="str">
-        <v>Absolutely</v>
+        <v>flowerovlove</v>
       </c>
       <c r="I116" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J116" t="str">
-        <v>https://music.apple.com/us/artist/absolutely/1690413236</v>
+        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
       </c>
       <c r="K116" t="str">
-        <v>https://music.apple.com/us/album/paracosm/1869706468</v>
+        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
       </c>
       <c r="L116" t="str">
-        <v>Paracosm - Absolutely</v>
+        <v>Casual Lady - flowerovlove</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="str">
-        <v>Casual Lady</v>
+        <v>Iris (Live from Apple Music Studios)</v>
       </c>
       <c r="B117" t="str">
         <v/>
       </c>
       <c r="C117" t="str">
-        <v>https://music.apple.com/us/song/casual-lady/1876361359</v>
+        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
       </c>
       <c r="D117" t="str">
         <v>2026-02-23</v>
@@ -4821,36 +4821,36 @@
         <v/>
       </c>
       <c r="F117" t="str">
-        <v>Casual Lady - Single</v>
+        <v>Iris (Live from Apple Music Studios) - Single</v>
       </c>
       <c r="G117" t="str">
-        <v>3:14</v>
+        <v>4:18</v>
       </c>
       <c r="H117" t="str">
-        <v>flowerovlove</v>
+        <v>The Goo Goo Dolls</v>
       </c>
       <c r="I117" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J117" t="str">
-        <v>https://music.apple.com/us/artist/flowerovlove/1521413851</v>
+        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
       </c>
       <c r="K117" t="str">
-        <v>https://music.apple.com/us/album/casual-lady/1876361353</v>
+        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
       </c>
       <c r="L117" t="str">
-        <v>Casual Lady - flowerovlove</v>
+        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="str">
-        <v>Iris (Live from Apple Music Studios)</v>
+        <v>Begging for Change</v>
       </c>
       <c r="B118" t="str">
         <v/>
       </c>
       <c r="C118" t="str">
-        <v>https://music.apple.com/us/song/iris-live-from-apple-music-studios/1877215177</v>
+        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
       </c>
       <c r="D118" t="str">
         <v>2026-02-23</v>
@@ -4859,36 +4859,36 @@
         <v/>
       </c>
       <c r="F118" t="str">
-        <v>Iris (Live from Apple Music Studios) - Single</v>
+        <v>HELP(2)</v>
       </c>
       <c r="G118" t="str">
-        <v>4:18</v>
+        <v>4:20</v>
       </c>
       <c r="H118" t="str">
-        <v>The Goo Goo Dolls</v>
+        <v>Pulp</v>
       </c>
       <c r="I118" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J118" t="str">
-        <v>https://music.apple.com/us/artist/the-goo-goo-dolls/147559</v>
+        <v>https://music.apple.com/us/artist/pulp/312518</v>
       </c>
       <c r="K118" t="str">
-        <v>https://music.apple.com/us/album/iris-live-from-apple-music-studios/1877215171</v>
+        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
       </c>
       <c r="L118" t="str">
-        <v>Iris (Live from Apple Music Studios) - The Goo Goo Dolls</v>
+        <v>Begging for Change - Pulp</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="str">
-        <v>Begging for Change</v>
+        <v>My Maker</v>
       </c>
       <c r="B119" t="str">
         <v/>
       </c>
       <c r="C119" t="str">
-        <v>https://music.apple.com/us/song/begging-for-change/1870313832</v>
+        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
       </c>
       <c r="D119" t="str">
         <v>2026-02-23</v>
@@ -4897,36 +4897,36 @@
         <v/>
       </c>
       <c r="F119" t="str">
-        <v>HELP(2)</v>
+        <v>Ricochet</v>
       </c>
       <c r="G119" t="str">
-        <v>4:20</v>
+        <v>4:19</v>
       </c>
       <c r="H119" t="str">
-        <v>Pulp</v>
+        <v>Snail Mail</v>
       </c>
       <c r="I119" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J119" t="str">
-        <v>https://music.apple.com/us/artist/pulp/312518</v>
+        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
       </c>
       <c r="K119" t="str">
-        <v>https://music.apple.com/us/album/begging-for-change/1870313498</v>
+        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
       </c>
       <c r="L119" t="str">
-        <v>Begging for Change - Pulp</v>
+        <v>My Maker - Snail Mail</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="str">
-        <v>My Maker</v>
+        <v>Opalite (BUNT. Remix)</v>
       </c>
       <c r="B120" t="str">
         <v/>
       </c>
       <c r="C120" t="str">
-        <v>https://music.apple.com/us/song/my-maker/1862845748</v>
+        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
       </c>
       <c r="D120" t="str">
         <v>2026-02-23</v>
@@ -4935,36 +4935,36 @@
         <v/>
       </c>
       <c r="F120" t="str">
-        <v>Ricochet</v>
+        <v>Opalite (BUNT. Remix) - Single</v>
       </c>
       <c r="G120" t="str">
-        <v>4:19</v>
+        <v>3:32</v>
       </c>
       <c r="H120" t="str">
-        <v>Snail Mail</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I120" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J120" t="str">
-        <v>https://music.apple.com/us/artist/snail-mail/1132854904</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K120" t="str">
-        <v>https://music.apple.com/us/album/my-maker/1862845733</v>
+        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
       </c>
       <c r="L120" t="str">
-        <v>My Maker - Snail Mail</v>
+        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="str">
-        <v>Opalite (BUNT. Remix)</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
       </c>
       <c r="B121" t="str">
         <v/>
       </c>
       <c r="C121" t="str">
-        <v>https://music.apple.com/us/song/opalite-bunt-remix/1878183696</v>
+        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
       </c>
       <c r="D121" t="str">
         <v>2026-02-23</v>
@@ -4973,36 +4973,36 @@
         <v/>
       </c>
       <c r="F121" t="str">
-        <v>Opalite (BUNT. Remix) - Single</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
       </c>
       <c r="G121" t="str">
-        <v>3:32</v>
+        <v>4:27</v>
       </c>
       <c r="H121" t="str">
-        <v>Taylor Swift</v>
+        <v>CHVRCHES</v>
       </c>
       <c r="I121" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J121" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
       </c>
       <c r="K121" t="str">
-        <v>https://music.apple.com/us/album/opalite-bunt-remix/1878183335</v>
+        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
       </c>
       <c r="L121" t="str">
-        <v>Opalite (BUNT. Remix) - Taylor Swift</v>
+        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)")</v>
+        <v>She Knows Too Much</v>
       </c>
       <c r="B122" t="str">
         <v/>
       </c>
       <c r="C122" t="str">
-        <v>https://music.apple.com/us/song/such-great-heights-from-tell-me-lies-season-3/1872222695</v>
+        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
       </c>
       <c r="D122" t="str">
         <v>2026-02-23</v>
@@ -5011,36 +5011,36 @@
         <v/>
       </c>
       <c r="F122" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - Single</v>
+        <v>Distracted</v>
       </c>
       <c r="G122" t="str">
-        <v>4:27</v>
+        <v>3:33</v>
       </c>
       <c r="H122" t="str">
-        <v>CHVRCHES</v>
+        <v>Thundercat</v>
       </c>
       <c r="I122" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J122" t="str">
-        <v>https://music.apple.com/us/artist/chvrches/566867492</v>
+        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
       </c>
       <c r="K122" t="str">
-        <v>https://music.apple.com/us/album/such-great-heights-from-tell-me-lies-season-3/1872222683</v>
+        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
       </c>
       <c r="L122" t="str">
-        <v>Such Great Heights (From "Tell Me Lies (Season 3)") - CHVRCHES</v>
+        <v>She Knows Too Much - Thundercat</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="str">
-        <v>She Knows Too Much</v>
+        <v>Tea Time</v>
       </c>
       <c r="B123" t="str">
         <v/>
       </c>
       <c r="C123" t="str">
-        <v>https://music.apple.com/us/song/she-knows-too-much/1861531670</v>
+        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
       </c>
       <c r="D123" t="str">
         <v>2026-02-23</v>
@@ -5049,36 +5049,36 @@
         <v/>
       </c>
       <c r="F123" t="str">
-        <v>Distracted</v>
+        <v>Tea Time - Single</v>
       </c>
       <c r="G123" t="str">
-        <v>3:33</v>
+        <v>2:25</v>
       </c>
       <c r="H123" t="str">
-        <v>Thundercat</v>
+        <v>Yung Miami</v>
       </c>
       <c r="I123" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J123" t="str">
-        <v>https://music.apple.com/us/artist/thundercat/367322286</v>
+        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
       </c>
       <c r="K123" t="str">
-        <v>https://music.apple.com/us/album/she-knows-too-much/1861531667</v>
+        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
       </c>
       <c r="L123" t="str">
-        <v>She Knows Too Much - Thundercat</v>
+        <v>Tea Time - Yung Miami</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="str">
-        <v>Tea Time</v>
+        <v>full moon. (fall in tokyo) [bonus track]</v>
       </c>
       <c r="B124" t="str">
         <v/>
       </c>
       <c r="C124" t="str">
-        <v>https://music.apple.com/us/song/tea-time/1877002914</v>
+        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
       </c>
       <c r="D124" t="str">
         <v>2026-02-23</v>
@@ -5087,36 +5087,36 @@
         <v/>
       </c>
       <c r="F124" t="str">
-        <v>Tea Time - Single</v>
+        <v>Icon (Director's Cut)</v>
       </c>
       <c r="G124" t="str">
-        <v>2:25</v>
+        <v>3:12</v>
       </c>
       <c r="H124" t="str">
-        <v>Yung Miami</v>
+        <v>Brent Faiyaz</v>
       </c>
       <c r="I124" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J124" t="str">
-        <v>https://music.apple.com/us/artist/yung-miami/1476226954</v>
+        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
       </c>
       <c r="K124" t="str">
-        <v>https://music.apple.com/us/album/tea-time/1877002906</v>
+        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
       </c>
       <c r="L124" t="str">
-        <v>Tea Time - Yung Miami</v>
+        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="str">
-        <v>full moon. (fall in tokyo) [bonus track]</v>
+        <v>Save My Love</v>
       </c>
       <c r="B125" t="str">
         <v/>
       </c>
       <c r="C125" t="str">
-        <v>https://music.apple.com/us/song/full-moon-fall-in-tokyo-bonus-track/1877180113</v>
+        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
       </c>
       <c r="D125" t="str">
         <v>2026-02-23</v>
@@ -5125,36 +5125,36 @@
         <v/>
       </c>
       <c r="F125" t="str">
-        <v>Icon (Director's Cut)</v>
+        <v>Save My Love - Single</v>
       </c>
       <c r="G125" t="str">
-        <v>3:12</v>
+        <v>3:30</v>
       </c>
       <c r="H125" t="str">
-        <v>Brent Faiyaz</v>
+        <v>Kygo</v>
       </c>
       <c r="I125" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J125" t="str">
-        <v>https://music.apple.com/us/artist/brent-faiyaz/960127446</v>
+        <v>https://music.apple.com/us/artist/kygo/635806094</v>
       </c>
       <c r="K125" t="str">
-        <v>https://music.apple.com/us/album/full-moon-fall-in-tokyo-bonus-track/1877179580</v>
+        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
       </c>
       <c r="L125" t="str">
-        <v>full moon. (fall in tokyo) [bonus track] - Brent Faiyaz</v>
+        <v>Save My Love - Kygo</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="str">
-        <v>Save My Love</v>
+        <v>FOREVER TU GANTEL</v>
       </c>
       <c r="B126" t="str">
         <v/>
       </c>
       <c r="C126" t="str">
-        <v>https://music.apple.com/us/song/save-my-love/1876235280</v>
+        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
       </c>
       <c r="D126" t="str">
         <v>2026-02-23</v>
@@ -5163,36 +5163,36 @@
         <v/>
       </c>
       <c r="F126" t="str">
-        <v>Save My Love - Single</v>
+        <v>POR SI MAÑANA NO ESTOY</v>
       </c>
       <c r="G126" t="str">
-        <v>3:30</v>
+        <v>3:46</v>
       </c>
       <c r="H126" t="str">
-        <v>Kygo</v>
+        <v>Omar Courtz</v>
       </c>
       <c r="I126" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J126" t="str">
-        <v>https://music.apple.com/us/artist/kygo/635806094</v>
+        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
       </c>
       <c r="K126" t="str">
-        <v>https://music.apple.com/us/album/save-my-love/1876235273</v>
+        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
       </c>
       <c r="L126" t="str">
-        <v>Save My Love - Kygo</v>
+        <v>FOREVER TU GANTEL - Omar Courtz</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="str">
-        <v>FOREVER TU GANTEL</v>
+        <v>Suburban Requiem</v>
       </c>
       <c r="B127" t="str">
         <v/>
       </c>
       <c r="C127" t="str">
-        <v>https://music.apple.com/us/song/forever-tu-gantel/1877482427</v>
+        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
       </c>
       <c r="D127" t="str">
         <v>2026-02-23</v>
@@ -5201,36 +5201,36 @@
         <v/>
       </c>
       <c r="F127" t="str">
-        <v>POR SI MAÑANA NO ESTOY</v>
+        <v>Idols (Complete)</v>
       </c>
       <c r="G127" t="str">
-        <v>3:46</v>
+        <v>4:39</v>
       </c>
       <c r="H127" t="str">
-        <v>Omar Courtz</v>
+        <v>YUNGBLUD</v>
       </c>
       <c r="I127" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J127" t="str">
-        <v>https://music.apple.com/us/artist/omar-courtz/1370744631</v>
+        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
       </c>
       <c r="K127" t="str">
-        <v>https://music.apple.com/us/album/forever-tu-gantel/1877481995</v>
+        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
       </c>
       <c r="L127" t="str">
-        <v>FOREVER TU GANTEL - Omar Courtz</v>
+        <v>Suburban Requiem - YUNGBLUD</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="str">
-        <v>Suburban Requiem</v>
+        <v>Good Grief</v>
       </c>
       <c r="B128" t="str">
         <v/>
       </c>
       <c r="C128" t="str">
-        <v>https://music.apple.com/us/song/suburban-requiem/1874720791</v>
+        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
       </c>
       <c r="D128" t="str">
         <v>2026-02-23</v>
@@ -5239,36 +5239,36 @@
         <v/>
       </c>
       <c r="F128" t="str">
-        <v>Idols (Complete)</v>
+        <v>(((((ultraSOUND)))))+</v>
       </c>
       <c r="G128" t="str">
-        <v>4:39</v>
+        <v>4:21</v>
       </c>
       <c r="H128" t="str">
-        <v>YUNGBLUD</v>
+        <v>The Neighbourhood</v>
       </c>
       <c r="I128" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J128" t="str">
-        <v>https://music.apple.com/us/artist/yungblud/213048599</v>
+        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
       </c>
       <c r="K128" t="str">
-        <v>https://music.apple.com/us/album/suburban-requiem/1874720357</v>
+        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
       </c>
       <c r="L128" t="str">
-        <v>Suburban Requiem - YUNGBLUD</v>
+        <v>Good Grief - The Neighbourhood</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="str">
-        <v>Good Grief</v>
+        <v>Freak On</v>
       </c>
       <c r="B129" t="str">
         <v/>
       </c>
       <c r="C129" t="str">
-        <v>https://music.apple.com/us/song/good-grief/1869516030</v>
+        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
       </c>
       <c r="D129" t="str">
         <v>2026-02-23</v>
@@ -5277,36 +5277,36 @@
         <v/>
       </c>
       <c r="F129" t="str">
-        <v>(((((ultraSOUND)))))+</v>
+        <v>Freak On - Single</v>
       </c>
       <c r="G129" t="str">
-        <v>4:21</v>
+        <v>2:49</v>
       </c>
       <c r="H129" t="str">
-        <v>The Neighbourhood</v>
+        <v>Steve Aoki</v>
       </c>
       <c r="I129" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J129" t="str">
-        <v>https://music.apple.com/us/artist/the-neighbourhood/219350813</v>
+        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
       </c>
       <c r="K129" t="str">
-        <v>https://music.apple.com/us/album/good-grief/1869516027</v>
+        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
       </c>
       <c r="L129" t="str">
-        <v>Good Grief - The Neighbourhood</v>
+        <v>Freak On - Steve Aoki</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="str">
-        <v>Freak On</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
       </c>
       <c r="B130" t="str">
         <v/>
       </c>
       <c r="C130" t="str">
-        <v>https://music.apple.com/us/song/freak-on/1874265564</v>
+        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
       </c>
       <c r="D130" t="str">
         <v>2026-02-23</v>
@@ -5315,36 +5315,36 @@
         <v/>
       </c>
       <c r="F130" t="str">
-        <v>Freak On - Single</v>
+        <v>Science (feat. Stevie Appleton) - Single</v>
       </c>
       <c r="G130" t="str">
-        <v>2:49</v>
+        <v>3:32</v>
       </c>
       <c r="H130" t="str">
-        <v>Steve Aoki</v>
+        <v>deadmau5</v>
       </c>
       <c r="I130" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J130" t="str">
-        <v>https://music.apple.com/us/artist/steve-aoki/271066694</v>
+        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
       </c>
       <c r="K130" t="str">
-        <v>https://music.apple.com/us/album/freak-on/1874265561</v>
+        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
       </c>
       <c r="L130" t="str">
-        <v>Freak On - Steve Aoki</v>
+        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit]</v>
+        <v>Opalite (Skream Remix)</v>
       </c>
       <c r="B131" t="str">
         <v/>
       </c>
       <c r="C131" t="str">
-        <v>https://music.apple.com/us/song/science-feat-stevie-appleton-radio-edit/1871036143</v>
+        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
       </c>
       <c r="D131" t="str">
         <v>2026-02-23</v>
@@ -5353,36 +5353,36 @@
         <v/>
       </c>
       <c r="F131" t="str">
-        <v>Science (feat. Stevie Appleton) - Single</v>
+        <v>Opalite (Skream Remix) - Single</v>
       </c>
       <c r="G131" t="str">
-        <v>3:32</v>
+        <v>3:55</v>
       </c>
       <c r="H131" t="str">
-        <v>deadmau5</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I131" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J131" t="str">
-        <v>https://music.apple.com/us/artist/deadmau5/78011850</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K131" t="str">
-        <v>https://music.apple.com/us/album/science-feat-stevie-appleton-radio-edit/1871036141</v>
+        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
       </c>
       <c r="L131" t="str">
-        <v>Science (feat. Stevie Appleton) [Radio Edit] - deadmau5</v>
+        <v>Opalite (Skream Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="str">
-        <v>Opalite (Skream Remix)</v>
+        <v>Yellow Eyes</v>
       </c>
       <c r="B132" t="str">
         <v/>
       </c>
       <c r="C132" t="str">
-        <v>https://music.apple.com/us/song/opalite-skream-remix/1878173708</v>
+        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
       </c>
       <c r="D132" t="str">
         <v>2026-02-23</v>
@@ -5391,36 +5391,36 @@
         <v/>
       </c>
       <c r="F132" t="str">
-        <v>Opalite (Skream Remix) - Single</v>
+        <v>Jean</v>
       </c>
       <c r="G132" t="str">
-        <v>3:55</v>
+        <v>2:42</v>
       </c>
       <c r="H132" t="str">
-        <v>Taylor Swift</v>
+        <v>Yebba</v>
       </c>
       <c r="I132" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J132" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
       </c>
       <c r="K132" t="str">
-        <v>https://music.apple.com/us/album/opalite-skream-remix/1878173707</v>
+        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
       </c>
       <c r="L132" t="str">
-        <v>Opalite (Skream Remix) - Taylor Swift</v>
+        <v>Yellow Eyes - Yebba</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="str">
-        <v>Yellow Eyes</v>
+        <v>Word On The Street</v>
       </c>
       <c r="B133" t="str">
         <v/>
       </c>
       <c r="C133" t="str">
-        <v>https://music.apple.com/us/song/yellow-eyes/1877157667</v>
+        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
       </c>
       <c r="D133" t="str">
         <v>2026-02-23</v>
@@ -5429,36 +5429,36 @@
         <v/>
       </c>
       <c r="F133" t="str">
-        <v>Jean</v>
+        <v>Word On The Street - Single</v>
       </c>
       <c r="G133" t="str">
-        <v>2:42</v>
+        <v>2:56</v>
       </c>
       <c r="H133" t="str">
-        <v>Yebba</v>
+        <v>Luke Bryan</v>
       </c>
       <c r="I133" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J133" t="str">
-        <v>https://music.apple.com/us/artist/yebba/1289015994</v>
+        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
       </c>
       <c r="K133" t="str">
-        <v>https://music.apple.com/us/album/yellow-eyes/1877157664</v>
+        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
       </c>
       <c r="L133" t="str">
-        <v>Yellow Eyes - Yebba</v>
+        <v>Word On The Street - Luke Bryan</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="str">
-        <v>Word On The Street</v>
+        <v>only the best</v>
       </c>
       <c r="B134" t="str">
         <v/>
       </c>
       <c r="C134" t="str">
-        <v>https://music.apple.com/us/song/word-on-the-street/1876607864</v>
+        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
       </c>
       <c r="D134" t="str">
         <v>2026-02-23</v>
@@ -5467,36 +5467,36 @@
         <v/>
       </c>
       <c r="F134" t="str">
-        <v>Word On The Street - Single</v>
+        <v>only the best - Single</v>
       </c>
       <c r="G134" t="str">
-        <v>2:56</v>
+        <v>3:22</v>
       </c>
       <c r="H134" t="str">
-        <v>Luke Bryan</v>
+        <v>horsegiirL</v>
       </c>
       <c r="I134" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J134" t="str">
-        <v>https://music.apple.com/us/artist/luke-bryan/20131064</v>
+        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
       </c>
       <c r="K134" t="str">
-        <v>https://music.apple.com/us/album/word-on-the-street/1876607713</v>
+        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
       </c>
       <c r="L134" t="str">
-        <v>Word On The Street - Luke Bryan</v>
+        <v>only the best - horsegiirL</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="str">
-        <v>only the best</v>
+        <v>Beautiful Places</v>
       </c>
       <c r="B135" t="str">
         <v/>
       </c>
       <c r="C135" t="str">
-        <v>https://music.apple.com/us/song/only-the-best/1876048177</v>
+        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
       </c>
       <c r="D135" t="str">
         <v>2026-02-23</v>
@@ -5505,36 +5505,36 @@
         <v/>
       </c>
       <c r="F135" t="str">
-        <v>only the best - Single</v>
+        <v>Beautiful Places - Single</v>
       </c>
       <c r="G135" t="str">
-        <v>3:22</v>
+        <v>2:59</v>
       </c>
       <c r="H135" t="str">
-        <v>horsegiirL</v>
+        <v>Tiësto</v>
       </c>
       <c r="I135" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J135" t="str">
-        <v>https://music.apple.com/us/artist/horsegiirl/1608374327</v>
+        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
       </c>
       <c r="K135" t="str">
-        <v>https://music.apple.com/us/album/only-the-best/1876048174</v>
+        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
       </c>
       <c r="L135" t="str">
-        <v>only the best - horsegiirL</v>
+        <v>Beautiful Places - Tiësto</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="str">
-        <v>Beautiful Places</v>
+        <v>STAMPEDE</v>
       </c>
       <c r="B136" t="str">
         <v/>
       </c>
       <c r="C136" t="str">
-        <v>https://music.apple.com/us/song/beautiful-places/1876326643</v>
+        <v>https://music.apple.com/us/song/stampede/1868995802</v>
       </c>
       <c r="D136" t="str">
         <v>2026-02-23</v>
@@ -5543,36 +5543,36 @@
         <v/>
       </c>
       <c r="F136" t="str">
-        <v>Beautiful Places - Single</v>
+        <v>STAMPEDE - Single</v>
       </c>
       <c r="G136" t="str">
-        <v>2:59</v>
+        <v>3:09</v>
       </c>
       <c r="H136" t="str">
-        <v>Tiësto</v>
+        <v>Genesis Owusu</v>
       </c>
       <c r="I136" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J136" t="str">
-        <v>https://music.apple.com/us/artist/ti%C3%ABsto/4091218</v>
+        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
       </c>
       <c r="K136" t="str">
-        <v>https://music.apple.com/us/album/beautiful-places/1876326642</v>
+        <v>https://music.apple.com/us/album/stampede/1868995797</v>
       </c>
       <c r="L136" t="str">
-        <v>Beautiful Places - Tiësto</v>
+        <v>STAMPEDE - Genesis Owusu</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="str">
-        <v>STAMPEDE</v>
+        <v>Infinite Beach</v>
       </c>
       <c r="B137" t="str">
         <v/>
       </c>
       <c r="C137" t="str">
-        <v>https://music.apple.com/us/song/stampede/1868995802</v>
+        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
       </c>
       <c r="D137" t="str">
         <v>2026-02-23</v>
@@ -5581,36 +5581,36 @@
         <v/>
       </c>
       <c r="F137" t="str">
-        <v>STAMPEDE - Single</v>
+        <v>Mārara</v>
       </c>
       <c r="G137" t="str">
-        <v>3:09</v>
+        <v>3:10</v>
       </c>
       <c r="H137" t="str">
-        <v>Genesis Owusu</v>
+        <v>15 15</v>
       </c>
       <c r="I137" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J137" t="str">
-        <v>https://music.apple.com/us/artist/genesis-owusu/1045380633</v>
+        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
       </c>
       <c r="K137" t="str">
-        <v>https://music.apple.com/us/album/stampede/1868995797</v>
+        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
       </c>
       <c r="L137" t="str">
-        <v>STAMPEDE - Genesis Owusu</v>
+        <v>Infinite Beach - 15 15</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="str">
-        <v>Infinite Beach</v>
+        <v>Championship Ring</v>
       </c>
       <c r="B138" t="str">
         <v/>
       </c>
       <c r="C138" t="str">
-        <v>https://music.apple.com/us/song/infinite-beach/1858554535</v>
+        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
       </c>
       <c r="D138" t="str">
         <v>2026-02-23</v>
@@ -5619,36 +5619,36 @@
         <v/>
       </c>
       <c r="F138" t="str">
-        <v>Mārara</v>
+        <v>I Want Blood</v>
       </c>
       <c r="G138" t="str">
-        <v>3:10</v>
+        <v>3:41</v>
       </c>
       <c r="H138" t="str">
-        <v>15 15</v>
+        <v>SleazyWorld Go</v>
       </c>
       <c r="I138" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J138" t="str">
-        <v>https://music.apple.com/us/artist/15-15/1532866284</v>
+        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
       </c>
       <c r="K138" t="str">
-        <v>https://music.apple.com/us/album/infinite-beach/1858554036</v>
+        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
       </c>
       <c r="L138" t="str">
-        <v>Infinite Beach - 15 15</v>
+        <v>Championship Ring - SleazyWorld Go</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="str">
-        <v>Championship Ring</v>
+        <v>miss u 2 (with Leon Thomas)</v>
       </c>
       <c r="B139" t="str">
         <v/>
       </c>
       <c r="C139" t="str">
-        <v>https://music.apple.com/us/song/championship-ring/1875186768</v>
+        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
       </c>
       <c r="D139" t="str">
         <v>2026-02-23</v>
@@ -5657,36 +5657,36 @@
         <v/>
       </c>
       <c r="F139" t="str">
-        <v>I Want Blood</v>
+        <v>girl music vol. 1 - EP</v>
       </c>
       <c r="G139" t="str">
-        <v>3:41</v>
+        <v>2:28</v>
       </c>
       <c r="H139" t="str">
-        <v>SleazyWorld Go</v>
+        <v>Ty Dolla $ign</v>
       </c>
       <c r="I139" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J139" t="str">
-        <v>https://music.apple.com/us/artist/sleazyworld-go/1503917115</v>
+        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
       </c>
       <c r="K139" t="str">
-        <v>https://music.apple.com/us/album/championship-ring/1875186762</v>
+        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
       </c>
       <c r="L139" t="str">
-        <v>Championship Ring - SleazyWorld Go</v>
+        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="str">
-        <v>miss u 2 (with Leon Thomas)</v>
+        <v>ILRB (feat. Babyface Ray)</v>
       </c>
       <c r="B140" t="str">
         <v/>
       </c>
       <c r="C140" t="str">
-        <v>https://music.apple.com/us/song/miss-u-2-with-leon-thomas/1878417355</v>
+        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
       </c>
       <c r="D140" t="str">
         <v>2026-02-23</v>
@@ -5695,36 +5695,36 @@
         <v/>
       </c>
       <c r="F140" t="str">
-        <v>girl music vol. 1 - EP</v>
+        <v>Da Realest</v>
       </c>
       <c r="G140" t="str">
-        <v>2:28</v>
+        <v>1:51</v>
       </c>
       <c r="H140" t="str">
-        <v>Ty Dolla $ign</v>
+        <v>Babyfxce E</v>
       </c>
       <c r="I140" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J140" t="str">
-        <v>https://music.apple.com/us/artist/ty-dolla-%24ign/602917745</v>
+        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
       </c>
       <c r="K140" t="str">
-        <v>https://music.apple.com/us/album/miss-u-2-with-leon-thomas/1878416755</v>
+        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
       </c>
       <c r="L140" t="str">
-        <v>miss u 2 (with Leon Thomas) - Ty Dolla $ign</v>
+        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="str">
-        <v>ILRB (feat. Babyface Ray)</v>
+        <v>Fine Shit</v>
       </c>
       <c r="B141" t="str">
         <v/>
       </c>
       <c r="C141" t="str">
-        <v>https://music.apple.com/us/song/ilrb-feat-babyface-ray/1860991793</v>
+        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
       </c>
       <c r="D141" t="str">
         <v>2026-02-23</v>
@@ -5733,36 +5733,36 @@
         <v/>
       </c>
       <c r="F141" t="str">
-        <v>Da Realest</v>
+        <v>Fine Shit - Single</v>
       </c>
       <c r="G141" t="str">
-        <v>1:51</v>
+        <v>1:53</v>
       </c>
       <c r="H141" t="str">
-        <v>Babyfxce E</v>
+        <v>Real Boston Richey</v>
       </c>
       <c r="I141" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J141" t="str">
-        <v>https://music.apple.com/us/artist/babyfxce-e/1573432856</v>
+        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
       </c>
       <c r="K141" t="str">
-        <v>https://music.apple.com/us/album/ilrb-feat-babyface-ray/1860991661</v>
+        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
       </c>
       <c r="L141" t="str">
-        <v>ILRB (feat. Babyface Ray) - Babyfxce E</v>
+        <v>Fine Shit - Real Boston Richey</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="str">
-        <v>Fine Shit</v>
+        <v>What's Your Name</v>
       </c>
       <c r="B142" t="str">
         <v/>
       </c>
       <c r="C142" t="str">
-        <v>https://music.apple.com/us/song/fine-shit/1878172118</v>
+        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
       </c>
       <c r="D142" t="str">
         <v>2026-02-23</v>
@@ -5771,36 +5771,36 @@
         <v/>
       </c>
       <c r="F142" t="str">
-        <v>Fine Shit - Single</v>
+        <v>What's Your Name - Single</v>
       </c>
       <c r="G142" t="str">
-        <v>1:53</v>
+        <v>2:20</v>
       </c>
       <c r="H142" t="str">
-        <v>Real Boston Richey</v>
+        <v>Soulidified</v>
       </c>
       <c r="I142" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J142" t="str">
-        <v>https://music.apple.com/us/artist/real-boston-richey/1595496755</v>
+        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
       </c>
       <c r="K142" t="str">
-        <v>https://music.apple.com/us/album/fine-shit/1878172115</v>
+        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
       </c>
       <c r="L142" t="str">
-        <v>Fine Shit - Real Boston Richey</v>
+        <v>What's Your Name - Soulidified</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="str">
-        <v>What's Your Name</v>
+        <v>Ends In Y</v>
       </c>
       <c r="B143" t="str">
         <v/>
       </c>
       <c r="C143" t="str">
-        <v>https://music.apple.com/us/song/whats-your-name/1878121936</v>
+        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
       </c>
       <c r="D143" t="str">
         <v>2026-02-23</v>
@@ -5809,36 +5809,36 @@
         <v/>
       </c>
       <c r="F143" t="str">
-        <v>What's Your Name - Single</v>
+        <v>Confessions: An Unexpected Turn of Events</v>
       </c>
       <c r="G143" t="str">
-        <v>2:20</v>
+        <v>2:53</v>
       </c>
       <c r="H143" t="str">
-        <v>Soulidified</v>
+        <v>Mimi Webb</v>
       </c>
       <c r="I143" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J143" t="str">
-        <v>https://music.apple.com/us/artist/soulidified/1824036220</v>
+        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
       </c>
       <c r="K143" t="str">
-        <v>https://music.apple.com/us/album/whats-your-name/1878121935</v>
+        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
       </c>
       <c r="L143" t="str">
-        <v>What's Your Name - Soulidified</v>
+        <v>Ends In Y - Mimi Webb</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="str">
-        <v>Ends In Y</v>
+        <v>Bully</v>
       </c>
       <c r="B144" t="str">
         <v/>
       </c>
       <c r="C144" t="str">
-        <v>https://music.apple.com/us/song/ends-in-y/1870981494</v>
+        <v>https://music.apple.com/us/song/bully/1874401861</v>
       </c>
       <c r="D144" t="str">
         <v>2026-02-23</v>
@@ -5847,36 +5847,36 @@
         <v/>
       </c>
       <c r="F144" t="str">
-        <v>Confessions: An Unexpected Turn of Events</v>
+        <v>Bully - Single</v>
       </c>
       <c r="G144" t="str">
-        <v>2:53</v>
+        <v>3:05</v>
       </c>
       <c r="H144" t="str">
-        <v>Mimi Webb</v>
+        <v>Iris Copperman</v>
       </c>
       <c r="I144" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J144" t="str">
-        <v>https://music.apple.com/us/artist/mimi-webb/1294518981</v>
+        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
       </c>
       <c r="K144" t="str">
-        <v>https://music.apple.com/us/album/ends-in-y/1870981483</v>
+        <v>https://music.apple.com/us/album/bully/1874401857</v>
       </c>
       <c r="L144" t="str">
-        <v>Ends In Y - Mimi Webb</v>
+        <v>Bully - Iris Copperman</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="str">
-        <v>Bully</v>
+        <v>MC24 (1:4)</v>
       </c>
       <c r="B145" t="str">
         <v/>
       </c>
       <c r="C145" t="str">
-        <v>https://music.apple.com/us/song/bully/1874401861</v>
+        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
       </c>
       <c r="D145" t="str">
         <v>2026-02-23</v>
@@ -5885,36 +5885,36 @@
         <v/>
       </c>
       <c r="F145" t="str">
-        <v>Bully - Single</v>
+        <v>MC24 &amp; SIN24 - Single</v>
       </c>
       <c r="G145" t="str">
-        <v>3:05</v>
+        <v>3:16</v>
       </c>
       <c r="H145" t="str">
-        <v>Iris Copperman</v>
+        <v>Charles Leclerc</v>
       </c>
       <c r="I145" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J145" t="str">
-        <v>https://music.apple.com/us/artist/iris-copperman/1741269048</v>
+        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
       </c>
       <c r="K145" t="str">
-        <v>https://music.apple.com/us/album/bully/1874401857</v>
+        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
       </c>
       <c r="L145" t="str">
-        <v>Bully - Iris Copperman</v>
+        <v>MC24 (1:4) - Charles Leclerc</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="str">
-        <v>MC24 (1:4)</v>
+        <v>Ride</v>
       </c>
       <c r="B146" t="str">
         <v/>
       </c>
       <c r="C146" t="str">
-        <v>https://music.apple.com/us/song/mc24-1-4/1793396732</v>
+        <v>https://music.apple.com/us/song/ride/1869414360</v>
       </c>
       <c r="D146" t="str">
         <v>2026-02-23</v>
@@ -5923,36 +5923,36 @@
         <v/>
       </c>
       <c r="F146" t="str">
-        <v>MC24 &amp; SIN24 - Single</v>
+        <v>Superbloom</v>
       </c>
       <c r="G146" t="str">
-        <v>3:16</v>
+        <v>4:39</v>
       </c>
       <c r="H146" t="str">
-        <v>Charles Leclerc</v>
+        <v>Jessie Ware</v>
       </c>
       <c r="I146" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J146" t="str">
-        <v>https://music.apple.com/us/artist/charles-leclerc/1687977492</v>
+        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
       </c>
       <c r="K146" t="str">
-        <v>https://music.apple.com/us/album/mc24-1-4/1793396725</v>
+        <v>https://music.apple.com/us/album/ride/1869414259</v>
       </c>
       <c r="L146" t="str">
-        <v>MC24 (1:4) - Charles Leclerc</v>
+        <v>Ride - Jessie Ware</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="str">
-        <v>Ride</v>
+        <v>Arkansas Mud</v>
       </c>
       <c r="B147" t="str">
         <v/>
       </c>
       <c r="C147" t="str">
-        <v>https://music.apple.com/us/song/ride/1869414360</v>
+        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
       </c>
       <c r="D147" t="str">
         <v>2026-02-23</v>
@@ -5961,36 +5961,36 @@
         <v/>
       </c>
       <c r="F147" t="str">
-        <v>Superbloom</v>
+        <v>Arkansas Mud - Single</v>
       </c>
       <c r="G147" t="str">
-        <v>4:39</v>
+        <v>4:18</v>
       </c>
       <c r="H147" t="str">
-        <v>Jessie Ware</v>
+        <v>Ashley McBryde</v>
       </c>
       <c r="I147" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J147" t="str">
-        <v>https://music.apple.com/us/artist/jessie-ware/471286553</v>
+        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
       </c>
       <c r="K147" t="str">
-        <v>https://music.apple.com/us/album/ride/1869414259</v>
+        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
       </c>
       <c r="L147" t="str">
-        <v>Ride - Jessie Ware</v>
+        <v>Arkansas Mud - Ashley McBryde</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="str">
-        <v>Arkansas Mud</v>
+        <v>Don't Leave</v>
       </c>
       <c r="B148" t="str">
         <v/>
       </c>
       <c r="C148" t="str">
-        <v>https://music.apple.com/us/song/arkansas-mud/1874413524</v>
+        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
       </c>
       <c r="D148" t="str">
         <v>2026-02-23</v>
@@ -5999,36 +5999,36 @@
         <v/>
       </c>
       <c r="F148" t="str">
-        <v>Arkansas Mud - Single</v>
+        <v>Don't Leave - Single</v>
       </c>
       <c r="G148" t="str">
-        <v>4:18</v>
+        <v>2:10</v>
       </c>
       <c r="H148" t="str">
-        <v>Ashley McBryde</v>
+        <v>Jorja Smith</v>
       </c>
       <c r="I148" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J148" t="str">
-        <v>https://music.apple.com/us/artist/ashley-mcbryde/452128870</v>
+        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
       </c>
       <c r="K148" t="str">
-        <v>https://music.apple.com/us/album/arkansas-mud/1874413516</v>
+        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
       </c>
       <c r="L148" t="str">
-        <v>Arkansas Mud - Ashley McBryde</v>
+        <v>Don't Leave - Jorja Smith</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="str">
-        <v>Don't Leave</v>
+        <v>FLAMED UP</v>
       </c>
       <c r="B149" t="str">
         <v/>
       </c>
       <c r="C149" t="str">
-        <v>https://music.apple.com/us/song/dont-leave/1872418573</v>
+        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
       </c>
       <c r="D149" t="str">
         <v>2026-02-23</v>
@@ -6037,36 +6037,36 @@
         <v/>
       </c>
       <c r="F149" t="str">
-        <v>Don't Leave - Single</v>
+        <v>FLAMED UP - Single</v>
       </c>
       <c r="G149" t="str">
-        <v>2:10</v>
+        <v>2:31</v>
       </c>
       <c r="H149" t="str">
-        <v>Jorja Smith</v>
+        <v>JayDon</v>
       </c>
       <c r="I149" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J149" t="str">
-        <v>https://music.apple.com/us/artist/jorja-smith/1088331223</v>
+        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
       </c>
       <c r="K149" t="str">
-        <v>https://music.apple.com/us/album/dont-leave/1872418571</v>
+        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
       </c>
       <c r="L149" t="str">
-        <v>Don't Leave - Jorja Smith</v>
+        <v>FLAMED UP - JayDon</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="str">
-        <v>FLAMED UP</v>
+        <v>3am in Paris</v>
       </c>
       <c r="B150" t="str">
         <v/>
       </c>
       <c r="C150" t="str">
-        <v>https://music.apple.com/us/song/flamed-up/1876888779</v>
+        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
       </c>
       <c r="D150" t="str">
         <v>2026-02-23</v>
@@ -6075,36 +6075,36 @@
         <v/>
       </c>
       <c r="F150" t="str">
-        <v>FLAMED UP - Single</v>
+        <v>3am in Paris - Single</v>
       </c>
       <c r="G150" t="str">
-        <v>2:31</v>
+        <v>2:49</v>
       </c>
       <c r="H150" t="str">
-        <v>JayDon</v>
+        <v>Anais Cardot</v>
       </c>
       <c r="I150" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J150" t="str">
-        <v>https://music.apple.com/us/artist/jaydon/1773146127</v>
+        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
       </c>
       <c r="K150" t="str">
-        <v>https://music.apple.com/us/album/flamed-up/1876888777</v>
+        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
       </c>
       <c r="L150" t="str">
-        <v>FLAMED UP - JayDon</v>
+        <v>3am in Paris - Anais Cardot</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="str">
-        <v>3am in Paris</v>
+        <v>I Got Saved (feat. Chris Brown) [Live]</v>
       </c>
       <c r="B151" t="str">
         <v/>
       </c>
       <c r="C151" t="str">
-        <v>https://music.apple.com/us/song/3am-in-paris/1838055454</v>
+        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
       </c>
       <c r="D151" t="str">
         <v>2026-02-23</v>
@@ -6113,36 +6113,36 @@
         <v/>
       </c>
       <c r="F151" t="str">
-        <v>3am in Paris - Single</v>
+        <v>SO BE IT (Live)</v>
       </c>
       <c r="G151" t="str">
-        <v>2:49</v>
+        <v>5:13</v>
       </c>
       <c r="H151" t="str">
-        <v>Anais Cardot</v>
+        <v>Elevation Worship</v>
       </c>
       <c r="I151" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J151" t="str">
-        <v>https://music.apple.com/us/artist/anais-cardot/1435833394</v>
+        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
       </c>
       <c r="K151" t="str">
-        <v>https://music.apple.com/us/album/3am-in-paris/1838055453</v>
+        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
       </c>
       <c r="L151" t="str">
-        <v>3am in Paris - Anais Cardot</v>
+        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live]</v>
+        <v>Migajero</v>
       </c>
       <c r="B152" t="str">
         <v/>
       </c>
       <c r="C152" t="str">
-        <v>https://music.apple.com/us/song/i-got-saved-feat-chris-brown-live/1870678652</v>
+        <v>https://music.apple.com/us/song/migajero/1873051149</v>
       </c>
       <c r="D152" t="str">
         <v>2026-02-23</v>
@@ -6151,36 +6151,36 @@
         <v/>
       </c>
       <c r="F152" t="str">
-        <v>SO BE IT (Live)</v>
+        <v>Migajero - Single</v>
       </c>
       <c r="G152" t="str">
-        <v>5:13</v>
+        <v>3:18</v>
       </c>
       <c r="H152" t="str">
-        <v>Elevation Worship</v>
+        <v>Grupo Marca Registrada</v>
       </c>
       <c r="I152" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J152" t="str">
-        <v>https://music.apple.com/us/artist/elevation-worship/287874918</v>
+        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
       </c>
       <c r="K152" t="str">
-        <v>https://music.apple.com/us/album/i-got-saved-feat-chris-brown-live/1870678481</v>
+        <v>https://music.apple.com/us/album/migajero/1873051145</v>
       </c>
       <c r="L152" t="str">
-        <v>I Got Saved (feat. Chris Brown) [Live] - Elevation Worship</v>
+        <v>Migajero - Grupo Marca Registrada</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="str">
-        <v>Migajero</v>
+        <v>Opalite (Ely Oaks Remix)</v>
       </c>
       <c r="B153" t="str">
         <v/>
       </c>
       <c r="C153" t="str">
-        <v>https://music.apple.com/us/song/migajero/1873051149</v>
+        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
       </c>
       <c r="D153" t="str">
         <v>2026-02-23</v>
@@ -6189,36 +6189,36 @@
         <v/>
       </c>
       <c r="F153" t="str">
-        <v>Migajero - Single</v>
+        <v>Opalite (Ely Oaks Remix) - Single</v>
       </c>
       <c r="G153" t="str">
-        <v>3:18</v>
+        <v>3:26</v>
       </c>
       <c r="H153" t="str">
-        <v>Grupo Marca Registrada</v>
+        <v>Taylor Swift</v>
       </c>
       <c r="I153" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J153" t="str">
-        <v>https://music.apple.com/us/artist/grupo-marca-registrada/1051127522</v>
+        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
       </c>
       <c r="K153" t="str">
-        <v>https://music.apple.com/us/album/migajero/1873051145</v>
+        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
       </c>
       <c r="L153" t="str">
-        <v>Migajero - Grupo Marca Registrada</v>
+        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="str">
-        <v>Opalite (Ely Oaks Remix)</v>
+        <v>Old Man</v>
       </c>
       <c r="B154" t="str">
         <v/>
       </c>
       <c r="C154" t="str">
-        <v>https://music.apple.com/us/song/opalite-ely-oaks-remix/1878155986</v>
+        <v>https://music.apple.com/us/song/old-man/1872189176</v>
       </c>
       <c r="D154" t="str">
         <v>2026-02-23</v>
@@ -6227,36 +6227,36 @@
         <v/>
       </c>
       <c r="F154" t="str">
-        <v>Opalite (Ely Oaks Remix) - Single</v>
+        <v>Old Man - Single</v>
       </c>
       <c r="G154" t="str">
-        <v>3:26</v>
+        <v>4:05</v>
       </c>
       <c r="H154" t="str">
-        <v>Taylor Swift</v>
+        <v>Trousdale</v>
       </c>
       <c r="I154" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J154" t="str">
-        <v>https://music.apple.com/us/artist/taylor-swift/159260351</v>
+        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
       </c>
       <c r="K154" t="str">
-        <v>https://music.apple.com/us/album/opalite-ely-oaks-remix/1878155587</v>
+        <v>https://music.apple.com/us/album/old-man/1872189159</v>
       </c>
       <c r="L154" t="str">
-        <v>Opalite (Ely Oaks Remix) - Taylor Swift</v>
+        <v>Old Man - Trousdale</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="str">
-        <v>Old Man</v>
+        <v>Of Joy (feat. ARY)</v>
       </c>
       <c r="B155" t="str">
         <v/>
       </c>
       <c r="C155" t="str">
-        <v>https://music.apple.com/us/song/old-man/1872189176</v>
+        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
       </c>
       <c r="D155" t="str">
         <v>2026-02-23</v>
@@ -6265,36 +6265,36 @@
         <v/>
       </c>
       <c r="F155" t="str">
-        <v>Old Man - Single</v>
+        <v>Of Joy (feat. ARY) - Single</v>
       </c>
       <c r="G155" t="str">
-        <v>4:05</v>
+        <v>3:19</v>
       </c>
       <c r="H155" t="str">
-        <v>Trousdale</v>
+        <v>DJ Seinfeld</v>
       </c>
       <c r="I155" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J155" t="str">
-        <v>https://music.apple.com/us/artist/trousdale/1534241692</v>
+        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
       </c>
       <c r="K155" t="str">
-        <v>https://music.apple.com/us/album/old-man/1872189159</v>
+        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
       </c>
       <c r="L155" t="str">
-        <v>Old Man - Trousdale</v>
+        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="str">
-        <v>Of Joy (feat. ARY)</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
       </c>
       <c r="B156" t="str">
         <v/>
       </c>
       <c r="C156" t="str">
-        <v>https://music.apple.com/us/song/of-joy-feat-ary/1870539621</v>
+        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
       </c>
       <c r="D156" t="str">
         <v>2026-02-23</v>
@@ -6303,36 +6303,36 @@
         <v/>
       </c>
       <c r="F156" t="str">
-        <v>Of Joy (feat. ARY) - Single</v>
+        <v>Strictly 4 The Scythe</v>
       </c>
       <c r="G156" t="str">
-        <v>3:19</v>
+        <v>2:56</v>
       </c>
       <c r="H156" t="str">
-        <v>DJ Seinfeld</v>
+        <v>Denzel Curry</v>
       </c>
       <c r="I156" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J156" t="str">
-        <v>https://music.apple.com/us/artist/dj-seinfeld/1184954167</v>
+        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
       </c>
       <c r="K156" t="str">
-        <v>https://music.apple.com/us/album/of-joy-feat-ary/1870539616</v>
+        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
       </c>
       <c r="L156" t="str">
-        <v>Of Joy (feat. ARY) - DJ Seinfeld</v>
+        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg)</v>
+        <v>Refuge</v>
       </c>
       <c r="B157" t="str">
         <v/>
       </c>
       <c r="C157" t="str">
-        <v>https://music.apple.com/us/song/the-scythe-feat-tiacorine-a%24ap-ferg/1868519273</v>
+        <v>https://music.apple.com/us/song/refuge/1867616924</v>
       </c>
       <c r="D157" t="str">
         <v>2026-02-23</v>
@@ -6341,36 +6341,36 @@
         <v/>
       </c>
       <c r="F157" t="str">
-        <v>Strictly 4 The Scythe</v>
+        <v>The Weight of the Woods</v>
       </c>
       <c r="G157" t="str">
-        <v>2:56</v>
+        <v>3:38</v>
       </c>
       <c r="H157" t="str">
-        <v>Denzel Curry</v>
+        <v>Dermot Kennedy</v>
       </c>
       <c r="I157" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J157" t="str">
-        <v>https://music.apple.com/us/artist/denzel-curry/631440154</v>
+        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
       </c>
       <c r="K157" t="str">
-        <v>https://music.apple.com/us/album/the-scythe-feat-tiacorine-a%24ap-ferg/1868519270</v>
+        <v>https://music.apple.com/us/album/refuge/1867616617</v>
       </c>
       <c r="L157" t="str">
-        <v>THE SCYTHE (feat. TiaCorine &amp; A$AP Ferg) - Denzel Curry</v>
+        <v>Refuge - Dermot Kennedy</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="str">
-        <v>Refuge</v>
+        <v>Goodbye Goodmorning</v>
       </c>
       <c r="B158" t="str">
         <v/>
       </c>
       <c r="C158" t="str">
-        <v>https://music.apple.com/us/song/refuge/1867616924</v>
+        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
       </c>
       <c r="D158" t="str">
         <v>2026-02-23</v>
@@ -6379,36 +6379,36 @@
         <v/>
       </c>
       <c r="F158" t="str">
-        <v>The Weight of the Woods</v>
+        <v>My Ego Told Me To</v>
       </c>
       <c r="G158" t="str">
-        <v>3:38</v>
+        <v>3:24</v>
       </c>
       <c r="H158" t="str">
-        <v>Dermot Kennedy</v>
+        <v>Leigh-Anne</v>
       </c>
       <c r="I158" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J158" t="str">
-        <v>https://music.apple.com/us/artist/dermot-kennedy/376564133</v>
+        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
       </c>
       <c r="K158" t="str">
-        <v>https://music.apple.com/us/album/refuge/1867616617</v>
+        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
       </c>
       <c r="L158" t="str">
-        <v>Refuge - Dermot Kennedy</v>
+        <v>Goodbye Goodmorning - Leigh-Anne</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="str">
-        <v>Goodbye Goodmorning</v>
+        <v>Smoke Screen</v>
       </c>
       <c r="B159" t="str">
         <v/>
       </c>
       <c r="C159" t="str">
-        <v>https://music.apple.com/us/song/goodbye-goodmorning/1844866123</v>
+        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
       </c>
       <c r="D159" t="str">
         <v>2026-02-23</v>
@@ -6417,36 +6417,36 @@
         <v/>
       </c>
       <c r="F159" t="str">
-        <v>My Ego Told Me To</v>
+        <v>Still There’s a Glow</v>
       </c>
       <c r="G159" t="str">
-        <v>3:24</v>
+        <v>2:51</v>
       </c>
       <c r="H159" t="str">
-        <v>Leigh-Anne</v>
+        <v>Sweet Pill</v>
       </c>
       <c r="I159" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J159" t="str">
-        <v>https://music.apple.com/us/artist/leigh-anne/1691386195</v>
+        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
       </c>
       <c r="K159" t="str">
-        <v>https://music.apple.com/us/album/goodbye-goodmorning/1844865923</v>
+        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
       </c>
       <c r="L159" t="str">
-        <v>Goodbye Goodmorning - Leigh-Anne</v>
+        <v>Smoke Screen - Sweet Pill</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="str">
-        <v>Smoke Screen</v>
+        <v>Twisting The Knife (feat. Mckenna Grace)</v>
       </c>
       <c r="B160" t="str">
         <v/>
       </c>
       <c r="C160" t="str">
-        <v>https://music.apple.com/us/song/smoke-screen/1851033864</v>
+        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
       </c>
       <c r="D160" t="str">
         <v>2026-02-23</v>
@@ -6455,36 +6455,36 @@
         <v/>
       </c>
       <c r="F160" t="str">
-        <v>Still There’s a Glow</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
       </c>
       <c r="G160" t="str">
-        <v>2:51</v>
+        <v>3:21</v>
       </c>
       <c r="H160" t="str">
-        <v>Sweet Pill</v>
+        <v>ICE NINE KILLS</v>
       </c>
       <c r="I160" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J160" t="str">
-        <v>https://music.apple.com/us/artist/sweet-pill/1459476044</v>
+        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
       </c>
       <c r="K160" t="str">
-        <v>https://music.apple.com/us/album/smoke-screen/1851033857</v>
+        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
       </c>
       <c r="L160" t="str">
-        <v>Smoke Screen - Sweet Pill</v>
+        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace)</v>
+        <v>Angel Wings</v>
       </c>
       <c r="B161" t="str">
         <v/>
       </c>
       <c r="C161" t="str">
-        <v>https://music.apple.com/us/song/twisting-the-knife-feat-mckenna-grace/1871023730</v>
+        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
       </c>
       <c r="D161" t="str">
         <v>2026-02-23</v>
@@ -6493,36 +6493,36 @@
         <v/>
       </c>
       <c r="F161" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - Single</v>
+        <v>Angel Wings - Single</v>
       </c>
       <c r="G161" t="str">
-        <v>3:21</v>
+        <v>3:52</v>
       </c>
       <c r="H161" t="str">
-        <v>ICE NINE KILLS</v>
+        <v>PRESIDENT</v>
       </c>
       <c r="I161" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J161" t="str">
-        <v>https://music.apple.com/us/artist/ice-nine-kills/204318665</v>
+        <v>https://music.apple.com/us/artist/president/1808681551</v>
       </c>
       <c r="K161" t="str">
-        <v>https://music.apple.com/us/album/twisting-the-knife-feat-mckenna-grace/1871023713</v>
+        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
       </c>
       <c r="L161" t="str">
-        <v>Twisting The Knife (feat. Mckenna Grace) - ICE NINE KILLS</v>
+        <v>Angel Wings - PRESIDENT</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="str">
-        <v>Angel Wings</v>
+        <v>Roamer</v>
       </c>
       <c r="B162" t="str">
         <v/>
       </c>
       <c r="C162" t="str">
-        <v>https://music.apple.com/us/song/angel-wings/1876325895</v>
+        <v>https://music.apple.com/us/song/roamer/1852775825</v>
       </c>
       <c r="D162" t="str">
         <v>2026-02-23</v>
@@ -6531,36 +6531,36 @@
         <v/>
       </c>
       <c r="F162" t="str">
-        <v>Angel Wings - Single</v>
+        <v>AngieAngieAngie</v>
       </c>
       <c r="G162" t="str">
-        <v>3:52</v>
+        <v>2:19</v>
       </c>
       <c r="H162" t="str">
-        <v>PRESIDENT</v>
+        <v>spill tab</v>
       </c>
       <c r="I162" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J162" t="str">
-        <v>https://music.apple.com/us/artist/president/1808681551</v>
+        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
       </c>
       <c r="K162" t="str">
-        <v>https://music.apple.com/us/album/angel-wings/1876325893</v>
+        <v>https://music.apple.com/us/album/roamer/1852775506</v>
       </c>
       <c r="L162" t="str">
-        <v>Angel Wings - PRESIDENT</v>
+        <v>Roamer - spill tab</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="str">
-        <v>Roamer</v>
+        <v>These Nights</v>
       </c>
       <c r="B163" t="str">
         <v/>
       </c>
       <c r="C163" t="str">
-        <v>https://music.apple.com/us/song/roamer/1852775825</v>
+        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
       </c>
       <c r="D163" t="str">
         <v>2026-02-23</v>
@@ -6569,36 +6569,36 @@
         <v/>
       </c>
       <c r="F163" t="str">
-        <v>AngieAngieAngie</v>
+        <v>Everything Glows</v>
       </c>
       <c r="G163" t="str">
-        <v>2:19</v>
+        <v>4:39</v>
       </c>
       <c r="H163" t="str">
-        <v>spill tab</v>
+        <v>Cannons</v>
       </c>
       <c r="I163" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J163" t="str">
-        <v>https://music.apple.com/us/artist/spill-tab/1440467280</v>
+        <v>https://music.apple.com/us/artist/cannons/65568551</v>
       </c>
       <c r="K163" t="str">
-        <v>https://music.apple.com/us/album/roamer/1852775506</v>
+        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
       </c>
       <c r="L163" t="str">
-        <v>Roamer - spill tab</v>
+        <v>These Nights - Cannons</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="str">
-        <v>These Nights</v>
+        <v>Locked and Loaded</v>
       </c>
       <c r="B164" t="str">
         <v/>
       </c>
       <c r="C164" t="str">
-        <v>https://music.apple.com/us/song/these-nights/1870989892</v>
+        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
       </c>
       <c r="D164" t="str">
         <v>2026-02-23</v>
@@ -6607,36 +6607,36 @@
         <v/>
       </c>
       <c r="F164" t="str">
-        <v>Everything Glows</v>
+        <v>Locked and Loaded - Single</v>
       </c>
       <c r="G164" t="str">
-        <v>4:39</v>
+        <v>2:55</v>
       </c>
       <c r="H164" t="str">
-        <v>Cannons</v>
+        <v>The Cab</v>
       </c>
       <c r="I164" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J164" t="str">
-        <v>https://music.apple.com/us/artist/cannons/65568551</v>
+        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
       </c>
       <c r="K164" t="str">
-        <v>https://music.apple.com/us/album/these-nights/1870989672</v>
+        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
       </c>
       <c r="L164" t="str">
-        <v>These Nights - Cannons</v>
+        <v>Locked and Loaded - The Cab</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="str">
-        <v>Locked and Loaded</v>
+        <v>Safe And Sound</v>
       </c>
       <c r="B165" t="str">
         <v/>
       </c>
       <c r="C165" t="str">
-        <v>https://music.apple.com/us/song/locked-and-loaded/1876992439</v>
+        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
       </c>
       <c r="D165" t="str">
         <v>2026-02-23</v>
@@ -6645,36 +6645,36 @@
         <v/>
       </c>
       <c r="F165" t="str">
-        <v>Locked and Loaded - Single</v>
+        <v>EI8HT</v>
       </c>
       <c r="G165" t="str">
-        <v>2:55</v>
+        <v>3:21</v>
       </c>
       <c r="H165" t="str">
-        <v>The Cab</v>
+        <v>Shinedown</v>
       </c>
       <c r="I165" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J165" t="str">
-        <v>https://music.apple.com/us/artist/the-cab/135077748</v>
+        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
       </c>
       <c r="K165" t="str">
-        <v>https://music.apple.com/us/album/locked-and-loaded/1876992433</v>
+        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
       </c>
       <c r="L165" t="str">
-        <v>Locked and Loaded - The Cab</v>
+        <v>Safe And Sound - Shinedown</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="str">
-        <v>Safe And Sound</v>
+        <v>Flinch</v>
       </c>
       <c r="B166" t="str">
         <v/>
       </c>
       <c r="C166" t="str">
-        <v>https://music.apple.com/us/song/safe-and-sound/1877229748</v>
+        <v>https://music.apple.com/us/song/flinch/1863072401</v>
       </c>
       <c r="D166" t="str">
         <v>2026-02-23</v>
@@ -6683,36 +6683,36 @@
         <v/>
       </c>
       <c r="F166" t="str">
-        <v>EI8HT</v>
+        <v>Autopilot</v>
       </c>
       <c r="G166" t="str">
-        <v>3:21</v>
+        <v>2:15</v>
       </c>
       <c r="H166" t="str">
-        <v>Shinedown</v>
+        <v>alexsucks</v>
       </c>
       <c r="I166" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J166" t="str">
-        <v>https://music.apple.com/us/artist/shinedown/1883858</v>
+        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
       </c>
       <c r="K166" t="str">
-        <v>https://music.apple.com/us/album/safe-and-sound/1877229738</v>
+        <v>https://music.apple.com/us/album/flinch/1863072393</v>
       </c>
       <c r="L166" t="str">
-        <v>Safe And Sound - Shinedown</v>
+        <v>Flinch - alexsucks</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="str">
-        <v>Flinch</v>
+        <v>Fall Up</v>
       </c>
       <c r="B167" t="str">
         <v/>
       </c>
       <c r="C167" t="str">
-        <v>https://music.apple.com/us/song/flinch/1863072401</v>
+        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
       </c>
       <c r="D167" t="str">
         <v>2026-02-23</v>
@@ -6721,36 +6721,36 @@
         <v/>
       </c>
       <c r="F167" t="str">
-        <v>Autopilot</v>
+        <v>Fall Up - Single</v>
       </c>
       <c r="G167" t="str">
-        <v>2:15</v>
+        <v>3:10</v>
       </c>
       <c r="H167" t="str">
-        <v>alexsucks</v>
+        <v>VOILÀ</v>
       </c>
       <c r="I167" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J167" t="str">
-        <v>https://music.apple.com/us/artist/alexsucks/1581888695</v>
+        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
       </c>
       <c r="K167" t="str">
-        <v>https://music.apple.com/us/album/flinch/1863072393</v>
+        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
       </c>
       <c r="L167" t="str">
-        <v>Flinch - alexsucks</v>
+        <v>Fall Up - VOILÀ</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="str">
-        <v>Fall Up</v>
+        <v>No Typo</v>
       </c>
       <c r="B168" t="str">
         <v/>
       </c>
       <c r="C168" t="str">
-        <v>https://music.apple.com/us/song/fall-up/1874959467</v>
+        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
       </c>
       <c r="D168" t="str">
         <v>2026-02-23</v>
@@ -6759,36 +6759,36 @@
         <v/>
       </c>
       <c r="F168" t="str">
-        <v>Fall Up - Single</v>
+        <v>Free (Deluxe)</v>
       </c>
       <c r="G168" t="str">
-        <v>3:10</v>
+        <v>1:43</v>
       </c>
       <c r="H168" t="str">
-        <v>VOILÀ</v>
+        <v>Nasty C</v>
       </c>
       <c r="I168" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J168" t="str">
-        <v>https://music.apple.com/us/artist/voil%C3%A0/1333272109</v>
+        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
       </c>
       <c r="K168" t="str">
-        <v>https://music.apple.com/us/album/fall-up/1874959466</v>
+        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
       </c>
       <c r="L168" t="str">
-        <v>Fall Up - VOILÀ</v>
+        <v>No Typo - Nasty C</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="str">
-        <v>No Typo</v>
+        <v>Desiree</v>
       </c>
       <c r="B169" t="str">
         <v/>
       </c>
       <c r="C169" t="str">
-        <v>https://music.apple.com/us/song/no-typo/1872454952</v>
+        <v>https://music.apple.com/us/song/desiree/1852556464</v>
       </c>
       <c r="D169" t="str">
         <v>2026-02-23</v>
@@ -6797,36 +6797,36 @@
         <v/>
       </c>
       <c r="F169" t="str">
-        <v>Free (Deluxe)</v>
+        <v>Wings of Desire</v>
       </c>
       <c r="G169" t="str">
-        <v>1:43</v>
+        <v>3:46</v>
       </c>
       <c r="H169" t="str">
-        <v>Nasty C</v>
+        <v>Hemi Hemingway</v>
       </c>
       <c r="I169" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J169" t="str">
-        <v>https://music.apple.com/us/artist/nasty-c/1041347781</v>
+        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
       </c>
       <c r="K169" t="str">
-        <v>https://music.apple.com/us/album/no-typo/1872454582</v>
+        <v>https://music.apple.com/us/album/desiree/1852556460</v>
       </c>
       <c r="L169" t="str">
-        <v>No Typo - Nasty C</v>
+        <v>Desiree - Hemi Hemingway</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="str">
-        <v>Desiree</v>
+        <v>Goliath (feat. Katie Jacoby)</v>
       </c>
       <c r="B170" t="str">
         <v/>
       </c>
       <c r="C170" t="str">
-        <v>https://music.apple.com/us/song/desiree/1852556464</v>
+        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
       </c>
       <c r="D170" t="str">
         <v>2026-02-23</v>
@@ -6835,36 +6835,36 @@
         <v/>
       </c>
       <c r="F170" t="str">
-        <v>Wings of Desire</v>
+        <v>Goliath</v>
       </c>
       <c r="G170" t="str">
-        <v>3:46</v>
+        <v>5:04</v>
       </c>
       <c r="H170" t="str">
-        <v>Hemi Hemingway</v>
+        <v>Exodus</v>
       </c>
       <c r="I170" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J170" t="str">
-        <v>https://music.apple.com/us/artist/hemi-hemingway/1560734927</v>
+        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
       </c>
       <c r="K170" t="str">
-        <v>https://music.apple.com/us/album/desiree/1852556460</v>
+        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
       </c>
       <c r="L170" t="str">
-        <v>Desiree - Hemi Hemingway</v>
+        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="str">
-        <v>Goliath (feat. Katie Jacoby)</v>
+        <v>Nomad</v>
       </c>
       <c r="B171" t="str">
         <v/>
       </c>
       <c r="C171" t="str">
-        <v>https://music.apple.com/us/song/goliath-feat-katie-jacoby/1862225627</v>
+        <v>https://music.apple.com/us/song/nomad/1843578167</v>
       </c>
       <c r="D171" t="str">
         <v>2026-02-23</v>
@@ -6873,36 +6873,36 @@
         <v/>
       </c>
       <c r="F171" t="str">
-        <v>Goliath</v>
+        <v>Loss</v>
       </c>
       <c r="G171" t="str">
-        <v>5:04</v>
+        <v>5:30</v>
       </c>
       <c r="H171" t="str">
-        <v>Exodus</v>
+        <v>Gaerea</v>
       </c>
       <c r="I171" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J171" t="str">
-        <v>https://music.apple.com/us/artist/exodus/1448557080</v>
+        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
       </c>
       <c r="K171" t="str">
-        <v>https://music.apple.com/us/album/goliath-feat-katie-jacoby/1862225385</v>
+        <v>https://music.apple.com/us/album/nomad/1843578156</v>
       </c>
       <c r="L171" t="str">
-        <v>Goliath (feat. Katie Jacoby) - Exodus</v>
+        <v>Nomad - Gaerea</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="str">
-        <v>Nomad</v>
+        <v>Empty Words</v>
       </c>
       <c r="B172" t="str">
         <v/>
       </c>
       <c r="C172" t="str">
-        <v>https://music.apple.com/us/song/nomad/1843578167</v>
+        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
       </c>
       <c r="D172" t="str">
         <v>2026-02-23</v>
@@ -6911,36 +6911,36 @@
         <v/>
       </c>
       <c r="F172" t="str">
-        <v>Loss</v>
+        <v>Empty Words - Single</v>
       </c>
       <c r="G172" t="str">
-        <v>5:30</v>
+        <v>2:32</v>
       </c>
       <c r="H172" t="str">
-        <v>Gaerea</v>
+        <v>Corey Kent</v>
       </c>
       <c r="I172" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J172" t="str">
-        <v>https://music.apple.com/us/artist/gaerea/1383640506</v>
+        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
       </c>
       <c r="K172" t="str">
-        <v>https://music.apple.com/us/album/nomad/1843578156</v>
+        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
       </c>
       <c r="L172" t="str">
-        <v>Nomad - Gaerea</v>
+        <v>Empty Words - Corey Kent</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="str">
-        <v>Empty Words</v>
+        <v>Didn't Forget</v>
       </c>
       <c r="B173" t="str">
         <v/>
       </c>
       <c r="C173" t="str">
-        <v>https://music.apple.com/us/song/empty-words/1876625198</v>
+        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
       </c>
       <c r="D173" t="str">
         <v>2026-02-23</v>
@@ -6949,36 +6949,36 @@
         <v/>
       </c>
       <c r="F173" t="str">
-        <v>Empty Words - Single</v>
+        <v>Didn't Forget - Single</v>
       </c>
       <c r="G173" t="str">
-        <v>2:32</v>
+        <v>3:48</v>
       </c>
       <c r="H173" t="str">
-        <v>Corey Kent</v>
+        <v>Waylon Wyatt</v>
       </c>
       <c r="I173" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J173" t="str">
-        <v>https://music.apple.com/us/artist/corey-kent/1171544097</v>
+        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
       </c>
       <c r="K173" t="str">
-        <v>https://music.apple.com/us/album/empty-words/1876625197</v>
+        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
       </c>
       <c r="L173" t="str">
-        <v>Empty Words - Corey Kent</v>
+        <v>Didn't Forget - Waylon Wyatt</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="str">
-        <v>Didn't Forget</v>
+        <v>Euphoria</v>
       </c>
       <c r="B174" t="str">
         <v/>
       </c>
       <c r="C174" t="str">
-        <v>https://music.apple.com/us/song/didnt-forget/1876997983</v>
+        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
       </c>
       <c r="D174" t="str">
         <v>2026-02-23</v>
@@ -6987,36 +6987,36 @@
         <v/>
       </c>
       <c r="F174" t="str">
-        <v>Didn't Forget - Single</v>
+        <v>Euphoria - Single</v>
       </c>
       <c r="G174" t="str">
-        <v>3:48</v>
+        <v>2:14</v>
       </c>
       <c r="H174" t="str">
-        <v>Waylon Wyatt</v>
+        <v>Bluff City</v>
       </c>
       <c r="I174" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J174" t="str">
-        <v>https://music.apple.com/us/artist/waylon-wyatt/1713519329</v>
+        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
       </c>
       <c r="K174" t="str">
-        <v>https://music.apple.com/us/album/didnt-forget/1876997982</v>
+        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
       </c>
       <c r="L174" t="str">
-        <v>Didn't Forget - Waylon Wyatt</v>
+        <v>Euphoria - Bluff City</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="str">
-        <v>Euphoria</v>
+        <v>hopeless romantic</v>
       </c>
       <c r="B175" t="str">
         <v/>
       </c>
       <c r="C175" t="str">
-        <v>https://music.apple.com/us/song/euphoria/1874295624</v>
+        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
       </c>
       <c r="D175" t="str">
         <v>2026-02-23</v>
@@ -7025,36 +7025,36 @@
         <v/>
       </c>
       <c r="F175" t="str">
-        <v>Euphoria - Single</v>
+        <v>hopeless romantic - Single</v>
       </c>
       <c r="G175" t="str">
-        <v>2:14</v>
+        <v>3:03</v>
       </c>
       <c r="H175" t="str">
-        <v>Bluff City</v>
+        <v>kwn</v>
       </c>
       <c r="I175" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J175" t="str">
-        <v>https://music.apple.com/us/artist/bluff-city/1491129891</v>
+        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
       </c>
       <c r="K175" t="str">
-        <v>https://music.apple.com/us/album/euphoria/1874295623</v>
+        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
       </c>
       <c r="L175" t="str">
-        <v>Euphoria - Bluff City</v>
+        <v>hopeless romantic - kwn</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="str">
-        <v>hopeless romantic</v>
+        <v>Stay Close</v>
       </c>
       <c r="B176" t="str">
         <v/>
       </c>
       <c r="C176" t="str">
-        <v>https://music.apple.com/us/song/hopeless-romantic/1877131451</v>
+        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
       </c>
       <c r="D176" t="str">
         <v>2026-02-23</v>
@@ -7063,36 +7063,36 @@
         <v/>
       </c>
       <c r="F176" t="str">
-        <v>hopeless romantic - Single</v>
+        <v>Stay Close - Single</v>
       </c>
       <c r="G176" t="str">
-        <v>3:03</v>
+        <v>2:58</v>
       </c>
       <c r="H176" t="str">
-        <v>kwn</v>
+        <v>Evelyn Cormier</v>
       </c>
       <c r="I176" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J176" t="str">
-        <v>https://music.apple.com/us/artist/kwn/1629656232</v>
+        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
       </c>
       <c r="K176" t="str">
-        <v>https://music.apple.com/us/album/hopeless-romantic/1877131450</v>
+        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
       </c>
       <c r="L176" t="str">
-        <v>hopeless romantic - kwn</v>
+        <v>Stay Close - Evelyn Cormier</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="str">
-        <v>Stay Close</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="B177" t="str">
         <v/>
       </c>
       <c r="C177" t="str">
-        <v>https://music.apple.com/us/song/stay-close/1871555365</v>
+        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
       </c>
       <c r="D177" t="str">
         <v>2026-02-23</v>
@@ -7101,36 +7101,36 @@
         <v/>
       </c>
       <c r="F177" t="str">
-        <v>Stay Close - Single</v>
+        <v>Metamorphosis</v>
       </c>
       <c r="G177" t="str">
-        <v>2:58</v>
+        <v>2:54</v>
       </c>
       <c r="H177" t="str">
-        <v>Evelyn Cormier</v>
+        <v>lydi lynn</v>
       </c>
       <c r="I177" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J177" t="str">
-        <v>https://music.apple.com/us/artist/evelyn-cormier/1222282253</v>
+        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
       </c>
       <c r="K177" t="str">
-        <v>https://music.apple.com/us/album/stay-close/1871555119</v>
+        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
       </c>
       <c r="L177" t="str">
-        <v>Stay Close - Evelyn Cormier</v>
+        <v>Metamorphosis - lydi lynn</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="str">
-        <v>Metamorphosis</v>
+        <v>peace at last</v>
       </c>
       <c r="B178" t="str">
         <v/>
       </c>
       <c r="C178" t="str">
-        <v>https://music.apple.com/us/song/metamorphosis/1870994810</v>
+        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
       </c>
       <c r="D178" t="str">
         <v>2026-02-23</v>
@@ -7139,36 +7139,36 @@
         <v/>
       </c>
       <c r="F178" t="str">
-        <v>Metamorphosis</v>
+        <v>peace at last - Single</v>
       </c>
       <c r="G178" t="str">
-        <v>2:54</v>
+        <v>2:34</v>
       </c>
       <c r="H178" t="str">
-        <v>lydi lynn</v>
+        <v>Aaron Cole</v>
       </c>
       <c r="I178" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J178" t="str">
-        <v>https://music.apple.com/us/artist/lydi-lynn/1596548664</v>
+        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
       </c>
       <c r="K178" t="str">
-        <v>https://music.apple.com/us/album/metamorphosis/1870994803</v>
+        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
       </c>
       <c r="L178" t="str">
-        <v>Metamorphosis - lydi lynn</v>
+        <v>peace at last - Aaron Cole</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="str">
-        <v>peace at last</v>
+        <v>Aguántame</v>
       </c>
       <c r="B179" t="str">
         <v/>
       </c>
       <c r="C179" t="str">
-        <v>https://music.apple.com/us/song/peace-at-last/1870895365</v>
+        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
       </c>
       <c r="D179" t="str">
         <v>2026-02-23</v>
@@ -7177,36 +7177,36 @@
         <v/>
       </c>
       <c r="F179" t="str">
-        <v>peace at last - Single</v>
+        <v>Aguántame - Single</v>
       </c>
       <c r="G179" t="str">
-        <v>2:34</v>
+        <v>2:08</v>
       </c>
       <c r="H179" t="str">
-        <v>Aaron Cole</v>
+        <v>Banda MS de Sergio Lizárraga</v>
       </c>
       <c r="I179" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J179" t="str">
-        <v>https://music.apple.com/us/artist/aaron-cole/507522696</v>
+        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
       </c>
       <c r="K179" t="str">
-        <v>https://music.apple.com/us/album/peace-at-last/1870895278</v>
+        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
       </c>
       <c r="L179" t="str">
-        <v>peace at last - Aaron Cole</v>
+        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="str">
-        <v>Aguántame</v>
+        <v>Para No Hacernos Daño</v>
       </c>
       <c r="B180" t="str">
         <v/>
       </c>
       <c r="C180" t="str">
-        <v>https://music.apple.com/us/song/agu%C3%A1ntame/1873075918</v>
+        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
       </c>
       <c r="D180" t="str">
         <v>2026-02-23</v>
@@ -7215,36 +7215,36 @@
         <v/>
       </c>
       <c r="F180" t="str">
-        <v>Aguántame - Single</v>
+        <v>Para No Hacernos Daño - Single</v>
       </c>
       <c r="G180" t="str">
-        <v>2:08</v>
+        <v>2:40</v>
       </c>
       <c r="H180" t="str">
-        <v>Banda MS de Sergio Lizárraga</v>
+        <v>Codiciado</v>
       </c>
       <c r="I180" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J180" t="str">
-        <v>https://music.apple.com/us/artist/banda-ms-de-sergio-liz%C3%A1rraga/413048014</v>
+        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
       </c>
       <c r="K180" t="str">
-        <v>https://music.apple.com/us/album/agu%C3%A1ntame/1873075917</v>
+        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
       </c>
       <c r="L180" t="str">
-        <v>Aguántame - Banda MS de Sergio Lizárraga</v>
+        <v>Para No Hacernos Daño - Codiciado</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="str">
-        <v>Para No Hacernos Daño</v>
+        <v>NADA PERSONAL</v>
       </c>
       <c r="B181" t="str">
         <v/>
       </c>
       <c r="C181" t="str">
-        <v>https://music.apple.com/us/song/para-no-hacernos-da%C3%B1o/1872743928</v>
+        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
       </c>
       <c r="D181" t="str">
         <v>2026-02-23</v>
@@ -7253,36 +7253,36 @@
         <v/>
       </c>
       <c r="F181" t="str">
-        <v>Para No Hacernos Daño - Single</v>
+        <v>NADA PERSONAL - Single</v>
       </c>
       <c r="G181" t="str">
-        <v>2:40</v>
+        <v>3:11</v>
       </c>
       <c r="H181" t="str">
-        <v>Codiciado</v>
+        <v>La Joaqui</v>
       </c>
       <c r="I181" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J181" t="str">
-        <v>https://music.apple.com/us/artist/codiciado/1434810911</v>
+        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
       </c>
       <c r="K181" t="str">
-        <v>https://music.apple.com/us/album/para-no-hacernos-da%C3%B1o/1872743927</v>
+        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
       </c>
       <c r="L181" t="str">
-        <v>Para No Hacernos Daño - Codiciado</v>
+        <v>NADA PERSONAL - La Joaqui</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="str">
-        <v>NADA PERSONAL</v>
+        <v>V3n3n0</v>
       </c>
       <c r="B182" t="str">
         <v/>
       </c>
       <c r="C182" t="str">
-        <v>https://music.apple.com/us/song/nada-personal/1875350202</v>
+        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
       </c>
       <c r="D182" t="str">
         <v>2026-02-23</v>
@@ -7291,36 +7291,36 @@
         <v/>
       </c>
       <c r="F182" t="str">
-        <v>NADA PERSONAL - Single</v>
+        <v>V3n3n0 - Single</v>
       </c>
       <c r="G182" t="str">
-        <v>3:11</v>
+        <v>2:32</v>
       </c>
       <c r="H182" t="str">
-        <v>La Joaqui</v>
+        <v>Esty</v>
       </c>
       <c r="I182" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J182" t="str">
-        <v>https://music.apple.com/us/artist/la-joaqui/1222726669</v>
+        <v>https://music.apple.com/us/artist/esty/255471858</v>
       </c>
       <c r="K182" t="str">
-        <v>https://music.apple.com/us/album/nada-personal/1875350196</v>
+        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
       </c>
       <c r="L182" t="str">
-        <v>NADA PERSONAL - La Joaqui</v>
+        <v>V3n3n0 - Esty</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="str">
-        <v>V3n3n0</v>
+        <v>Moth In The Headlights</v>
       </c>
       <c r="B183" t="str">
         <v/>
       </c>
       <c r="C183" t="str">
-        <v>https://music.apple.com/us/song/v3n3n0/1874454947</v>
+        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
       </c>
       <c r="D183" t="str">
         <v>2026-02-23</v>
@@ -7329,36 +7329,36 @@
         <v/>
       </c>
       <c r="F183" t="str">
-        <v>V3n3n0 - Single</v>
+        <v>Inanimate Objects of the 21st Century</v>
       </c>
       <c r="G183" t="str">
-        <v>2:32</v>
+        <v>4:23</v>
       </c>
       <c r="H183" t="str">
-        <v>Esty</v>
+        <v>The Pale White</v>
       </c>
       <c r="I183" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J183" t="str">
-        <v>https://music.apple.com/us/artist/esty/255471858</v>
+        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
       </c>
       <c r="K183" t="str">
-        <v>https://music.apple.com/us/album/v3n3n0/1874454944</v>
+        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
       </c>
       <c r="L183" t="str">
-        <v>V3n3n0 - Esty</v>
+        <v>Moth In The Headlights - The Pale White</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="str">
-        <v>Moth In The Headlights</v>
+        <v>lately in the void</v>
       </c>
       <c r="B184" t="str">
         <v/>
       </c>
       <c r="C184" t="str">
-        <v>https://music.apple.com/us/song/moth-in-the-headlights/1870538542</v>
+        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
       </c>
       <c r="D184" t="str">
         <v>2026-02-23</v>
@@ -7367,36 +7367,36 @@
         <v/>
       </c>
       <c r="F184" t="str">
-        <v>Inanimate Objects of the 21st Century</v>
+        <v>lately in the void - EP</v>
       </c>
       <c r="G184" t="str">
-        <v>4:23</v>
+        <v>3:41</v>
       </c>
       <c r="H184" t="str">
-        <v>The Pale White</v>
+        <v>bad tuner</v>
       </c>
       <c r="I184" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J184" t="str">
-        <v>https://music.apple.com/us/artist/the-pale-white/1127116907</v>
+        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
       </c>
       <c r="K184" t="str">
-        <v>https://music.apple.com/us/album/moth-in-the-headlights/1870538540</v>
+        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
       </c>
       <c r="L184" t="str">
-        <v>Moth In The Headlights - The Pale White</v>
+        <v>lately in the void - bad tuner</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="str">
-        <v>lately in the void</v>
+        <v>When I Fall in Love</v>
       </c>
       <c r="B185" t="str">
         <v/>
       </c>
       <c r="C185" t="str">
-        <v>https://music.apple.com/us/song/lately-in-the-void/1847993197</v>
+        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
       </c>
       <c r="D185" t="str">
         <v>2026-02-23</v>
@@ -7405,36 +7405,36 @@
         <v/>
       </c>
       <c r="F185" t="str">
-        <v>lately in the void - EP</v>
+        <v>Nightjar</v>
       </c>
       <c r="G185" t="str">
-        <v>3:41</v>
+        <v>4:45</v>
       </c>
       <c r="H185" t="str">
-        <v>bad tuner</v>
+        <v>David Gray</v>
       </c>
       <c r="I185" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J185" t="str">
-        <v>https://music.apple.com/us/artist/bad-tuner/1051446214</v>
+        <v>https://music.apple.com/us/artist/david-gray/316381</v>
       </c>
       <c r="K185" t="str">
-        <v>https://music.apple.com/us/album/lately-in-the-void/1847993191</v>
+        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
       </c>
       <c r="L185" t="str">
-        <v>lately in the void - bad tuner</v>
+        <v>When I Fall in Love - David Gray</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="str">
-        <v>When I Fall in Love</v>
+        <v>Repeat Offender</v>
       </c>
       <c r="B186" t="str">
         <v/>
       </c>
       <c r="C186" t="str">
-        <v>https://music.apple.com/us/song/when-i-fall-in-love/1860381107</v>
+        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
       </c>
       <c r="D186" t="str">
         <v>2026-02-23</v>
@@ -7443,36 +7443,36 @@
         <v/>
       </c>
       <c r="F186" t="str">
-        <v>Nightjar</v>
+        <v>Repeat Offender - Single</v>
       </c>
       <c r="G186" t="str">
-        <v>4:45</v>
+        <v>2:33</v>
       </c>
       <c r="H186" t="str">
-        <v>David Gray</v>
+        <v>yeemz</v>
       </c>
       <c r="I186" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J186" t="str">
-        <v>https://music.apple.com/us/artist/david-gray/316381</v>
+        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
       </c>
       <c r="K186" t="str">
-        <v>https://music.apple.com/us/album/when-i-fall-in-love/1860381106</v>
+        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
       </c>
       <c r="L186" t="str">
-        <v>When I Fall in Love - David Gray</v>
+        <v>Repeat Offender - yeemz</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="str">
-        <v>Repeat Offender</v>
+        <v>Class Reunion</v>
       </c>
       <c r="B187" t="str">
         <v/>
       </c>
       <c r="C187" t="str">
-        <v>https://music.apple.com/us/song/repeat-offender/1873099829</v>
+        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
       </c>
       <c r="D187" t="str">
         <v>2026-02-23</v>
@@ -7481,36 +7481,36 @@
         <v/>
       </c>
       <c r="F187" t="str">
-        <v>Repeat Offender - Single</v>
+        <v>We Swallowed The Sky</v>
       </c>
       <c r="G187" t="str">
-        <v>2:33</v>
+        <v>4:11</v>
       </c>
       <c r="H187" t="str">
-        <v>yeemz</v>
+        <v>Beatrix</v>
       </c>
       <c r="I187" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J187" t="str">
-        <v>https://music.apple.com/us/artist/yeemz/1561474492</v>
+        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
       </c>
       <c r="K187" t="str">
-        <v>https://music.apple.com/us/album/repeat-offender/1873099828</v>
+        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
       </c>
       <c r="L187" t="str">
-        <v>Repeat Offender - yeemz</v>
+        <v>Class Reunion - Beatrix</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="str">
-        <v>Class Reunion</v>
+        <v>Promise Me</v>
       </c>
       <c r="B188" t="str">
         <v/>
       </c>
       <c r="C188" t="str">
-        <v>https://music.apple.com/us/song/class-reunion/1876698294</v>
+        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
       </c>
       <c r="D188" t="str">
         <v>2026-02-23</v>
@@ -7519,36 +7519,36 @@
         <v/>
       </c>
       <c r="F188" t="str">
-        <v>We Swallowed The Sky</v>
+        <v>Instant Comfort</v>
       </c>
       <c r="G188" t="str">
-        <v>4:11</v>
+        <v>5:34</v>
       </c>
       <c r="H188" t="str">
-        <v>Beatrix</v>
+        <v>Lucid Express</v>
       </c>
       <c r="I188" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J188" t="str">
-        <v>https://music.apple.com/us/artist/beatrix/1732651124</v>
+        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
       </c>
       <c r="K188" t="str">
-        <v>https://music.apple.com/us/album/class-reunion/1876698281</v>
+        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
       </c>
       <c r="L188" t="str">
-        <v>Class Reunion - Beatrix</v>
+        <v>Promise Me - Lucid Express</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="str">
-        <v>Promise Me</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
       </c>
       <c r="B189" t="str">
         <v/>
       </c>
       <c r="C189" t="str">
-        <v>https://music.apple.com/us/song/promise-me/1848977981</v>
+        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
       </c>
       <c r="D189" t="str">
         <v>2026-02-23</v>
@@ -7557,36 +7557,36 @@
         <v/>
       </c>
       <c r="F189" t="str">
-        <v>Instant Comfort</v>
+        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
       </c>
       <c r="G189" t="str">
-        <v>5:34</v>
+        <v>3:33</v>
       </c>
       <c r="H189" t="str">
-        <v>Lucid Express</v>
+        <v>Zee Nxumalo</v>
       </c>
       <c r="I189" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J189" t="str">
-        <v>https://music.apple.com/us/artist/lucid-express/1560683497</v>
+        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
       </c>
       <c r="K189" t="str">
-        <v>https://music.apple.com/us/album/promise-me/1848977978</v>
+        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
       </c>
       <c r="L189" t="str">
-        <v>Promise Me - Lucid Express</v>
+        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions)</v>
+        <v>Hit and Run (feat. AZ Chike)</v>
       </c>
       <c r="B190" t="str">
         <v/>
       </c>
       <c r="C190" t="str">
-        <v>https://music.apple.com/us/song/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873677</v>
+        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
       </c>
       <c r="D190" t="str">
         <v>2026-02-23</v>
@@ -7595,36 +7595,36 @@
         <v/>
       </c>
       <c r="F190" t="str">
-        <v>Awe Mah (feat. Shakes &amp; Les, MK Productions &amp; Funky Qla) - Single</v>
+        <v>Hit and Run (feat. AZ Chike) - Single</v>
       </c>
       <c r="G190" t="str">
-        <v>3:33</v>
+        <v>3:19</v>
       </c>
       <c r="H190" t="str">
-        <v>Zee Nxumalo</v>
+        <v>Ray Vaughn</v>
       </c>
       <c r="I190" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J190" t="str">
-        <v>https://music.apple.com/us/artist/zee-nxumalo/1606439969</v>
+        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
       </c>
       <c r="K190" t="str">
-        <v>https://music.apple.com/us/album/awe-mah-feat-funky-qla-shakes-les-mk-productions/1852873675</v>
+        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
       </c>
       <c r="L190" t="str">
-        <v>Awe Mah (feat. Funky Qla, Shakes &amp; Les &amp; MK Productions) - Zee Nxumalo</v>
+        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="str">
-        <v>Hit and Run (feat. AZ Chike)</v>
+        <v>So Good</v>
       </c>
       <c r="B191" t="str">
         <v/>
       </c>
       <c r="C191" t="str">
-        <v>https://music.apple.com/us/song/hit-and-run-feat-az-chike/1877912904</v>
+        <v>https://music.apple.com/us/song/so-good/1874733689</v>
       </c>
       <c r="D191" t="str">
         <v>2026-02-23</v>
@@ -7633,36 +7633,36 @@
         <v/>
       </c>
       <c r="F191" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Single</v>
+        <v>So Good - Single</v>
       </c>
       <c r="G191" t="str">
-        <v>3:19</v>
+        <v>2:47</v>
       </c>
       <c r="H191" t="str">
-        <v>Ray Vaughn</v>
+        <v>Ari Abdul</v>
       </c>
       <c r="I191" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J191" t="str">
-        <v>https://music.apple.com/us/artist/ray-vaughn/1303356758</v>
+        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
       </c>
       <c r="K191" t="str">
-        <v>https://music.apple.com/us/album/hit-and-run-feat-az-chike/1877912892</v>
+        <v>https://music.apple.com/us/album/so-good/1874733688</v>
       </c>
       <c r="L191" t="str">
-        <v>Hit and Run (feat. AZ Chike) - Ray Vaughn</v>
+        <v>So Good - Ari Abdul</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="str">
-        <v>So Good</v>
+        <v>YDH</v>
       </c>
       <c r="B192" t="str">
         <v/>
       </c>
       <c r="C192" t="str">
-        <v>https://music.apple.com/us/song/so-good/1874733689</v>
+        <v>https://music.apple.com/us/song/ydh/1874940744</v>
       </c>
       <c r="D192" t="str">
         <v>2026-02-23</v>
@@ -7671,36 +7671,36 @@
         <v/>
       </c>
       <c r="F192" t="str">
-        <v>So Good - Single</v>
+        <v>YDH - Single</v>
       </c>
       <c r="G192" t="str">
-        <v>2:47</v>
+        <v>3:17</v>
       </c>
       <c r="H192" t="str">
-        <v>Ari Abdul</v>
+        <v>Chloe Qisha</v>
       </c>
       <c r="I192" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J192" t="str">
-        <v>https://music.apple.com/us/artist/ari-abdul/1606828852</v>
+        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
       </c>
       <c r="K192" t="str">
-        <v>https://music.apple.com/us/album/so-good/1874733688</v>
+        <v>https://music.apple.com/us/album/ydh/1874940739</v>
       </c>
       <c r="L192" t="str">
-        <v>So Good - Ari Abdul</v>
+        <v>YDH - Chloe Qisha</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="str">
-        <v>YDH</v>
+        <v>Eucalyptus</v>
       </c>
       <c r="B193" t="str">
         <v/>
       </c>
       <c r="C193" t="str">
-        <v>https://music.apple.com/us/song/ydh/1874940744</v>
+        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
       </c>
       <c r="D193" t="str">
         <v>2026-02-23</v>
@@ -7709,36 +7709,36 @@
         <v/>
       </c>
       <c r="F193" t="str">
-        <v>YDH - Single</v>
+        <v>Porcelain</v>
       </c>
       <c r="G193" t="str">
-        <v>3:17</v>
+        <v>3:00</v>
       </c>
       <c r="H193" t="str">
-        <v>Chloe Qisha</v>
+        <v>Peach PRC</v>
       </c>
       <c r="I193" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J193" t="str">
-        <v>https://music.apple.com/us/artist/chloe-qisha/1751460376</v>
+        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
       </c>
       <c r="K193" t="str">
-        <v>https://music.apple.com/us/album/ydh/1874940739</v>
+        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
       </c>
       <c r="L193" t="str">
-        <v>YDH - Chloe Qisha</v>
+        <v>Eucalyptus - Peach PRC</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="str">
-        <v>Eucalyptus</v>
+        <v>Pearls In The Trap</v>
       </c>
       <c r="B194" t="str">
         <v/>
       </c>
       <c r="C194" t="str">
-        <v>https://music.apple.com/us/song/eucalyptus/1861380250</v>
+        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
       </c>
       <c r="D194" t="str">
         <v>2026-02-23</v>
@@ -7747,36 +7747,36 @@
         <v/>
       </c>
       <c r="F194" t="str">
-        <v>Porcelain</v>
+        <v>Pearls In The Trap - Single</v>
       </c>
       <c r="G194" t="str">
-        <v>3:00</v>
+        <v>1:38</v>
       </c>
       <c r="H194" t="str">
-        <v>Peach PRC</v>
+        <v>carolesdaughter</v>
       </c>
       <c r="I194" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J194" t="str">
-        <v>https://music.apple.com/us/artist/peach-prc/1469263677</v>
+        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
       </c>
       <c r="K194" t="str">
-        <v>https://music.apple.com/us/album/eucalyptus/1861380240</v>
+        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
       </c>
       <c r="L194" t="str">
-        <v>Eucalyptus - Peach PRC</v>
+        <v>Pearls In The Trap - carolesdaughter</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="str">
-        <v>Pearls In The Trap</v>
+        <v>The Fever Mask</v>
       </c>
       <c r="B195" t="str">
         <v/>
       </c>
       <c r="C195" t="str">
-        <v>https://music.apple.com/us/song/pearls-in-the-trap/1877892477</v>
+        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
       </c>
       <c r="D195" t="str">
         <v>2026-02-23</v>
@@ -7785,36 +7785,36 @@
         <v/>
       </c>
       <c r="F195" t="str">
-        <v>Pearls In The Trap - Single</v>
+        <v>The Ghost of a Future Dead</v>
       </c>
       <c r="G195" t="str">
-        <v>1:38</v>
+        <v>3:12</v>
       </c>
       <c r="H195" t="str">
-        <v>carolesdaughter</v>
+        <v>At The Gates</v>
       </c>
       <c r="I195" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J195" t="str">
-        <v>https://music.apple.com/us/artist/carolesdaughter/1502564996</v>
+        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
       </c>
       <c r="K195" t="str">
-        <v>https://music.apple.com/us/album/pearls-in-the-trap/1877892476</v>
+        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
       </c>
       <c r="L195" t="str">
-        <v>Pearls In The Trap - carolesdaughter</v>
+        <v>The Fever Mask - At The Gates</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="str">
-        <v>The Fever Mask</v>
+        <v>The Air's on Fire</v>
       </c>
       <c r="B196" t="str">
         <v/>
       </c>
       <c r="C196" t="str">
-        <v>https://music.apple.com/us/song/the-fever-mask/1873364810</v>
+        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
       </c>
       <c r="D196" t="str">
         <v>2026-02-23</v>
@@ -7823,36 +7823,36 @@
         <v/>
       </c>
       <c r="F196" t="str">
-        <v>The Ghost of a Future Dead</v>
+        <v>Location Lost</v>
       </c>
       <c r="G196" t="str">
-        <v>3:12</v>
+        <v>5:15</v>
       </c>
       <c r="H196" t="str">
-        <v>At The Gates</v>
+        <v>Failure</v>
       </c>
       <c r="I196" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J196" t="str">
-        <v>https://music.apple.com/us/artist/at-the-gates/57658038</v>
+        <v>https://music.apple.com/us/artist/failure/1646309</v>
       </c>
       <c r="K196" t="str">
-        <v>https://music.apple.com/us/album/the-fever-mask/1873364809</v>
+        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
       </c>
       <c r="L196" t="str">
-        <v>The Fever Mask - At The Gates</v>
+        <v>The Air's on Fire - Failure</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="str">
-        <v>The Air's on Fire</v>
+        <v>To The Last Breath</v>
       </c>
       <c r="B197" t="str">
         <v/>
       </c>
       <c r="C197" t="str">
-        <v>https://music.apple.com/us/song/the-airs-on-fire/1867015799</v>
+        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
       </c>
       <c r="D197" t="str">
         <v>2026-02-23</v>
@@ -7861,68 +7861,30 @@
         <v/>
       </c>
       <c r="F197" t="str">
-        <v>Location Lost</v>
+        <v>To The Last Breath - Single</v>
       </c>
       <c r="G197" t="str">
-        <v>5:15</v>
+        <v>4:57</v>
       </c>
       <c r="H197" t="str">
-        <v>Failure</v>
+        <v>Arch Enemy</v>
       </c>
       <c r="I197" t="str">
         <v>מוזיקה לועזית חדשה</v>
       </c>
       <c r="J197" t="str">
-        <v>https://music.apple.com/us/artist/failure/1646309</v>
+        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
       </c>
       <c r="K197" t="str">
-        <v>https://music.apple.com/us/album/the-airs-on-fire/1867015665</v>
+        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
       </c>
       <c r="L197" t="str">
-        <v>The Air's on Fire - Failure</v>
-      </c>
-    </row>
-    <row r="198">
-      <c r="A198" t="str">
-        <v>To The Last Breath</v>
-      </c>
-      <c r="B198" t="str">
-        <v/>
-      </c>
-      <c r="C198" t="str">
-        <v>https://music.apple.com/us/song/to-the-last-breath/1874618974</v>
-      </c>
-      <c r="D198" t="str">
-        <v>2026-02-23</v>
-      </c>
-      <c r="E198" t="str">
-        <v/>
-      </c>
-      <c r="F198" t="str">
-        <v>To The Last Breath - Single</v>
-      </c>
-      <c r="G198" t="str">
-        <v>4:57</v>
-      </c>
-      <c r="H198" t="str">
-        <v>Arch Enemy</v>
-      </c>
-      <c r="I198" t="str">
-        <v>מוזיקה לועזית חדשה</v>
-      </c>
-      <c r="J198" t="str">
-        <v>https://music.apple.com/us/artist/arch-enemy/18098340</v>
-      </c>
-      <c r="K198" t="str">
-        <v>https://music.apple.com/us/album/to-the-last-breath/1874618973</v>
-      </c>
-      <c r="L198" t="str">
         <v>To The Last Breath - Arch Enemy</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L198"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L197"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/global/2026-02-week04/titles.xlsx
+++ b/data/global/2026-02-week04/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L197"/>
+  <dimension ref="A1:L208"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio)</v>
+        <v>חיים איפרגן - אשרף טק</v>
       </c>
       <c r="B2" t="str">
-        <v>4 hours ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C2" t="str">
-        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409731&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D2" t="str">
         <v>2026-02-23</v>
@@ -451,16 +451,16 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>4 hours ago</v>
+        <v/>
       </c>
       <c r="G2" t="str">
-        <v>5:32</v>
+        <v/>
       </c>
       <c r="H2" t="str">
-        <v>earMUSIC</v>
+        <v/>
       </c>
       <c r="I2" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J2" t="str">
         <v/>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>HOLLYWOOD VAMPIRES - School's Out (Live in Rio) - earMUSIC</v>
+        <v>חיים איפרגן - אשרף טק</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
+        <v>דוריה חממי - טעויות מהעבר</v>
       </c>
       <c r="B3" t="str">
-        <v>8 hours ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C3" t="str">
-        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409730&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D3" t="str">
         <v>2026-02-23</v>
@@ -489,16 +489,16 @@
         <v/>
       </c>
       <c r="F3" t="str">
-        <v>8 hours ago</v>
+        <v/>
       </c>
       <c r="G3" t="str">
-        <v>4:39</v>
+        <v/>
       </c>
       <c r="H3" t="str">
-        <v>georgemichael</v>
+        <v/>
       </c>
       <c r="I3" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J3" t="str">
         <v/>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
+        <v>דוריה חממי - טעויות מהעבר</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
+        <v>בר צברי - ראש לאריות</v>
       </c>
       <c r="B4" t="str">
-        <v>8 hours ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C4" t="str">
-        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409729&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D4" t="str">
         <v>2026-02-23</v>
@@ -527,16 +527,16 @@
         <v/>
       </c>
       <c r="F4" t="str">
-        <v>8 hours ago</v>
+        <v/>
       </c>
       <c r="G4" t="str">
-        <v>3:40</v>
+        <v/>
       </c>
       <c r="H4" t="str">
-        <v>Nothing But Thieves</v>
+        <v/>
       </c>
       <c r="I4" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J4" t="str">
         <v/>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
+        <v>בר צברי - ראש לאריות</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
+        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
       </c>
       <c r="B5" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C5" t="str">
-        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409728&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D5" t="str">
         <v>2026-02-23</v>
@@ -565,16 +565,16 @@
         <v/>
       </c>
       <c r="F5" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G5" t="str">
-        <v>3:57</v>
+        <v/>
       </c>
       <c r="H5" t="str">
-        <v>Self Esteem</v>
+        <v/>
       </c>
       <c r="I5" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J5" t="str">
         <v/>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
+        <v>בן אל תבורי &amp; דנה אינטרנשיונל &amp; אמיר שורוש - מה עושים בלילות</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>070 Shake - If You’re Free</v>
+        <v>אמיר ישראל - מי עושה קפה</v>
       </c>
       <c r="B6" t="str">
-        <v>1 day ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C6" t="str">
-        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409727&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D6" t="str">
         <v>2026-02-23</v>
@@ -603,16 +603,16 @@
         <v/>
       </c>
       <c r="F6" t="str">
-        <v>1 day ago</v>
+        <v/>
       </c>
       <c r="G6" t="str">
-        <v>2:27</v>
+        <v/>
       </c>
       <c r="H6" t="str">
-        <v>070 Shake</v>
+        <v/>
       </c>
       <c r="I6" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J6" t="str">
         <v/>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>070 Shake - If You’re Free - 070 Shake</v>
+        <v>אמיר ישראל - מי עושה קפה</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
+        <v>אייל ישי - לא דיברנו שנינו</v>
       </c>
       <c r="B7" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C7" t="str">
-        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409726&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D7" t="str">
         <v>2026-02-23</v>
@@ -641,16 +641,16 @@
         <v/>
       </c>
       <c r="F7" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G7" t="str">
-        <v>4:49</v>
+        <v/>
       </c>
       <c r="H7" t="str">
-        <v>georgemichael</v>
+        <v/>
       </c>
       <c r="I7" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J7" t="str">
         <v/>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
+        <v>אייל ישי - לא דיברנו שנינו</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
+        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
       </c>
       <c r="B8" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C8" t="str">
-        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409725&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D8" t="str">
         <v>2026-02-23</v>
@@ -679,16 +679,16 @@
         <v/>
       </c>
       <c r="F8" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G8" t="str">
-        <v>5:52</v>
+        <v/>
       </c>
       <c r="H8" t="str">
-        <v>georgemichael</v>
+        <v/>
       </c>
       <c r="I8" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J8" t="str">
         <v/>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
+        <v>אוראל מנצור - מחרוזת נועצת מבט 2026</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
+        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
       </c>
       <c r="B9" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C9" t="str">
-        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=409724&amp;sid=b7524068d0c67c249ff82f0b4d80f8bb</v>
       </c>
       <c r="D9" t="str">
         <v>2026-02-23</v>
@@ -717,16 +717,16 @@
         <v/>
       </c>
       <c r="F9" t="str">
-        <v>2 days ago</v>
+        <v/>
       </c>
       <c r="G9" t="str">
-        <v>3:22</v>
+        <v/>
       </c>
       <c r="H9" t="str">
-        <v>Foo Fighters</v>
+        <v/>
       </c>
       <c r="I9" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J9" t="str">
         <v/>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
+        <v>אבי ביטר - מחרוזת לב פצוע 2026</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026)</v>
+        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
       </c>
       <c r="B10" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C10" t="str">
-        <v>https://www.youtube.com/watch?v=t2F_hgmF0DI</v>
+        <v>https://yosmusic.com/%d7%94%d7%a4%d7%a8%d7%95%d7%99%d7%a7%d7%98-%d7%a9%d7%9c-%d7%aa%d7%9e%d7%a8%d7%99-%d7%95%d7%90%d7%94%d7%95%d7%93-%d7%91%d7%a0%d7%90%d7%99-%d7%99%d7%95%d7%a6%d7%90-%d7%9c%d7%90%d7%95%d7%a8/</v>
       </c>
       <c r="D10" t="str">
         <v>2026-02-23</v>
@@ -755,16 +755,16 @@
         <v/>
       </c>
       <c r="F10" t="str">
-        <v>2 days ago</v>
+        <v>חוזרים לשביל של אהוד בנאי עם "הפרויקט של תמרי" בשיתוף היוצר. השביל הזה מתחיל מכאן, כלומר – מהמקום בו אתה עומד – מתחיל שביל שמוליך אל דבר לא ברור, אל אותו דבר שאתה רוצה לעשות, אבל אתה לא יודע איך"…</v>
       </c>
       <c r="G10" t="str">
-        <v>4:08</v>
+        <v/>
       </c>
       <c r="H10" t="str">
-        <v>Romeo Santos</v>
+        <v/>
       </c>
       <c r="I10" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J10" t="str">
         <v/>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>Romeo Santos, Prince Royce - Lokita Por Mí &amp; Dardos (Premio Lo Nuestro 2026) - Romeo Santos</v>
+        <v>הפרויקט של תמרי ואהוד בנאי – יוצא לאור</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier)</v>
+        <v>אייל אבן צור – פסל</v>
       </c>
       <c r="B11" t="str">
-        <v>2 days ago</v>
+        <v>2026-02-23</v>
       </c>
       <c r="C11" t="str">
-        <v>https://www.youtube.com/watch?v=kSOWR3SFm2U</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%99%d7%9c-%d7%90%d7%91%d7%9f-%d7%a6%d7%95%d7%a8-%d7%a4%d7%a1%d7%9c/</v>
       </c>
       <c r="D11" t="str">
         <v>2026-02-23</v>
@@ -793,16 +793,16 @@
         <v/>
       </c>
       <c r="F11" t="str">
-        <v>2 days ago</v>
+        <v>השיר "פסל" של אייל אבן צור הוא יצירה אינטימית ועדינה, שנשענת על עיבוד פופ־פולק מלודי בעל אווירה מלנכולית מאופקת. הביצוע בטון גבוה ומתכוון יוצר תחושת פגיעות – קול שנשמע כבוי במידה מסוימת, אך לא נשבר. יש בו המשכיות מתכוונת, כמו</v>
       </c>
       <c r="G11" t="str">
-        <v>7:31</v>
+        <v/>
       </c>
       <c r="H11" t="str">
-        <v>Jacob Collier</v>
+        <v/>
       </c>
       <c r="I11" t="str">
-        <v>מוזיקה לועזית חדשה</v>
+        <v>סינגלים חדשים</v>
       </c>
       <c r="J11" t="str">
         <v/>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>Jacob Collier – Something Heavy (Live with Audience Orchestra - cond. Suzie Collier) - Jacob Collier</v>
+        <v>אייל אבן צור – פסל</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>Gabi Sklar - Snowbird</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio)</v>
       </c>
       <c r="B12" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="C12" t="str">
-        <v>https://www.youtube.com/watch?v=LtM-0SNbEac</v>
+        <v>https://www.youtube.com/watch?v=oEvE_MRJ89U</v>
       </c>
       <c r="D12" t="str">
         <v>2026-02-23</v>
@@ -831,13 +831,13 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>2 days ago</v>
+        <v>7 hours ago</v>
       </c>
       <c r="G12" t="str">
-        <v>3:21</v>
+        <v>5:32</v>
       </c>
       <c r="H12" t="str">
-        <v>Gabi Sklar</v>
+        <v>earMUSIC</v>
       </c>
       <c r="I12" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -849,18 +849,18 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>Gabi Sklar - Snowbird - Gabi Sklar</v>
+        <v>HOLLYWOOD VAMPIRES | School's Out (Live in Rio) - earMUSIC</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video)</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser)</v>
       </c>
       <c r="B13" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C13" t="str">
-        <v>https://www.youtube.com/watch?v=io5mLKLDwcc</v>
+        <v>https://www.youtube.com/watch?v=p000IuglHAQ</v>
       </c>
       <c r="D13" t="str">
         <v>2026-02-23</v>
@@ -869,13 +869,13 @@
         <v/>
       </c>
       <c r="F13" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G13" t="str">
-        <v>4:36</v>
+        <v>4:39</v>
       </c>
       <c r="H13" t="str">
-        <v>YUNGBLUD</v>
+        <v>georgemichael</v>
       </c>
       <c r="I13" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -887,18 +887,18 @@
         <v/>
       </c>
       <c r="L13" t="str">
-        <v>YUNGBLUD - Suburban Requiem (Official Lyric Video) - YUNGBLUD</v>
+        <v>George Michael - Look at Your Hands (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Chris Norman - Run (Official Video)</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio)</v>
       </c>
       <c r="B14" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="C14" t="str">
-        <v>https://www.youtube.com/watch?v=Kwmn9JhbNko</v>
+        <v>https://www.youtube.com/watch?v=ilCkB003kaA</v>
       </c>
       <c r="D14" t="str">
         <v>2026-02-23</v>
@@ -907,13 +907,13 @@
         <v/>
       </c>
       <c r="F14" t="str">
-        <v>3 days ago</v>
+        <v>11 hours ago</v>
       </c>
       <c r="G14" t="str">
-        <v>5:06</v>
+        <v>3:40</v>
       </c>
       <c r="H14" t="str">
-        <v>Chris Norman and STARS</v>
+        <v>Nothing But Thieves</v>
       </c>
       <c r="I14" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -925,18 +925,18 @@
         <v/>
       </c>
       <c r="L14" t="str">
-        <v>Chris Norman - Run (Official Video) - Chris Norman and STARS</v>
+        <v>Nothing But Thieves - Excuse Me (Official Audio) - Nothing But Thieves</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026)</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show</v>
       </c>
       <c r="B15" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="C15" t="str">
-        <v>https://www.youtube.com/watch?v=hHLYopk2bng</v>
+        <v>https://www.youtube.com/watch?v=roJECPyiVVM</v>
       </c>
       <c r="D15" t="str">
         <v>2026-02-23</v>
@@ -945,13 +945,13 @@
         <v/>
       </c>
       <c r="F15" t="str">
-        <v>2 days ago</v>
+        <v>1 day ago</v>
       </c>
       <c r="G15" t="str">
-        <v>4:17</v>
+        <v>3:57</v>
       </c>
       <c r="H15" t="str">
-        <v>Marc Anthony</v>
+        <v>Self Esteem</v>
       </c>
       <c r="I15" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -963,18 +963,18 @@
         <v/>
       </c>
       <c r="L15" t="str">
-        <v>Marc Anthony, NATHY PELUSO - Como en el Idilio (Premio Lo Nuestro 2026) - Marc Anthony</v>
+        <v>Self Esteem - The Deep Blue Okay Alt Version | The Jonathan Ross Show - Self Esteem</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008)</v>
+        <v>070 Shake - If You’re Free</v>
       </c>
       <c r="B16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C16" t="str">
-        <v>https://www.youtube.com/watch?v=ymUw0Umflnk</v>
+        <v>https://www.youtube.com/watch?v=NbQXtti-Nng</v>
       </c>
       <c r="D16" t="str">
         <v>2026-02-23</v>
@@ -983,13 +983,13 @@
         <v/>
       </c>
       <c r="F16" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G16" t="str">
-        <v>3:20</v>
+        <v>2:27</v>
       </c>
       <c r="H16" t="str">
-        <v>georgemichael</v>
+        <v>070 Shake</v>
       </c>
       <c r="I16" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1001,18 +1001,18 @@
         <v/>
       </c>
       <c r="L16" t="str">
-        <v>George Michael - Faith (25 Live Tour - Live from Earls Court 2008) - georgemichael</v>
+        <v>070 Shake - If You’re Free - 070 Shake</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert)</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser)</v>
       </c>
       <c r="B17" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C17" t="str">
-        <v>https://www.youtube.com/watch?v=YqUlwUy3Lhk</v>
+        <v>https://www.youtube.com/watch?v=7TJ8TM3R5uM</v>
       </c>
       <c r="D17" t="str">
         <v>2026-02-23</v>
@@ -1021,13 +1021,13 @@
         <v/>
       </c>
       <c r="F17" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G17" t="str">
-        <v>4:50</v>
+        <v>4:49</v>
       </c>
       <c r="H17" t="str">
-        <v>Cliff Richard</v>
+        <v>georgemichael</v>
       </c>
       <c r="I17" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1039,18 +1039,18 @@
         <v/>
       </c>
       <c r="L17" t="str">
-        <v>Cliff Richard - It's In Every One Of Us (The Countdown Concert) - Cliff Richard</v>
+        <v>George Michael - Hard Day (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video)</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser)</v>
       </c>
       <c r="B18" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C18" t="str">
-        <v>https://www.youtube.com/watch?v=ekwnYFyzGnw</v>
+        <v>https://www.youtube.com/watch?v=IelEuP-_yQs</v>
       </c>
       <c r="D18" t="str">
         <v>2026-02-23</v>
@@ -1059,13 +1059,13 @@
         <v/>
       </c>
       <c r="F18" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G18" t="str">
-        <v>3:14</v>
+        <v>5:52</v>
       </c>
       <c r="H18" t="str">
-        <v>Freya Ridings</v>
+        <v>georgemichael</v>
       </c>
       <c r="I18" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1077,18 +1077,18 @@
         <v/>
       </c>
       <c r="L18" t="str">
-        <v>Freya Ridings - Wild Horse (Official Video) - Freya Ridings</v>
+        <v>George Michael - One More Try (Remastered - Official Visualiser) - georgemichael</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Jessie Ware - Ride</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show)</v>
       </c>
       <c r="B19" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="C19" t="str">
-        <v>https://www.youtube.com/watch?v=B-NjEx6v-tk</v>
+        <v>https://www.youtube.com/watch?v=_kyLJ6pdGUE</v>
       </c>
       <c r="D19" t="str">
         <v>2026-02-23</v>
@@ -1097,13 +1097,13 @@
         <v/>
       </c>
       <c r="F19" t="str">
-        <v>3 days ago</v>
+        <v>2 days ago</v>
       </c>
       <c r="G19" t="str">
-        <v>4:37</v>
+        <v>3:22</v>
       </c>
       <c r="H19" t="str">
-        <v>Jessie Ware</v>
+        <v>Foo Fighters</v>
       </c>
       <c r="I19" t="str">
         <v>מוזיקה לועזית חדשה</v>
@@ -1115,18 +1115,18 @@
         <v/>
       </c>
       <c r="L19" t="str">
-        <v>Jessie Ware - Ride - Jessie Ware</v>
+        <v>Your Favorite Toy (Live on The Graham Norton Show) - Foo Fighters</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Alan Walker, Farruko &amp; Sofia Reyes - O